--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,29 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F40FE168-1F44-0442-A2CF-BBE96FE96BFE}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9662ACE1-A0B3-5444-9BAF-EEA93772C139}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AG$59</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="393">
   <si>
     <t>Año</t>
   </si>
@@ -2191,6 +2204,48 @@
   </si>
   <si>
     <t>Book</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence and Misinformation in Art: Can Vision Language Models Judge the Hand or the Machine Behind the Canvas?</t>
+  </si>
+  <si>
+    <t>ACM Journal on Computing and Cultural Heritage</t>
+  </si>
+  <si>
+    <t>T. Fu, J. Conde, G. Martínez, P. Reviriego, E. Merino-Gómez, F. Moral</t>
+  </si>
+  <si>
+    <t>http://doi.org/10.1145/3807498</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2508.01408, https://huggingface.co/papers/2508.01408]</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2024): 2.2 (112/177, Q3)</t>
+  </si>
+  <si>
+    <t>COMPUTER SCIENCE, INTERDISCIPLINARY APPLICATIONS- SCIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[https://github.com/aMa2210/AI_impostors, https://ama2210.github.io/WikiArt_VLM_Web/, https://zenodo.org/records/17880956] </t>
+  </si>
+  <si>
+    <t>[https://www.growkudos.com/publications/10.1145%25252F3807498/reader]</t>
+  </si>
+  <si>
+    <t>[https://www.linkedin.com/posts/iptc-upm_ai-research-iptc-activity-7452007237356605440-82L3?utm_source=share&amp;utm_medium=member_android&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, IEEE Spectrum,  https://short.upm.es/fca0j, radio, AI Index Report Stanford 2026]</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[https://arxiv.org/abs/2604.22829] </t>
+  </si>
+  <si>
+    <t>Lost in the Vibrations: Vision Language Models Fail the Dynamic Gauges Test</t>
+  </si>
+  <si>
+    <t>T. Fu, F. J. Santos-Martín, J. Conde, P. Reviriego, E. Merino-Gómez</t>
   </si>
 </sst>
 </file>
@@ -2453,7 +2508,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2620,6 +2675,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2925,10 +2984,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="40"/>
@@ -4190,7 +4249,9 @@
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
+      <c r="Z16" s="5" t="s">
+        <v>388</v>
+      </c>
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
       <c r="AC16" s="5" t="s">
@@ -4743,7 +4804,7 @@
       <c r="AE26" s="5"/>
       <c r="AF26" s="17"/>
     </row>
-    <row r="27" spans="1:32" s="19" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" s="19" customFormat="1" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>51</v>
       </c>
@@ -5006,7 +5067,7 @@
       <c r="AE31" s="5"/>
       <c r="AF31" s="17"/>
     </row>
-    <row r="32" spans="1:32" ht="65" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>374</v>
       </c>
@@ -5036,7 +5097,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="65" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>374</v>
       </c>
@@ -5066,7 +5127,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="52" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="52" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>374</v>
       </c>
@@ -5090,7 +5151,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" ht="52" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="52" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>374</v>
       </c>
@@ -5148,7 +5209,7 @@
       </c>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" ht="78" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="78" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>374</v>
       </c>
@@ -5206,7 +5267,7 @@
       </c>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" ht="78" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="78" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>374</v>
       </c>
@@ -5234,7 +5295,7 @@
       </c>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" ht="65" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>374</v>
       </c>
@@ -5322,7 +5383,7 @@
       </c>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" ht="65" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>374</v>
       </c>
@@ -5350,7 +5411,7 @@
       </c>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" ht="65" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -5378,7 +5439,7 @@
       </c>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" ht="52" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="52" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>378</v>
       </c>
@@ -5398,7 +5459,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="102" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>378</v>
       </c>
@@ -5421,7 +5482,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="153" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>378</v>
       </c>
@@ -5444,7 +5505,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="102" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>378</v>
       </c>
@@ -5467,7 +5528,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="91" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" ht="91" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="55" t="s">
         <v>329</v>
       </c>
@@ -5502,7 +5563,7 @@
       <c r="T49" s="59"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" spans="1:21" ht="39" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26" ht="39" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="55" t="s">
         <v>329</v>
       </c>
@@ -5537,7 +5598,7 @@
       <c r="T50" s="59"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="1:21" ht="78" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" ht="78" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="55" t="s">
         <v>329</v>
       </c>
@@ -5572,7 +5633,7 @@
       <c r="T51" s="59"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="1:21" ht="65" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26" ht="65" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="55" t="s">
         <v>329</v>
       </c>
@@ -5607,7 +5668,7 @@
       <c r="T52" s="59"/>
       <c r="U52" s="1"/>
     </row>
-    <row r="53" spans="1:21" ht="39" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26" ht="39" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="55" t="s">
         <v>329</v>
       </c>
@@ -5642,7 +5703,7 @@
       <c r="T53" s="59"/>
       <c r="U53" s="1"/>
     </row>
-    <row r="54" spans="1:21" ht="52" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26" ht="52" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="55" t="s">
         <v>329</v>
       </c>
@@ -5677,7 +5738,7 @@
       <c r="T54" s="59"/>
       <c r="U54" s="1"/>
     </row>
-    <row r="55" spans="1:21" ht="143" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" ht="143" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="55" t="s">
         <v>329</v>
       </c>
@@ -5712,7 +5773,7 @@
       <c r="T55" s="59"/>
       <c r="U55" s="1"/>
     </row>
-    <row r="56" spans="1:21" ht="48" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="55" t="s">
         <v>329</v>
       </c>
@@ -5747,7 +5808,7 @@
       <c r="T56" s="59"/>
       <c r="U56" s="1"/>
     </row>
-    <row r="57" spans="1:21" ht="26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="55" t="s">
         <v>329</v>
       </c>
@@ -5782,7 +5843,7 @@
       <c r="T57" s="59"/>
       <c r="U57" s="1"/>
     </row>
-    <row r="58" spans="1:21" ht="26" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:26" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="55" t="s">
         <v>329</v>
       </c>
@@ -5817,8 +5878,78 @@
       <c r="T58" s="59"/>
       <c r="U58" s="1"/>
     </row>
+    <row r="59" spans="1:26" ht="136" x14ac:dyDescent="0.2">
+      <c r="A59" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="41">
+        <v>2026</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="E59" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="L59" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M59" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N59" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="V59" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="W59" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z59" s="19" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" ht="119" x14ac:dyDescent="0.2">
+      <c r="A60" s="60" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60" s="41">
+        <v>2026</v>
+      </c>
+      <c r="D60" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="N60" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="V60" s="61" t="s">
+        <v>390</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AG59" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="E32" r:id="rId1" xr:uid="{4B5B929C-7A79-6F41-A67E-175BE183C620}"/>
     <hyperlink ref="E33" r:id="rId2" xr:uid="{EBDA8170-3F43-9041-8F4F-BB51546B6F94}"/>
@@ -5844,6 +5975,8 @@
     <hyperlink ref="E56" r:id="rId22" xr:uid="{8DD2F201-274F-864C-84D2-7A88128FF43A}"/>
     <hyperlink ref="E57" r:id="rId23" xr:uid="{FC3B4EAF-FDE4-454C-84BA-CB4880C5FC73}"/>
     <hyperlink ref="E58" r:id="rId24" xr:uid="{FEB3D0CC-AB9F-2647-9A5C-0AB383944534}"/>
+    <hyperlink ref="E59" r:id="rId25" xr:uid="{3E708637-7DFC-BC4F-8277-D5126B7ACC4D}"/>
+    <hyperlink ref="W59" r:id="rId26" display="https://github.com/aMa2210/AI_impostors " xr:uid="{2C7D1680-1A8D-2249-9D40-455273633F2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C2FB2D-0B36-CE46-8447-04B10A97B2DD}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44B201E-4D1F-304E-B21A-BAE9F1800A14}"/>
   <bookViews>
-    <workbookView xWindow="-38420" yWindow="-1340" windowWidth="35960" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="35960" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1912,7 +1912,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1940,146 +1940,6 @@
       <fill>
         <patternFill>
           <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6414,6 +6274,9 @@
       <c r="A70" s="54" t="s">
         <v>469</v>
       </c>
+      <c r="B70" s="52">
+        <v>2026</v>
+      </c>
       <c r="D70" s="50" t="s">
         <v>478</v>
       </c>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="650" documentId="11_B4FEE90F0E867F547D45747291906F8527311C5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886B5481-432A-364C-AB4A-80C235DBDD48}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_220CE0D83A725766AD066C3559B1863E075FD0F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA491456-D40C-FB42-9797-0C8AF7E3975C}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="19280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AI$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AI$73</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="784">
   <si>
     <t>Tipo</t>
   </si>
@@ -99,12 +94,12 @@
     <t>Open Access</t>
   </si>
   <si>
+    <t>En el repo de UPM</t>
+  </si>
+  <si>
     <t>Datos/Repos</t>
   </si>
   <si>
-    <t>En el repo de UPM</t>
-  </si>
-  <si>
     <t>Proyectos ligados</t>
   </si>
   <si>
@@ -166,6 +161,9 @@
   </si>
   <si>
     <t>[https://oa.upm.es/52004/]</t>
+  </si>
+  <si>
+    <t>Final degree project on extending the functionality of the VPLS application for the ONOS controller, an open-source SDN platform developed at ETSIT-UPM.</t>
   </si>
   <si>
     <t>@misc{Conde2018VPLS,
@@ -190,6 +188,12 @@
     <t>https://oa.upm.es/62772/</t>
   </si>
   <si>
+    <t>[https://oa.upm.es/62772/]</t>
+  </si>
+  <si>
+    <t>Master’s thesis on the digital integration of administrative and academic processes at ETSIT-UPM, exploring solutions for the modernization of institutional procedures.</t>
+  </si>
+  <si>
     <t>@misc{Conde2020Integracion,
   title = {Integración Digital de Procesos Administrativos y Académicos de la ETSIT},
   author = {Conde Díaz, Javier},
@@ -227,6 +231,9 @@
   </si>
   <si>
     <t>A. Munoz-Arcentales, S. López-Pernas, J. Conde, Á. Alonso, J. Salvachúa, J. J. Hierro</t>
+  </si>
+  <si>
+    <t>[https://www.mdpi.com/1424-8220/21/21/7095, https://oa.upm.es/74845/]</t>
   </si>
   <si>
     <t>https://oa.upm.es/74845/</t>
@@ -272,6 +279,9 @@
     <t>J. Conde, S. López-Pernas, A. Pozo, A. Munoz-Arcentales, G. Huecas, Á. Alonso</t>
   </si>
   <si>
+    <t>[https://www.mdpi.com/2079-9292/10/13/1523, https://oa.upm.es/71049/]</t>
+  </si>
+  <si>
     <t>https://oa.upm.es/71049/</t>
   </si>
   <si>
@@ -336,6 +346,9 @@
     <t>[https://www.fiware.org/wp-content/uploads/FF_ImpactStories_Arportwin.pdf]</t>
   </si>
   <si>
+    <t>[Arportwin]</t>
+  </si>
+  <si>
     <t>FIWARE Impact Story describing the A/Rportwin augmented reality tool for airport operations, presenting the use case, technical architecture, and business impact of implementing AR digital twin capabilities.</t>
   </si>
   <si>
@@ -378,10 +391,10 @@
     <t>[https://arxiv.org/pdf/2408.14291, https://www.researchgate.net/publication/383428295]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/74849/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.18734748, https://github.com/ging/arport_twin_deployment, https://github.com/smart-data-models/dataModel.Aeronautics]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/74849/</t>
   </si>
   <si>
     <t>[https://x.com/GING_UPM/status/1975911555243061622?s=20,  https://x.com/JaviConD3/status/1520041949847244800?s=20]</t>
@@ -438,10 +451,10 @@
     <t>[ https://arxiv.org/abs/2309.12358]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/84893/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.18734900, https://github.com/ging/fiware_parking_digital_twin]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/84893/</t>
   </si>
   <si>
     <t xml:space="preserve">[https://x.com/JaviConD3/status/1545016361432367104?s=20, https://x.com/GING_UPM/status/1975911547726864768?s=20,  </t>
@@ -493,6 +506,9 @@
     <t>[https://arxiv.org/abs/2402.02252]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/74846/</t>
+  </si>
+  <si>
     <t>The collaboration of the real world and the virtual world, known as Digital Twin, has become a trend with numerous successful use cases. However, there are challenges mentioned in the literature that must be addressed. One of the most important issues is the difficulty of collaboration of Digital Twins due to the lack of standardization in their implementation. This article continues a previous work that proposed a generic architecture based on the FIWARE components to build Digital Twins in any field. Our work proposes the use of Linked Open Data as a mechanism to facilitate the communication of Digital Twins. We validate our proposal with a use case of an urban Digital Twin that collaborates with a parking Digital Twin. We conclude that Linked Open Data in combination with the FIWARE ecosystem is a real reference option to deploy Digital Twins and to enable the collaboration between Digital Twins.</t>
   </si>
   <si>
@@ -527,6 +543,15 @@
     <t>J. Conde, A. Munoz-Arcentales, J. Choque, G. Huecas, A. Alonso</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2408.14315]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/74848/</t>
+  </si>
+  <si>
+    <t>[YODA]</t>
+  </si>
+  <si>
     <t>We study the benefits and challenges of using Linked Open Data in smart city applications and propose a set of open source, highly scalable tools within the case of a public-rental bicycle system, which can act as a reference guide for other smart city applications.</t>
   </si>
   <si>
@@ -595,6 +620,9 @@
     <t xml:space="preserve">J. Hernández, J. Conde, B. Querol, G. Martínez, P. Reviriego </t>
   </si>
   <si>
+    <t>https://oa.upm.es/82775/</t>
+  </si>
+  <si>
     <t>Libro de divulgación sobre ChatGPT con 100 ejemplos de prompts organizados por categorías. Guía práctica para iniciarse en el uso de modelos de lenguaje grandes mediante técnicas de prompting.</t>
   </si>
   <si>
@@ -620,6 +648,9 @@
   </si>
   <si>
     <t>https://oa.upm.es/74176/</t>
+  </si>
+  <si>
+    <t>Doctoral thesis on architectures and solutions for implementing digital twins based on open data using FIWARE. It covers everything from integrating heterogeneous data to collaboration between digital twins through Linked Open Data.</t>
   </si>
   <si>
     <t>@misc{Conde2023Tesis,
@@ -645,6 +676,9 @@
     <t>Authorea Preprints</t>
   </si>
   <si>
+    <t>IEEE TechRxiv</t>
+  </si>
+  <si>
     <t>J. Hernandez, J. Conde, P. Reviriego, G. Martínez</t>
   </si>
   <si>
@@ -664,6 +698,9 @@
 }</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>Adaptive Resolution Inference (ARI): Energy Efficient Machine Learning for the Internet of Things</t>
   </si>
   <si>
@@ -688,10 +725,13 @@
     <t>[https://arxiv.org/abs/2408.14528, https://www.researchgate.net/publication/383460294]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/76847/</t>
+  </si>
+  <si>
     <t>[http://ufldl.stanford.edu/housenumbers/, https://github.com/zalandoresearch/fashion-mnist, https://www.cs.toronto.edu/~kriz/cifar.html]</t>
   </si>
   <si>
-    <t>https://oa.upm.es/76847/</t>
+    <t>[FUN4DATE, SMARTY]</t>
   </si>
   <si>
     <t xml:space="preserve">[https://x.com/HPCPapers/status/1828674673246081463?s=20, https://scispace.com/papers/adaptive-resolution-inference-ari-energy-efficient-machine-yka3u8nny0] </t>
@@ -743,19 +783,19 @@
     <t>P. Reviriego, J. Conde, E. Merino-Gómez, J.A. Hernández</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>muchas</t>
   </si>
   <si>
     <t>[https://arxiv.org/abs/2308.07462, https://www.researchgate.net/publication/385756888]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/85304/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.11199029]</t>
   </si>
   <si>
-    <t>https://oa.upm.es/85304/</t>
+    <t>[FUN4DATE, OpenAI Research Access Program]</t>
   </si>
   <si>
     <t>[https://www.forbes.com/sites/jasonsnyder/2025/05/14/ai-is-rewriting-reality-one-word-at-a-time/, https://www.linkedin.com/posts/parameterlab_playing-with-words-comparing-the-vocabulary-activity-7100703445124280320-2lNj?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
@@ -797,10 +837,13 @@
     <t>[https://arxiv.org/abs/2409.08284, https://www.researchgate.net/publication/375812200, https://zenodo.org/records/12742172]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/76738/</t>
+  </si>
+  <si>
     <t>[https://edatos.consorciomadrono.es/dataset.xhtml?persistentId=doi:10.21950/L7VJZV, https://github.com/ging/escapp, ]</t>
   </si>
   <si>
-    <t>https://oa.upm.es/76738/</t>
+    <t>[FUN4DATE]</t>
   </si>
   <si>
     <t>[https://innovacioneducativa.upm.es/articulos/empowering-database-learning-through-remote-educational-escape-rooms?utm_source=chatgpt.com, https://cyberaula.github.io/research, https://x.com/WGOV/status/1835538317942706214?s=20]</t>
@@ -852,13 +895,10 @@
     <t>[https://arxiv.org/abs/2411.13583, https://www.researchgate.net/publication/386021372]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/84890/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.14173285]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/84890/</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY]</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/posts/javier-conde-diaz_enhanced-fiware-based-architecture-for-cyberphysical-activity-7264301875078852611-sux-, https://github.com/gauravfs-14/awesome-tinyml]</t>
@@ -911,6 +951,12 @@
     <t>bastantes</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2502.16721]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/90614/</t>
+  </si>
+  <si>
     <t>Lo malo que es columna</t>
   </si>
   <si>
@@ -942,6 +988,12 @@
     <t>J.Conde, P. Reviriego, J. Salvachúa, G. Martínez, J.A. Hernández, F. Lombardi</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2502.16713]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/77072</t>
+  </si>
+  <si>
     <t>This column advocates for including artificial intelligence (AI)-specific metadata on those academic papers that are written with the help of AI in an attempt to analyze the use of such tools for disseminating research.</t>
   </si>
   <si>
@@ -982,6 +1034,18 @@
     <t>G. Martínez, J. Conde, E. Merino-Gómez, B. Bermúdez-Margaretto, J. Hernández, P. Reviriego, M. Brysbaert</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2310.14703]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/85330/</t>
+  </si>
+  <si>
+    <t>[https://github.com/WordsGPT/LLM_Vocabulary_Evaluation]</t>
+  </si>
+  <si>
+    <t>[CyberTutor, FUN4DATE, SMARTY]</t>
+  </si>
+  <si>
     <t>Vocabulary tests, once a cornerstone of language modeling evaluation, have been largely overlooked in the current landscape of Large Language Models (LLMs) like Llama 2, Mistral, and GPT. While most LLM evaluation benchmarks focus on specific tasks or domain-specific knowledge, they often neglect the fundamental linguistic aspects of language understanding. In this paper, we advocate for the revival of vocabulary tests as a valuable tool for assessing LLM performance. We evaluate seven LLMs using two vocabulary test formats across two languages and uncover surprising gaps in their lexical knowledge. These findings shed light on the intricacies of LLM word representations, their learning mechanisms, and performance variations across models and languages. Moreover, the ability to automatically generate and perform vocabulary tests offers new opportunities to expand the approach and provide a more complete picture of LLMs’ language skills.</t>
   </si>
   <si>
@@ -1025,6 +1089,13 @@
     <t>[https://osf.io/preprints/psyarxiv/zqfsj]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/85140/</t>
+  </si>
+  <si>
+    <t>[https://osf.io/frc6a/
+]</t>
+  </si>
+  <si>
     <t>This study investigates whether estimates of familiarity, valence, arousal, and concreteness based on artificial intelligence (AI) are useful alternatives to word counts and human ratings in Spanish. We replicate and extend previous findings in English and show that GPT-4o is effective in estimating these word features. Validity checks even suggest that AI-generated estimates sometimes outperform traditional measurements. The ability to generate AI estimates for large numbers of words at low cost simplifies the process of obtaining word features and provides a new resource for researchers working in Spanish. We provide Excel lists of the collected word features, which can be freely used for research and teaching.</t>
   </si>
   <si>
@@ -1071,6 +1142,10 @@
     <t>https://oa.upm.es/93786/</t>
   </si>
   <si>
+    <t>[https://zenodo.org/doi/10.5281/zenodo.
+10797991          ]</t>
+  </si>
+  <si>
     <t>The growing interest in Large Language Models (LLMs) and in particular in conversational models with which users can interact has led to the development of a large number of open-source chat LLMs. These models are evaluated on a wide range of benchmarks to assess their capabilities in answering questions or solving problems on almost any possible topic or to test their ability to reason or interpret texts. Instead, the evaluation of the knowledge that these models have of the languages has received much less attention. For example, the words that they can recognize and use in different languages. In this paper, we evaluate the knowledge that open-source chat LLMs have of Spanish words by testing a sample of words in a reference dictionary. The results show that open-source chat LLMs produce incorrect meanings for an important fraction of the words and are not able to use most of the words correctly to write sentences with context. These results show how Spanish is left behind in the open-source LLM race and highlight the need to push for linguistic fairness in conversational LLMs ensuring that they provide similar performance across languages.</t>
   </si>
   <si>
@@ -1108,6 +1183,9 @@
     <t>[https://doi.org/10.1145/3605098.3636201]</t>
   </si>
   <si>
+    <t>[https://oa.upm.es/83196]</t>
+  </si>
+  <si>
     <t>Academic writing is one of the most important tasks in Academia. The pressure to "publish or perish" drives researchers to use all the tools available to try to improve their papers and their impact. Generative artificial intelligence (AI) that can create content such as text, tables, and images can be used for many tasks in academic writing such as summarizing, translating, paraphrasing, data analysis, and presentation. Therefore, AI is expected to be widely used in academic writing in the near future and have a significant impact. Understanding this impact is far from trivial and needs to be carefully studied. The first step in doing so is to be able to identify papers written with the help of AI tools. This can be done by adding metadata on the use of AI in academic results. In this paper, we embark on an initial endeavor to devise such metadata and delineate the potential advantages that the inclusion of AI-related metadata in academic publications may bring forth.</t>
   </si>
   <si>
@@ -1139,6 +1217,12 @@
     <t>[https://doi.org/10.1145/3605098.3636072]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/83197/</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, Programa Propio UPM]</t>
+  </si>
+  <si>
     <t>Procrastination is one of the most common problems among students causing mental health issues, low motivation, and poor academic performance. The emergence of Learning Management Systems has made it possible to accurately pinpoint when procrastination takes place due to the unobtrusive collection of fine-grained data from students. However, most studies that analyze procrastination regard it as an intrinsic characteristic of students. In this work, we study procrastination as a process that unfolds with time. We use sequence analysis to map the evolution of students' procrastination behavior over a task-oriented programming course. Our findings evince that students' procrastination is not constant throughout a course and that students who tend to procrastinate are those who achieve worse academic performance.</t>
   </si>
   <si>
@@ -1170,6 +1254,9 @@
     <t>J. Conde, G. Martínez, P. Reviriego, J. Hernández</t>
   </si>
   <si>
+    <t>https://oa.upm.es/83194</t>
+  </si>
+  <si>
     <t>One of the potential advantages of Low Earth Orbiting (LEO) satellite constellation networks is the reduction in delay, which is critical for some services and applications. Theoretically, LEO satellite networks have a lower propagation delay when the endpoints are at distances longer than a few thousand km due to the higher propagation speed of radio transmission compared to fiber. However, the theoretical analysis makes assumptions about transmission paths that are not valid in all cases and does not account for other factors that influence delay, such as processing or queuing delays. Therefore, experimental studies are needed based on measurements and simulations. This paper presents the first comparison between real Round Trip Time (RTT) measurements on terrestrial networks and simulated RTTs on different LEO constellations. The results confirm the potential benefits of LEO constellations not only in reducing RTT values, but also in reducing their dispersion versus distance.</t>
   </si>
   <si>
@@ -1207,6 +1294,9 @@
     <t>[https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf]</t>
   </si>
   <si>
+    <t>[https://www.upm.es/?id=CON03210&amp;prefmt=articulo&amp;fmt=detail]</t>
+  </si>
+  <si>
     <t>Comunicación en SEL 2024 sobre la evaluación del conocimiento léxico de ChatGPT con ChatWords, herramienta para valorar la competencia léxica de LLMs en español.</t>
   </si>
   <si>
@@ -1356,6 +1446,9 @@
     <t>[https://arxiv.org/abs/2412.18626]</t>
   </si>
   <si>
+    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
+  </si>
+  <si>
     <t>Large Language Models (LLMs) have achieved unprecedented performance on many complex tasks, being able, for example, to answer questions on almost any topic. However, they struggle with other simple tasks, such as counting the occurrences of letters in a word, as illustrated by the inability of many LLMs to count the number of &amp;#34;r&amp;#34; letters in &amp;#34;strawberry&amp;#34;. Several works have studied this problem and linked it to the tokenization used by LLMs, to the intrinsic limitations of the attention mechanism, or to the lack of character-level training data. In this paper, we conduct an experimental study to evaluate the relations between the LLM errors when counting letters with 1) the frequency of the word and its components in the training dataset and 2) the complexity of the counting operation. We present a comprehensive analysis of the errors of LLMs when counting letter occurrences by evaluating a representative group of models over a large number of words. The results show a number of consistent trends in the models evaluated: 1) models are capable of recognizing the letters but not counting them; 2) the frequency of the word and tokens in the word does not have a significant impact on the LLM errors; 3) there is a positive correlation of letter frequency with errors, more frequent letters tend to have more counting errors, 4) the errors show a strong correlation with the number of letters or tokens in a word and 5) the strongest correlation occurs with the number of letters with counts larger than one, with most models being unable to correctly count words in which letters appear more than twice.</t>
   </si>
   <si>
@@ -1369,6 +1462,9 @@
 }</t>
   </si>
   <si>
+    <t>sent to ACM TIST</t>
+  </si>
+  <si>
     <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
   </si>
   <si>
@@ -1382,6 +1478,9 @@
   </si>
   <si>
     <t>[https://arxiv.org/abs/2402.06693]</t>
+  </si>
+  <si>
+    <t>[Eunomia, YODA]</t>
   </si>
   <si>
     <t>The term Data Space, understood as the secure exchange of data in distributed systems, ensuring openness, transparency, decentralization, sovereignty, and interoperability of information, has gained importance during the last years. However, Data Spaces are in an initial phase of definition, and new research is necessary to address their requirements. The Open Data ecosystem can be understood as one of the precursors of Data Spaces as it provides mechanisms to ensure the interoperability of information through resource discovery, information exchange, and aggregation via metadata. However, Data Spaces require more advanced capabilities including the automatic and scalable generation and publication of high-quality metadata. In this work, we present a set of software tools that facilitate the automatic generation and publication of metadata, the modeling of datasets through standards, and the assessment of the quality of the generated metadata. We validate all these tools through the YODA Open Data Portal showing how they can be connected to integrate Open Data into Data Spaces.</t>
@@ -1418,10 +1517,10 @@
     <t>[https://arxiv.org/abs/2402.15518]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/83872/</t>
+  </si>
+  <si>
     <t>[https://zenodo.org/doi/10.5281/zenodo.10646081]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83872/</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/posts/pedro-reviriego-b582094_chatgpt-lexicalrichness-generativeai-activity-7168153851135565824-kHuP, https://www.linkedin.com/feed/update/urn:li:activity:7431080457901076481, https://x.com/GING_UPM/status/2025317567779242275?s=20]</t>
@@ -1470,10 +1569,13 @@
     <t>[https://arxiv.org/abs/2403.16393]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/90710/</t>
+  </si>
+  <si>
     <t>[https://github.com/WordsGPT/CLED_injection_errors, https://doi.org/10.5281/zenodo.10647623]</t>
   </si>
   <si>
-    <t>https://oa.upm.es/90710/</t>
+    <t>[SMARTY, TUCAN6-CM]</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/posts/javier-conde-diaz_concurrent-linguistic-error-detection-cled-activity-7371892393534623744-a3TY?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, https://www.linkedin.com/feed/update/urn:li:activity:7178422077975052288?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, https://x.com/SciFi/status/1772770591818314108?s=20,]</t>
@@ -1522,10 +1624,13 @@
     <t>[https://arxiv.org/abs/2409.05674, https://www.researchgate.net/publication/396089486]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/91436/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.18734591, https://huggingface.co/datasets/speechcolab/gigaspeech]</t>
   </si>
   <si>
-    <t>https://oa.upm.es/91436/</t>
+    <t>[FUN4DATE, TUCAN6-CM]</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/feed/update/urn:li:activity:7406068795590590464, https://x.com/HEI/status/1834422463444250842?s=20]</t>
@@ -1571,6 +1676,9 @@
     <t>https://oa.upm.es/88857/</t>
   </si>
   <si>
+    <t>[FUN4DATE, SMARTY, TUCAN6-CM]</t>
+  </si>
+  <si>
     <t>[https://x.com/Memoirs/status/1956079657746391178?s=20, ]</t>
   </si>
   <si>
@@ -1617,10 +1725,10 @@
     <t>[https://arxiv.org/abs/2407.09549]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/89166/</t>
+  </si>
+  <si>
     <t>[https://zenodo.org/records/15098223, https://huggingface.co/spaces/GING-UPM/recursive_inpainting, ]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/89166/</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/feed/update/urn:li:activity:7219058630413737986?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
@@ -1658,6 +1766,16 @@
     <t>T. Fu, M. González, J. Conde, E. Merino-Gómez, P. Reviriego</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2505.10862]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/92641/</t>
+  </si>
+  <si>
+    <t>[tps://huggingface.co/datasets/
+migonsa/analog_clocks_combinations_for_finetuning, https://github.com/aMa2210/MLLMs_read_analog_clocks]</t>
+  </si>
+  <si>
     <t>[https://www.linkedin.com/posts/iptc-upm_ai-research-iptc-activity-7452007237356605440-82L3?utm_source=share&amp;utm_medium=member_android&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, IEEE Spectrum,  https://short.upm.es/fca0j, radio, AI Index Report Stanford 2026]</t>
   </si>
   <si>
@@ -1689,6 +1807,12 @@
     <t>J. Conde, G. Martínez, P. Reviriego, Z. Gao, S. Liu, F. Lombardi</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2502.16705]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/87994</t>
+  </si>
+  <si>
     <t>Lo malo que es un paper de columna</t>
   </si>
   <si>
@@ -1735,6 +1859,18 @@
     <t>E. Sendín, J. Conde, P. Reviriego, J. Haro, P. Ferré, J. Hinojosa, M. Brysbaert</t>
   </si>
   <si>
+    <t>https://oa.upm.es/91144</t>
+  </si>
+  <si>
+    <t>[https://osf.io/p6fuy/]</t>
+  </si>
+  <si>
+    <t>[https://www.cienciacognitiva.org/?p=2641]</t>
+  </si>
+  <si>
+    <t>Es open access diamond</t>
+  </si>
+  <si>
     <t>Study combining LLMs with fine-tuning based on strategically collected human ratings, with a case study on age-of-acquisition estimates of Spanish words showing that LLMs fine-tuned with small human datasets closely match large-scale norming studies.</t>
   </si>
   <si>
@@ -1763,6 +1899,9 @@
   </si>
   <si>
     <t>Z. Gao, L. Yuan, J. Wang, Q. Liu, J. Conde, P. Reviriego</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/88428</t>
   </si>
   <si>
     <t>Large Language Models (LLMs) pose significant challenges in terms of speed and energy dissipation of AI systems. Dependability is a further important issue for LLM implementations; this is especially relevant for FPGAs that are vulnerable to soft errors in the configuration memory. Moreover, as current GPU based implementations are not energy efficient, there is interest in running LLMs on different technology platforms, such as FlightLLM (an FPGA based accelerator designed to run LLMs for energy efficiency). In this paper, we analyze and evaluate the robustness of FPGA-based LLMs against faults/errors in the configuration memories. For the evaluation, we first propose a PyTorch based fault injection simulator and based on the analysis of FlightLLM and we study its robustness against stuck-at faults on the configuration memory. Furthermore, we propose an efficient error detection technique based on a concurrent classifier. Evaluation results show that stuck-at errors on high bits of the logic units can dramatically degrade the LLM performance, and the proposed concurrent classifier can effectively detect errors with negligible complexity and overhead. Finally, a low-cost fault location scheme is proposed, so that the fault can be easily recovered by dynamic partial reconfiguration. The combination of the concurrent classifier error detection and fault location can be used to improve the robustness of a FPGA-based LLM efficiently, such as FlightLLM.</t>
@@ -1799,6 +1938,18 @@
     <t xml:space="preserve"> “Psychology, Mathematical” - SSCI</t>
   </si>
   <si>
+    <t>[https://www.researchgate.net/publication/395768986, https://osf.io/p5ybm/files/37m6j]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/91146/</t>
+  </si>
+  <si>
+    <t>[https://osf.io/p5ybm/overview]</t>
+  </si>
+  <si>
+    <t>OJO solo subida la versión submitted no la accepted a otros repos</t>
+  </si>
+  <si>
     <t>Study evaluating the ability of large language models to simulate lexical decision times, demonstrating that LLMs can supplement traditional crowdsourcing approaches for psycholinguistic norming.</t>
   </si>
   <si>
@@ -1832,6 +1983,12 @@
     <t>M. Mayor-Rocher, N. Melero, E. Merino-Gómez, M. González, R. Ferrando, J. Conde, P. Reviriego</t>
   </si>
   <si>
+    <t>https://oa.upm.es/88338/</t>
+  </si>
+  <si>
+    <t>[ https://zenodo.org/doi/10.5281/zenodo.12571762]</t>
+  </si>
+  <si>
     <t>This paper presents TELEIA, a dataset for the evaluation of Spanish language knowledge in Large Language Models (LLMs). TELEIA is designed to complement existing LLMs tests that evaluate many knowledge areas or tasks and are written in English. To evaluate LLMs in Spanish these English tests are translated, which is reasonable for most technical areas and for many tasks, but not when evaluating the knowledge of the Spanish language. New tests specifically designed for Spanish are needed to evaluate the knowledge of the language. This paper introduces TELEIA, a dataset that is an initial step in that direction. The dataset is designed as a set of multiple-choice questions that have the same format and level as those used in several Spanish evaluation tests for humans. The multiple-choice questions enable automation of LLM testing and the use of TELEIA in existing LLM Leaderboards. The questions are divided in three blocks which resemble existing tests of Spanish for foreign learners and for University access. In total, one hundred questions are included that have been prepared and revised by experts on Spanish language, and that have been validated by comparing with the original exams. The dataset will be included in the first Leaderboard of Spanish LLMs.</t>
   </si>
   <si>
@@ -1859,6 +2016,15 @@
     <t>G. Martínez, J. Molero, S. González, J. Conde, M. Brysbaert, P. Reviriego</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2408.16012, https://www.researchgate.net/profile/Marc-Brysbaert/publication/385448704]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/85232/</t>
+  </si>
+  <si>
+    <t>[ https://osf.io/k5a4x/]</t>
+  </si>
+  <si>
     <t>This study investigates the potential of large language models (LLMs) to provide accurate estimates of concreteness, valence, and arousal for multi-word expressions. Unlike previous artificial intelligence (AI) methods, LLMs can capture the nuanced meanings of multi-word expressions. We systematically evaluated GPT-4o's ability to predict concreteness, valence, and arousal. In Study 1, GPT-4o showed strong correlations with human concreteness ratings (r = .8) for multi-word expressions. In Study 2, these findings were repeated for valence and arousal ratings of individual words, matching or outperforming previous AI models. Studies 3–5 extended the valence and arousal analysis to multi-word expressions and showed good validity of the LLM-generated estimates for these stimuli as well. To help researchers with stimulus selection, we provide datasets with LLM-generated norms of concreteness, valence, and arousal for 126,397 English single words and 63,680 multi-word expressions.</t>
   </si>
   <si>
@@ -1895,6 +2061,15 @@
     <t>[https://arxiv.org/abs/2409.16297]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/95204/</t>
+  </si>
+  <si>
+    <t>[https://zenodo.org/doi/10.5281/zenodo.13362646]</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program, Programa Propio UPM]</t>
+  </si>
+  <si>
     <t>One of the latest trends in generative Artificial Intelligence is tools that generate and analyze content in different modalities, such as text and images, and convert information from one to the other. From a conceptual point of view, it is interesting to study whether these modality changes incur information loss and to what extent. This is analogous to variants of the classical game telephone, where players alternate between describing images and creating drawings based on those descriptions leading to unexpected transformations of the original content. In the case of AI, modality changes can be applied recursively, starting from an image to extract a text that describes it; using the text to generate a second image, extracting a text that describes it, and so on. As this process is applied recursively, AI tools are generating content from one mode to use them to create content in another mode and so on. Ideally, the embeddings of all of them would remain close to those of the original content so that only small variations are observed in the generated content versus the original one. However, it may also be the case the distance to the original embeddings increases in each iteration leading to a divergence in the process and to content that is barely related to the original one. In this paper, we present the results of an empirical study on the impact of recursive modality changes using GPT-4o, a state-of-the-art AI multimodal tool, and DALL-E 3. The results show that the multimodality loop diverges from the initial image without converging to anything specific. We have observed differences depending on the type of initial image and the configuration of the models. These findings are particularly relevant due to the increasing use of these tools for content generation, reconstruction, and adaptation, and their potential implications for the content on the Internet of the future.</t>
   </si>
   <si>
@@ -1981,7 +2156,19 @@
     <t>ACL</t>
   </si>
   <si>
+    <t>CORE A*</t>
+  </si>
+  <si>
     <t>M. Grandury, J. Aula-Blasco, […], J. Conde, […], I. Zubiaga</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2507.00999]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/89095</t>
+  </si>
+  <si>
+    <t>[https://huggingface.co/datasets/la-leaderboard]</t>
   </si>
   <si>
     <t>Leaderboards showcase the current capabilities and limitations of Large Language Models (LLMs). To motivate the development of LLMs that represent the linguistic and cultural diversity of the Spanish-speaking community, we present La Leaderboard, the first open-source leaderboard to evaluate generative LLMs in languages and language varieties of Spain and Latin America. La Leaderboard is a community-driven project that aims to establish an evaluation standard for everyone interested in developing LLMs for the Spanish-speaking community. This initial version combines 66 datasets in Basque, Catalan, Galician, and different Spanish varieties, showcasing the evaluation results of 50 models. To encourage community-driven development of leaderboards in other languages, we explain our methodology, including guidance on selecting the most suitable evaluation setup for each downstream task. In particular, we provide a rationale for using fewer few-shot examples than typically found in the literature, aiming to reduce environmental impact and facilitate access to reproducible results for a broader research community.</t>
@@ -2009,10 +2196,13 @@
     <t>Proceedings of the Fourth Workshop on Generation, Evaluation and Metrics (GEM)</t>
   </si>
   <si>
-    <t>CORE A*</t>
-  </si>
-  <si>
     <t>J. Conde, M. González, M. Grandury, G. Martínez, P. Reviriego, M. Brysbaert</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2506.22439]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/90381</t>
   </si>
   <si>
     <t>The evaluation of LLMs has so far focused primarily on how well they can perform different tasks such as reasoning, question-answering, paraphrasing, or translating. For most of these tasks, performance can be measured with objective metrics, such as the number of correct answers. However, other language features are not easily quantified. For example, arousal, concreteness, or gender associated with a given word, as well as the extent to which we experience words with senses and relate them to a specific sense. Those features have been studied for many years by psycholinguistics, conducting large-scale experiments with humans to produce ratings for thousands of words. This opens an opportunity to evaluate how well LLMs align with human ratings on these word features, taking advantage of existing studies that cover many different language features in a large number of words. In this paper, we evaluate the alignment of a representative group of LLMs with human ratings on two psycholinguistic datasets: the Glasgow and Lancaster norms. These datasets cover thirteen features over thousands of words. The results show that alignment is \textcolor{black}{generally} better in the Glasgow norms evaluated (arousal, valence, dominance, concreteness, imageability, familiarity, and gender) than on the Lancaster norms evaluated (introceptive, gustatory, olfactory, haptic, auditory, and visual). This suggests a potential limitation of current LLMs in aligning with human sensory associations for words, which may be due to their lack of embodied cognition present in humans and illustrates the usefulness of evaluating LLMs with psycholinguistic datasets.</t>
@@ -2047,6 +2237,15 @@
     <t>I. Plaza, N. Melero, C. del Pozo, J. Conde, P. Reviriego, M. Mayor</t>
   </si>
   <si>
+    <t>[https://arxiv.org/abs/2406.17789]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/92045/</t>
+  </si>
+  <si>
+    <t>[https://zenodo.org/records/11314109]</t>
+  </si>
+  <si>
     <t>The evaluation of Large Language Models (LLMs) is a key element in their continuous improvement process and many benchmarks have been developed to assess the performance of LLMs in different tasks and topics. As LLMs become adopted worldwide, evaluating them in languages other than English is increasingly important. However, most LLM benchmarks are simply translated using an automated tool and then run in the target language. This means that the results depend not only on the LLM performance in that language but also on the quality of the translation. In this paper, we consider the case of the well-known Massive Multitask Language Understanding (MMLU) benchmark. Selected categories of the benchmark are translated into Spanish using Azure Translator and ChatGPT4 and run on ChatGPT4. Next, the results are processed to identify the test items that produce different answers in Spanish and English. Those are then analyzed manually to understand if the automatic translation caused the change. The results show that a significant fraction of the failing items can be attributed to mistakes in the translation of the benchmark. These results make a strong case for improving benchmarks in languages other than English by at least revising the translations of the items and preferably by adapting the tests to the target language by experts.</t>
   </si>
   <si>
@@ -2219,6 +2418,9 @@
     <t>[https://arxiv.org/abs/2506.18674]</t>
   </si>
   <si>
+    <t>[https://github.com/RaquelFerrando/conversational_tokenizers]</t>
+  </si>
+  <si>
     <t>The computational and energy costs of Large Language Models (LLMs) have increased exponentially driven by the growing model sizes and the massive adoption of LLMs by hundreds of millions of users. The unit cost of an LLM is the computation of a token. Therefore, the tokenizer plays an important role in the efficiency of a model, and they are carefully optimized to minimize the number of tokens for the text in their training corpus. One of the most popular applications of LLMs are chatbots that interact with users. A key observation is that, for those chatbots, what is important is the performance of the tokenizer in the user text input and the chatbot responses. Those are most likely different from the text in the training corpus. So, a question that immediately arises is whether there is a potential benefit in optimizing tokenizers for chatbot conversations. In this paper, this idea is explored for different tokenizers by using a publicly available corpus of chatbot conversations to redesign their vocabularies and evaluate their performance in this domain. The results show that conversation-optimized tokenizers consistently reduce the number of tokens in chatbot dialogues, which can lead to meaningful energy savings, in the range of 5% to 10% while having minimal or even slightly positive impact on tokenization efficiency for the original training corpus.</t>
   </si>
   <si>
@@ -2232,6 +2434,9 @@
 }</t>
   </si>
   <si>
+    <t xml:space="preserve">sent </t>
+  </si>
+  <si>
     <t>Real-time spatial retrieval augmented generation for urban environments</t>
   </si>
   <si>
@@ -2245,6 +2450,9 @@
   </si>
   <si>
     <t>[https://arxiv.org/abs/2505.02271]</t>
+  </si>
+  <si>
+    <t>[https://github.com/dncampo/real-time-spatial-rag-for-smart-cities, https://github.com/javicond3/spatial_rag_vector_rag]</t>
   </si>
   <si>
     <t>The proliferation of Generative Artificial Ingelligence (AI), especially Large Language Models, presents transformative opportunities for urban applications through Urban Foundation Models. However, base models face limitations, as they only contain the knowledge available at the time of training, and updating them is both time-consuming and costly. Retrieval Augmented Generation (RAG) has emerged in the literature as the preferred approach for injecting contextual information into Foundation Models. It prevails over techniques such as fine-tuning, which are less effective in dynamic, real-time scenarios like those found in urban environments. However, traditional RAG architectures, based on semantic databases, knowledge graphs, structured data, or AI-powered web searches, do not fully meet the demands of urban contexts. Urban environments are complex systems characterized by large volumes of interconnected data, frequent updates, real-time processing requirements, security needs, and strong links to the physical world. This work proposes a real-time spatial RAG architecture that defines the necessary components for the effective integration of generative AI into cities, leveraging temporal and spatial filtering capabilities through linked data. The proposed architecture is implemented using FIWARE, an ecosystem of software components to develop smart city solutions and digital twins. The design and implementation are demonstrated through the use case of a tourism assistant in the city of Madrid. The use case serves to validate the correct integration of Foundation Models through the proposed RAG architecture.</t>
@@ -2269,7 +2477,16 @@
     <t>https://arxiv.org/abs/2509.14405</t>
   </si>
   <si>
+    <t>J. Conde, M. Grandury, T. Fu, C. Arriaga, G. Martínez, T. Clark, S. Trott, C. G. Green, P. Reviriego, M. Brysbaert</t>
+  </si>
+  <si>
     <t>[https://arxiv.org/abs/2509.14405]</t>
+  </si>
+  <si>
+    <t>[https://github.com/WordsGPT/psycholinguistics_framework]</t>
+  </si>
+  <si>
+    <t>[SMARTY, Programa Propio UPM]</t>
   </si>
   <si>
     <t>Word-level psycholinguistic norms lend empirical support to theories of language processing. However, obtaining such human-based measures is not always feasible or straightforward. One promising approach is to augment human norming datasets by using Large Language Models (LLMs) to predict these characteristics directly, a practice that is rapidly gaining popularity in psycholinguistics and cognitive science. However, the novelty of this approach (and the relative inscrutability of LLMs) necessitates the adoption of rigorous methodologies that guide researchers through this process, present the range of possible approaches, and clarify limitations that are not immediately apparent, but may, in some cases, render the use of LLMs impractical. In this work, we present a comprehensive methodology for estimating word characteristics with LLMs, enriched with practical advice and lessons learned from our own experience. Our approach covers both the direct use of base LLMs and the fine-tuning of models, an alternative that can yield substantial performance gains in certain scenarios. A major emphasis in the guide is the validation of LLM-generated data with human &amp;#34;gold standard&amp;#34; norms. We also present a software framework that implements our methodology and supports both commercial and open-weight models. We illustrate the proposed approach with a case study on estimating word familiarity in English. Using base models, we achieved a Spearman correlation of 0.8 with human ratings, which increased to 0.9 when employing fine-tuned models. This methodology, framework, and set of best practices aim to serve as a reference for future research on leveraging LLMs for psycholinguistic and lexical studies.</t>
@@ -2285,6 +2502,9 @@
 }</t>
   </si>
   <si>
+    <t>sent to BRM</t>
+  </si>
+  <si>
     <t>Stochastic Streets: A Walk Through Random LLM Address Generation in four European Cities</t>
   </si>
   <si>
@@ -2297,16 +2517,22 @@
     <t xml:space="preserve"> “Computer Science, Hardware &amp; Architecture” - SCIE</t>
   </si>
   <si>
+    <t>T. Fu, D. Campo-Nazareno, J. Coronado-Blázquez, J. Conde, P. Reviriego, F. Lombardi</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2509.12914]</t>
+  </si>
+  <si>
+    <t>[https://github.com/aMa2210/LLM_Addresses]</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, SMARTY, TUCAN6-CM, OpenAI Research Access Program]</t>
+  </si>
+  <si>
+    <t>[https://www.linkedin.com/posts/iptc-upm_stochastic-streets-biases-and-limitations-activity-7431663640086327296-gahG?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, https://x.com/IPTC_upm/status/2025898571426357369?s=20, https://short.upm.es/wp5jn, https://www.linkedin.com/posts/iptc-upm_stochastic-streets-biases-and-limitations-activity-7431663640086327296-gahG?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+  </si>
+  <si>
     <t>Columna</t>
-  </si>
-  <si>
-    <t>T. Fu, D. Campo-Nazareno, J. Coronado-Blázquez, J. Conde, P. Reviriego, F. Lombardi</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2509.12914]</t>
-  </si>
-  <si>
-    <t>[https://www.linkedin.com/posts/iptc-upm_stochastic-streets-biases-and-limitations-activity-7431663640086327296-gahG?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0, https://x.com/IPTC_upm/status/2025898571426357369?s=20, https://short.upm.es/wp5jn, https://www.linkedin.com/posts/iptc-upm_stochastic-streets-biases-and-limitations-activity-7431663640086327296-gahG?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
   </si>
   <si>
     <t>Large Language Models (LLMs) are capable of solving complex math problems or answer difficult questions on almost any topic, but can they generate random street addresses for European cities?</t>
@@ -2349,10 +2575,10 @@
     <t>[https://arxiv.org/abs/2501.09775]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/93787</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.18610843, https://github.com/aMa2210/LLM_MCQ_LogProbs]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/93787</t>
   </si>
   <si>
     <t>[https://www.linkedin.com/posts/pedro-reviriego-b582094_ai-llm-machinelearning-share-7428493309662179328-7ulC?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0
@@ -2395,6 +2621,15 @@
   </si>
   <si>
     <t>J. Fu, J. Conde, G. Martínez, M. Grandury, C. Arriaga, J. Haro, S. Schroeder, F. Hintz, P. Reviriego, M. Brysbaert</t>
+  </si>
+  <si>
+    <t>[https://www.researchgate.net/publication/394454526]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/93777/</t>
+  </si>
+  <si>
+    <t>[https://osf.io/ghjd2/]</t>
   </si>
   <si>
     <t>This article presents AI-generated estimates for five characteristics of German words: concreteness, valence, arousal, age of acquisition (AoA), and word familiarity. The estimates were generated using GPT-4o-mini, which was selected due to its good performance in previous studies. Validation studies were conducted comparing the AI-generated estimates with both human ratings and previously generated AI data to ensure their usefulness for research applications. The main results are as follows. The GPT estimates of word concreteness, valence, and arousal show a strong correlation with human ratings but are not better than the best available AI-generated estimates based on semantic vectors. The GPT estimates of AoA are good approximations of human ratings and outperform other available alternatives (except for human ratings), especially after the model was fine-tuned based on 2,000 human ratings. Fine-tuned AI-generated estimates of word familiarity have better predictive value than word frequency for word recognition in lexical decision tasks and vocabulary tests. Estimates for concreteness, valence, arousal, and AoA are available for 167,000 words, which are likely to be known to more than 90% of participants in typical adult studies. Word familiarity estimates are presented for 928,000 word forms. All data and codes, including newly collected human familiarity ratings for 11,000 words, are publicly available at https://osf.io/ghjd2/. The data may be freely used for research purposes, but not for commercial purposes.</t>
@@ -2494,6 +2729,12 @@
     <t xml:space="preserve">[https://arxiv.org/abs/2604.22829] </t>
   </si>
   <si>
+    <t>[https://doi.org/10.5281/zenodo.19040441, https://github.com/aMa2210/VLM_gauge]</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, SMARTY, TUCAN6-CM, Google Cloud Research Credits]</t>
+  </si>
+  <si>
     <t>The digital transformation of industrial manufacturing increasingly relies on the ability of autonomous robots to interact with legacy infrastructure, particularly analog gauges. While Vision-Language Models (VLMs) have demonstrated potential in zero-shot instrument recognition, their deployment in measurement systems remains constrained by an inherent inability to accurately analyze high-frequency temporal events and needle vibrations. This paper evaluates state-of-the-art models, including GPT-5 and Gemini 3, against the strict requirements of metrology and uncertainty quantification. To facilitate this evaluation, we introduce a novel dataset comprising video sequences of various gauge types: circular, linear, and Vernier, under diverse motion speed profiles. Our findings indicate that current VLMs exhibit limited ability in interpreting needle trajectories and scale semantics, failing to provide the traceability and reliability needed for safety-critical monitoring. The results demonstrate that these models have not yet achieved the performance necessary to be classified as trustworthy synthetic instruments under existing IEEE and ISO standards.</t>
   </si>
   <si>
@@ -2656,6 +2897,12 @@
     <t>abG-DnoFyZgC</t>
   </si>
   <si>
+    <t>https://www.cienciacognitiva.org/?p=2641</t>
+  </si>
+  <si>
+    <t>Ciencia Cognitiva</t>
+  </si>
+  <si>
     <t>E. Sendín, J. Conde, P. Reviriego, J. Haro, P. Ferré, J.A. Hinojosa</t>
   </si>
   <si>
@@ -2676,7 +2923,16 @@
     <t>_xSYboBqXhAC</t>
   </si>
   <si>
+    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6258103</t>
+  </si>
+  <si>
+    <t>SSRN</t>
+  </si>
+  <si>
     <t>H. Melero, G. Martínez, N. Root, J. Conde, N. Melero, P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6258103]</t>
   </si>
   <si>
     <t>Preprint investigating whether large language models exhibit synesthetic associations similar to humans, exploring whether LLMs associate letters, numbers, and weekdays with specific colors in consistent, human-like patterns.</t>
@@ -2690,265 +2946,13 @@
 }</t>
   </si>
   <si>
-    <t>Final degree project on extending the functionality of the VPLS application for the ONOS controller, an open-source SDN platform developed at ETSIT-UPM.</t>
-  </si>
-  <si>
-    <t>Master’s thesis on the digital integration of administrative and academic processes at ETSIT-UPM, exploring solutions for the modernization of institutional procedures.</t>
-  </si>
-  <si>
-    <t>[https://oa.upm.es/62772/]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2408.14315]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/74848/</t>
-  </si>
-  <si>
-    <t>[https://www.mdpi.com/2079-9292/10/13/1523, https://oa.upm.es/71049/]</t>
-  </si>
-  <si>
-    <t>[https://www.mdpi.com/1424-8220/21/21/7095, https://oa.upm.es/74845/]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/74846/</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/82775/</t>
-  </si>
-  <si>
-    <t>Doctoral thesis on architectures and solutions for implementing digital twins based on open data using FIWARE. It covers everything from integrating heterogeneous data to collaboration between digital twins through Linked Open Data.</t>
-  </si>
-  <si>
-    <t>IEEE TechRxiv</t>
-  </si>
-  <si>
-    <t>[FUN4DATE]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, OpenAI Research Access Program]</t>
-  </si>
-  <si>
-    <t>[YODA]</t>
-  </si>
-  <si>
-    <t>[Arportwin]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/90614/</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2502.16721]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2502.16713]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/77072</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2310.14703]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/85330/</t>
-  </si>
-  <si>
-    <t>[CyberTutor, FUN4DATE, SMARTY]</t>
-  </si>
-  <si>
-    <t>[https://github.com/WordsGPT/LLM_Vocabulary_Evaluation]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/85140/</t>
-  </si>
-  <si>
-    <t>[https://osf.io/frc6a/
-]</t>
-  </si>
-  <si>
-    <t>[https://zenodo.org/doi/10.5281/zenodo.
-10797991          ]</t>
-  </si>
-  <si>
-    <t>[https://oa.upm.es/83196]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, Programa Propio UPM]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83197/</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83194</t>
-  </si>
-  <si>
-    <t>[https://www.upm.es/?id=CON03210&amp;prefmt=articulo&amp;fmt=detail]</t>
-  </si>
-  <si>
-    <t>sent to ACM TIST</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
-  </si>
-  <si>
-    <t>[Eunomia, YODA]</t>
-  </si>
-  <si>
-    <t>[SMARTY, TUCAN6-CM]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, TUCAN6-CM]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, TUCAN6-CM]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2505.10862]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/92641/</t>
-  </si>
-  <si>
-    <t>[tps://huggingface.co/datasets/
-migonsa/analog_clocks_combinations_for_finetuning, https://github.com/aMa2210/MLLMs_read_analog_clocks]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2502.16705]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/87994</t>
-  </si>
-  <si>
-    <t>Es open access diamond</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/91144</t>
-  </si>
-  <si>
-    <t>[https://osf.io/p6fuy/]</t>
-  </si>
-  <si>
-    <t>[https://www.cienciacognitiva.org/?p=2641]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/88428</t>
-  </si>
-  <si>
-    <t>[https://www.researchgate.net/publication/395768986, https://osf.io/p5ybm/files/37m6j]</t>
-  </si>
-  <si>
-    <t>OJO solo subida la versión submitted no la accepted a otros repos</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/91146/</t>
-  </si>
-  <si>
-    <t>[https://osf.io/p5ybm/overview]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/88338/</t>
-  </si>
-  <si>
-    <t>[ https://zenodo.org/doi/10.5281/zenodo.12571762]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2408.16012, https://www.researchgate.net/profile/Marc-Brysbaert/publication/385448704]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/85232/</t>
-  </si>
-  <si>
-    <t>[ https://osf.io/k5a4x/]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/95204/</t>
-  </si>
-  <si>
-    <t>[https://zenodo.org/doi/10.5281/zenodo.13362646]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program, Programa Propio UPM]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2507.00999]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/89095</t>
-  </si>
-  <si>
-    <t>[https://huggingface.co/datasets/la-leaderboard]</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2506.22439]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/90381</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2406.17789]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/92045/</t>
-  </si>
-  <si>
-    <t>[https://zenodo.org/records/11314109]</t>
-  </si>
-  <si>
-    <t>[https://github.com/RaquelFerrando/conversational_tokenizers]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sent </t>
-  </si>
-  <si>
-    <t>[https://github.com/dncampo/real-time-spatial-rag-for-smart-cities, https://github.com/javicond3/spatial_rag_vector_rag]</t>
-  </si>
-  <si>
-    <t>J. Conde, M. Grandury, T. Fu, C. Arriaga, G. Martínez, T. Clark, S. Trott, C. G. Green, P. Reviriego, M. Brysbaert</t>
-  </si>
-  <si>
-    <t>[https://github.com/WordsGPT/psycholinguistics_framework]</t>
-  </si>
-  <si>
-    <t>[SMARTY, Programa Propio UPM]</t>
-  </si>
-  <si>
-    <t>sent to BRM</t>
-  </si>
-  <si>
-    <t>[https://github.com/aMa2210/LLM_Addresses]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, TUCAN6-CM, OpenAI Research Access Program]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/93777/</t>
-  </si>
-  <si>
-    <t>[https://osf.io/ghjd2/]</t>
-  </si>
-  <si>
-    <t>[https://www.researchgate.net/publication/394454526]</t>
-  </si>
-  <si>
-    <t>https://www.cienciacognitiva.org/?p=2641</t>
-  </si>
-  <si>
-    <t>Ciencia Cognitiva</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.5281/zenodo.19040441, https://github.com/aMa2210/VLM_gauge]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, TUCAN6-CM, Google Cloud Research Credits]</t>
-  </si>
-  <si>
-    <t>SSRN</t>
-  </si>
-  <si>
-    <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6258103</t>
-  </si>
-  <si>
-    <t>[https://papers.ssrn.com/sol3/papers.cfm?abstract_id=6258103]</t>
+    <t>accepted to ACM TIST</t>
+  </si>
+  <si>
+    <t>Update the zenodo link in the paper, and update the arxiv with the new title When…</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.5281/zenodo.20112756, https://github.com/aMa2210/LLM_CounterLettersWithoutFT.git]</t>
   </si>
 </sst>
 </file>
@@ -3182,7 +3186,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3391,27 +3395,6 @@
     <xf numFmtId="4" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3443,17 +3426,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -3484,17 +3456,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -3513,27 +3475,7 @@
         <family val="2"/>
         <charset val="1"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0"/>
+      <alignment horizontal="general" vertical="bottom"/>
     </dxf>
     <dxf>
       <font>
@@ -3552,6 +3494,16 @@
       <fill>
         <patternFill>
           <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3838,27 +3790,28 @@
   <dimension ref="A1:AI73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="87" customWidth="1"/>
+    <col min="1" max="1" width="9" style="80" customWidth="1"/>
     <col min="2" max="2" width="5.1640625" style="29" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" style="29" customWidth="1"/>
     <col min="4" max="4" width="36.1640625" style="38" customWidth="1"/>
     <col min="5" max="5" width="22" style="38" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="38"/>
+    <col min="6" max="6" width="8.83203125" style="38" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="38" customWidth="1"/>
-    <col min="8" max="14" width="8.83203125" style="38"/>
+    <col min="8" max="14" width="8.83203125" style="38" customWidth="1"/>
     <col min="15" max="15" width="25.83203125" style="38" customWidth="1"/>
-    <col min="16" max="17" width="8.83203125" style="29"/>
-    <col min="18" max="18" width="8.83203125" style="38"/>
-    <col min="19" max="20" width="8.83203125" style="29"/>
-    <col min="21" max="21" width="8.83203125" style="40"/>
-    <col min="22" max="22" width="8.83203125" style="38"/>
+    <col min="16" max="17" width="8.83203125" style="29" customWidth="1"/>
+    <col min="18" max="18" width="8.83203125" style="38" customWidth="1"/>
+    <col min="19" max="20" width="8.83203125" style="29" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" style="40" customWidth="1"/>
+    <col min="22" max="22" width="8.83203125" style="38" customWidth="1"/>
     <col min="23" max="23" width="14" style="38" customWidth="1"/>
-    <col min="24" max="25" width="8.83203125" style="38"/>
+    <col min="24" max="25" width="8.83203125" style="38" customWidth="1"/>
     <col min="26" max="26" width="18.5" style="38" customWidth="1"/>
     <col min="27" max="27" width="63.33203125" style="38" customWidth="1"/>
-    <col min="28" max="34" width="8.83203125" style="38"/>
+    <col min="28" max="34" width="8.83203125" style="38" customWidth="1"/>
     <col min="35" max="35" width="134.5" style="38" customWidth="1"/>
-    <col min="36" max="16384" width="8.83203125" style="1"/>
+    <col min="36" max="36" width="8.83203125" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="2" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3932,10 +3885,10 @@
         <v>22</v>
       </c>
       <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>25</v>
@@ -3969,10 +3922,10 @@
       </c>
     </row>
     <row r="2" spans="1:35" s="13" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="81">
+      <c r="B2" s="74">
         <v>2018</v>
       </c>
       <c r="C2" s="7"/>
@@ -4044,33 +3997,33 @@
       <c r="AC2" s="10"/>
       <c r="AD2" s="10"/>
       <c r="AE2" s="10" t="s">
-        <v>695</v>
+        <v>46</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG2" s="10"/>
       <c r="AH2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI2" s="10"/>
     </row>
     <row r="3" spans="1:35" s="13" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="81">
+      <c r="B3" s="74">
         <v>2020</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>39</v>
@@ -4112,11 +4065,11 @@
       <c r="V3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="W3" s="82" t="s">
-        <v>697</v>
-      </c>
-      <c r="X3" s="82" t="s">
-        <v>50</v>
+      <c r="W3" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="75" t="s">
+        <v>51</v>
       </c>
       <c r="Y3" s="10" t="s">
         <v>41</v>
@@ -4131,62 +4084,62 @@
       <c r="AC3" s="10"/>
       <c r="AD3" s="10"/>
       <c r="AE3" s="10" t="s">
-        <v>696</v>
+        <v>53</v>
       </c>
       <c r="AF3" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AG3" s="10"/>
       <c r="AH3" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI3" s="10"/>
     </row>
     <row r="4" spans="1:35" s="13" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="80">
+        <v>55</v>
+      </c>
+      <c r="B4" s="73">
         <v>2021</v>
       </c>
       <c r="C4" s="14">
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="N4" s="17" t="s">
         <v>43</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P4" s="19">
         <v>6</v>
@@ -4205,11 +4158,11 @@
       <c r="V4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="W4" s="83" t="s">
-        <v>701</v>
-      </c>
-      <c r="X4" s="84" t="s">
-        <v>62</v>
+      <c r="W4" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="77" t="s">
+        <v>66</v>
       </c>
       <c r="Y4" s="17" t="s">
         <v>41</v>
@@ -4224,62 +4177,62 @@
       <c r="AC4" s="17"/>
       <c r="AD4" s="17"/>
       <c r="AE4" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AG4" s="17"/>
-      <c r="AH4" s="85" t="s">
-        <v>47</v>
+      <c r="AH4" s="78" t="s">
+        <v>48</v>
       </c>
       <c r="AI4" s="10"/>
     </row>
     <row r="5" spans="1:35" s="54" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="86">
+        <v>55</v>
+      </c>
+      <c r="B5" s="79">
         <v>2021</v>
       </c>
       <c r="C5" s="22">
         <v>4</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="84" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>71</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I5" s="49" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="50" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K5" s="47" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L5" s="47" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M5" s="49" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N5" s="49" t="s">
         <v>44</v>
       </c>
       <c r="O5" s="51" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P5" s="52">
         <v>6</v>
@@ -4291,7 +4244,7 @@
         <v>43</v>
       </c>
       <c r="S5" s="53">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" s="53"/>
       <c r="U5" s="71"/>
@@ -4299,10 +4252,10 @@
         <v>44</v>
       </c>
       <c r="W5" s="49" t="s">
-        <v>700</v>
+        <v>77</v>
       </c>
       <c r="X5" s="49" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Y5" s="49" t="s">
         <v>41</v>
@@ -4317,39 +4270,39 @@
       <c r="AC5" s="49"/>
       <c r="AD5" s="49"/>
       <c r="AE5" s="49" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AF5" s="49" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG5" s="49"/>
       <c r="AH5" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI5" s="64"/>
     </row>
     <row r="6" spans="1:35" s="13" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="74">
         <v>2021</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>41</v>
@@ -4366,7 +4319,7 @@
         <v>41</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="P6" s="10">
         <v>11</v>
@@ -4386,7 +4339,7 @@
         <v>44</v>
       </c>
       <c r="W6" s="10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="X6" s="10" t="s">
         <v>41</v>
@@ -4404,39 +4357,39 @@
       <c r="AC6" s="10"/>
       <c r="AD6" s="10"/>
       <c r="AE6" s="10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AG6" s="10"/>
       <c r="AH6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI6" s="10"/>
     </row>
     <row r="7" spans="1:35" s="13" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="74">
         <v>2021</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>41</v>
@@ -4453,7 +4406,7 @@
         <v>41</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="P7" s="10">
         <v>4</v>
@@ -4473,7 +4426,7 @@
         <v>44</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="X7" s="10" t="s">
         <v>41</v>
@@ -4482,7 +4435,7 @@
         <v>41</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>709</v>
+        <v>94</v>
       </c>
       <c r="AA7" s="10" t="s">
         <v>41</v>
@@ -4491,62 +4444,62 @@
       <c r="AC7" s="10"/>
       <c r="AD7" s="10"/>
       <c r="AE7" s="10" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AF7" s="10" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AG7" s="10"/>
       <c r="AH7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI7" s="10"/>
     </row>
     <row r="8" spans="1:35" s="54" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="86">
+        <v>55</v>
+      </c>
+      <c r="B8" s="79">
         <v>2022</v>
       </c>
       <c r="C8" s="30">
         <v>10</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I8" s="58" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="58" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L8" s="58" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N8" s="58" t="s">
         <v>43</v>
       </c>
       <c r="O8" s="58" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="P8" s="50">
         <v>7</v>
@@ -4568,84 +4521,84 @@
         <v>43</v>
       </c>
       <c r="W8" s="58" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="X8" s="57" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Y8" s="58" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Z8" s="58" t="s">
-        <v>709</v>
+        <v>94</v>
       </c>
       <c r="AA8" s="58" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AB8" s="58"/>
       <c r="AC8" s="58" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AD8" s="58" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AE8" s="58" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AF8" s="58" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG8" s="58"/>
       <c r="AH8" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI8" s="64"/>
     </row>
     <row r="9" spans="1:35" s="54" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="86">
+        <v>55</v>
+      </c>
+      <c r="B9" s="79">
         <v>2022</v>
       </c>
       <c r="C9" s="30">
         <v>10</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I9" s="58" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="58" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K9" s="58" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L9" s="58" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N9" s="58" t="s">
         <v>13</v>
       </c>
       <c r="O9" s="58" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="P9" s="50">
         <v>5</v>
@@ -4667,84 +4620,84 @@
         <v>43</v>
       </c>
       <c r="W9" s="58" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="X9" s="58" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Y9" s="58" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Z9" s="58" t="s">
         <v>41</v>
       </c>
       <c r="AA9" s="58" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AB9" s="58"/>
       <c r="AC9" s="58" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="AD9" s="58" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="AE9" s="58" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="AF9" s="58" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG9" s="58"/>
       <c r="AH9" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI9" s="64"/>
     </row>
     <row r="10" spans="1:35" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="87">
+        <v>55</v>
+      </c>
+      <c r="B10" s="80">
         <v>2022</v>
       </c>
       <c r="C10" s="33">
         <v>7</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I10" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N10" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="P10" s="23">
         <v>5</v>
@@ -4764,10 +4717,10 @@
         <v>43</v>
       </c>
       <c r="W10" s="24" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="X10" s="24" t="s">
-        <v>702</v>
+        <v>139</v>
       </c>
       <c r="Y10" s="24" t="s">
         <v>41</v>
@@ -4780,60 +4733,60 @@
       <c r="AC10" s="24"/>
       <c r="AD10" s="24"/>
       <c r="AE10" s="24" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF10" s="24" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG10" s="24"/>
       <c r="AH10" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI10" s="38"/>
     </row>
     <row r="11" spans="1:35" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="87">
+        <v>55</v>
+      </c>
+      <c r="B11" s="80">
         <v>2022</v>
       </c>
       <c r="C11" s="35">
         <v>4</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E11" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="81" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="88" t="s">
-        <v>137</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>130</v>
-      </c>
       <c r="M11" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N11" s="24"/>
       <c r="O11" s="23" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="P11" s="23">
         <v>5</v>
@@ -4853,58 +4806,58 @@
         <v>43</v>
       </c>
       <c r="W11" s="24" t="s">
-        <v>698</v>
-      </c>
-      <c r="X11" s="88" t="s">
-        <v>699</v>
+        <v>148</v>
+      </c>
+      <c r="X11" s="81" t="s">
+        <v>149</v>
       </c>
       <c r="Y11" s="24" t="s">
         <v>41</v>
       </c>
       <c r="Z11" s="24" t="s">
-        <v>708</v>
+        <v>150</v>
       </c>
       <c r="AA11" s="24"/>
       <c r="AB11" s="24"/>
       <c r="AC11" s="24"/>
       <c r="AD11" s="24"/>
       <c r="AE11" s="24" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="AF11" s="24" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="AG11" s="24"/>
       <c r="AH11" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI11" s="38"/>
     </row>
     <row r="12" spans="1:35" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="87">
+      <c r="A12" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="80">
         <v>2023</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="36" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J12" s="38" t="s">
         <v>41</v>
@@ -4918,7 +4871,7 @@
         <v>41</v>
       </c>
       <c r="O12" s="36" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="P12" s="38">
         <v>5</v>
@@ -4954,39 +4907,39 @@
       <c r="AC12" s="38"/>
       <c r="AD12" s="38"/>
       <c r="AE12" s="38" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF12" s="38" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AG12" s="38"/>
       <c r="AH12" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI12" s="38"/>
     </row>
     <row r="13" spans="1:35" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="89">
+      <c r="B13" s="82">
         <v>2023</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="36" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I13" s="39" t="s">
         <v>41</v>
@@ -5003,7 +4956,7 @@
         <v>41</v>
       </c>
       <c r="O13" s="36" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P13" s="38">
         <v>5</v>
@@ -5015,7 +4968,7 @@
         <v>43</v>
       </c>
       <c r="S13" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" s="29"/>
       <c r="U13" s="40"/>
@@ -5025,8 +4978,8 @@
       <c r="W13" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="X13" s="88" t="s">
-        <v>703</v>
+      <c r="X13" s="81" t="s">
+        <v>168</v>
       </c>
       <c r="Y13" s="38" t="s">
         <v>41</v>
@@ -5041,39 +4994,39 @@
       <c r="AC13" s="38"/>
       <c r="AD13" s="38"/>
       <c r="AE13" s="38" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AF13" s="38" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="AG13" s="38"/>
       <c r="AH13" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI13" s="38"/>
     </row>
     <row r="14" spans="1:35" s="54" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="90">
+      <c r="B14" s="83">
         <v>2023</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="62" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="G14" s="62" t="s">
         <v>39</v>
       </c>
       <c r="H14" s="64" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I14" s="65" t="s">
         <v>41</v>
@@ -5113,7 +5066,7 @@
         <v>41</v>
       </c>
       <c r="X14" s="64" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="Y14" s="64" t="s">
         <v>41</v>
@@ -5128,39 +5081,39 @@
       <c r="AC14" s="64"/>
       <c r="AD14" s="64"/>
       <c r="AE14" s="64" t="s">
-        <v>704</v>
+        <v>176</v>
       </c>
       <c r="AF14" s="64" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="AG14" s="64"/>
       <c r="AH14" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI14" s="64"/>
     </row>
     <row r="15" spans="1:35" s="54" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="90">
+      <c r="B15" s="83">
         <v>2023</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="62" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H15" s="64" t="s">
-        <v>705</v>
+        <v>182</v>
       </c>
       <c r="I15" s="65" t="s">
         <v>41</v>
@@ -5177,7 +5130,7 @@
         <v>41</v>
       </c>
       <c r="O15" s="62" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="P15" s="64">
         <v>4</v>
@@ -5197,7 +5150,7 @@
         <v>44</v>
       </c>
       <c r="W15" s="64" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="X15" s="64" t="s">
         <v>41</v>
@@ -5215,62 +5168,62 @@
       <c r="AC15" s="64"/>
       <c r="AD15" s="64"/>
       <c r="AE15" s="64" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="AF15" s="64" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AG15" s="64"/>
       <c r="AH15" s="64" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="AI15" s="64"/>
     </row>
     <row r="16" spans="1:35" s="54" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="86">
+        <v>55</v>
+      </c>
+      <c r="B16" s="79">
         <v>2024</v>
       </c>
       <c r="C16" s="42">
         <v>9</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I16" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="L16" s="50" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="M16" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N16" s="50" t="s">
         <v>43</v>
       </c>
       <c r="O16" s="50" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="P16" s="50">
         <v>6</v>
@@ -5294,84 +5247,84 @@
         <v>43</v>
       </c>
       <c r="W16" s="50" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="X16" s="57" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Y16" s="50" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="Z16" s="50" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA16" s="50" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="AB16" s="64"/>
       <c r="AC16" s="50" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="AD16" s="50" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="AE16" s="64" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AF16" s="64" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="AG16" s="64"/>
       <c r="AH16" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI16" s="64"/>
     </row>
     <row r="17" spans="1:35" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="86">
+        <v>55</v>
+      </c>
+      <c r="B17" s="79">
         <v>2024</v>
       </c>
       <c r="C17" s="44">
         <v>8.5</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="G17" s="50" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="I17" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="L17" s="50" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="M17" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N17" s="50" t="s">
         <v>13</v>
       </c>
       <c r="O17" s="50" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="P17" s="50">
         <v>4</v>
@@ -5380,13 +5333,13 @@
         <v>2</v>
       </c>
       <c r="R17" s="50" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="S17" s="68">
         <v>68</v>
       </c>
       <c r="T17" s="70" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="U17" s="68">
         <v>15</v>
@@ -5395,82 +5348,82 @@
         <v>44</v>
       </c>
       <c r="W17" s="50" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="X17" s="57" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="Y17" s="50" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="Z17" s="50" t="s">
-        <v>707</v>
+        <v>216</v>
       </c>
       <c r="AA17" s="50" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="AB17" s="64"/>
       <c r="AC17" s="64"/>
       <c r="AD17" s="50" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="AE17" s="64" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AF17" s="64" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AG17" s="64"/>
       <c r="AH17" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI17" s="64"/>
     </row>
     <row r="18" spans="1:35" s="54" customFormat="1" ht="387.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="86">
+        <v>55</v>
+      </c>
+      <c r="B18" s="79">
         <v>2024</v>
       </c>
       <c r="C18" s="42">
         <v>8</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I18" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="L18" s="50" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M18" s="50" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N18" s="50" t="s">
         <v>13</v>
       </c>
       <c r="O18" s="50" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="P18" s="50">
         <v>6</v>
@@ -5494,84 +5447,84 @@
         <v>44</v>
       </c>
       <c r="W18" s="50" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="X18" s="57" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="Y18" s="50" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="Z18" s="50" t="s">
-        <v>706</v>
+        <v>229</v>
       </c>
       <c r="AA18" s="50" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AB18" s="64"/>
       <c r="AC18" s="50" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AD18" s="50" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="AE18" s="64" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AF18" s="64" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="AG18" s="64"/>
       <c r="AH18" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI18" s="64"/>
     </row>
     <row r="19" spans="1:35" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="86">
+        <v>55</v>
+      </c>
+      <c r="B19" s="79">
         <v>2024</v>
       </c>
       <c r="C19" s="46">
         <v>8</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="G19" s="56" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I19" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="L19" s="50" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="M19" s="50" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N19" s="50" t="s">
         <v>43</v>
       </c>
       <c r="O19" s="50" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="P19" s="50">
         <v>5</v>
@@ -5595,82 +5548,82 @@
         <v>44</v>
       </c>
       <c r="W19" s="50" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="X19" s="57" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="Y19" s="50" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="Z19" s="50" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA19" s="50" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="AB19" s="64"/>
       <c r="AC19" s="64"/>
       <c r="AD19" s="50" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="AE19" s="64" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="AF19" s="64" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="AG19" s="64"/>
       <c r="AH19" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI19" s="64"/>
     </row>
     <row r="20" spans="1:35" s="2" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="87">
+        <v>55</v>
+      </c>
+      <c r="B20" s="80">
         <v>2024</v>
       </c>
       <c r="C20" s="46">
         <v>6</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>41</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N20" s="26" t="s">
         <v>43</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="P20" s="23">
         <v>6</v>
@@ -5682,88 +5635,88 @@
         <v>44</v>
       </c>
       <c r="S20" s="45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T20" s="45" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="U20" s="40"/>
       <c r="V20" s="38" t="s">
         <v>44</v>
       </c>
       <c r="W20" s="38" t="s">
-        <v>711</v>
-      </c>
-      <c r="X20" s="88" t="s">
-        <v>710</v>
+        <v>257</v>
+      </c>
+      <c r="X20" s="81" t="s">
+        <v>258</v>
       </c>
       <c r="Y20" s="38"/>
       <c r="Z20" s="38" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA20" s="38"/>
       <c r="AB20" s="38"/>
       <c r="AC20" s="38"/>
       <c r="AD20" s="26" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="AE20" s="38" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="AF20" s="38" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="AG20" s="38"/>
       <c r="AH20" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI20" s="38"/>
     </row>
     <row r="21" spans="1:35" s="2" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="87">
+        <v>55</v>
+      </c>
+      <c r="B21" s="80">
         <v>2024</v>
       </c>
       <c r="C21" s="35">
         <v>4</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I21" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N21" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="P21" s="27">
         <v>6</v>
@@ -5775,7 +5728,7 @@
         <v>44</v>
       </c>
       <c r="S21" s="28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T21" s="28"/>
       <c r="U21" s="34"/>
@@ -5783,258 +5736,258 @@
         <v>43</v>
       </c>
       <c r="W21" s="24" t="s">
-        <v>712</v>
-      </c>
-      <c r="X21" s="88" t="s">
-        <v>713</v>
+        <v>266</v>
+      </c>
+      <c r="X21" s="81" t="s">
+        <v>267</v>
       </c>
       <c r="Y21" s="24"/>
       <c r="Z21" s="24" t="s">
-        <v>706</v>
+        <v>229</v>
       </c>
       <c r="AA21" s="24"/>
       <c r="AB21" s="24"/>
       <c r="AC21" s="24"/>
       <c r="AD21" s="24"/>
       <c r="AE21" s="24" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="AF21" s="24" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="AG21" s="24"/>
       <c r="AH21" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI21" s="38"/>
     </row>
-    <row r="22" spans="1:35" s="72" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="92">
+    <row r="22" spans="1:35" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="80">
         <v>2024</v>
       </c>
       <c r="C22" s="35">
         <v>3</v>
       </c>
-      <c r="D22" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>252</v>
-      </c>
-      <c r="F22" s="74" t="s">
-        <v>253</v>
-      </c>
-      <c r="G22" s="75" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="74" t="s">
-        <v>255</v>
-      </c>
-      <c r="I22" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" s="73" t="s">
-        <v>256</v>
-      </c>
-      <c r="L22" s="73" t="s">
-        <v>257</v>
-      </c>
-      <c r="M22" s="74" t="s">
-        <v>52</v>
-      </c>
-      <c r="N22" s="74" t="s">
+      <c r="D22" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="O22" s="73" t="s">
-        <v>258</v>
-      </c>
-      <c r="P22" s="73">
+      <c r="O22" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="P22" s="23">
         <v>7</v>
       </c>
-      <c r="Q22" s="73">
+      <c r="Q22" s="23">
         <v>2</v>
       </c>
-      <c r="R22" s="74" t="s">
+      <c r="R22" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="S22" s="77">
+      <c r="S22" s="28">
         <v>8</v>
       </c>
-      <c r="T22" s="77"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="74" t="s">
+      <c r="T22" s="28"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="W22" s="74" t="s">
-        <v>714</v>
-      </c>
-      <c r="X22" s="74" t="s">
-        <v>715</v>
-      </c>
-      <c r="Y22" s="74" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z22" s="74" t="s">
-        <v>716</v>
-      </c>
-      <c r="AA22" s="74"/>
-      <c r="AB22" s="74"/>
-      <c r="AC22" s="74"/>
-      <c r="AD22" s="74"/>
-      <c r="AE22" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="AF22" s="74" t="s">
-        <v>260</v>
-      </c>
-      <c r="AG22" s="74"/>
-      <c r="AH22" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI22" s="91"/>
+      <c r="W22" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="Y22" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z22" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="24"/>
+      <c r="AE22" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="AF22" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="AG22" s="24"/>
+      <c r="AH22" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI22" s="38"/>
     </row>
-    <row r="23" spans="1:35" s="72" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="91" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="92">
+    <row r="23" spans="1:35" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="80">
         <v>2024</v>
       </c>
       <c r="C23" s="22">
         <v>0</v>
       </c>
-      <c r="D23" s="73" t="s">
-        <v>261</v>
-      </c>
-      <c r="E23" s="73" t="s">
-        <v>262</v>
-      </c>
-      <c r="F23" s="94" t="s">
-        <v>263</v>
-      </c>
-      <c r="G23" s="75" t="s">
-        <v>264</v>
-      </c>
-      <c r="H23" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="K23" s="73" t="s">
-        <v>266</v>
-      </c>
-      <c r="L23" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="M23" s="74" t="s">
-        <v>52</v>
-      </c>
-      <c r="N23" s="74" t="s">
+      <c r="D23" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="81" t="s">
+        <v>286</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="O23" s="73" t="s">
-        <v>268</v>
-      </c>
-      <c r="P23" s="73">
+      <c r="O23" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="P23" s="23">
         <v>4</v>
       </c>
-      <c r="Q23" s="73">
+      <c r="Q23" s="23">
         <v>2</v>
       </c>
-      <c r="R23" s="74" t="s">
+      <c r="R23" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="77">
+      <c r="S23" s="28">
         <v>21</v>
       </c>
-      <c r="T23" s="77"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="74" t="s">
+      <c r="T23" s="28"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="W23" s="74" t="s">
-        <v>269</v>
-      </c>
-      <c r="X23" s="94" t="s">
-        <v>718</v>
-      </c>
-      <c r="Y23" s="74" t="s">
-        <v>719</v>
-      </c>
-      <c r="Z23" s="74" t="s">
-        <v>706</v>
-      </c>
-      <c r="AA23" s="74"/>
-      <c r="AB23" s="74"/>
-      <c r="AC23" s="74"/>
-      <c r="AD23" s="74"/>
-      <c r="AE23" s="74" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF23" s="74" t="s">
-        <v>271</v>
-      </c>
-      <c r="AG23" s="74"/>
-      <c r="AH23" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI23" s="91"/>
+      <c r="W23" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="X23" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="Y23" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z23" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="24"/>
+      <c r="AE23" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="AF23" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="AG23" s="24"/>
+      <c r="AH23" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI23" s="38"/>
     </row>
     <row r="24" spans="1:35" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="87">
+        <v>55</v>
+      </c>
+      <c r="B24" s="80">
         <v>2024</v>
       </c>
       <c r="C24" s="35">
         <v>0</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F24" s="88" t="s">
-        <v>274</v>
+        <v>298</v>
+      </c>
+      <c r="F24" s="81" t="s">
+        <v>299</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="I24" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="M24" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N24" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O24" s="23" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="P24" s="23">
         <v>8</v>
@@ -6054,58 +6007,58 @@
         <v>44</v>
       </c>
       <c r="W24" s="24" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="X24" s="24" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="Y24" s="24" t="s">
-        <v>720</v>
+        <v>307</v>
       </c>
       <c r="Z24" s="24" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA24" s="24"/>
       <c r="AB24" s="24"/>
       <c r="AC24" s="24"/>
       <c r="AD24" s="24"/>
       <c r="AE24" s="24" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="AF24" s="24" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="AG24" s="24"/>
       <c r="AH24" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI24" s="38"/>
     </row>
     <row r="25" spans="1:35" s="54" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B25" s="86">
+      <c r="A25" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="79">
         <v>2024</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="62" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="F25" s="79" t="s">
-        <v>286</v>
+        <v>311</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>312</v>
       </c>
       <c r="G25" s="62" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="H25" s="64" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="I25" s="65" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="J25" s="64" t="s">
         <v>41</v>
@@ -6119,7 +6072,7 @@
         <v>41</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="P25" s="64">
         <v>5</v>
@@ -6139,10 +6092,10 @@
         <v>44</v>
       </c>
       <c r="W25" s="64" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="X25" s="64" t="s">
-        <v>721</v>
+        <v>318</v>
       </c>
       <c r="Y25" s="64" t="s">
         <v>41</v>
@@ -6157,45 +6110,45 @@
       <c r="AC25" s="64"/>
       <c r="AD25" s="64"/>
       <c r="AE25" s="64" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="AF25" s="64" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="AG25" s="64"/>
       <c r="AH25" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI25" s="64"/>
     </row>
     <row r="26" spans="1:35" s="54" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="86">
+      <c r="A26" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="79">
         <v>2024</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="62" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>295</v>
-      </c>
-      <c r="F26" s="79" t="s">
-        <v>296</v>
+        <v>322</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>323</v>
       </c>
       <c r="G26" s="62" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="H26" s="64" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="I26" s="65" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="J26" s="64" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="K26" s="64"/>
       <c r="L26" s="64"/>
@@ -6206,7 +6159,7 @@
         <v>41</v>
       </c>
       <c r="O26" s="62" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="P26" s="64">
         <v>4</v>
@@ -6226,16 +6179,16 @@
         <v>44</v>
       </c>
       <c r="W26" s="64" t="s">
-        <v>299</v>
-      </c>
-      <c r="X26" s="84" t="s">
-        <v>723</v>
+        <v>326</v>
+      </c>
+      <c r="X26" s="77" t="s">
+        <v>327</v>
       </c>
       <c r="Y26" s="64" t="s">
         <v>41</v>
       </c>
       <c r="Z26" s="64" t="s">
-        <v>722</v>
+        <v>328</v>
       </c>
       <c r="AA26" s="64" t="s">
         <v>41</v>
@@ -6244,45 +6197,45 @@
       <c r="AC26" s="64"/>
       <c r="AD26" s="64"/>
       <c r="AE26" s="64" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="AF26" s="64" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="AG26" s="64"/>
       <c r="AH26" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI26" s="64"/>
     </row>
     <row r="27" spans="1:35" s="54" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="86">
+      <c r="A27" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="79">
         <v>2024</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="62" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>303</v>
-      </c>
-      <c r="F27" s="79" t="s">
-        <v>304</v>
+        <v>332</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>333</v>
       </c>
       <c r="G27" s="62" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="H27" s="64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I27" s="65" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="J27" s="64" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="K27" s="64"/>
       <c r="L27" s="64"/>
@@ -6293,7 +6246,7 @@
         <v>41</v>
       </c>
       <c r="O27" s="62" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="P27" s="64">
         <v>4</v>
@@ -6315,8 +6268,8 @@
       <c r="W27" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="X27" s="84" t="s">
-        <v>724</v>
+      <c r="X27" s="77" t="s">
+        <v>337</v>
       </c>
       <c r="Y27" s="64" t="s">
         <v>41</v>
@@ -6331,42 +6284,42 @@
       <c r="AC27" s="64"/>
       <c r="AD27" s="64"/>
       <c r="AE27" s="64" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="AF27" s="64" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="AG27" s="64"/>
       <c r="AH27" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI27" s="64"/>
     </row>
     <row r="28" spans="1:35" s="54" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="86">
+      <c r="A28" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="79">
         <v>2024</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="62" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="E28" s="62" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="F28" s="63" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="G28" s="62" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="H28" s="64" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="I28" s="65" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="J28" s="64" t="s">
         <v>41</v>
@@ -6380,7 +6333,7 @@
         <v>41</v>
       </c>
       <c r="O28" s="62" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="P28" s="64">
         <v>5</v>
@@ -6400,7 +6353,7 @@
         <v>44</v>
       </c>
       <c r="W28" s="64" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="X28" s="64" t="s">
         <v>41</v>
@@ -6412,45 +6365,45 @@
         <v>41</v>
       </c>
       <c r="AA28" s="64" t="s">
-        <v>725</v>
+        <v>348</v>
       </c>
       <c r="AB28" s="64"/>
       <c r="AC28" s="64"/>
       <c r="AD28" s="64"/>
       <c r="AE28" s="64" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="AF28" s="64" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="AG28" s="64"/>
       <c r="AH28" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI28" s="64"/>
     </row>
     <row r="29" spans="1:35" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="86" t="s">
-        <v>320</v>
-      </c>
-      <c r="B29" s="90">
+      <c r="A29" s="79" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" s="83">
         <v>2024</v>
       </c>
       <c r="C29" s="29"/>
       <c r="D29" s="62" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="F29" s="63" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="G29" s="65" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H29" s="64" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I29" s="64" t="s">
         <v>41</v>
@@ -6467,7 +6420,7 @@
         <v>41</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="P29" s="64">
         <v>6</v>
@@ -6505,39 +6458,39 @@
       <c r="AC29" s="64"/>
       <c r="AD29" s="64"/>
       <c r="AE29" s="64" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="AF29" s="64" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="AG29" s="64"/>
       <c r="AH29" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI29" s="64"/>
     </row>
     <row r="30" spans="1:35" s="54" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="86" t="s">
-        <v>320</v>
-      </c>
-      <c r="B30" s="90">
+      <c r="A30" s="79" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" s="83">
         <v>2024</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="62" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="E30" s="62" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="G30" s="65" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="H30" s="64" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="I30" s="64" t="s">
         <v>41</v>
@@ -6554,7 +6507,7 @@
         <v>41</v>
       </c>
       <c r="O30" s="64" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="P30" s="64">
         <v>4</v>
@@ -6574,7 +6527,7 @@
         <v>44</v>
       </c>
       <c r="W30" s="64" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="X30" s="64" t="s">
         <v>41</v>
@@ -6592,36 +6545,36 @@
       <c r="AC30" s="64"/>
       <c r="AD30" s="64"/>
       <c r="AE30" s="64" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="AF30" s="64" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="AG30" s="64"/>
       <c r="AH30" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI30" s="64"/>
     </row>
     <row r="31" spans="1:35" s="54" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="90">
+      <c r="B31" s="83">
         <v>2024</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="62" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="E31" s="62" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="F31" s="63" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="G31" s="62" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H31" s="64" t="s">
         <v>40</v>
@@ -6641,7 +6594,7 @@
         <v>41</v>
       </c>
       <c r="O31" s="62" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="P31" s="64">
         <v>6</v>
@@ -6653,7 +6606,7 @@
         <v>43</v>
       </c>
       <c r="S31" s="66">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T31" s="66"/>
       <c r="U31" s="67"/>
@@ -6664,7 +6617,7 @@
         <v>41</v>
       </c>
       <c r="X31" s="64" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="Y31" s="64" t="s">
         <v>41</v>
@@ -6679,36 +6632,36 @@
       <c r="AC31" s="64"/>
       <c r="AD31" s="64"/>
       <c r="AE31" s="64" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="AF31" s="64" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="AG31" s="64"/>
       <c r="AH31" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI31" s="64"/>
     </row>
     <row r="32" spans="1:35" s="55" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="86" t="s">
-        <v>342</v>
+      <c r="A32" s="79" t="s">
+        <v>373</v>
       </c>
       <c r="B32" s="66">
         <v>2024</v>
       </c>
       <c r="C32" s="29"/>
       <c r="D32" s="64" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="F32" s="64" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="G32" s="64" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="H32" s="64" t="s">
         <v>40</v>
@@ -6720,7 +6673,7 @@
       <c r="M32" s="64"/>
       <c r="N32" s="64"/>
       <c r="O32" s="64" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="P32" s="66">
         <v>4</v>
@@ -6741,7 +6694,7 @@
         <v>41</v>
       </c>
       <c r="X32" s="64" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="Y32" s="64" t="s">
         <v>41</v>
@@ -6756,41 +6709,41 @@
       <c r="AC32" s="64"/>
       <c r="AD32" s="64"/>
       <c r="AE32" s="64" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="AF32" s="64" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="AG32" s="64"/>
       <c r="AH32" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI32" s="64"/>
     </row>
     <row r="33" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="87" t="s">
-        <v>350</v>
+      <c r="A33" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B33" s="29">
         <v>2024</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O33" s="38" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="P33" s="29">
         <v>5</v>
@@ -6808,51 +6761,54 @@
         <v>44</v>
       </c>
       <c r="W33" s="38" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="X33" s="38" t="s">
         <v>41</v>
       </c>
       <c r="Y33" s="38" t="s">
-        <v>41</v>
+        <v>783</v>
       </c>
       <c r="Z33" s="38" t="s">
-        <v>727</v>
+        <v>388</v>
       </c>
       <c r="AE33" s="38" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="AF33" s="38" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="AH33" s="38" t="s">
-        <v>726</v>
+        <v>781</v>
+      </c>
+      <c r="AI33" s="38" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="34" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="87" t="s">
-        <v>350</v>
+      <c r="A34" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B34" s="29">
         <v>2024</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O34" s="38" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="P34" s="29">
         <v>5</v>
@@ -6870,7 +6826,7 @@
         <v>44</v>
       </c>
       <c r="W34" s="38" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="X34" s="38" t="s">
         <v>41</v>
@@ -6879,60 +6835,60 @@
         <v>41</v>
       </c>
       <c r="Z34" s="38" t="s">
-        <v>728</v>
+        <v>397</v>
       </c>
       <c r="AE34" s="38" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="AF34" s="38" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:35" s="55" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="86">
+        <v>55</v>
+      </c>
+      <c r="B35" s="79">
         <v>2025</v>
       </c>
       <c r="C35" s="42">
         <v>10</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="F35" s="57" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="L35" s="50" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="M35" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N35" s="50" t="s">
         <v>13</v>
       </c>
       <c r="O35" s="50" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="P35" s="58">
         <v>5</v>
@@ -6947,87 +6903,87 @@
         <v>41</v>
       </c>
       <c r="T35" s="70" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="U35" s="67"/>
       <c r="V35" s="50" t="s">
         <v>44</v>
       </c>
       <c r="W35" s="50" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="X35" s="57" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="Y35" s="50" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="Z35" s="50" t="s">
-        <v>707</v>
+        <v>216</v>
       </c>
       <c r="AA35" s="50" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="AB35" s="64"/>
       <c r="AC35" s="64"/>
       <c r="AD35" s="64"/>
       <c r="AE35" s="64" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="AF35" s="64" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="AG35" s="64"/>
       <c r="AH35" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI35" s="64"/>
     </row>
     <row r="36" spans="1:35" s="55" customFormat="1" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="86">
+        <v>55</v>
+      </c>
+      <c r="B36" s="79">
         <v>2025</v>
       </c>
-      <c r="C36" s="95">
+      <c r="C36" s="84">
         <v>9</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="F36" s="57" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="G36" s="50" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I36" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J36" s="50" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="L36" s="50" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="M36" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N36" s="50" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="O36" s="50" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="P36" s="47">
         <v>6</v>
@@ -7051,82 +7007,82 @@
         <v>43</v>
       </c>
       <c r="W36" s="50" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="X36" s="57" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="Y36" s="50" t="s">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="Z36" s="50" t="s">
-        <v>729</v>
+        <v>423</v>
       </c>
       <c r="AA36" s="50" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="AB36" s="64"/>
       <c r="AC36" s="64"/>
       <c r="AD36" s="50" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="AE36" s="64" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="AF36" s="64" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="AG36" s="64"/>
       <c r="AH36" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI36" s="64"/>
     </row>
     <row r="37" spans="1:35" s="55" customFormat="1" ht="255" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="86">
+        <v>55</v>
+      </c>
+      <c r="B37" s="79">
         <v>2025</v>
       </c>
-      <c r="C37" s="96">
+      <c r="C37" s="85">
         <v>8.5</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="F37" s="57" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I37" s="49" t="s">
         <v>41</v>
       </c>
       <c r="J37" s="47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K37" s="47" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="L37" s="47" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="M37" s="49" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N37" s="49" t="s">
         <v>13</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="P37" s="50">
         <v>4</v>
@@ -7137,93 +7093,93 @@
       <c r="R37" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="S37" s="97">
+      <c r="S37" s="86">
         <v>14</v>
       </c>
       <c r="T37" s="53"/>
       <c r="U37" s="71" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="V37" s="49" t="s">
         <v>44</v>
       </c>
       <c r="W37" s="49" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="X37" s="49" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="Y37" s="49" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="Z37" s="49" t="s">
-        <v>730</v>
+        <v>438</v>
       </c>
       <c r="AA37" s="49" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="AB37" s="49"/>
       <c r="AC37" s="49"/>
       <c r="AD37" s="49" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="AE37" s="49" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="AF37" s="49" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="AG37" s="49"/>
       <c r="AH37" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI37" s="64"/>
     </row>
     <row r="38" spans="1:35" s="55" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="86">
+        <v>55</v>
+      </c>
+      <c r="B38" s="79">
         <v>2025</v>
       </c>
       <c r="C38" s="43">
         <v>8</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="E38" s="56" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="F38" s="57" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="G38" s="50" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I38" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J38" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="L38" s="50" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="M38" s="50" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N38" s="50" t="s">
         <v>43</v>
       </c>
       <c r="O38" s="50" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="P38" s="50">
         <v>7</v>
@@ -7247,82 +7203,82 @@
         <v>43</v>
       </c>
       <c r="W38" s="50" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="X38" s="57" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="Y38" s="50" t="s">
         <v>41</v>
       </c>
       <c r="Z38" s="50" t="s">
-        <v>731</v>
+        <v>450</v>
       </c>
       <c r="AA38" s="50" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="AB38" s="64"/>
       <c r="AC38" s="64"/>
       <c r="AD38" s="50" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="AE38" s="64" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="AF38" s="64" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="AG38" s="64"/>
       <c r="AH38" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI38" s="64"/>
     </row>
     <row r="39" spans="1:35" s="55" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="86">
+        <v>55</v>
+      </c>
+      <c r="B39" s="79">
         <v>2025</v>
       </c>
-      <c r="C39" s="98">
+      <c r="C39" s="87">
         <v>7</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="F39" s="57" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="I39" s="50" t="s">
         <v>41</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="L39" s="50" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="M39" s="50" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N39" s="50" t="s">
         <v>43</v>
       </c>
       <c r="O39" s="50" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="P39" s="52">
         <v>6</v>
@@ -7344,82 +7300,82 @@
         <v>44</v>
       </c>
       <c r="W39" s="50" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="X39" s="57" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="Y39" s="50" t="s">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="Z39" s="50" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA39" s="50" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="AB39" s="64"/>
       <c r="AC39" s="64"/>
       <c r="AD39" s="50" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="AE39" s="64" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="AF39" s="64" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="AG39" s="64"/>
       <c r="AH39" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI39" s="64"/>
     </row>
     <row r="40" spans="1:35" s="55" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="86">
+        <v>55</v>
+      </c>
+      <c r="B40" s="79">
         <v>2025</v>
       </c>
-      <c r="C40" s="98">
+      <c r="C40" s="87">
         <v>7</v>
       </c>
       <c r="D40" s="47" t="s">
+        <v>469</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>470</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>471</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="K40" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="L40" s="47" t="s">
         <v>432</v>
       </c>
-      <c r="E40" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="F40" s="84" t="s">
-        <v>434</v>
-      </c>
-      <c r="G40" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="I40" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="K40" s="47" t="s">
-        <v>396</v>
-      </c>
-      <c r="L40" s="47" t="s">
-        <v>397</v>
-      </c>
       <c r="M40" s="49" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N40" s="49" t="s">
         <v>43</v>
       </c>
       <c r="O40" s="47" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="P40" s="52">
         <v>5</v>
@@ -7439,82 +7395,82 @@
         <v>44</v>
       </c>
       <c r="W40" s="49" t="s">
-        <v>732</v>
-      </c>
-      <c r="X40" s="84" t="s">
-        <v>733</v>
+        <v>473</v>
+      </c>
+      <c r="X40" s="77" t="s">
+        <v>474</v>
       </c>
       <c r="Y40" s="49" t="s">
-        <v>734</v>
+        <v>475</v>
       </c>
       <c r="Z40" s="49" t="s">
         <v>41</v>
       </c>
       <c r="AA40" s="49" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="AB40" s="49"/>
       <c r="AC40" s="49"/>
       <c r="AD40" s="49" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="AE40" s="49" t="s">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="AF40" s="49" t="s">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="AG40" s="49"/>
       <c r="AH40" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI40" s="64"/>
     </row>
     <row r="41" spans="1:35" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="87">
+        <v>55</v>
+      </c>
+      <c r="B41" s="80">
         <v>2025</v>
       </c>
       <c r="C41" s="33">
         <v>6</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>439</v>
+        <v>479</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="F41" s="88" t="s">
-        <v>441</v>
+        <v>480</v>
+      </c>
+      <c r="F41" s="81" t="s">
+        <v>481</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I41" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="M41" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N41" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O41" s="23" t="s">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="P41" s="26">
         <v>6</v>
@@ -7534,77 +7490,77 @@
         <v>43</v>
       </c>
       <c r="W41" s="24" t="s">
-        <v>735</v>
-      </c>
-      <c r="X41" s="88" t="s">
-        <v>736</v>
+        <v>483</v>
+      </c>
+      <c r="X41" s="81" t="s">
+        <v>484</v>
       </c>
       <c r="Y41" s="24"/>
       <c r="Z41" s="24" t="s">
-        <v>727</v>
+        <v>388</v>
       </c>
       <c r="AA41" s="24"/>
       <c r="AB41" s="24"/>
       <c r="AC41" s="24"/>
       <c r="AD41" s="24" t="s">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="AE41" s="24" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="AF41" s="24" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="AG41" s="24"/>
       <c r="AH41" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:35" s="55" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="86">
+        <v>55</v>
+      </c>
+      <c r="B42" s="79">
         <v>2025</v>
       </c>
       <c r="C42" s="35">
         <v>0</v>
       </c>
       <c r="D42" s="47" t="s">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>447</v>
-      </c>
-      <c r="F42" s="84" t="s">
-        <v>448</v>
+        <v>489</v>
+      </c>
+      <c r="F42" s="77" t="s">
+        <v>490</v>
       </c>
       <c r="G42" s="48" t="s">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="H42" s="49" t="s">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="I42" s="49" t="s">
         <v>41</v>
       </c>
       <c r="J42" s="50" t="s">
-        <v>451</v>
+        <v>493</v>
       </c>
       <c r="K42" s="47" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
       <c r="L42" s="47" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="M42" s="49" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N42" s="49" t="s">
         <v>43</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="P42" s="52">
         <v>7</v>
@@ -7627,58 +7583,58 @@
         <v>41</v>
       </c>
       <c r="X42" s="49" t="s">
-        <v>738</v>
+        <v>497</v>
       </c>
       <c r="Y42" s="49" t="s">
-        <v>739</v>
+        <v>498</v>
       </c>
       <c r="Z42" s="49" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA42" s="49" t="s">
-        <v>740</v>
+        <v>499</v>
       </c>
       <c r="AB42" s="49"/>
       <c r="AC42" s="49"/>
       <c r="AD42" s="49" t="s">
-        <v>737</v>
+        <v>500</v>
       </c>
       <c r="AE42" s="49" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="AF42" s="49" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="AG42" s="49"/>
       <c r="AH42" s="58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI42" s="64"/>
     </row>
     <row r="43" spans="1:35" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="87">
+        <v>55</v>
+      </c>
+      <c r="B43" s="80">
         <v>2025</v>
       </c>
       <c r="C43" s="35">
         <v>0</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>458</v>
-      </c>
-      <c r="F43" s="88" t="s">
-        <v>459</v>
+        <v>504</v>
+      </c>
+      <c r="F43" s="81" t="s">
+        <v>505</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>460</v>
+        <v>506</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I43" s="24" t="s">
         <v>41</v>
@@ -7687,17 +7643,17 @@
         <v>41</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="L43" s="25"/>
       <c r="M43" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N43" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c r="P43" s="23">
         <v>6</v>
@@ -7718,74 +7674,74 @@
       </c>
       <c r="W43" s="24"/>
       <c r="X43" s="24" t="s">
-        <v>741</v>
+        <v>509</v>
       </c>
       <c r="Y43" s="24" t="s">
         <v>41</v>
       </c>
       <c r="Z43" s="24" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA43" s="24"/>
       <c r="AB43" s="24"/>
       <c r="AC43" s="24"/>
       <c r="AD43" s="24"/>
       <c r="AE43" s="24" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="AF43" s="24" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="AG43" s="24"/>
       <c r="AH43" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="87">
+        <v>55</v>
+      </c>
+      <c r="B44" s="80">
         <v>2025</v>
       </c>
       <c r="C44" s="35">
         <v>0</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>466</v>
+        <v>513</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="I44" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>470</v>
+        <v>517</v>
       </c>
       <c r="M44" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N44" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O44" s="23" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="P44" s="23">
         <v>4</v>
@@ -7805,84 +7761,84 @@
         <v>43</v>
       </c>
       <c r="W44" s="24" t="s">
-        <v>742</v>
-      </c>
-      <c r="X44" s="88" t="s">
-        <v>744</v>
+        <v>518</v>
+      </c>
+      <c r="X44" s="81" t="s">
+        <v>519</v>
       </c>
       <c r="Y44" s="24" t="s">
-        <v>745</v>
+        <v>520</v>
       </c>
       <c r="Z44" s="24" t="s">
-        <v>707</v>
+        <v>216</v>
       </c>
       <c r="AA44" s="24"/>
       <c r="AB44" s="24"/>
       <c r="AC44" s="24"/>
       <c r="AD44" s="24" t="s">
-        <v>743</v>
+        <v>521</v>
       </c>
       <c r="AE44" s="24" t="s">
-        <v>471</v>
+        <v>522</v>
       </c>
       <c r="AF44" s="24" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="AG44" s="24"/>
       <c r="AH44" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:35" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="87">
+        <v>55</v>
+      </c>
+      <c r="B45" s="80">
         <v>2025</v>
       </c>
       <c r="C45" s="35">
         <v>0</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="F45" s="88" t="s">
-        <v>475</v>
+        <v>525</v>
+      </c>
+      <c r="F45" s="81" t="s">
+        <v>526</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I45" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J45" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="M45" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N45" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O45" s="23" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="P45" s="23">
         <v>7</v>
       </c>
-      <c r="Q45" s="99">
+      <c r="Q45" s="88">
         <v>6</v>
       </c>
       <c r="R45" s="24" t="s">
@@ -7900,74 +7856,74 @@
         <v>41</v>
       </c>
       <c r="X45" s="24" t="s">
-        <v>746</v>
+        <v>530</v>
       </c>
       <c r="Y45" s="24" t="s">
-        <v>747</v>
+        <v>531</v>
       </c>
       <c r="Z45" s="24" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA45" s="24"/>
       <c r="AB45" s="24"/>
       <c r="AC45" s="24"/>
       <c r="AD45" s="24"/>
       <c r="AE45" s="24" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="AF45" s="24" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="AG45" s="24"/>
       <c r="AH45" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:35" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="87">
+        <v>55</v>
+      </c>
+      <c r="B46" s="80">
         <v>2025</v>
       </c>
       <c r="C46" s="35">
         <v>0</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="I46" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>470</v>
+        <v>517</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N46" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O46" s="23" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="P46" s="36">
         <v>6</v>
@@ -7979,7 +7935,7 @@
         <v>44</v>
       </c>
       <c r="S46" s="28">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T46" s="28"/>
       <c r="U46" s="34"/>
@@ -7987,56 +7943,57 @@
         <v>43</v>
       </c>
       <c r="W46" s="24" t="s">
-        <v>748</v>
-      </c>
-      <c r="X46" s="88" t="s">
-        <v>749</v>
+        <v>538</v>
+      </c>
+      <c r="X46" s="81" t="s">
+        <v>539</v>
       </c>
       <c r="Y46" s="24" t="s">
-        <v>750</v>
+        <v>540</v>
       </c>
       <c r="Z46" s="24" t="s">
-        <v>707</v>
+        <v>216</v>
       </c>
       <c r="AA46" s="24"/>
       <c r="AB46" s="24"/>
       <c r="AC46" s="24"/>
       <c r="AD46" s="24"/>
       <c r="AE46" s="24" t="s">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="AF46" s="24" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="AG46" s="24"/>
       <c r="AH46" s="24" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AI46"/>
     </row>
     <row r="47" spans="1:35" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47" s="87">
+      <c r="A47" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" s="80">
         <v>2025</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>488</v>
+        <v>544</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="G47" s="36" t="s">
-        <v>490</v>
+        <v>546</v>
       </c>
       <c r="H47" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I47" s="39" t="s">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="J47" s="38" t="s">
         <v>41</v>
@@ -8048,9 +8005,9 @@
         <v>41</v>
       </c>
       <c r="O47" s="36" t="s">
-        <v>492</v>
-      </c>
-      <c r="P47" s="99">
+        <v>548</v>
+      </c>
+      <c r="P47" s="88">
         <v>5</v>
       </c>
       <c r="Q47" s="38">
@@ -8065,52 +8022,52 @@
       <c r="V47" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="W47" s="100" t="s">
-        <v>493</v>
-      </c>
-      <c r="X47" s="88" t="s">
-        <v>751</v>
+      <c r="W47" s="89" t="s">
+        <v>549</v>
+      </c>
+      <c r="X47" s="81" t="s">
+        <v>550</v>
       </c>
       <c r="Y47" s="38" t="s">
-        <v>752</v>
+        <v>551</v>
       </c>
       <c r="Z47" s="38" t="s">
-        <v>753</v>
+        <v>552</v>
       </c>
       <c r="AE47" s="38" t="s">
-        <v>494</v>
+        <v>553</v>
       </c>
       <c r="AF47" s="38" t="s">
-        <v>495</v>
+        <v>554</v>
       </c>
       <c r="AH47" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:35" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B48" s="87">
+      <c r="A48" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="80">
         <v>2025</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>496</v>
+        <v>555</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>497</v>
+        <v>556</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>498</v>
+        <v>557</v>
       </c>
       <c r="G48" s="36" t="s">
-        <v>490</v>
+        <v>546</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="J48" s="38" t="s">
         <v>41</v>
@@ -8122,9 +8079,9 @@
         <v>41</v>
       </c>
       <c r="O48" s="36" t="s">
-        <v>499</v>
-      </c>
-      <c r="P48" s="99">
+        <v>558</v>
+      </c>
+      <c r="P48" s="88">
         <v>5</v>
       </c>
       <c r="Q48" s="38">
@@ -8139,50 +8096,50 @@
       <c r="V48" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="W48" s="100" t="s">
-        <v>500</v>
+      <c r="W48" s="89" t="s">
+        <v>559</v>
       </c>
       <c r="Y48" s="38" t="s">
         <v>41</v>
       </c>
       <c r="Z48" s="38" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AE48" s="38" t="s">
-        <v>501</v>
+        <v>560</v>
       </c>
       <c r="AF48" s="38" t="s">
-        <v>502</v>
+        <v>561</v>
       </c>
       <c r="AH48" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:35" s="55" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B49" s="86">
+      <c r="A49" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="79">
         <v>2025</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="62" t="s">
-        <v>503</v>
+        <v>562</v>
       </c>
       <c r="E49" s="62" t="s">
         <v>41</v>
       </c>
       <c r="F49" s="63" t="s">
-        <v>504</v>
+        <v>563</v>
       </c>
       <c r="G49" s="62" t="s">
-        <v>505</v>
+        <v>564</v>
       </c>
       <c r="H49" s="64" t="s">
-        <v>506</v>
-      </c>
-      <c r="I49" s="86" t="s">
-        <v>507</v>
+        <v>565</v>
+      </c>
+      <c r="I49" s="79" t="s">
+        <v>566</v>
       </c>
       <c r="J49" s="64" t="s">
         <v>41</v>
@@ -8196,7 +8153,7 @@
         <v>41</v>
       </c>
       <c r="O49" s="62" t="s">
-        <v>508</v>
+        <v>567</v>
       </c>
       <c r="P49" s="64">
         <v>4</v>
@@ -8232,44 +8189,44 @@
       <c r="AC49" s="64"/>
       <c r="AD49" s="64"/>
       <c r="AE49" s="64" t="s">
-        <v>509</v>
+        <v>568</v>
       </c>
       <c r="AF49" s="64" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="AG49" s="64"/>
       <c r="AH49" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI49" s="64"/>
     </row>
     <row r="50" spans="1:35" ht="204" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B50" s="87">
+      <c r="A50" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="80">
         <v>2025</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>512</v>
+        <v>571</v>
       </c>
       <c r="F50" s="41" t="s">
-        <v>513</v>
+        <v>572</v>
       </c>
       <c r="G50" s="36" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>523</v>
+        <v>575</v>
       </c>
       <c r="M50" s="38" t="s">
         <v>41</v>
@@ -8278,7 +8235,7 @@
         <v>41</v>
       </c>
       <c r="O50" s="36" t="s">
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="P50" s="38">
         <v>25</v>
@@ -8296,52 +8253,52 @@
         <v>44</v>
       </c>
       <c r="W50" s="38" t="s">
-        <v>754</v>
-      </c>
-      <c r="X50" s="88" t="s">
-        <v>755</v>
+        <v>577</v>
+      </c>
+      <c r="X50" s="81" t="s">
+        <v>578</v>
       </c>
       <c r="Y50" s="38" t="s">
-        <v>756</v>
+        <v>579</v>
       </c>
       <c r="Z50" s="38" t="s">
         <v>41</v>
       </c>
       <c r="AE50" s="38" t="s">
-        <v>517</v>
+        <v>580</v>
       </c>
       <c r="AF50" s="38" t="s">
-        <v>518</v>
+        <v>581</v>
       </c>
       <c r="AH50" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:35" s="55" customFormat="1" ht="153" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B51" s="86">
+      <c r="A51" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="79">
         <v>2025</v>
       </c>
       <c r="C51" s="29"/>
       <c r="D51" s="62" t="s">
-        <v>519</v>
+        <v>582</v>
       </c>
       <c r="E51" s="62" t="s">
-        <v>520</v>
-      </c>
-      <c r="F51" s="79" t="s">
-        <v>521</v>
+        <v>583</v>
+      </c>
+      <c r="F51" s="72" t="s">
+        <v>584</v>
       </c>
       <c r="G51" s="62" t="s">
-        <v>522</v>
+        <v>585</v>
       </c>
       <c r="H51" s="64" t="s">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="I51" s="65" t="s">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="J51" s="64" t="s">
         <v>41</v>
@@ -8355,7 +8312,7 @@
         <v>41</v>
       </c>
       <c r="O51" s="62" t="s">
-        <v>524</v>
+        <v>586</v>
       </c>
       <c r="P51" s="64">
         <v>6</v>
@@ -8375,16 +8332,16 @@
         <v>44</v>
       </c>
       <c r="W51" s="64" t="s">
-        <v>757</v>
-      </c>
-      <c r="X51" s="84" t="s">
-        <v>758</v>
+        <v>587</v>
+      </c>
+      <c r="X51" s="77" t="s">
+        <v>588</v>
       </c>
       <c r="Y51" s="64" t="s">
         <v>41</v>
       </c>
       <c r="Z51" s="64" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA51" s="64" t="s">
         <v>41</v>
@@ -8393,42 +8350,42 @@
       <c r="AC51" s="64"/>
       <c r="AD51" s="64"/>
       <c r="AE51" s="64" t="s">
-        <v>525</v>
+        <v>589</v>
       </c>
       <c r="AF51" s="64" t="s">
-        <v>526</v>
+        <v>590</v>
       </c>
       <c r="AG51" s="64"/>
       <c r="AH51" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI51" s="64"/>
     </row>
     <row r="52" spans="1:35" s="55" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B52" s="86">
+      <c r="A52" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="79">
         <v>2025</v>
       </c>
       <c r="C52" s="29"/>
       <c r="D52" s="62" t="s">
-        <v>527</v>
+        <v>591</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>528</v>
-      </c>
-      <c r="F52" s="79" t="s">
-        <v>529</v>
+        <v>592</v>
+      </c>
+      <c r="F52" s="72" t="s">
+        <v>593</v>
       </c>
       <c r="G52" s="62" t="s">
-        <v>530</v>
+        <v>594</v>
       </c>
       <c r="H52" s="64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I52" s="65" t="s">
-        <v>531</v>
+        <v>595</v>
       </c>
       <c r="J52" s="64" t="s">
         <v>41</v>
@@ -8442,7 +8399,7 @@
         <v>41</v>
       </c>
       <c r="O52" s="62" t="s">
-        <v>532</v>
+        <v>596</v>
       </c>
       <c r="P52" s="64">
         <v>6</v>
@@ -8462,13 +8419,13 @@
         <v>43</v>
       </c>
       <c r="W52" s="64" t="s">
-        <v>759</v>
-      </c>
-      <c r="X52" s="84" t="s">
-        <v>760</v>
+        <v>597</v>
+      </c>
+      <c r="X52" s="77" t="s">
+        <v>598</v>
       </c>
       <c r="Y52" s="64" t="s">
-        <v>761</v>
+        <v>599</v>
       </c>
       <c r="Z52" s="64" t="s">
         <v>41</v>
@@ -8480,44 +8437,44 @@
       <c r="AC52" s="64"/>
       <c r="AD52" s="64"/>
       <c r="AE52" s="64" t="s">
-        <v>533</v>
+        <v>600</v>
       </c>
       <c r="AF52" s="64" t="s">
-        <v>534</v>
+        <v>601</v>
       </c>
       <c r="AG52" s="64"/>
       <c r="AH52" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI52" s="64"/>
     </row>
     <row r="53" spans="1:35" ht="153" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B53" s="87">
+      <c r="A53" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="80">
         <v>2025</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>535</v>
+        <v>602</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>536</v>
-      </c>
-      <c r="F53" s="100" t="s">
-        <v>537</v>
+        <v>603</v>
+      </c>
+      <c r="F53" s="89" t="s">
+        <v>604</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>538</v>
+        <v>605</v>
       </c>
       <c r="H53" s="38" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I53" s="39" t="s">
-        <v>539</v>
+        <v>606</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>540</v>
+        <v>607</v>
       </c>
       <c r="M53" s="38" t="s">
         <v>41</v>
@@ -8526,7 +8483,7 @@
         <v>41</v>
       </c>
       <c r="O53" s="36" t="s">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="P53" s="38">
         <v>6</v>
@@ -8556,40 +8513,40 @@
         <v>41</v>
       </c>
       <c r="AE53" s="38" t="s">
-        <v>542</v>
+        <v>609</v>
       </c>
       <c r="AF53" s="38" t="s">
-        <v>543</v>
+        <v>610</v>
       </c>
       <c r="AH53" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:35" s="55" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B54" s="86">
+      <c r="A54" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="79">
         <v>2025</v>
       </c>
       <c r="C54" s="29"/>
       <c r="D54" s="62" t="s">
-        <v>544</v>
+        <v>611</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>545</v>
+        <v>612</v>
       </c>
       <c r="F54" s="63" t="s">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>547</v>
+        <v>614</v>
       </c>
       <c r="H54" s="64" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="I54" s="65" t="s">
-        <v>548</v>
+        <v>615</v>
       </c>
       <c r="J54" s="64" t="s">
         <v>41</v>
@@ -8603,7 +8560,7 @@
         <v>41</v>
       </c>
       <c r="O54" s="62" t="s">
-        <v>549</v>
+        <v>616</v>
       </c>
       <c r="P54" s="64">
         <v>6</v>
@@ -8641,39 +8598,39 @@
       <c r="AC54" s="64"/>
       <c r="AD54" s="64"/>
       <c r="AE54" s="64" t="s">
-        <v>550</v>
+        <v>617</v>
       </c>
       <c r="AF54" s="64" t="s">
-        <v>551</v>
+        <v>618</v>
       </c>
       <c r="AG54" s="64"/>
       <c r="AH54" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI54" s="64"/>
     </row>
     <row r="55" spans="1:35" s="55" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="86" t="s">
-        <v>320</v>
-      </c>
-      <c r="B55" s="90">
+      <c r="A55" s="79" t="s">
+        <v>351</v>
+      </c>
+      <c r="B55" s="83">
         <v>2025</v>
       </c>
       <c r="C55" s="29"/>
       <c r="D55" s="62" t="s">
-        <v>552</v>
+        <v>619</v>
       </c>
       <c r="E55" s="62" t="s">
-        <v>553</v>
+        <v>620</v>
       </c>
       <c r="F55" s="63" t="s">
-        <v>554</v>
+        <v>621</v>
       </c>
       <c r="G55" s="65" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H55" s="64" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I55" s="64" t="s">
         <v>41</v>
@@ -8690,7 +8647,7 @@
         <v>41</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>555</v>
+        <v>622</v>
       </c>
       <c r="P55" s="64">
         <v>4</v>
@@ -8728,39 +8685,39 @@
       <c r="AC55" s="64"/>
       <c r="AD55" s="64"/>
       <c r="AE55" s="64" t="s">
-        <v>556</v>
+        <v>623</v>
       </c>
       <c r="AF55" s="64" t="s">
-        <v>557</v>
+        <v>624</v>
       </c>
       <c r="AG55" s="64"/>
       <c r="AH55" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI55" s="64"/>
     </row>
     <row r="56" spans="1:35" s="55" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="86" t="s">
+      <c r="A56" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="90">
+      <c r="B56" s="83">
         <v>2025</v>
       </c>
       <c r="C56" s="29"/>
       <c r="D56" s="62" t="s">
-        <v>558</v>
+        <v>625</v>
       </c>
       <c r="E56" s="62" t="s">
-        <v>559</v>
+        <v>626</v>
       </c>
       <c r="F56" s="63" t="s">
-        <v>560</v>
+        <v>627</v>
       </c>
       <c r="G56" s="62" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H56" s="64" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I56" s="65" t="s">
         <v>41</v>
@@ -8777,7 +8734,7 @@
         <v>41</v>
       </c>
       <c r="O56" s="62" t="s">
-        <v>561</v>
+        <v>628</v>
       </c>
       <c r="P56" s="64">
         <v>6</v>
@@ -8800,7 +8757,7 @@
         <v>41</v>
       </c>
       <c r="X56" s="64" t="s">
-        <v>562</v>
+        <v>629</v>
       </c>
       <c r="Y56" s="64" t="s">
         <v>41</v>
@@ -8815,39 +8772,39 @@
       <c r="AC56" s="64"/>
       <c r="AD56" s="64"/>
       <c r="AE56" s="64" t="s">
-        <v>563</v>
+        <v>630</v>
       </c>
       <c r="AF56" s="64" t="s">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="AG56" s="64"/>
       <c r="AH56" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI56" s="64"/>
     </row>
     <row r="57" spans="1:35" s="55" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="90">
+      <c r="B57" s="83">
         <v>2025</v>
       </c>
       <c r="C57" s="29"/>
       <c r="D57" s="62" t="s">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="E57" s="62" t="s">
-        <v>566</v>
+        <v>633</v>
       </c>
       <c r="F57" s="63" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H57" s="64" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I57" s="65" t="s">
         <v>41</v>
@@ -8864,7 +8821,7 @@
         <v>41</v>
       </c>
       <c r="O57" s="62" t="s">
-        <v>568</v>
+        <v>635</v>
       </c>
       <c r="P57" s="64">
         <v>3</v>
@@ -8887,7 +8844,7 @@
         <v>41</v>
       </c>
       <c r="X57" s="64" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
       <c r="Y57" s="64" t="s">
         <v>41</v>
@@ -8902,41 +8859,41 @@
       <c r="AC57" s="64"/>
       <c r="AD57" s="64"/>
       <c r="AE57" s="64" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="AF57" s="64" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="AG57" s="64"/>
       <c r="AH57" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI57" s="64"/>
     </row>
     <row r="58" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="87" t="s">
-        <v>350</v>
+      <c r="A58" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B58" s="29">
         <v>2025</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>572</v>
-      </c>
-      <c r="F58" s="88" t="s">
-        <v>573</v>
+        <v>639</v>
+      </c>
+      <c r="F58" s="81" t="s">
+        <v>640</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H58" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O58" s="38" t="s">
-        <v>574</v>
+        <v>641</v>
       </c>
       <c r="P58" s="29">
         <v>4</v>
@@ -8954,48 +8911,48 @@
         <v>44</v>
       </c>
       <c r="W58" s="38" t="s">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="Y58" s="38" t="s">
-        <v>762</v>
+        <v>643</v>
       </c>
       <c r="Z58" s="38" t="s">
         <v>41</v>
       </c>
       <c r="AE58" s="38" t="s">
-        <v>576</v>
+        <v>644</v>
       </c>
       <c r="AF58" s="38" t="s">
-        <v>577</v>
+        <v>645</v>
       </c>
       <c r="AH58" s="38" t="s">
-        <v>763</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="87" t="s">
-        <v>350</v>
+      <c r="A59" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B59" s="29">
         <v>2025</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>578</v>
+        <v>647</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>579</v>
+        <v>648</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>580</v>
+        <v>649</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O59" s="38" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="P59" s="29">
         <v>6</v>
@@ -9013,48 +8970,48 @@
         <v>44</v>
       </c>
       <c r="W59" s="38" t="s">
-        <v>582</v>
+        <v>651</v>
       </c>
       <c r="Y59" s="38" t="s">
-        <v>764</v>
+        <v>652</v>
       </c>
       <c r="Z59" s="38" t="s">
-        <v>731</v>
+        <v>450</v>
       </c>
       <c r="AE59" s="38" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
       <c r="AF59" s="38" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="AH59" s="38" t="s">
-        <v>726</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="87" t="s">
-        <v>350</v>
+      <c r="A60" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B60" s="29">
         <v>2025</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>585</v>
+        <v>655</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>586</v>
+        <v>656</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O60" s="38" t="s">
-        <v>765</v>
+        <v>658</v>
       </c>
       <c r="P60" s="29">
         <v>10</v>
@@ -9072,67 +9029,67 @@
         <v>44</v>
       </c>
       <c r="W60" s="38" t="s">
-        <v>588</v>
+        <v>659</v>
       </c>
       <c r="Y60" s="38" t="s">
-        <v>766</v>
+        <v>660</v>
       </c>
       <c r="Z60" s="38" t="s">
-        <v>767</v>
+        <v>661</v>
       </c>
       <c r="AE60" s="38" t="s">
-        <v>589</v>
+        <v>662</v>
       </c>
       <c r="AF60" s="38" t="s">
-        <v>590</v>
+        <v>663</v>
       </c>
       <c r="AH60" s="38" t="s">
-        <v>768</v>
+        <v>664</v>
       </c>
     </row>
     <row r="61" spans="1:35" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="87">
+        <v>55</v>
+      </c>
+      <c r="B61" s="80">
         <v>2026</v>
       </c>
-      <c r="C61" s="101"/>
+      <c r="C61" s="90"/>
       <c r="D61" s="23" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>592</v>
-      </c>
-      <c r="F61" s="88" t="s">
-        <v>593</v>
+        <v>666</v>
+      </c>
+      <c r="F61" s="81" t="s">
+        <v>667</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I61" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J61" s="32" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="L61" s="23" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="M61" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N61" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O61" s="23" t="s">
-        <v>596</v>
+        <v>669</v>
       </c>
       <c r="P61" s="23">
         <v>6</v>
@@ -9152,77 +9109,77 @@
         <v>43</v>
       </c>
       <c r="W61" s="24" t="s">
-        <v>597</v>
+        <v>670</v>
       </c>
       <c r="X61" s="24"/>
       <c r="Y61" s="24" t="s">
-        <v>769</v>
+        <v>671</v>
       </c>
       <c r="Z61" s="24" t="s">
-        <v>770</v>
+        <v>672</v>
       </c>
       <c r="AA61" s="24" t="s">
-        <v>598</v>
+        <v>673</v>
       </c>
       <c r="AB61" s="24"/>
       <c r="AC61" s="24"/>
       <c r="AD61" s="24" t="s">
-        <v>595</v>
+        <v>674</v>
       </c>
       <c r="AE61" s="24" t="s">
-        <v>599</v>
+        <v>675</v>
       </c>
       <c r="AF61" s="24" t="s">
-        <v>600</v>
+        <v>676</v>
       </c>
       <c r="AG61" s="24"/>
       <c r="AH61" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:35" s="55" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="86">
+        <v>55</v>
+      </c>
+      <c r="B62" s="79">
         <v>2026</v>
       </c>
-      <c r="C62" s="101"/>
+      <c r="C62" s="90"/>
       <c r="D62" s="47" t="s">
-        <v>601</v>
+        <v>677</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>602</v>
+        <v>678</v>
       </c>
       <c r="F62" s="49" t="s">
-        <v>603</v>
+        <v>679</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>604</v>
+        <v>680</v>
       </c>
       <c r="H62" s="49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I62" s="49" t="s">
         <v>41</v>
       </c>
       <c r="J62" s="50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K62" s="47" t="s">
-        <v>605</v>
+        <v>681</v>
       </c>
       <c r="L62" s="47" t="s">
-        <v>606</v>
+        <v>682</v>
       </c>
       <c r="M62" s="49" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N62" s="49" t="s">
         <v>44</v>
       </c>
       <c r="O62" s="47" t="s">
-        <v>607</v>
+        <v>683</v>
       </c>
       <c r="P62" s="58">
         <v>5</v>
@@ -9242,82 +9199,82 @@
         <v>44</v>
       </c>
       <c r="W62" s="49" t="s">
-        <v>608</v>
-      </c>
-      <c r="X62" s="102" t="s">
-        <v>610</v>
+        <v>684</v>
+      </c>
+      <c r="X62" s="91" t="s">
+        <v>685</v>
       </c>
       <c r="Y62" s="49" t="s">
-        <v>609</v>
+        <v>686</v>
       </c>
       <c r="Z62" s="49" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA62" s="49" t="s">
-        <v>611</v>
+        <v>687</v>
       </c>
       <c r="AB62" s="49"/>
       <c r="AC62" s="49"/>
       <c r="AD62" s="49"/>
       <c r="AE62" s="49" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="AF62" s="49" t="s">
-        <v>613</v>
+        <v>689</v>
       </c>
       <c r="AG62" s="49"/>
       <c r="AH62" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI62" s="64"/>
     </row>
     <row r="63" spans="1:35" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="87">
+        <v>55</v>
+      </c>
+      <c r="B63" s="80">
         <v>2026</v>
       </c>
       <c r="C63" s="35">
         <v>0</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>614</v>
+        <v>690</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>615</v>
-      </c>
-      <c r="F63" s="88" t="s">
-        <v>616</v>
+        <v>691</v>
+      </c>
+      <c r="F63" s="81" t="s">
+        <v>692</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>617</v>
+        <v>693</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>618</v>
+        <v>694</v>
       </c>
       <c r="I63" s="24" t="s">
         <v>41</v>
       </c>
       <c r="J63" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>619</v>
+        <v>695</v>
       </c>
       <c r="L63" s="23" t="s">
-        <v>620</v>
+        <v>696</v>
       </c>
       <c r="M63" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N63" s="24" t="s">
         <v>43</v>
       </c>
       <c r="O63" s="23" t="s">
-        <v>621</v>
-      </c>
-      <c r="P63" s="99">
+        <v>697</v>
+      </c>
+      <c r="P63" s="88">
         <v>10</v>
       </c>
       <c r="Q63" s="36">
@@ -9334,55 +9291,55 @@
       <c r="V63" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="W63" s="103" t="s">
-        <v>773</v>
-      </c>
-      <c r="X63" s="88" t="s">
-        <v>771</v>
+      <c r="W63" s="92" t="s">
+        <v>698</v>
+      </c>
+      <c r="X63" s="81" t="s">
+        <v>699</v>
       </c>
       <c r="Y63" s="24" t="s">
-        <v>772</v>
+        <v>700</v>
       </c>
       <c r="Z63" s="24" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="AA63" s="24"/>
       <c r="AB63" s="24"/>
       <c r="AC63" s="24"/>
       <c r="AD63" s="24"/>
       <c r="AE63" s="24" t="s">
-        <v>622</v>
+        <v>701</v>
       </c>
       <c r="AF63" s="24" t="s">
-        <v>623</v>
+        <v>702</v>
       </c>
       <c r="AG63" s="24"/>
       <c r="AH63" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:35" s="55" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="86" t="s">
-        <v>320</v>
-      </c>
-      <c r="B64" s="90">
+      <c r="A64" s="79" t="s">
+        <v>351</v>
+      </c>
+      <c r="B64" s="83">
         <v>2026</v>
       </c>
       <c r="C64" s="29"/>
       <c r="D64" s="62" t="s">
-        <v>624</v>
+        <v>703</v>
       </c>
       <c r="E64" s="62" t="s">
         <v>41</v>
       </c>
       <c r="F64" s="64" t="s">
-        <v>625</v>
+        <v>704</v>
       </c>
       <c r="G64" s="65" t="s">
-        <v>626</v>
+        <v>705</v>
       </c>
       <c r="H64" s="64" t="s">
-        <v>626</v>
+        <v>705</v>
       </c>
       <c r="I64" s="64" t="s">
         <v>41</v>
@@ -9399,7 +9356,7 @@
         <v>41</v>
       </c>
       <c r="O64" s="64" t="s">
-        <v>627</v>
+        <v>706</v>
       </c>
       <c r="P64" s="64">
         <v>2</v>
@@ -9435,59 +9392,59 @@
       <c r="AC64" s="64"/>
       <c r="AD64" s="64"/>
       <c r="AE64" s="64" t="s">
-        <v>628</v>
+        <v>707</v>
       </c>
       <c r="AF64" s="64" t="s">
-        <v>629</v>
+        <v>708</v>
       </c>
       <c r="AG64" s="64"/>
       <c r="AH64" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI64" s="64"/>
     </row>
     <row r="65" spans="1:35" ht="288.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="87" t="s">
-        <v>52</v>
+      <c r="A65" s="80" t="s">
+        <v>55</v>
       </c>
       <c r="B65" s="29">
         <v>2026</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>630</v>
+        <v>709</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>631</v>
+        <v>710</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>632</v>
+        <v>711</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>633</v>
+        <v>712</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="I65" s="38" t="s">
         <v>41</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>634</v>
+        <v>713</v>
       </c>
       <c r="L65" s="38" t="s">
-        <v>635</v>
+        <v>714</v>
       </c>
       <c r="M65" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N65" s="38" t="s">
         <v>43</v>
       </c>
       <c r="O65" s="38" t="s">
-        <v>636</v>
+        <v>715</v>
       </c>
       <c r="P65" s="38">
         <v>6</v>
@@ -9505,51 +9462,51 @@
         <v>43</v>
       </c>
       <c r="W65" s="38" t="s">
-        <v>637</v>
+        <v>716</v>
       </c>
       <c r="Y65" s="41" t="s">
-        <v>638</v>
+        <v>717</v>
       </c>
       <c r="Z65" s="38" t="s">
-        <v>731</v>
+        <v>450</v>
       </c>
       <c r="AA65" s="38" t="s">
-        <v>639</v>
+        <v>718</v>
       </c>
       <c r="AE65" s="38" t="s">
-        <v>640</v>
+        <v>719</v>
       </c>
       <c r="AF65" s="38" t="s">
-        <v>641</v>
+        <v>720</v>
       </c>
       <c r="AH65" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="87" t="s">
-        <v>350</v>
+      <c r="A66" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B66" s="29">
         <v>2026</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>642</v>
+        <v>721</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>643</v>
+        <v>722</v>
       </c>
       <c r="F66" s="38" t="s">
-        <v>644</v>
+        <v>723</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O66" s="38" t="s">
-        <v>645</v>
+        <v>724</v>
       </c>
       <c r="P66" s="38">
         <v>5</v>
@@ -9567,51 +9524,51 @@
         <v>44</v>
       </c>
       <c r="W66" s="38" t="s">
-        <v>646</v>
+        <v>725</v>
       </c>
       <c r="X66" s="38" t="s">
         <v>41</v>
       </c>
       <c r="Y66" s="38" t="s">
-        <v>776</v>
+        <v>726</v>
       </c>
       <c r="Z66" s="38" t="s">
-        <v>777</v>
+        <v>727</v>
       </c>
       <c r="AE66" s="38" t="s">
-        <v>647</v>
+        <v>728</v>
       </c>
       <c r="AF66" s="38" t="s">
-        <v>648</v>
+        <v>729</v>
       </c>
       <c r="AH66" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="87" t="s">
-        <v>350</v>
+      <c r="A67" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B67" s="29">
         <v>2026</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>649</v>
+        <v>730</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>650</v>
+        <v>731</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>651</v>
+        <v>732</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>652</v>
+        <v>733</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>652</v>
+        <v>733</v>
       </c>
       <c r="O67" s="38" t="s">
-        <v>653</v>
+        <v>734</v>
       </c>
       <c r="P67" s="29">
         <v>5</v>
@@ -9629,39 +9586,39 @@
         <v>44</v>
       </c>
       <c r="W67" s="38" t="s">
-        <v>654</v>
+        <v>735</v>
       </c>
       <c r="AE67" s="38" t="s">
-        <v>655</v>
+        <v>736</v>
       </c>
       <c r="AF67" s="38" t="s">
-        <v>656</v>
+        <v>737</v>
       </c>
     </row>
     <row r="68" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="87" t="s">
-        <v>350</v>
+      <c r="A68" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B68" s="29">
         <v>2026</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>657</v>
+        <v>738</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>658</v>
+        <v>739</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>659</v>
+        <v>740</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O68" s="38" t="s">
-        <v>660</v>
+        <v>741</v>
       </c>
       <c r="P68" s="29">
         <v>5</v>
@@ -9679,39 +9636,39 @@
         <v>44</v>
       </c>
       <c r="W68" s="38" t="s">
-        <v>661</v>
+        <v>742</v>
       </c>
       <c r="AE68" s="38" t="s">
-        <v>662</v>
+        <v>743</v>
       </c>
       <c r="AF68" s="38" t="s">
-        <v>663</v>
+        <v>744</v>
       </c>
     </row>
     <row r="69" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="87" t="s">
-        <v>350</v>
+      <c r="A69" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B69" s="29">
         <v>2026</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>664</v>
+        <v>745</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>665</v>
+        <v>746</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>666</v>
+        <v>747</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O69" s="38" t="s">
-        <v>667</v>
+        <v>748</v>
       </c>
       <c r="P69" s="29">
         <v>5</v>
@@ -9729,39 +9686,39 @@
         <v>44</v>
       </c>
       <c r="W69" s="38" t="s">
-        <v>668</v>
+        <v>749</v>
       </c>
       <c r="AE69" s="38" t="s">
-        <v>669</v>
+        <v>750</v>
       </c>
       <c r="AF69" s="38" t="s">
-        <v>670</v>
+        <v>751</v>
       </c>
     </row>
     <row r="70" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="87" t="s">
-        <v>350</v>
+      <c r="A70" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B70" s="29">
         <v>2026</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>671</v>
+        <v>752</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>672</v>
+        <v>753</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>673</v>
+        <v>754</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H70" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O70" s="38" t="s">
-        <v>674</v>
+        <v>755</v>
       </c>
       <c r="P70" s="29">
         <v>4</v>
@@ -9779,39 +9736,39 @@
         <v>44</v>
       </c>
       <c r="W70" s="38" t="s">
-        <v>675</v>
+        <v>756</v>
       </c>
       <c r="AE70" s="38" t="s">
-        <v>676</v>
+        <v>757</v>
       </c>
       <c r="AF70" s="38" t="s">
-        <v>677</v>
+        <v>758</v>
       </c>
     </row>
     <row r="71" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="87" t="s">
-        <v>350</v>
+      <c r="A71" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B71" s="29">
         <v>2026</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>678</v>
+        <v>759</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>679</v>
+        <v>760</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>680</v>
+        <v>761</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H71" s="38" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="O71" s="38" t="s">
-        <v>681</v>
+        <v>762</v>
       </c>
       <c r="P71" s="29">
         <v>7</v>
@@ -9829,37 +9786,37 @@
         <v>44</v>
       </c>
       <c r="W71" s="38" t="s">
-        <v>682</v>
+        <v>763</v>
       </c>
       <c r="AE71" s="38" t="s">
-        <v>683</v>
+        <v>764</v>
       </c>
       <c r="AF71" s="38" t="s">
-        <v>684</v>
+        <v>765</v>
       </c>
     </row>
     <row r="72" spans="1:35" s="55" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="86" t="s">
-        <v>342</v>
+      <c r="A72" s="79" t="s">
+        <v>373</v>
       </c>
       <c r="B72" s="66">
         <v>2026</v>
       </c>
       <c r="C72" s="29"/>
       <c r="D72" s="64" t="s">
-        <v>685</v>
+        <v>766</v>
       </c>
       <c r="E72" s="64" t="s">
-        <v>686</v>
-      </c>
-      <c r="F72" s="84" t="s">
-        <v>774</v>
+        <v>767</v>
+      </c>
+      <c r="F72" s="77" t="s">
+        <v>768</v>
       </c>
       <c r="G72" s="64" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="H72" s="64" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="I72" s="64" t="s">
         <v>41</v>
@@ -9876,7 +9833,7 @@
         <v>41</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>687</v>
+        <v>770</v>
       </c>
       <c r="P72" s="66">
         <v>6</v>
@@ -9914,41 +9871,41 @@
       <c r="AC72" s="64"/>
       <c r="AD72" s="64"/>
       <c r="AE72" s="64" t="s">
-        <v>688</v>
+        <v>771</v>
       </c>
       <c r="AF72" s="64" t="s">
-        <v>689</v>
+        <v>772</v>
       </c>
       <c r="AG72" s="64"/>
       <c r="AH72" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI72" s="64"/>
     </row>
     <row r="73" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="87" t="s">
-        <v>350</v>
+      <c r="A73" s="80" t="s">
+        <v>381</v>
       </c>
       <c r="B73" s="29">
         <v>2026</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>690</v>
+        <v>773</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>691</v>
-      </c>
-      <c r="F73" s="88" t="s">
-        <v>779</v>
+        <v>774</v>
+      </c>
+      <c r="F73" s="81" t="s">
+        <v>775</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="H73" s="38" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="O73" s="38" t="s">
-        <v>692</v>
+        <v>777</v>
       </c>
       <c r="P73" s="29">
         <v>6</v>
@@ -9966,132 +9923,132 @@
         <v>44</v>
       </c>
       <c r="W73" s="38" t="s">
+        <v>778</v>
+      </c>
+      <c r="AE73" s="38" t="s">
+        <v>779</v>
+      </c>
+      <c r="AF73" s="38" t="s">
         <v>780</v>
-      </c>
-      <c r="AE73" s="38" t="s">
-        <v>693</v>
-      </c>
-      <c r="AF73" s="38" t="s">
-        <v>694</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="Preprint">
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1048576 E1:J1048576 M1:R1048576 V1:V1048576 Y3 X1:Y2 Z1:AA1048576 X4:Y1048576">
-    <cfRule type="expression" dxfId="7" priority="5">
+  <conditionalFormatting sqref="W1:W1048576">
+    <cfRule type="containsBlanks" dxfId="5" priority="1">
+      <formula>LEN(TRIM(W1))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1:Y2 A1:B1048576 E1:J1048576 M1:R1048576 V1:V1048576 Z1:AA1048576 Y3 X4:Y1048576">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH1:AH1048576">
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Status_internal">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Status_internal">
       <formula>NOT(ISERROR(SEARCH("Status_internal",AH1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="notEqual">
       <formula>"published"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI1:AI1048576">
-    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>LEN(TRIM(AI1))=0</formula>
     </cfRule>
-    <cfRule type="notContainsText" dxfId="3" priority="7" operator="notContains" text="TODO">
+    <cfRule type="notContainsText" dxfId="0" priority="7" operator="notContains" text="TODO">
       <formula>ISERROR(SEARCH("TODO",AI1))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W1:W1048576">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(W1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="X2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="W4" r:id="rId6" display="https://www.mdpi.com/1424-8220/21/21/7095" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X4" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F7" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F9" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="X9" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="X16" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="X17" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="X18" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F19" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="X19" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F35" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="X35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="X36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="X37" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F38" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="X38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="X39" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F47" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F48" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F50" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F51" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F52" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F54" r:id="rId47" location="page=487" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F55" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F56" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F57" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="X62" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F65" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F5" r:id="rId53" xr:uid="{A4B3A2DB-02D1-BC4F-AC10-0407DB34636D}"/>
-    <hyperlink ref="F11" r:id="rId54" xr:uid="{9F4328A7-99E8-D74D-8272-5E8A167B6D87}"/>
-    <hyperlink ref="X11" r:id="rId55" xr:uid="{6EA1416D-9D2F-1C47-8C8D-28235FD36FF7}"/>
-    <hyperlink ref="X8" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X13" r:id="rId57" xr:uid="{BF1A2EBF-AA11-9F4D-B243-3F5DAEE3F183}"/>
-    <hyperlink ref="X20" r:id="rId58" xr:uid="{3BE40024-F74E-224B-9D70-8F1343ABB793}"/>
-    <hyperlink ref="X21" r:id="rId59" xr:uid="{25727197-A9CE-7440-B37C-94A679523DFD}"/>
-    <hyperlink ref="F23" r:id="rId60" xr:uid="{E5C24F35-F4B6-FE40-87B3-13BD1A6D04F7}"/>
-    <hyperlink ref="X23" r:id="rId61" xr:uid="{A55066F4-78D8-064B-BEB8-152AAA976BDA}"/>
-    <hyperlink ref="F24" r:id="rId62" xr:uid="{33A8E01E-C77A-A046-A86F-7FBFBF3D01A2}"/>
-    <hyperlink ref="X26" r:id="rId63" xr:uid="{8E5782F7-17F7-A240-B140-3D87DB4734B0}"/>
-    <hyperlink ref="X27" r:id="rId64" xr:uid="{A5F861E2-B5AA-724D-98DC-85D50AA9BE91}"/>
-    <hyperlink ref="F40" r:id="rId65" xr:uid="{5584525B-BFA6-0643-9998-7B5920B8A1C4}"/>
-    <hyperlink ref="X40" r:id="rId66" xr:uid="{9965E00B-97E0-E244-AEF7-1BCF415AB81E}"/>
-    <hyperlink ref="F41" r:id="rId67" xr:uid="{D2288FE7-3899-FD43-9BDC-1510BD426398}"/>
-    <hyperlink ref="X41" r:id="rId68" xr:uid="{4BD9D464-7935-7942-9B09-179425F41F0C}"/>
-    <hyperlink ref="F42" r:id="rId69" xr:uid="{E6814A42-6168-F549-9843-042E717C23EB}"/>
-    <hyperlink ref="F43" r:id="rId70" xr:uid="{104E85D3-5135-F64C-8B98-A6EFB6D87574}"/>
-    <hyperlink ref="X44" r:id="rId71" xr:uid="{ED7FC20F-3F8A-7F44-8AD3-F2FCCBB60E17}"/>
-    <hyperlink ref="F45" r:id="rId72" xr:uid="{466F5C01-75CD-834C-97A8-F9B3BD3567BD}"/>
-    <hyperlink ref="X46" r:id="rId73" xr:uid="{12A67B88-6E2F-454D-B94A-2E1E35AA5186}"/>
-    <hyperlink ref="X47" r:id="rId74" xr:uid="{E8CA958D-B318-AF4F-8405-864F20D316C5}"/>
-    <hyperlink ref="X50" r:id="rId75" xr:uid="{A4DC15E5-DF81-B144-B76F-98B08E2443EE}"/>
-    <hyperlink ref="X51" r:id="rId76" xr:uid="{7E182DA7-6010-2940-AD26-6C94F215841E}"/>
-    <hyperlink ref="X52" r:id="rId77" xr:uid="{4E154569-7242-BB4C-91F2-E69DA4376163}"/>
-    <hyperlink ref="F58" r:id="rId78" xr:uid="{7A505274-86B6-FE46-A628-88D8526FBE51}"/>
-    <hyperlink ref="F61" r:id="rId79" xr:uid="{EAF5154B-2655-6C42-99CB-696D48A8B6F9}"/>
-    <hyperlink ref="F63" r:id="rId80" xr:uid="{3CC57E5E-E824-E046-8191-9696A86FC0E3}"/>
-    <hyperlink ref="X63" r:id="rId81" xr:uid="{242E0C40-867F-8B4C-A65D-2901A7AD4D4B}"/>
-    <hyperlink ref="F72" r:id="rId82" xr:uid="{B1F57A89-BDAF-6849-A886-9E2F3CD32B32}"/>
-    <hyperlink ref="F73" r:id="rId83" xr:uid="{46DA7A5E-489B-E145-BC16-E37A7AFEFE86}"/>
+    <hyperlink ref="X3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="W4" r:id="rId6" display="https://www.mdpi.com/1424-8220/21/21/7095" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X4" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F7" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F8" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X8" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="X9" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F11" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="X11" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F13" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="X13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F14" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F15" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F16" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="X16" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F17" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="X17" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F18" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="X18" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F19" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="X19" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="X20" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="X21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F23" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="X23" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F24" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F25" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F26" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="X26" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F27" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="X27" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F28" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F29" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F30" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F31" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F35" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="X35" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F36" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="X36" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F37" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="X37" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F38" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="X38" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F39" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="X39" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F40" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="X40" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F41" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="X41" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F42" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F43" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="X44" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F45" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="X46" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F47" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="X47" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F48" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F50" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="X50" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F51" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="X51" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F52" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="X52" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F54" r:id="rId72" location="page=487" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F55" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F56" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F57" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F58" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F61" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="X62" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F63" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="X63" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F65" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F72" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F73" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_220CE0D83A725766AD066C3559B1863E075FD0F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA491456-D40C-FB42-9797-0C8AF7E3975C}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{065BCD9C-EF6C-CC48-8816-168E75E7FCDF}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="790">
   <si>
     <t>Tipo</t>
   </si>
@@ -1425,53 +1425,53 @@
 }</t>
   </si>
   <si>
+    <t>When Do Large Language Models (LLMs) Struggle to Count Letters?</t>
+  </si>
+  <si>
+    <t>j3f4tGmQtD8C</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3818606</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Intelligent Systems and Technology</t>
+  </si>
+  <si>
+    <t>T. Fu, R. Ferrando, J. Conde, C. Arriaga, P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2412.18626]</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
+  </si>
+  <si>
+    <t>Large Language Models (LLMs) have achieved unprecedented performance on many complex tasks, being able, for example, to answer questions on almost any topic. However, they struggle with other simple tasks, such as counting the occurrences of letters in a word, as illustrated by the inability of many LLMs to count the number of &amp;#34;r&amp;#34; letters in &amp;#34;strawberry&amp;#34;. Several works have studied this problem and linked it to the tokenization used by LLMs, to the intrinsic limitations of the attention mechanism, or to the lack of character-level training data. In this paper, we conduct an experimental study to evaluate the relations between the LLM errors when counting letters with 1) the frequency of the word and its components in the training dataset and 2) the complexity of the counting operation. We present a comprehensive analysis of the errors of LLMs when counting letter occurrences by evaluating a representative group of models over a large number of words. The results show a number of consistent trends in the models evaluated: 1) models are capable of recognizing the letters but not counting them; 2) the frequency of the word and tokens in the word does not have a significant impact on the LLM errors; 3) there is a positive correlation of letter frequency with errors, more frequent letters tend to have more counting errors, 4) the errors show a strong correlation with the number of letters or tokens in a word and 5) the strongest correlation occurs with the number of letters with counts larger than one, with most models being unable to correctly count words in which letters appear more than twice.</t>
+  </si>
+  <si>
+    <t>@article{fu2024when,
+  title={When Do Large Language Models (LLMs) Struggle to Count Letters?},
+  author={Fu, Tairan and Ferrando, Raquel and Conde, Javier and Arriaga, Carlos and Reviriego, Pedro},
+  journal={ACM Transactions on Intelligent Systems and Technology},
+  year={2024},
+  publisher={ACM},
+  doi={10.1145/3818606}
+}</t>
+  </si>
+  <si>
     <t>Preprint</t>
   </si>
   <si>
-    <t>Why do large language models (llms) struggle to count letters?</t>
-  </si>
-  <si>
-    <t>j3f4tGmQtD8C</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2412.18626</t>
+    <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
+  </si>
+  <si>
+    <t>qxL8FJ1GzNcC</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2402.06693</t>
   </si>
   <si>
     <t>arXiv</t>
-  </si>
-  <si>
-    <t>T. Fu, R. Ferrando, J. Conde, C. Arriaga, P. Reviriego</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2412.18626]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
-  </si>
-  <si>
-    <t>Large Language Models (LLMs) have achieved unprecedented performance on many complex tasks, being able, for example, to answer questions on almost any topic. However, they struggle with other simple tasks, such as counting the occurrences of letters in a word, as illustrated by the inability of many LLMs to count the number of &amp;#34;r&amp;#34; letters in &amp;#34;strawberry&amp;#34;. Several works have studied this problem and linked it to the tokenization used by LLMs, to the intrinsic limitations of the attention mechanism, or to the lack of character-level training data. In this paper, we conduct an experimental study to evaluate the relations between the LLM errors when counting letters with 1) the frequency of the word and its components in the training dataset and 2) the complexity of the counting operation. We present a comprehensive analysis of the errors of LLMs when counting letter occurrences by evaluating a representative group of models over a large number of words. The results show a number of consistent trends in the models evaluated: 1) models are capable of recognizing the letters but not counting them; 2) the frequency of the word and tokens in the word does not have a significant impact on the LLM errors; 3) there is a positive correlation of letter frequency with errors, more frequent letters tend to have more counting errors, 4) the errors show a strong correlation with the number of letters or tokens in a word and 5) the strongest correlation occurs with the number of letters with counts larger than one, with most models being unable to correctly count words in which letters appear more than twice.</t>
-  </si>
-  <si>
-    <t>@misc{Conde2024Why,
-  title = {Why Do Large Language Models (LLMs) Struggle to Count Letters?},
-  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro},
-  year = {2024},
-  eprint = {2412.18626},
-  archivePrefix = {arXiv},
-  note = {arXiv:2412.18626},
-}</t>
-  </si>
-  <si>
-    <t>sent to ACM TIST</t>
-  </si>
-  <si>
-    <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
-  </si>
-  <si>
-    <t>qxL8FJ1GzNcC</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2402.06693</t>
   </si>
   <si>
     <t>J. Conde, A. Pozo, A. Munoz-Arcentales, J. Choque, Á. Alonso</t>
@@ -1503,9 +1503,6 @@
   </si>
   <si>
     <t>https://doi.org/10.1145/3696459</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Intelligent Systems and Technology</t>
   </si>
   <si>
     <t>Índice de impacto JCR (2024): 6.6 (25/258 – Q1 [D1])</t>
@@ -2468,6 +2465,9 @@
 }</t>
   </si>
   <si>
+    <t>sent to ACM TIST</t>
+  </si>
+  <si>
     <t>Adding LLMs to the psycholinguistic norming toolbox: A practical guide to getting the most out of human ratings</t>
   </si>
   <si>
@@ -2698,9 +2698,6 @@
     <t xml:space="preserve">[https://github.com/aMa2210/AI_impostors, https://ama2210.github.io/WikiArt_VLM_Web/, https://zenodo.org/records/17880956] </t>
   </si>
   <si>
-    <t>[https://www.growkudos.com/publications/10.1145%25252F3807498/reader]</t>
-  </si>
-  <si>
     <t>The attribution of artworks in general and of paintings in particular has always been an issue in art. The advent of powerful artificial intelligence models that can generate and analyze images creates new challenges for painting attribution. On the one hand, AI models can create images that mimic the style of a painter, which can be incorrectly identified as made by that painter, for example, by other AI models. On the other hand, AI models may not be able to correctly identify the artist for real paintings, inducing users to attribute paintings incorrectly. In this paper, both problems, are experimentally studied at scale using state-of-the-art AI models for image generation and analysis on a large dataset with close to 40,000 paintings from 128 artists. This dataset has been extended to include AI-generated captions for the paintings, as well as AI-generated images derived from these captions. The enhanced dataset is publicly available for download and interactive visualization. The results show that vision language models have limited capabilities to: 1) identify the authors of real canvas and 2) to identify AI-generated images. As users increasingly rely on queries to AI models to get information, these results show the need to improve the capabilities of VLMs to reliably perform artist identification and detection of AI-generated images to prevent the spread of incorrect information.</t>
   </si>
   <si>
@@ -2946,13 +2943,42 @@
 }</t>
   </si>
   <si>
-    <t>accepted to ACM TIST</t>
-  </si>
-  <si>
-    <t>Update the zenodo link in the paper, and update the arxiv with the new title When…</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.5281/zenodo.20112756, https://github.com/aMa2210/LLM_CounterLettersWithoutFT.git]</t>
+    <t>Lost in Sampling: Assessing Lexical Reachability in LLMs via the Word Coverage Score (WCS)</t>
+  </si>
+  <si>
+    <t>xtRiw3GOFMkC</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2605.27268</t>
+  </si>
+  <si>
+    <t>S. Awad, J. Conde, C. Arriaga, T. Fu, J. Coronado-Blázquez, P. Reviriego</t>
+  </si>
+  <si>
+    <t>["https://arxiv.org/abs/2605.27268"]</t>
+  </si>
+  <si>
+    <t>Modern Large Language Models (LLMs) are often criticized for producing repetitive and homogeneous text, despite possessing vast latent vocabularies. While previous research has focused on model knowledge and training data, we investigate the role of decoding mechanics in suppressing linguistic diversity. We introduce the Word Coverage Score (WCS), a metric that quantifies the extent to which contextually appropriate human vocabulary is mathematically pruned by standard sampling filters (e.g., Top-k, Top-p, and Min-p). Rather than assessing static knowledge, the WCS measures the lexical survival rate of low-frequency, high-information human words as a function of sampling parameters. By auditing open-weight models on human-authored corpus fragments, we identify which logical lexical choices are rendered unreachable by the decoder, even when they reside within the probability space. Our results provide quantitative evidence that industry-standard sampling defaults act as unintended censorship mechanisms, smoothing the unique textures of human expression into a homogenized discourse. The WCS offers a rigorous framework for optimizing the trade-off between text coherence and lexical richness, providing a diagnostic tool for preserving the diversity of human language in generative models.</t>
+  </si>
+  <si>
+    <t>@misc{awad2026lost,
+  title={Lost in Sampling: Assessing Lexical Reachability in LLMs via the Word Coverage Score (WCS)},
+  author={Awad, Samer and Conde, Javier and Arriaga, Carlos and Fu, Tairan and Coronado-Blázquez, Javier and Reviriego, Pedro},
+  year={2026},
+  eprint={2605.27268},
+  archivePrefix={arXiv},
+  primaryClass={cs.CL},
+  doi={10.48550/arXiv.2605.27268}
+}</t>
+  </si>
+  <si>
+    <t>[https://www.linkedin.com/posts/javier-conde-diaz_upm-polimi-airesearch-share-7464786001824120832-5kPN/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+  </si>
+  <si>
+    <t>[https://www.growkudos.com/publications/10.1145%25252F3807498/reader, https://www.linkedin.com/posts/pedro-reviriego-b582094_wikiart-image-viewer-share-7462442086575951872-806e]</t>
+  </si>
+  <si>
+    <t>FUN4DATE, TUCAN6-CM, BRIDGE-AI</t>
   </si>
 </sst>
 </file>
@@ -3456,7 +3482,37 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -3787,11 +3843,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI73"/>
+  <dimension ref="A1:AI74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="80" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="20" style="29" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" style="29" customWidth="1"/>
     <col min="4" max="4" width="36.1640625" style="38" customWidth="1"/>
     <col min="5" max="5" width="22" style="38" customWidth="1"/>
@@ -3810,8 +3866,8 @@
     <col min="27" max="27" width="63.33203125" style="38" customWidth="1"/>
     <col min="28" max="34" width="8.83203125" style="38" customWidth="1"/>
     <col min="35" max="35" width="134.5" style="38" customWidth="1"/>
-    <col min="36" max="36" width="8.83203125" style="1" customWidth="1"/>
-    <col min="37" max="16384" width="8.83203125" style="1"/>
+    <col min="36" max="37" width="8.83203125" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="2" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4151,7 +4207,7 @@
         <v>43</v>
       </c>
       <c r="S4" s="20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T4" s="20"/>
       <c r="U4" s="21"/>
@@ -4511,7 +4567,7 @@
         <v>44</v>
       </c>
       <c r="S8" s="59">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T8" s="59"/>
       <c r="U8" s="60">
@@ -4610,7 +4666,7 @@
         <v>43</v>
       </c>
       <c r="S9" s="59">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T9" s="59"/>
       <c r="U9" s="61">
@@ -5336,7 +5392,7 @@
         <v>187</v>
       </c>
       <c r="S17" s="68">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="T17" s="70" t="s">
         <v>212</v>
@@ -5728,7 +5784,7 @@
         <v>44</v>
       </c>
       <c r="S21" s="28">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T21" s="28"/>
       <c r="U21" s="34"/>
@@ -5817,7 +5873,7 @@
         <v>44</v>
       </c>
       <c r="S22" s="28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" s="28"/>
       <c r="U22" s="34"/>
@@ -5908,7 +5964,7 @@
         <v>44</v>
       </c>
       <c r="S23" s="28">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T23" s="28"/>
       <c r="U23" s="34"/>
@@ -5999,7 +6055,7 @@
         <v>43</v>
       </c>
       <c r="S24" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" s="28"/>
       <c r="U24" s="34"/>
@@ -6171,7 +6227,7 @@
         <v>44</v>
       </c>
       <c r="S26" s="66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" s="66"/>
       <c r="U26" s="67"/>
@@ -6345,7 +6401,7 @@
         <v>43</v>
       </c>
       <c r="S28" s="66">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T28" s="66"/>
       <c r="U28" s="67"/>
@@ -6432,7 +6488,7 @@
         <v>43</v>
       </c>
       <c r="S29" s="66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" s="66"/>
       <c r="U29" s="67"/>
@@ -6722,28 +6778,43 @@
     </row>
     <row r="33" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="29">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="38" t="s">
         <v>381</v>
       </c>
-      <c r="B33" s="29">
-        <v>2024</v>
-      </c>
-      <c r="D33" s="38" t="s">
+      <c r="E33" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="F33" s="81" t="s">
         <v>383</v>
       </c>
-      <c r="F33" s="38" t="s">
+      <c r="G33" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="H33" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="50" t="s">
+        <v>403</v>
+      </c>
+      <c r="L33" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="M33" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="O33" s="38" t="s">
         <v>385</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O33" s="38" t="s">
-        <v>386</v>
       </c>
       <c r="P33" s="29">
         <v>5</v>
@@ -6761,51 +6832,51 @@
         <v>44</v>
       </c>
       <c r="W33" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="X33" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y33" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z33" s="38" t="s">
         <v>387</v>
       </c>
-      <c r="X33" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y33" s="38" t="s">
-        <v>783</v>
-      </c>
-      <c r="Z33" s="38" t="s">
+      <c r="AA33" s="38" t="s">
+        <v>787</v>
+      </c>
+      <c r="AE33" s="38" t="s">
         <v>388</v>
       </c>
-      <c r="AE33" s="38" t="s">
+      <c r="AF33" s="38" t="s">
         <v>389</v>
       </c>
-      <c r="AF33" s="38" t="s">
-        <v>390</v>
-      </c>
       <c r="AH33" s="38" t="s">
-        <v>781</v>
-      </c>
-      <c r="AI33" s="38" t="s">
-        <v>782</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B34" s="29">
         <v>2024</v>
       </c>
       <c r="D34" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="E34" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="F34" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="G34" s="38" t="s">
         <v>394</v>
       </c>
-      <c r="G34" s="38" t="s">
-        <v>385</v>
-      </c>
       <c r="H34" s="38" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="O34" s="38" t="s">
         <v>395</v>
@@ -6820,7 +6891,7 @@
         <v>43</v>
       </c>
       <c r="S34" s="29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V34" s="38" t="s">
         <v>44</v>
@@ -6843,6 +6914,7 @@
       <c r="AF34" s="38" t="s">
         <v>399</v>
       </c>
+      <c r="AI34"/>
     </row>
     <row r="35" spans="1:35" s="55" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="64" t="s">
@@ -6864,7 +6936,7 @@
         <v>402</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="H35" s="50" t="s">
         <v>314</v>
@@ -6876,7 +6948,7 @@
         <v>102</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L35" s="50" t="s">
         <v>240</v>
@@ -6888,7 +6960,7 @@
         <v>13</v>
       </c>
       <c r="O35" s="50" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P35" s="58">
         <v>5</v>
@@ -6900,7 +6972,7 @@
         <v>43</v>
       </c>
       <c r="S35" s="70">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T35" s="70" t="s">
         <v>212</v>
@@ -6910,28 +6982,28 @@
         <v>44</v>
       </c>
       <c r="W35" s="50" t="s">
+        <v>405</v>
+      </c>
+      <c r="X35" s="57" t="s">
         <v>406</v>
       </c>
-      <c r="X35" s="57" t="s">
+      <c r="Y35" s="50" t="s">
         <v>407</v>
-      </c>
-      <c r="Y35" s="50" t="s">
-        <v>408</v>
       </c>
       <c r="Z35" s="50" t="s">
         <v>216</v>
       </c>
       <c r="AA35" s="50" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AB35" s="64"/>
       <c r="AC35" s="64"/>
       <c r="AD35" s="64"/>
       <c r="AE35" s="64" t="s">
+        <v>409</v>
+      </c>
+      <c r="AF35" s="64" t="s">
         <v>410</v>
-      </c>
-      <c r="AF35" s="64" t="s">
-        <v>411</v>
       </c>
       <c r="AG35" s="64"/>
       <c r="AH35" s="58" t="s">
@@ -6950,16 +7022,16 @@
         <v>9</v>
       </c>
       <c r="D36" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="E36" s="50" t="s">
         <v>412</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="F36" s="57" t="s">
         <v>413</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="G36" s="50" t="s">
         <v>414</v>
-      </c>
-      <c r="G36" s="50" t="s">
-        <v>415</v>
       </c>
       <c r="H36" s="50" t="s">
         <v>118</v>
@@ -6971,19 +7043,19 @@
         <v>61</v>
       </c>
       <c r="K36" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="L36" s="50" t="s">
         <v>416</v>
-      </c>
-      <c r="L36" s="50" t="s">
-        <v>417</v>
       </c>
       <c r="M36" s="50" t="s">
         <v>55</v>
       </c>
       <c r="N36" s="50" t="s">
+        <v>417</v>
+      </c>
+      <c r="O36" s="50" t="s">
         <v>418</v>
-      </c>
-      <c r="O36" s="50" t="s">
-        <v>419</v>
       </c>
       <c r="P36" s="47">
         <v>6</v>
@@ -7007,30 +7079,30 @@
         <v>43</v>
       </c>
       <c r="W36" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="X36" s="57" t="s">
         <v>420</v>
       </c>
-      <c r="X36" s="57" t="s">
+      <c r="Y36" s="50" t="s">
         <v>421</v>
       </c>
-      <c r="Y36" s="50" t="s">
+      <c r="Z36" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="Z36" s="50" t="s">
+      <c r="AA36" s="50" t="s">
         <v>423</v>
-      </c>
-      <c r="AA36" s="50" t="s">
-        <v>424</v>
       </c>
       <c r="AB36" s="64"/>
       <c r="AC36" s="64"/>
       <c r="AD36" s="50" t="s">
+        <v>424</v>
+      </c>
+      <c r="AE36" s="64" t="s">
         <v>425</v>
       </c>
-      <c r="AE36" s="64" t="s">
+      <c r="AF36" s="64" t="s">
         <v>426</v>
-      </c>
-      <c r="AF36" s="64" t="s">
-        <v>427</v>
       </c>
       <c r="AG36" s="64"/>
       <c r="AH36" s="58" t="s">
@@ -7049,13 +7121,13 @@
         <v>8.5</v>
       </c>
       <c r="D37" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="E37" s="50" t="s">
         <v>428</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="F37" s="57" t="s">
         <v>429</v>
-      </c>
-      <c r="F37" s="57" t="s">
-        <v>430</v>
       </c>
       <c r="G37" s="48" t="s">
         <v>117</v>
@@ -7070,10 +7142,10 @@
         <v>102</v>
       </c>
       <c r="K37" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="L37" s="47" t="s">
         <v>431</v>
-      </c>
-      <c r="L37" s="47" t="s">
-        <v>432</v>
       </c>
       <c r="M37" s="49" t="s">
         <v>121</v>
@@ -7082,7 +7154,7 @@
         <v>13</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P37" s="50">
         <v>4</v>
@@ -7098,36 +7170,36 @@
       </c>
       <c r="T37" s="53"/>
       <c r="U37" s="71" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V37" s="49" t="s">
         <v>44</v>
       </c>
       <c r="W37" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="X37" s="49" t="s">
         <v>435</v>
       </c>
-      <c r="X37" s="49" t="s">
+      <c r="Y37" s="49" t="s">
         <v>436</v>
       </c>
-      <c r="Y37" s="49" t="s">
+      <c r="Z37" s="49" t="s">
         <v>437</v>
       </c>
-      <c r="Z37" s="49" t="s">
+      <c r="AA37" s="49" t="s">
         <v>438</v>
-      </c>
-      <c r="AA37" s="49" t="s">
-        <v>439</v>
       </c>
       <c r="AB37" s="49"/>
       <c r="AC37" s="49"/>
       <c r="AD37" s="49" t="s">
+        <v>439</v>
+      </c>
+      <c r="AE37" s="49" t="s">
         <v>440</v>
       </c>
-      <c r="AE37" s="49" t="s">
+      <c r="AF37" s="49" t="s">
         <v>441</v>
-      </c>
-      <c r="AF37" s="49" t="s">
-        <v>442</v>
       </c>
       <c r="AG37" s="49"/>
       <c r="AH37" s="58" t="s">
@@ -7146,13 +7218,13 @@
         <v>8</v>
       </c>
       <c r="D38" s="56" t="s">
+        <v>442</v>
+      </c>
+      <c r="E38" s="56" t="s">
         <v>443</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="F38" s="57" t="s">
         <v>444</v>
-      </c>
-      <c r="F38" s="57" t="s">
-        <v>445</v>
       </c>
       <c r="G38" s="50" t="s">
         <v>191</v>
@@ -7170,7 +7242,7 @@
         <v>192</v>
       </c>
       <c r="L38" s="50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M38" s="50" t="s">
         <v>193</v>
@@ -7179,7 +7251,7 @@
         <v>43</v>
       </c>
       <c r="O38" s="50" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P38" s="50">
         <v>7</v>
@@ -7203,30 +7275,30 @@
         <v>43</v>
       </c>
       <c r="W38" s="50" t="s">
+        <v>447</v>
+      </c>
+      <c r="X38" s="57" t="s">
         <v>448</v>
       </c>
-      <c r="X38" s="57" t="s">
+      <c r="Y38" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z38" s="50" t="s">
         <v>449</v>
       </c>
-      <c r="Y38" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z38" s="50" t="s">
+      <c r="AA38" s="50" t="s">
         <v>450</v>
-      </c>
-      <c r="AA38" s="50" t="s">
-        <v>451</v>
       </c>
       <c r="AB38" s="64"/>
       <c r="AC38" s="64"/>
       <c r="AD38" s="50" t="s">
+        <v>451</v>
+      </c>
+      <c r="AE38" s="64" t="s">
         <v>452</v>
       </c>
-      <c r="AE38" s="64" t="s">
+      <c r="AF38" s="64" t="s">
         <v>453</v>
-      </c>
-      <c r="AF38" s="64" t="s">
-        <v>454</v>
       </c>
       <c r="AG38" s="64"/>
       <c r="AH38" s="58" t="s">
@@ -7245,16 +7317,16 @@
         <v>7</v>
       </c>
       <c r="D39" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="E39" s="50" t="s">
         <v>455</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="F39" s="57" t="s">
         <v>456</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="G39" s="50" t="s">
         <v>457</v>
-      </c>
-      <c r="G39" s="50" t="s">
-        <v>458</v>
       </c>
       <c r="H39" s="50" t="s">
         <v>361</v>
@@ -7266,10 +7338,10 @@
         <v>61</v>
       </c>
       <c r="K39" s="50" t="s">
+        <v>458</v>
+      </c>
+      <c r="L39" s="50" t="s">
         <v>459</v>
-      </c>
-      <c r="L39" s="50" t="s">
-        <v>460</v>
       </c>
       <c r="M39" s="50" t="s">
         <v>55</v>
@@ -7278,7 +7350,7 @@
         <v>43</v>
       </c>
       <c r="O39" s="50" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P39" s="52">
         <v>6</v>
@@ -7300,30 +7372,30 @@
         <v>44</v>
       </c>
       <c r="W39" s="50" t="s">
+        <v>461</v>
+      </c>
+      <c r="X39" s="57" t="s">
         <v>462</v>
       </c>
-      <c r="X39" s="57" t="s">
+      <c r="Y39" s="50" t="s">
         <v>463</v>
-      </c>
-      <c r="Y39" s="50" t="s">
-        <v>464</v>
       </c>
       <c r="Z39" s="50" t="s">
         <v>198</v>
       </c>
       <c r="AA39" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AB39" s="64"/>
       <c r="AC39" s="64"/>
       <c r="AD39" s="50" t="s">
+        <v>465</v>
+      </c>
+      <c r="AE39" s="64" t="s">
         <v>466</v>
       </c>
-      <c r="AE39" s="64" t="s">
+      <c r="AF39" s="64" t="s">
         <v>467</v>
-      </c>
-      <c r="AF39" s="64" t="s">
-        <v>468</v>
       </c>
       <c r="AG39" s="64"/>
       <c r="AH39" s="58" t="s">
@@ -7342,13 +7414,13 @@
         <v>7</v>
       </c>
       <c r="D40" s="47" t="s">
+        <v>468</v>
+      </c>
+      <c r="E40" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="E40" s="47" t="s">
+      <c r="F40" s="77" t="s">
         <v>470</v>
-      </c>
-      <c r="F40" s="77" t="s">
-        <v>471</v>
       </c>
       <c r="G40" s="48" t="s">
         <v>117</v>
@@ -7363,10 +7435,10 @@
         <v>102</v>
       </c>
       <c r="K40" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="L40" s="47" t="s">
         <v>431</v>
-      </c>
-      <c r="L40" s="47" t="s">
-        <v>432</v>
       </c>
       <c r="M40" s="49" t="s">
         <v>121</v>
@@ -7375,7 +7447,7 @@
         <v>43</v>
       </c>
       <c r="O40" s="47" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P40" s="52">
         <v>5</v>
@@ -7395,19 +7467,19 @@
         <v>44</v>
       </c>
       <c r="W40" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="X40" s="77" t="s">
         <v>473</v>
       </c>
-      <c r="X40" s="77" t="s">
+      <c r="Y40" s="49" t="s">
         <v>474</v>
       </c>
-      <c r="Y40" s="49" t="s">
+      <c r="Z40" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA40" s="49" t="s">
         <v>475</v>
-      </c>
-      <c r="Z40" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA40" s="49" t="s">
-        <v>476</v>
       </c>
       <c r="AB40" s="49"/>
       <c r="AC40" s="49"/>
@@ -7415,10 +7487,10 @@
         <v>259</v>
       </c>
       <c r="AE40" s="49" t="s">
+        <v>476</v>
+      </c>
+      <c r="AF40" s="49" t="s">
         <v>477</v>
-      </c>
-      <c r="AF40" s="49" t="s">
-        <v>478</v>
       </c>
       <c r="AG40" s="49"/>
       <c r="AH40" s="58" t="s">
@@ -7437,13 +7509,13 @@
         <v>6</v>
       </c>
       <c r="D41" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="E41" s="23" t="s">
         <v>479</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="F41" s="81" t="s">
         <v>480</v>
-      </c>
-      <c r="F41" s="81" t="s">
-        <v>481</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>145</v>
@@ -7470,7 +7542,7 @@
         <v>43</v>
       </c>
       <c r="O41" s="23" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P41" s="26">
         <v>6</v>
@@ -7490,26 +7562,26 @@
         <v>43</v>
       </c>
       <c r="W41" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="X41" s="81" t="s">
         <v>483</v>
-      </c>
-      <c r="X41" s="81" t="s">
-        <v>484</v>
       </c>
       <c r="Y41" s="24"/>
       <c r="Z41" s="24" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA41" s="24"/>
       <c r="AB41" s="24"/>
       <c r="AC41" s="24"/>
       <c r="AD41" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="AE41" s="24" t="s">
         <v>485</v>
       </c>
-      <c r="AE41" s="24" t="s">
+      <c r="AF41" s="24" t="s">
         <v>486</v>
-      </c>
-      <c r="AF41" s="24" t="s">
-        <v>487</v>
       </c>
       <c r="AG41" s="24"/>
       <c r="AH41" s="32" t="s">
@@ -7527,31 +7599,31 @@
         <v>0</v>
       </c>
       <c r="D42" s="47" t="s">
+        <v>487</v>
+      </c>
+      <c r="E42" s="47" t="s">
         <v>488</v>
       </c>
-      <c r="E42" s="47" t="s">
+      <c r="F42" s="77" t="s">
         <v>489</v>
       </c>
-      <c r="F42" s="77" t="s">
+      <c r="G42" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="H42" s="49" t="s">
         <v>491</v>
       </c>
-      <c r="H42" s="49" t="s">
+      <c r="I42" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" s="50" t="s">
         <v>492</v>
       </c>
-      <c r="I42" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" s="50" t="s">
+      <c r="K42" s="47" t="s">
         <v>493</v>
       </c>
-      <c r="K42" s="47" t="s">
+      <c r="L42" s="47" t="s">
         <v>494</v>
-      </c>
-      <c r="L42" s="47" t="s">
-        <v>495</v>
       </c>
       <c r="M42" s="49" t="s">
         <v>55</v>
@@ -7560,7 +7632,7 @@
         <v>43</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P42" s="52">
         <v>7</v>
@@ -7572,7 +7644,7 @@
         <v>44</v>
       </c>
       <c r="S42" s="53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T42" s="53"/>
       <c r="U42" s="71"/>
@@ -7583,27 +7655,27 @@
         <v>41</v>
       </c>
       <c r="X42" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y42" s="49" t="s">
         <v>497</v>
-      </c>
-      <c r="Y42" s="49" t="s">
-        <v>498</v>
       </c>
       <c r="Z42" s="49" t="s">
         <v>198</v>
       </c>
       <c r="AA42" s="49" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AB42" s="49"/>
       <c r="AC42" s="49"/>
       <c r="AD42" s="49" t="s">
+        <v>499</v>
+      </c>
+      <c r="AE42" s="49" t="s">
         <v>500</v>
       </c>
-      <c r="AE42" s="49" t="s">
+      <c r="AF42" s="49" t="s">
         <v>501</v>
-      </c>
-      <c r="AF42" s="49" t="s">
-        <v>502</v>
       </c>
       <c r="AG42" s="49"/>
       <c r="AH42" s="58" t="s">
@@ -7622,16 +7694,16 @@
         <v>0</v>
       </c>
       <c r="D43" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="E43" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="F43" s="81" t="s">
         <v>504</v>
       </c>
-      <c r="F43" s="81" t="s">
+      <c r="G43" s="25" t="s">
         <v>505</v>
-      </c>
-      <c r="G43" s="25" t="s">
-        <v>506</v>
       </c>
       <c r="H43" s="24" t="s">
         <v>118</v>
@@ -7643,7 +7715,7 @@
         <v>41</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L43" s="25"/>
       <c r="M43" s="24" t="s">
@@ -7653,7 +7725,7 @@
         <v>43</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="P43" s="23">
         <v>6</v>
@@ -7665,7 +7737,7 @@
         <v>44</v>
       </c>
       <c r="S43" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" s="28"/>
       <c r="U43" s="34"/>
@@ -7674,7 +7746,7 @@
       </c>
       <c r="W43" s="24"/>
       <c r="X43" s="24" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Y43" s="24" t="s">
         <v>41</v>
@@ -7687,15 +7759,16 @@
       <c r="AC43" s="24"/>
       <c r="AD43" s="24"/>
       <c r="AE43" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="AF43" s="24" t="s">
         <v>510</v>
-      </c>
-      <c r="AF43" s="24" t="s">
-        <v>511</v>
       </c>
       <c r="AG43" s="24"/>
       <c r="AH43" s="24" t="s">
         <v>48</v>
       </c>
+      <c r="AI43"/>
     </row>
     <row r="44" spans="1:35" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="38" t="s">
@@ -7708,16 +7781,16 @@
         <v>0</v>
       </c>
       <c r="D44" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="E44" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="F44" s="24" t="s">
         <v>513</v>
       </c>
-      <c r="F44" s="24" t="s">
+      <c r="G44" s="25" t="s">
         <v>514</v>
-      </c>
-      <c r="G44" s="25" t="s">
-        <v>515</v>
       </c>
       <c r="H44" s="24" t="s">
         <v>361</v>
@@ -7729,10 +7802,10 @@
         <v>102</v>
       </c>
       <c r="K44" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="L44" s="23" t="s">
         <v>516</v>
-      </c>
-      <c r="L44" s="23" t="s">
-        <v>517</v>
       </c>
       <c r="M44" s="24" t="s">
         <v>55</v>
@@ -7761,13 +7834,13 @@
         <v>43</v>
       </c>
       <c r="W44" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="X44" s="81" t="s">
         <v>518</v>
       </c>
-      <c r="X44" s="81" t="s">
+      <c r="Y44" s="24" t="s">
         <v>519</v>
-      </c>
-      <c r="Y44" s="24" t="s">
-        <v>520</v>
       </c>
       <c r="Z44" s="24" t="s">
         <v>216</v>
@@ -7776,13 +7849,13 @@
       <c r="AB44" s="24"/>
       <c r="AC44" s="24"/>
       <c r="AD44" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="AE44" s="24" t="s">
         <v>521</v>
       </c>
-      <c r="AE44" s="24" t="s">
+      <c r="AF44" s="24" t="s">
         <v>522</v>
-      </c>
-      <c r="AF44" s="24" t="s">
-        <v>523</v>
       </c>
       <c r="AG44" s="24"/>
       <c r="AH44" s="24" t="s">
@@ -7800,16 +7873,16 @@
         <v>0</v>
       </c>
       <c r="D45" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="E45" s="23" t="s">
         <v>524</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="F45" s="81" t="s">
         <v>525</v>
       </c>
-      <c r="F45" s="81" t="s">
+      <c r="G45" s="25" t="s">
         <v>526</v>
-      </c>
-      <c r="G45" s="25" t="s">
-        <v>527</v>
       </c>
       <c r="H45" s="24" t="s">
         <v>101</v>
@@ -7821,7 +7894,7 @@
         <v>73</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L45" s="23" t="s">
         <v>276</v>
@@ -7833,7 +7906,7 @@
         <v>43</v>
       </c>
       <c r="O45" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P45" s="23">
         <v>7</v>
@@ -7856,10 +7929,10 @@
         <v>41</v>
       </c>
       <c r="X45" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y45" s="24" t="s">
         <v>530</v>
-      </c>
-      <c r="Y45" s="24" t="s">
-        <v>531</v>
       </c>
       <c r="Z45" s="24" t="s">
         <v>198</v>
@@ -7869,10 +7942,10 @@
       <c r="AC45" s="24"/>
       <c r="AD45" s="24"/>
       <c r="AE45" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="AF45" s="24" t="s">
         <v>532</v>
-      </c>
-      <c r="AF45" s="24" t="s">
-        <v>533</v>
       </c>
       <c r="AG45" s="24"/>
       <c r="AH45" s="24" t="s">
@@ -7890,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="D46" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="E46" s="23" t="s">
         <v>534</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="F46" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="F46" s="24" t="s">
-        <v>536</v>
-      </c>
       <c r="G46" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H46" s="24" t="s">
         <v>361</v>
@@ -7911,10 +7984,10 @@
         <v>102</v>
       </c>
       <c r="K46" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="L46" s="23" t="s">
         <v>516</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>517</v>
       </c>
       <c r="M46" s="24" t="s">
         <v>55</v>
@@ -7923,7 +7996,7 @@
         <v>43</v>
       </c>
       <c r="O46" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P46" s="36">
         <v>6</v>
@@ -7935,7 +8008,7 @@
         <v>44</v>
       </c>
       <c r="S46" s="28">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T46" s="28"/>
       <c r="U46" s="34"/>
@@ -7943,13 +8016,13 @@
         <v>43</v>
       </c>
       <c r="W46" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="X46" s="81" t="s">
         <v>538</v>
       </c>
-      <c r="X46" s="81" t="s">
+      <c r="Y46" s="24" t="s">
         <v>539</v>
-      </c>
-      <c r="Y46" s="24" t="s">
-        <v>540</v>
       </c>
       <c r="Z46" s="24" t="s">
         <v>216</v>
@@ -7959,10 +8032,10 @@
       <c r="AC46" s="24"/>
       <c r="AD46" s="24"/>
       <c r="AE46" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="AF46" s="24" t="s">
         <v>541</v>
-      </c>
-      <c r="AF46" s="24" t="s">
-        <v>542</v>
       </c>
       <c r="AG46" s="24"/>
       <c r="AH46" s="24" t="s">
@@ -7978,34 +8051,34 @@
         <v>2025</v>
       </c>
       <c r="D47" s="36" t="s">
+        <v>542</v>
+      </c>
+      <c r="E47" s="36" t="s">
         <v>543</v>
       </c>
-      <c r="E47" s="36" t="s">
+      <c r="F47" s="37" t="s">
         <v>544</v>
       </c>
-      <c r="F47" s="37" t="s">
+      <c r="G47" s="36" t="s">
         <v>545</v>
-      </c>
-      <c r="G47" s="36" t="s">
-        <v>546</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>118</v>
       </c>
       <c r="I47" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="J47" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="M47" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N47" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O47" s="36" t="s">
         <v>547</v>
-      </c>
-      <c r="J47" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="M47" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="N47" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="O47" s="36" t="s">
-        <v>548</v>
       </c>
       <c r="P47" s="88">
         <v>5</v>
@@ -8023,22 +8096,22 @@
         <v>43</v>
       </c>
       <c r="W47" s="89" t="s">
+        <v>548</v>
+      </c>
+      <c r="X47" s="81" t="s">
         <v>549</v>
       </c>
-      <c r="X47" s="81" t="s">
+      <c r="Y47" s="38" t="s">
         <v>550</v>
       </c>
-      <c r="Y47" s="38" t="s">
+      <c r="Z47" s="38" t="s">
         <v>551</v>
       </c>
-      <c r="Z47" s="38" t="s">
+      <c r="AE47" s="38" t="s">
         <v>552</v>
       </c>
-      <c r="AE47" s="38" t="s">
+      <c r="AF47" s="38" t="s">
         <v>553</v>
-      </c>
-      <c r="AF47" s="38" t="s">
-        <v>554</v>
       </c>
       <c r="AH47" s="38" t="s">
         <v>48</v>
@@ -8052,22 +8125,22 @@
         <v>2025</v>
       </c>
       <c r="D48" s="36" t="s">
+        <v>554</v>
+      </c>
+      <c r="E48" s="36" t="s">
         <v>555</v>
       </c>
-      <c r="E48" s="36" t="s">
+      <c r="F48" s="37" t="s">
         <v>556</v>
       </c>
-      <c r="F48" s="37" t="s">
-        <v>557</v>
-      </c>
       <c r="G48" s="36" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H48" s="38" t="s">
         <v>118</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J48" s="38" t="s">
         <v>41</v>
@@ -8079,7 +8152,7 @@
         <v>41</v>
       </c>
       <c r="O48" s="36" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P48" s="88">
         <v>5</v>
@@ -8097,7 +8170,7 @@
         <v>43</v>
       </c>
       <c r="W48" s="89" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Y48" s="38" t="s">
         <v>41</v>
@@ -8106,10 +8179,10 @@
         <v>198</v>
       </c>
       <c r="AE48" s="38" t="s">
+        <v>559</v>
+      </c>
+      <c r="AF48" s="38" t="s">
         <v>560</v>
-      </c>
-      <c r="AF48" s="38" t="s">
-        <v>561</v>
       </c>
       <c r="AH48" s="38" t="s">
         <v>48</v>
@@ -8124,22 +8197,22 @@
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="62" t="s">
+        <v>561</v>
+      </c>
+      <c r="E49" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="63" t="s">
         <v>562</v>
       </c>
-      <c r="E49" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="F49" s="63" t="s">
+      <c r="G49" s="62" t="s">
         <v>563</v>
       </c>
-      <c r="G49" s="62" t="s">
+      <c r="H49" s="64" t="s">
         <v>564</v>
       </c>
-      <c r="H49" s="64" t="s">
+      <c r="I49" s="79" t="s">
         <v>565</v>
-      </c>
-      <c r="I49" s="79" t="s">
-        <v>566</v>
       </c>
       <c r="J49" s="64" t="s">
         <v>41</v>
@@ -8153,7 +8226,7 @@
         <v>41</v>
       </c>
       <c r="O49" s="62" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="P49" s="64">
         <v>4</v>
@@ -8189,10 +8262,10 @@
       <c r="AC49" s="64"/>
       <c r="AD49" s="64"/>
       <c r="AE49" s="64" t="s">
+        <v>567</v>
+      </c>
+      <c r="AF49" s="64" t="s">
         <v>568</v>
-      </c>
-      <c r="AF49" s="64" t="s">
-        <v>569</v>
       </c>
       <c r="AG49" s="64"/>
       <c r="AH49" s="64" t="s">
@@ -8208,34 +8281,34 @@
         <v>2025</v>
       </c>
       <c r="D50" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="E50" s="36" t="s">
         <v>570</v>
       </c>
-      <c r="E50" s="36" t="s">
+      <c r="F50" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="F50" s="41" t="s">
+      <c r="G50" s="36" t="s">
         <v>572</v>
       </c>
-      <c r="G50" s="36" t="s">
+      <c r="H50" s="38" t="s">
         <v>573</v>
       </c>
-      <c r="H50" s="38" t="s">
+      <c r="I50" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="J50" s="38" t="s">
         <v>574</v>
       </c>
-      <c r="I50" s="39" t="s">
-        <v>547</v>
-      </c>
-      <c r="J50" s="38" t="s">
+      <c r="M50" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N50" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O50" s="36" t="s">
         <v>575</v>
-      </c>
-      <c r="M50" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="N50" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="O50" s="36" t="s">
-        <v>576</v>
       </c>
       <c r="P50" s="38">
         <v>25</v>
@@ -8253,22 +8326,22 @@
         <v>44</v>
       </c>
       <c r="W50" s="38" t="s">
+        <v>576</v>
+      </c>
+      <c r="X50" s="81" t="s">
         <v>577</v>
       </c>
-      <c r="X50" s="81" t="s">
+      <c r="Y50" s="38" t="s">
         <v>578</v>
       </c>
-      <c r="Y50" s="38" t="s">
+      <c r="Z50" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE50" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="Z50" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE50" s="38" t="s">
+      <c r="AF50" s="38" t="s">
         <v>580</v>
-      </c>
-      <c r="AF50" s="38" t="s">
-        <v>581</v>
       </c>
       <c r="AH50" s="38" t="s">
         <v>48</v>
@@ -8283,22 +8356,22 @@
       </c>
       <c r="C51" s="29"/>
       <c r="D51" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="E51" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="E51" s="62" t="s">
+      <c r="F51" s="72" t="s">
         <v>583</v>
       </c>
-      <c r="F51" s="72" t="s">
+      <c r="G51" s="62" t="s">
         <v>584</v>
       </c>
-      <c r="G51" s="62" t="s">
-        <v>585</v>
-      </c>
       <c r="H51" s="64" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I51" s="65" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J51" s="64" t="s">
         <v>41</v>
@@ -8312,7 +8385,7 @@
         <v>41</v>
       </c>
       <c r="O51" s="62" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P51" s="64">
         <v>6</v>
@@ -8324,7 +8397,7 @@
         <v>44</v>
       </c>
       <c r="S51" s="66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" s="66"/>
       <c r="U51" s="67"/>
@@ -8332,10 +8405,10 @@
         <v>44</v>
       </c>
       <c r="W51" s="64" t="s">
+        <v>586</v>
+      </c>
+      <c r="X51" s="77" t="s">
         <v>587</v>
-      </c>
-      <c r="X51" s="77" t="s">
-        <v>588</v>
       </c>
       <c r="Y51" s="64" t="s">
         <v>41</v>
@@ -8350,10 +8423,10 @@
       <c r="AC51" s="64"/>
       <c r="AD51" s="64"/>
       <c r="AE51" s="64" t="s">
+        <v>588</v>
+      </c>
+      <c r="AF51" s="64" t="s">
         <v>589</v>
-      </c>
-      <c r="AF51" s="64" t="s">
-        <v>590</v>
       </c>
       <c r="AG51" s="64"/>
       <c r="AH51" s="49" t="s">
@@ -8370,22 +8443,22 @@
       </c>
       <c r="C52" s="29"/>
       <c r="D52" s="62" t="s">
+        <v>590</v>
+      </c>
+      <c r="E52" s="62" t="s">
         <v>591</v>
       </c>
-      <c r="E52" s="62" t="s">
+      <c r="F52" s="72" t="s">
         <v>592</v>
       </c>
-      <c r="F52" s="72" t="s">
+      <c r="G52" s="62" t="s">
         <v>593</v>
-      </c>
-      <c r="G52" s="62" t="s">
-        <v>594</v>
       </c>
       <c r="H52" s="64" t="s">
         <v>118</v>
       </c>
       <c r="I52" s="65" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J52" s="64" t="s">
         <v>41</v>
@@ -8399,7 +8472,7 @@
         <v>41</v>
       </c>
       <c r="O52" s="62" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P52" s="64">
         <v>6</v>
@@ -8411,7 +8484,7 @@
         <v>43</v>
       </c>
       <c r="S52" s="66">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T52" s="66"/>
       <c r="U52" s="67"/>
@@ -8419,13 +8492,13 @@
         <v>43</v>
       </c>
       <c r="W52" s="64" t="s">
+        <v>596</v>
+      </c>
+      <c r="X52" s="77" t="s">
         <v>597</v>
       </c>
-      <c r="X52" s="77" t="s">
+      <c r="Y52" s="64" t="s">
         <v>598</v>
-      </c>
-      <c r="Y52" s="64" t="s">
-        <v>599</v>
       </c>
       <c r="Z52" s="64" t="s">
         <v>41</v>
@@ -8437,10 +8510,10 @@
       <c r="AC52" s="64"/>
       <c r="AD52" s="64"/>
       <c r="AE52" s="64" t="s">
+        <v>599</v>
+      </c>
+      <c r="AF52" s="64" t="s">
         <v>600</v>
-      </c>
-      <c r="AF52" s="64" t="s">
-        <v>601</v>
       </c>
       <c r="AG52" s="64"/>
       <c r="AH52" s="64" t="s">
@@ -8456,34 +8529,34 @@
         <v>2025</v>
       </c>
       <c r="D53" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="E53" s="36" t="s">
         <v>602</v>
       </c>
-      <c r="E53" s="36" t="s">
+      <c r="F53" s="89" t="s">
         <v>603</v>
       </c>
-      <c r="F53" s="89" t="s">
+      <c r="G53" s="36" t="s">
         <v>604</v>
-      </c>
-      <c r="G53" s="36" t="s">
-        <v>605</v>
       </c>
       <c r="H53" s="38" t="s">
         <v>118</v>
       </c>
       <c r="I53" s="39" t="s">
+        <v>605</v>
+      </c>
+      <c r="J53" s="38" t="s">
         <v>606</v>
       </c>
-      <c r="J53" s="38" t="s">
+      <c r="M53" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N53" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O53" s="36" t="s">
         <v>607</v>
-      </c>
-      <c r="M53" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="N53" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="O53" s="36" t="s">
-        <v>608</v>
       </c>
       <c r="P53" s="38">
         <v>6</v>
@@ -8513,10 +8586,10 @@
         <v>41</v>
       </c>
       <c r="AE53" s="38" t="s">
+        <v>608</v>
+      </c>
+      <c r="AF53" s="38" t="s">
         <v>609</v>
-      </c>
-      <c r="AF53" s="38" t="s">
-        <v>610</v>
       </c>
       <c r="AH53" s="24" t="s">
         <v>48</v>
@@ -8531,22 +8604,22 @@
       </c>
       <c r="C54" s="29"/>
       <c r="D54" s="62" t="s">
+        <v>610</v>
+      </c>
+      <c r="E54" s="62" t="s">
         <v>611</v>
       </c>
-      <c r="E54" s="62" t="s">
+      <c r="F54" s="63" t="s">
         <v>612</v>
       </c>
-      <c r="F54" s="63" t="s">
+      <c r="G54" s="62" t="s">
         <v>613</v>
-      </c>
-      <c r="G54" s="62" t="s">
-        <v>614</v>
       </c>
       <c r="H54" s="64" t="s">
         <v>344</v>
       </c>
       <c r="I54" s="65" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J54" s="64" t="s">
         <v>41</v>
@@ -8560,7 +8633,7 @@
         <v>41</v>
       </c>
       <c r="O54" s="62" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P54" s="64">
         <v>6</v>
@@ -8598,10 +8671,10 @@
       <c r="AC54" s="64"/>
       <c r="AD54" s="64"/>
       <c r="AE54" s="64" t="s">
+        <v>616</v>
+      </c>
+      <c r="AF54" s="64" t="s">
         <v>617</v>
-      </c>
-      <c r="AF54" s="64" t="s">
-        <v>618</v>
       </c>
       <c r="AG54" s="64"/>
       <c r="AH54" s="64" t="s">
@@ -8618,13 +8691,13 @@
       </c>
       <c r="C55" s="29"/>
       <c r="D55" s="62" t="s">
+        <v>618</v>
+      </c>
+      <c r="E55" s="62" t="s">
         <v>619</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="F55" s="63" t="s">
         <v>620</v>
-      </c>
-      <c r="F55" s="63" t="s">
-        <v>621</v>
       </c>
       <c r="G55" s="65" t="s">
         <v>101</v>
@@ -8647,7 +8720,7 @@
         <v>41</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P55" s="64">
         <v>4</v>
@@ -8685,10 +8758,10 @@
       <c r="AC55" s="64"/>
       <c r="AD55" s="64"/>
       <c r="AE55" s="64" t="s">
+        <v>622</v>
+      </c>
+      <c r="AF55" s="64" t="s">
         <v>623</v>
-      </c>
-      <c r="AF55" s="64" t="s">
-        <v>624</v>
       </c>
       <c r="AG55" s="64"/>
       <c r="AH55" s="64" t="s">
@@ -8705,13 +8778,13 @@
       </c>
       <c r="C56" s="29"/>
       <c r="D56" s="62" t="s">
+        <v>624</v>
+      </c>
+      <c r="E56" s="62" t="s">
         <v>625</v>
       </c>
-      <c r="E56" s="62" t="s">
+      <c r="F56" s="63" t="s">
         <v>626</v>
-      </c>
-      <c r="F56" s="63" t="s">
-        <v>627</v>
       </c>
       <c r="G56" s="62" t="s">
         <v>369</v>
@@ -8734,7 +8807,7 @@
         <v>41</v>
       </c>
       <c r="O56" s="62" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P56" s="64">
         <v>6</v>
@@ -8757,7 +8830,7 @@
         <v>41</v>
       </c>
       <c r="X56" s="64" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="Y56" s="64" t="s">
         <v>41</v>
@@ -8772,10 +8845,10 @@
       <c r="AC56" s="64"/>
       <c r="AD56" s="64"/>
       <c r="AE56" s="64" t="s">
+        <v>629</v>
+      </c>
+      <c r="AF56" s="64" t="s">
         <v>630</v>
-      </c>
-      <c r="AF56" s="64" t="s">
-        <v>631</v>
       </c>
       <c r="AG56" s="64"/>
       <c r="AH56" s="64" t="s">
@@ -8792,13 +8865,13 @@
       </c>
       <c r="C57" s="29"/>
       <c r="D57" s="62" t="s">
+        <v>631</v>
+      </c>
+      <c r="E57" s="62" t="s">
         <v>632</v>
       </c>
-      <c r="E57" s="62" t="s">
+      <c r="F57" s="63" t="s">
         <v>633</v>
-      </c>
-      <c r="F57" s="63" t="s">
-        <v>634</v>
       </c>
       <c r="G57" s="62" t="s">
         <v>369</v>
@@ -8821,7 +8894,7 @@
         <v>41</v>
       </c>
       <c r="O57" s="62" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="P57" s="64">
         <v>3</v>
@@ -8844,7 +8917,7 @@
         <v>41</v>
       </c>
       <c r="X57" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="Y57" s="64" t="s">
         <v>41</v>
@@ -8859,10 +8932,10 @@
       <c r="AC57" s="64"/>
       <c r="AD57" s="64"/>
       <c r="AE57" s="64" t="s">
+        <v>635</v>
+      </c>
+      <c r="AF57" s="64" t="s">
         <v>636</v>
-      </c>
-      <c r="AF57" s="64" t="s">
-        <v>637</v>
       </c>
       <c r="AG57" s="64"/>
       <c r="AH57" s="64" t="s">
@@ -8872,28 +8945,28 @@
     </row>
     <row r="58" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B58" s="29">
         <v>2025</v>
       </c>
       <c r="D58" s="38" t="s">
+        <v>637</v>
+      </c>
+      <c r="E58" s="38" t="s">
         <v>638</v>
       </c>
-      <c r="E58" s="38" t="s">
+      <c r="F58" s="81" t="s">
         <v>639</v>
       </c>
-      <c r="F58" s="81" t="s">
+      <c r="G58" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H58" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O58" s="38" t="s">
         <v>640</v>
-      </c>
-      <c r="G58" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H58" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O58" s="38" t="s">
-        <v>641</v>
       </c>
       <c r="P58" s="29">
         <v>4</v>
@@ -8911,48 +8984,48 @@
         <v>44</v>
       </c>
       <c r="W58" s="38" t="s">
+        <v>641</v>
+      </c>
+      <c r="Y58" s="38" t="s">
         <v>642</v>
       </c>
-      <c r="Y58" s="38" t="s">
+      <c r="Z58" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE58" s="38" t="s">
         <v>643</v>
       </c>
-      <c r="Z58" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE58" s="38" t="s">
+      <c r="AF58" s="38" t="s">
         <v>644</v>
       </c>
-      <c r="AF58" s="38" t="s">
+      <c r="AH58" s="38" t="s">
         <v>645</v>
-      </c>
-      <c r="AH58" s="38" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B59" s="29">
         <v>2025</v>
       </c>
       <c r="D59" s="38" t="s">
+        <v>646</v>
+      </c>
+      <c r="E59" s="38" t="s">
         <v>647</v>
       </c>
-      <c r="E59" s="38" t="s">
+      <c r="F59" s="38" t="s">
         <v>648</v>
       </c>
-      <c r="F59" s="38" t="s">
+      <c r="G59" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H59" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O59" s="38" t="s">
         <v>649</v>
-      </c>
-      <c r="G59" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H59" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O59" s="38" t="s">
-        <v>650</v>
       </c>
       <c r="P59" s="29">
         <v>6</v>
@@ -8970,27 +9043,27 @@
         <v>44</v>
       </c>
       <c r="W59" s="38" t="s">
+        <v>650</v>
+      </c>
+      <c r="Y59" s="38" t="s">
         <v>651</v>
       </c>
-      <c r="Y59" s="38" t="s">
+      <c r="Z59" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="AE59" s="38" t="s">
         <v>652</v>
       </c>
-      <c r="Z59" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="AE59" s="38" t="s">
+      <c r="AF59" s="38" t="s">
         <v>653</v>
       </c>
-      <c r="AF59" s="38" t="s">
+      <c r="AH59" s="38" t="s">
         <v>654</v>
-      </c>
-      <c r="AH59" s="38" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B60" s="29">
         <v>2025</v>
@@ -9005,10 +9078,10 @@
         <v>657</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="O60" s="38" t="s">
         <v>658</v>
@@ -9023,7 +9096,7 @@
         <v>44</v>
       </c>
       <c r="S60" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V60" s="38" t="s">
         <v>44</v>
@@ -9046,6 +9119,7 @@
       <c r="AH60" s="38" t="s">
         <v>664</v>
       </c>
+      <c r="AI60"/>
     </row>
     <row r="61" spans="1:35" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="38" t="s">
@@ -9284,7 +9358,7 @@
         <v>44</v>
       </c>
       <c r="S63" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" s="28"/>
       <c r="U63" s="34"/>
@@ -9317,6 +9391,7 @@
       <c r="AH63" s="24" t="s">
         <v>48</v>
       </c>
+      <c r="AI63"/>
     </row>
     <row r="64" spans="1:35" s="55" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="79" t="s">
@@ -9468,16 +9543,16 @@
         <v>717</v>
       </c>
       <c r="Z65" s="38" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AA65" s="38" t="s">
+        <v>788</v>
+      </c>
+      <c r="AE65" s="38" t="s">
         <v>718</v>
       </c>
-      <c r="AE65" s="38" t="s">
+      <c r="AF65" s="38" t="s">
         <v>719</v>
-      </c>
-      <c r="AF65" s="38" t="s">
-        <v>720</v>
       </c>
       <c r="AH65" s="24" t="s">
         <v>48</v>
@@ -9485,28 +9560,28 @@
     </row>
     <row r="66" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B66" s="29">
         <v>2026</v>
       </c>
       <c r="D66" s="38" t="s">
+        <v>720</v>
+      </c>
+      <c r="E66" s="38" t="s">
         <v>721</v>
       </c>
-      <c r="E66" s="38" t="s">
+      <c r="F66" s="38" t="s">
         <v>722</v>
       </c>
-      <c r="F66" s="38" t="s">
+      <c r="G66" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H66" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O66" s="38" t="s">
         <v>723</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H66" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O66" s="38" t="s">
-        <v>724</v>
       </c>
       <c r="P66" s="38">
         <v>5</v>
@@ -9524,22 +9599,22 @@
         <v>44</v>
       </c>
       <c r="W66" s="38" t="s">
+        <v>724</v>
+      </c>
+      <c r="X66" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y66" s="38" t="s">
         <v>725</v>
       </c>
-      <c r="X66" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y66" s="38" t="s">
+      <c r="Z66" s="38" t="s">
         <v>726</v>
       </c>
-      <c r="Z66" s="38" t="s">
+      <c r="AE66" s="38" t="s">
         <v>727</v>
       </c>
-      <c r="AE66" s="38" t="s">
+      <c r="AF66" s="38" t="s">
         <v>728</v>
-      </c>
-      <c r="AF66" s="38" t="s">
-        <v>729</v>
       </c>
       <c r="AH66" s="38" t="s">
         <v>48</v>
@@ -9547,28 +9622,28 @@
     </row>
     <row r="67" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B67" s="29">
         <v>2026</v>
       </c>
       <c r="D67" s="38" t="s">
+        <v>729</v>
+      </c>
+      <c r="E67" s="38" t="s">
         <v>730</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="F67" s="38" t="s">
         <v>731</v>
       </c>
-      <c r="F67" s="38" t="s">
+      <c r="G67" s="38" t="s">
         <v>732</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="H67" s="38" t="s">
+        <v>732</v>
+      </c>
+      <c r="O67" s="38" t="s">
         <v>733</v>
-      </c>
-      <c r="H67" s="38" t="s">
-        <v>733</v>
-      </c>
-      <c r="O67" s="38" t="s">
-        <v>734</v>
       </c>
       <c r="P67" s="29">
         <v>5</v>
@@ -9586,39 +9661,39 @@
         <v>44</v>
       </c>
       <c r="W67" s="38" t="s">
+        <v>734</v>
+      </c>
+      <c r="AE67" s="38" t="s">
         <v>735</v>
       </c>
-      <c r="AE67" s="38" t="s">
+      <c r="AF67" s="38" t="s">
         <v>736</v>
-      </c>
-      <c r="AF67" s="38" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="68" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B68" s="29">
         <v>2026</v>
       </c>
       <c r="D68" s="38" t="s">
+        <v>737</v>
+      </c>
+      <c r="E68" s="38" t="s">
         <v>738</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="F68" s="38" t="s">
         <v>739</v>
       </c>
-      <c r="F68" s="38" t="s">
+      <c r="G68" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H68" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O68" s="38" t="s">
         <v>740</v>
-      </c>
-      <c r="G68" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H68" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O68" s="38" t="s">
-        <v>741</v>
       </c>
       <c r="P68" s="29">
         <v>5</v>
@@ -9636,39 +9711,39 @@
         <v>44</v>
       </c>
       <c r="W68" s="38" t="s">
+        <v>741</v>
+      </c>
+      <c r="AE68" s="38" t="s">
         <v>742</v>
       </c>
-      <c r="AE68" s="38" t="s">
+      <c r="AF68" s="38" t="s">
         <v>743</v>
-      </c>
-      <c r="AF68" s="38" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="69" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B69" s="29">
         <v>2026</v>
       </c>
       <c r="D69" s="38" t="s">
+        <v>744</v>
+      </c>
+      <c r="E69" s="38" t="s">
         <v>745</v>
       </c>
-      <c r="E69" s="38" t="s">
+      <c r="F69" s="38" t="s">
         <v>746</v>
       </c>
-      <c r="F69" s="38" t="s">
+      <c r="G69" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H69" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O69" s="38" t="s">
         <v>747</v>
-      </c>
-      <c r="G69" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H69" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O69" s="38" t="s">
-        <v>748</v>
       </c>
       <c r="P69" s="29">
         <v>5</v>
@@ -9686,39 +9761,39 @@
         <v>44</v>
       </c>
       <c r="W69" s="38" t="s">
+        <v>748</v>
+      </c>
+      <c r="AE69" s="38" t="s">
         <v>749</v>
       </c>
-      <c r="AE69" s="38" t="s">
+      <c r="AF69" s="38" t="s">
         <v>750</v>
-      </c>
-      <c r="AF69" s="38" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="70" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B70" s="29">
         <v>2026</v>
       </c>
       <c r="D70" s="38" t="s">
+        <v>751</v>
+      </c>
+      <c r="E70" s="38" t="s">
         <v>752</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="F70" s="38" t="s">
         <v>753</v>
       </c>
-      <c r="F70" s="38" t="s">
+      <c r="G70" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H70" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O70" s="38" t="s">
         <v>754</v>
-      </c>
-      <c r="G70" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H70" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O70" s="38" t="s">
-        <v>755</v>
       </c>
       <c r="P70" s="29">
         <v>4</v>
@@ -9736,39 +9811,39 @@
         <v>44</v>
       </c>
       <c r="W70" s="38" t="s">
+        <v>755</v>
+      </c>
+      <c r="AE70" s="38" t="s">
         <v>756</v>
       </c>
-      <c r="AE70" s="38" t="s">
+      <c r="AF70" s="38" t="s">
         <v>757</v>
-      </c>
-      <c r="AF70" s="38" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="71" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B71" s="29">
         <v>2026</v>
       </c>
       <c r="D71" s="38" t="s">
+        <v>758</v>
+      </c>
+      <c r="E71" s="38" t="s">
         <v>759</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="F71" s="38" t="s">
         <v>760</v>
       </c>
-      <c r="F71" s="38" t="s">
+      <c r="G71" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="H71" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="O71" s="38" t="s">
         <v>761</v>
-      </c>
-      <c r="G71" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="H71" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="O71" s="38" t="s">
-        <v>762</v>
       </c>
       <c r="P71" s="29">
         <v>7</v>
@@ -9786,13 +9861,13 @@
         <v>44</v>
       </c>
       <c r="W71" s="38" t="s">
+        <v>762</v>
+      </c>
+      <c r="AE71" s="38" t="s">
         <v>763</v>
       </c>
-      <c r="AE71" s="38" t="s">
+      <c r="AF71" s="38" t="s">
         <v>764</v>
-      </c>
-      <c r="AF71" s="38" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="72" spans="1:35" s="55" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -9804,19 +9879,19 @@
       </c>
       <c r="C72" s="29"/>
       <c r="D72" s="64" t="s">
+        <v>765</v>
+      </c>
+      <c r="E72" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="E72" s="64" t="s">
+      <c r="F72" s="77" t="s">
         <v>767</v>
       </c>
-      <c r="F72" s="77" t="s">
+      <c r="G72" s="64" t="s">
         <v>768</v>
       </c>
-      <c r="G72" s="64" t="s">
-        <v>769</v>
-      </c>
       <c r="H72" s="64" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I72" s="64" t="s">
         <v>41</v>
@@ -9833,7 +9908,7 @@
         <v>41</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P72" s="66">
         <v>6</v>
@@ -9871,10 +9946,10 @@
       <c r="AC72" s="64"/>
       <c r="AD72" s="64"/>
       <c r="AE72" s="64" t="s">
+        <v>770</v>
+      </c>
+      <c r="AF72" s="64" t="s">
         <v>771</v>
-      </c>
-      <c r="AF72" s="64" t="s">
-        <v>772</v>
       </c>
       <c r="AG72" s="64"/>
       <c r="AH72" s="64" t="s">
@@ -9884,28 +9959,28 @@
     </row>
     <row r="73" spans="1:35" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="80" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B73" s="29">
         <v>2026</v>
       </c>
       <c r="D73" s="38" t="s">
+        <v>772</v>
+      </c>
+      <c r="E73" s="38" t="s">
         <v>773</v>
       </c>
-      <c r="E73" s="38" t="s">
+      <c r="F73" s="81" t="s">
         <v>774</v>
       </c>
-      <c r="F73" s="81" t="s">
+      <c r="G73" s="38" t="s">
         <v>775</v>
       </c>
-      <c r="G73" s="38" t="s">
+      <c r="H73" s="38" t="s">
+        <v>775</v>
+      </c>
+      <c r="O73" s="38" t="s">
         <v>776</v>
-      </c>
-      <c r="H73" s="38" t="s">
-        <v>776</v>
-      </c>
-      <c r="O73" s="38" t="s">
-        <v>777</v>
       </c>
       <c r="P73" s="29">
         <v>6</v>
@@ -9923,46 +9998,108 @@
         <v>44</v>
       </c>
       <c r="W73" s="38" t="s">
+        <v>777</v>
+      </c>
+      <c r="AE73" s="38" t="s">
         <v>778</v>
       </c>
-      <c r="AE73" s="38" t="s">
+      <c r="AF73" s="38" t="s">
         <v>779</v>
       </c>
-      <c r="AF73" s="38" t="s">
+    </row>
+    <row r="74" spans="1:35" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>390</v>
+      </c>
+      <c r="B74">
+        <v>2026</v>
+      </c>
+      <c r="D74" t="s">
         <v>780</v>
       </c>
+      <c r="E74" t="s">
+        <v>781</v>
+      </c>
+      <c r="F74" t="s">
+        <v>782</v>
+      </c>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="O74" t="s">
+        <v>783</v>
+      </c>
+      <c r="P74">
+        <v>6</v>
+      </c>
+      <c r="Q74">
+        <v>2</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="V74" t="s">
+        <v>44</v>
+      </c>
+      <c r="W74" t="s">
+        <v>784</v>
+      </c>
+      <c r="Z74" s="38" t="s">
+        <v>789</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>785</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>786</v>
+      </c>
+      <c r="AI74"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AI73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Preprint">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W1:W1048576">
-    <cfRule type="containsBlanks" dxfId="5" priority="1">
+  <conditionalFormatting sqref="W1:W32 W34:W1048576">
+    <cfRule type="containsBlanks" dxfId="8" priority="4">
       <formula>LEN(TRIM(W1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X1:Y2 A1:B1048576 E1:J1048576 M1:R1048576 V1:V1048576 Z1:AA1048576 Y3 X4:Y1048576">
-    <cfRule type="expression" dxfId="4" priority="5">
+  <conditionalFormatting sqref="X1:Y2 A1:B1048576 E1:J32 M1:R32 V1:V32 Z1:AA32 Y3 X4:Y32 X34:AA73 V34:V1048576 M34:R1048576 E34:J1048576 X75:AA1048576 X74:Y74 AA74">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH1:AH1048576">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Status_internal">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="Status_internal">
       <formula>NOT(ISERROR(SEARCH("Status_internal",AH1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="notEqual">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="notEqual">
       <formula>"published"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI1:AI1048576">
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
       <formula>LEN(TRIM(AI1))=0</formula>
     </cfRule>
-    <cfRule type="notContainsText" dxfId="0" priority="7" operator="notContains" text="TODO">
+    <cfRule type="notContainsText" dxfId="3" priority="10" operator="notContains" text="TODO">
       <formula>ISERROR(SEARCH("TODO",AI1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W33">
+    <cfRule type="containsBlanks" dxfId="2" priority="2">
+      <formula>LEN(TRIM(W33))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33:J33 M33:R33 V33 X33:AA33">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>LEN(TRIM(E33))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z74">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>LEN(TRIM(Z74))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -10049,6 +10186,7 @@
     <hyperlink ref="F65" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
     <hyperlink ref="F72" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
     <hyperlink ref="F73" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F33" r:id="rId84" xr:uid="{D9D478F8-DDB7-114F-AABA-2CAA4751C717}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E89C89-2961-174A-A9BF-70B755CA8082}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1DA75DC-5395-8848-A590-278447BCE92E}"/>
   <bookViews>
     <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AJ$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AJ$74</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="801">
   <si>
     <t>Tipo</t>
   </si>
@@ -1077,9 +1077,6 @@
     <t>SAGE</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 1.4 (65/93, Q3)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Psychology” - SCIE</t>
   </si>
   <si>
@@ -1505,9 +1502,6 @@
     <t>https://doi.org/10.1145/3696459</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 6.6 (25/258 – Q1 [D1])</t>
-  </si>
-  <si>
     <t>G. Martínez, J. Hernández, J. Conde, P. Reviriego, E. Merino-Gomez</t>
   </si>
   <si>
@@ -1551,9 +1545,6 @@
     <t>IEEE Transactions on Computers</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 3.8 (16/69 – Q2)</t>
-  </si>
-  <si>
     <t>Computer Science, Hardware &amp; Architecture - SCIE</t>
   </si>
   <si>
@@ -1606,9 +1597,6 @@
     <t>https://doi.org/10.1109/MIC.2025.3614363</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 4.5 (19/129, Q1)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Computer Science, Software Engineering” - SCIE</t>
   </si>
   <si>
@@ -1710,9 +1698,6 @@
     <t>AI and Society</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 4.7 (58/204 – Q2)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Computer Science, Artificial Intelligence” - ESCI</t>
   </si>
   <si>
@@ -1847,9 +1832,6 @@
     <t>Q4</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 1.2 (90/102 – Q4)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Psychology, Experimental” - SSCI</t>
   </si>
   <si>
@@ -1929,9 +1911,6 @@
     <t>Behavior Research Methods</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 3.9 (1/13, Q1[D1])</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Psychology, Mathematical” - SSCI</t>
   </si>
   <si>
@@ -1972,9 +1951,6 @@
   </si>
   <si>
     <t>Data in Brief</t>
-  </si>
-  <si>
-    <t>Índice de impacto JCR (2024): 1.4 (69/136, Q3)</t>
   </si>
   <si>
     <t>M. Mayor-Rocher, N. Melero, E. Merino-Gómez, M. González, R. Ferrando, J. Conde, P. Reviriego</t>
@@ -2563,9 +2539,6 @@
     <t>IEEE Intelligent Systems</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 6.3 (45/368 – Q1)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> “Engineering, Electrical &amp; Electronic” - SCIE</t>
   </si>
   <si>
@@ -2612,9 +2585,6 @@
   </si>
   <si>
     <t>Ubiquity Press</t>
-  </si>
-  <si>
-    <t>Índice de impacto JCR (2024): 2.3 (38/102 – Q2)</t>
   </si>
   <si>
     <t xml:space="preserve"> “Psychology, Experimental” - ESCI</t>
@@ -2683,9 +2653,6 @@
     <t>ACM Journal on Computing and Cultural Heritage</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 2.2 (112/177, Q3)</t>
-  </si>
-  <si>
     <t>COMPUTER SCIENCE, INTERDISCIPLINARY APPLICATIONS- SCIE</t>
   </si>
   <si>
@@ -3000,6 +2967,51 @@
   </si>
   <si>
     <t>[https://doi.org/10.5281/zenodo.20112756]</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 1.8 (58/93, Q3)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 10.7 (9/266 – Q1 [D1])</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 4.9.8 (18/60 – Q2)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 3.3 (47/128, Q2)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 8.7 (16/266 – Q1 [D1])</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 6.1 (53/210 – Q2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> “Category Computer Science, Software Engineering” - SCIE</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2024): 1.0 (100/104 – Q4)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 5 (1/13, Q1[D1])</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> “Multidisciplinary Sciences” - ESCI</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 1.9 (64/140, Q2)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 2.2 (69/128 – Q3)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2024): 4.5 (115/369 – Q2)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 3.1 (26/104 – Q1)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 3.1 (99/185, Q3)</t>
   </si>
 </sst>
 </file>
@@ -3226,7 +3238,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3495,6 +3507,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3881,7 +3900,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ74"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AJ951"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="79" customWidth="1"/>
@@ -4013,13 +4033,13 @@
         <v>33</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="AJ1" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" s="12" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
@@ -4107,7 +4127,7 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" spans="1:36" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" s="12" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
@@ -4195,7 +4215,7 @@
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
     </row>
-    <row r="4" spans="1:36" s="12" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" s="12" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
@@ -4289,7 +4309,7 @@
       <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
     </row>
-    <row r="5" spans="1:36" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" s="53" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="63" t="s">
         <v>55</v>
       </c>
@@ -4383,7 +4403,7 @@
       <c r="AI5" s="63"/>
       <c r="AJ5" s="63"/>
     </row>
-    <row r="6" spans="1:36" s="12" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="12" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="72" t="s">
         <v>35</v>
       </c>
@@ -4471,7 +4491,7 @@
       <c r="AI6" s="9"/>
       <c r="AJ6" s="9"/>
     </row>
-    <row r="7" spans="1:36" s="12" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" s="12" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="72" t="s">
         <v>35</v>
       </c>
@@ -4559,7 +4579,7 @@
       <c r="AI7" s="9"/>
       <c r="AJ7" s="9"/>
     </row>
-    <row r="8" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
         <v>55</v>
       </c>
@@ -4659,7 +4679,7 @@
       <c r="AI8" s="63"/>
       <c r="AJ8" s="63"/>
     </row>
-    <row r="9" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="63" t="s">
         <v>55</v>
       </c>
@@ -4759,7 +4779,7 @@
       <c r="AI9" s="63"/>
       <c r="AJ9" s="63"/>
     </row>
-    <row r="10" spans="1:36" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="2" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
         <v>55</v>
       </c>
@@ -4851,7 +4871,7 @@
       <c r="AI10" s="37"/>
       <c r="AJ10" s="37"/>
     </row>
-    <row r="11" spans="1:36" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="2" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
         <v>55</v>
       </c>
@@ -4941,7 +4961,7 @@
       <c r="AI11" s="37"/>
       <c r="AJ11" s="37"/>
     </row>
-    <row r="12" spans="1:36" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="2" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="79" t="s">
         <v>153</v>
       </c>
@@ -5027,7 +5047,7 @@
       <c r="AI12" s="37"/>
       <c r="AJ12" s="37"/>
     </row>
-    <row r="13" spans="1:36" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="2" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="79" t="s">
         <v>35</v>
       </c>
@@ -5115,7 +5135,7 @@
       <c r="AI13" s="37"/>
       <c r="AJ13" s="37"/>
     </row>
-    <row r="14" spans="1:36" s="53" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="53" customFormat="1" ht="84.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="78" t="s">
         <v>35</v>
       </c>
@@ -5203,7 +5223,7 @@
       <c r="AI14" s="63"/>
       <c r="AJ14" s="63"/>
     </row>
-    <row r="15" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="78" t="s">
         <v>35</v>
       </c>
@@ -5291,7 +5311,7 @@
       <c r="AI15" s="63"/>
       <c r="AJ15" s="63"/>
     </row>
-    <row r="16" spans="1:36" s="53" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="53" customFormat="1" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="63" t="s">
         <v>55</v>
       </c>
@@ -5393,7 +5413,7 @@
       <c r="AI16" s="63"/>
       <c r="AJ16" s="63"/>
     </row>
-    <row r="17" spans="1:36" s="53" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="53" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="63" t="s">
         <v>55</v>
       </c>
@@ -5493,7 +5513,7 @@
       <c r="AI17" s="63"/>
       <c r="AJ17" s="63"/>
     </row>
-    <row r="18" spans="1:36" s="53" customFormat="1" ht="387.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" s="53" customFormat="1" ht="387.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="63" t="s">
         <v>55</v>
       </c>
@@ -5595,7 +5615,7 @@
       <c r="AI18" s="63"/>
       <c r="AJ18" s="63"/>
     </row>
-    <row r="19" spans="1:36" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" s="53" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="63" t="s">
         <v>55</v>
       </c>
@@ -5695,7 +5715,7 @@
       <c r="AI19" s="63"/>
       <c r="AJ19" s="63"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" s="2" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
         <v>55</v>
       </c>
@@ -5789,7 +5809,7 @@
       <c r="AI20" s="37"/>
       <c r="AJ20" s="37"/>
     </row>
-    <row r="21" spans="1:36" s="2" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="2" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>55</v>
       </c>
@@ -5879,7 +5899,7 @@
       <c r="AI21" s="37"/>
       <c r="AJ21" s="37"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37" t="s">
         <v>55</v>
       </c>
@@ -5976,7 +5996,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="79">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C23" s="21">
         <v>0</v>
@@ -6003,10 +6023,10 @@
         <v>73</v>
       </c>
       <c r="K23" s="22" t="s">
+        <v>786</v>
+      </c>
+      <c r="L23" s="22" t="s">
         <v>289</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>290</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>55</v>
@@ -6015,7 +6035,7 @@
         <v>43</v>
       </c>
       <c r="O23" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P23" s="22">
         <v>4</v>
@@ -6035,13 +6055,13 @@
         <v>43</v>
       </c>
       <c r="W23" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="X23" s="80" t="s">
         <v>292</v>
       </c>
-      <c r="X23" s="80" t="s">
+      <c r="Y23" s="23" t="s">
         <v>293</v>
-      </c>
-      <c r="Y23" s="23" t="s">
-        <v>294</v>
       </c>
       <c r="Z23" s="23" t="s">
         <v>229</v>
@@ -6051,10 +6071,10 @@
       <c r="AC23" s="23"/>
       <c r="AD23" s="23"/>
       <c r="AE23" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF23" s="23" t="s">
         <v>295</v>
-      </c>
-      <c r="AF23" s="23" t="s">
-        <v>296</v>
       </c>
       <c r="AG23" s="23"/>
       <c r="AH23" s="31" t="s">
@@ -6063,7 +6083,7 @@
       <c r="AI23" s="37"/>
       <c r="AJ23" s="37"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37" t="s">
         <v>55</v>
       </c>
@@ -6074,19 +6094,19 @@
         <v>0</v>
       </c>
       <c r="D24" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="F24" s="80" t="s">
         <v>298</v>
       </c>
-      <c r="F24" s="80" t="s">
+      <c r="G24" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="H24" s="23" t="s">
         <v>300</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>301</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>41</v>
@@ -6095,10 +6115,10 @@
         <v>61</v>
       </c>
       <c r="K24" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="L24" s="22" t="s">
         <v>302</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>303</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>55</v>
@@ -6107,7 +6127,7 @@
         <v>43</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P24" s="22">
         <v>8</v>
@@ -6127,13 +6147,13 @@
         <v>44</v>
       </c>
       <c r="W24" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="X24" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="23" t="s">
+      <c r="Y24" s="23" t="s">
         <v>306</v>
-      </c>
-      <c r="Y24" s="23" t="s">
-        <v>307</v>
       </c>
       <c r="Z24" s="23" t="s">
         <v>198</v>
@@ -6143,10 +6163,10 @@
       <c r="AC24" s="23"/>
       <c r="AD24" s="23"/>
       <c r="AE24" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF24" s="23" t="s">
         <v>308</v>
-      </c>
-      <c r="AF24" s="23" t="s">
-        <v>309</v>
       </c>
       <c r="AG24" s="23"/>
       <c r="AH24" s="31" t="s">
@@ -6155,7 +6175,7 @@
       <c r="AI24" s="37"/>
       <c r="AJ24" s="37"/>
     </row>
-    <row r="25" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="78" t="s">
         <v>153</v>
       </c>
@@ -6164,22 +6184,22 @@
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="61" t="s">
+        <v>309</v>
+      </c>
+      <c r="E25" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="E25" s="61" t="s">
+      <c r="F25" s="71" t="s">
         <v>311</v>
       </c>
-      <c r="F25" s="71" t="s">
+      <c r="G25" s="61" t="s">
         <v>312</v>
       </c>
-      <c r="G25" s="61" t="s">
+      <c r="H25" s="63" t="s">
         <v>313</v>
       </c>
-      <c r="H25" s="63" t="s">
+      <c r="I25" s="64" t="s">
         <v>314</v>
-      </c>
-      <c r="I25" s="64" t="s">
-        <v>315</v>
       </c>
       <c r="J25" s="63" t="s">
         <v>41</v>
@@ -6193,7 +6213,7 @@
         <v>41</v>
       </c>
       <c r="O25" s="61" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P25" s="63">
         <v>5</v>
@@ -6213,10 +6233,10 @@
         <v>44</v>
       </c>
       <c r="W25" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="X25" s="63" t="s">
         <v>317</v>
-      </c>
-      <c r="X25" s="63" t="s">
-        <v>318</v>
       </c>
       <c r="Y25" s="63" t="s">
         <v>41</v>
@@ -6231,10 +6251,10 @@
       <c r="AC25" s="63"/>
       <c r="AD25" s="63"/>
       <c r="AE25" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF25" s="63" t="s">
         <v>319</v>
-      </c>
-      <c r="AF25" s="63" t="s">
-        <v>320</v>
       </c>
       <c r="AG25" s="63"/>
       <c r="AH25" s="63" t="s">
@@ -6243,7 +6263,7 @@
       <c r="AI25" s="63"/>
       <c r="AJ25" s="63"/>
     </row>
-    <row r="26" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="78" t="s">
         <v>153</v>
       </c>
@@ -6252,25 +6272,25 @@
       </c>
       <c r="C26" s="28"/>
       <c r="D26" s="61" t="s">
+        <v>320</v>
+      </c>
+      <c r="E26" s="61" t="s">
         <v>321</v>
       </c>
-      <c r="E26" s="61" t="s">
+      <c r="F26" s="71" t="s">
         <v>322</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="G26" s="61" t="s">
+        <v>312</v>
+      </c>
+      <c r="H26" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="63" t="s">
         <v>323</v>
-      </c>
-      <c r="G26" s="61" t="s">
-        <v>313</v>
-      </c>
-      <c r="H26" s="63" t="s">
-        <v>314</v>
-      </c>
-      <c r="I26" s="64" t="s">
-        <v>315</v>
-      </c>
-      <c r="J26" s="63" t="s">
-        <v>324</v>
       </c>
       <c r="K26" s="63"/>
       <c r="L26" s="63"/>
@@ -6281,7 +6301,7 @@
         <v>41</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P26" s="63">
         <v>4</v>
@@ -6301,16 +6321,16 @@
         <v>44</v>
       </c>
       <c r="W26" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="X26" s="76" t="s">
         <v>326</v>
       </c>
-      <c r="X26" s="76" t="s">
+      <c r="Y26" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z26" s="63" t="s">
         <v>327</v>
-      </c>
-      <c r="Y26" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z26" s="63" t="s">
-        <v>328</v>
       </c>
       <c r="AA26" s="63" t="s">
         <v>41</v>
@@ -6319,10 +6339,10 @@
       <c r="AC26" s="63"/>
       <c r="AD26" s="63"/>
       <c r="AE26" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="AF26" s="63" t="s">
         <v>329</v>
-      </c>
-      <c r="AF26" s="63" t="s">
-        <v>330</v>
       </c>
       <c r="AG26" s="63"/>
       <c r="AH26" s="48" t="s">
@@ -6331,7 +6351,7 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="63"/>
     </row>
-    <row r="27" spans="1:36" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" s="53" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="78" t="s">
         <v>153</v>
       </c>
@@ -6340,25 +6360,25 @@
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="61" t="s">
+        <v>330</v>
+      </c>
+      <c r="E27" s="61" t="s">
         <v>331</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="F27" s="71" t="s">
         <v>332</v>
       </c>
-      <c r="F27" s="71" t="s">
+      <c r="G27" s="61" t="s">
         <v>333</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>334</v>
       </c>
       <c r="H27" s="63" t="s">
         <v>118</v>
       </c>
       <c r="I27" s="64" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J27" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K27" s="63"/>
       <c r="L27" s="63"/>
@@ -6369,7 +6389,7 @@
         <v>41</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P27" s="63">
         <v>4</v>
@@ -6392,7 +6412,7 @@
         <v>41</v>
       </c>
       <c r="X27" s="76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Y27" s="63" t="s">
         <v>41</v>
@@ -6407,10 +6427,10 @@
       <c r="AC27" s="63"/>
       <c r="AD27" s="63"/>
       <c r="AE27" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="AF27" s="63" t="s">
         <v>338</v>
-      </c>
-      <c r="AF27" s="63" t="s">
-        <v>339</v>
       </c>
       <c r="AG27" s="63"/>
       <c r="AH27" s="48" t="s">
@@ -6419,7 +6439,7 @@
       <c r="AI27" s="63"/>
       <c r="AJ27" s="63"/>
     </row>
-    <row r="28" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="78" t="s">
         <v>153</v>
       </c>
@@ -6428,22 +6448,22 @@
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="E28" s="61" t="s">
         <v>340</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="F28" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="F28" s="62" t="s">
+      <c r="G28" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="H28" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="H28" s="63" t="s">
+      <c r="I28" s="64" t="s">
         <v>344</v>
-      </c>
-      <c r="I28" s="64" t="s">
-        <v>345</v>
       </c>
       <c r="J28" s="63" t="s">
         <v>41</v>
@@ -6457,7 +6477,7 @@
         <v>41</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P28" s="63">
         <v>5</v>
@@ -6477,28 +6497,28 @@
         <v>44</v>
       </c>
       <c r="W28" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="X28" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y28" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z28" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA28" s="63" t="s">
         <v>347</v>
-      </c>
-      <c r="X28" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y28" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z28" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA28" s="63" t="s">
-        <v>348</v>
       </c>
       <c r="AB28" s="63"/>
       <c r="AC28" s="63"/>
       <c r="AD28" s="63"/>
       <c r="AE28" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="AF28" s="63" t="s">
         <v>349</v>
-      </c>
-      <c r="AF28" s="63" t="s">
-        <v>350</v>
       </c>
       <c r="AG28" s="63"/>
       <c r="AH28" s="63" t="s">
@@ -6507,22 +6527,22 @@
       <c r="AI28" s="63"/>
       <c r="AJ28" s="63"/>
     </row>
-    <row r="29" spans="1:36" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" s="53" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B29" s="82">
         <v>2024</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="61" t="s">
+        <v>351</v>
+      </c>
+      <c r="E29" s="61" t="s">
         <v>352</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="F29" s="62" t="s">
         <v>353</v>
-      </c>
-      <c r="F29" s="62" t="s">
-        <v>354</v>
       </c>
       <c r="G29" s="64" t="s">
         <v>101</v>
@@ -6545,7 +6565,7 @@
         <v>41</v>
       </c>
       <c r="O29" s="63" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P29" s="63">
         <v>6</v>
@@ -6583,10 +6603,10 @@
       <c r="AC29" s="63"/>
       <c r="AD29" s="63"/>
       <c r="AE29" s="63" t="s">
+        <v>355</v>
+      </c>
+      <c r="AF29" s="63" t="s">
         <v>356</v>
-      </c>
-      <c r="AF29" s="63" t="s">
-        <v>357</v>
       </c>
       <c r="AG29" s="63"/>
       <c r="AH29" s="63" t="s">
@@ -6595,28 +6615,28 @@
       <c r="AI29" s="63"/>
       <c r="AJ29" s="63"/>
     </row>
-    <row r="30" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B30" s="82">
         <v>2024</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="61" t="s">
+        <v>357</v>
+      </c>
+      <c r="E30" s="61" t="s">
         <v>358</v>
       </c>
-      <c r="E30" s="61" t="s">
+      <c r="F30" s="62" t="s">
         <v>359</v>
       </c>
-      <c r="F30" s="62" t="s">
+      <c r="G30" s="64" t="s">
         <v>360</v>
       </c>
-      <c r="G30" s="64" t="s">
-        <v>361</v>
-      </c>
       <c r="H30" s="63" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I30" s="63" t="s">
         <v>41</v>
@@ -6633,7 +6653,7 @@
         <v>41</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P30" s="63">
         <v>4</v>
@@ -6653,7 +6673,7 @@
         <v>44</v>
       </c>
       <c r="W30" s="63" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="X30" s="63" t="s">
         <v>41</v>
@@ -6671,10 +6691,10 @@
       <c r="AC30" s="63"/>
       <c r="AD30" s="63"/>
       <c r="AE30" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF30" s="63" t="s">
         <v>364</v>
-      </c>
-      <c r="AF30" s="63" t="s">
-        <v>365</v>
       </c>
       <c r="AG30" s="63"/>
       <c r="AH30" s="63" t="s">
@@ -6683,7 +6703,7 @@
       <c r="AI30" s="63"/>
       <c r="AJ30" s="63"/>
     </row>
-    <row r="31" spans="1:36" s="53" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" s="53" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="78" t="s">
         <v>35</v>
       </c>
@@ -6692,16 +6712,16 @@
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" s="61" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="61" t="s">
+      <c r="F31" s="62" t="s">
         <v>367</v>
       </c>
-      <c r="F31" s="62" t="s">
+      <c r="G31" s="61" t="s">
         <v>368</v>
-      </c>
-      <c r="G31" s="61" t="s">
-        <v>369</v>
       </c>
       <c r="H31" s="63" t="s">
         <v>40</v>
@@ -6721,7 +6741,7 @@
         <v>41</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P31" s="63">
         <v>6</v>
@@ -6744,7 +6764,7 @@
         <v>41</v>
       </c>
       <c r="X31" s="63" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y31" s="63" t="s">
         <v>41</v>
@@ -6759,10 +6779,10 @@
       <c r="AC31" s="63"/>
       <c r="AD31" s="63"/>
       <c r="AE31" s="63" t="s">
+        <v>370</v>
+      </c>
+      <c r="AF31" s="63" t="s">
         <v>371</v>
-      </c>
-      <c r="AF31" s="63" t="s">
-        <v>372</v>
       </c>
       <c r="AG31" s="63"/>
       <c r="AH31" s="63" t="s">
@@ -6771,25 +6791,25 @@
       <c r="AI31" s="63"/>
       <c r="AJ31" s="63"/>
     </row>
-    <row r="32" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="78" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B32" s="65">
         <v>2024</v>
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="E32" s="63" t="s">
         <v>374</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="F32" s="63" t="s">
         <v>375</v>
       </c>
-      <c r="F32" s="63" t="s">
+      <c r="G32" s="63" t="s">
         <v>376</v>
-      </c>
-      <c r="G32" s="63" t="s">
-        <v>377</v>
       </c>
       <c r="H32" s="63" t="s">
         <v>40</v>
@@ -6801,7 +6821,7 @@
       <c r="M32" s="63"/>
       <c r="N32" s="63"/>
       <c r="O32" s="63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P32" s="65">
         <v>4</v>
@@ -6822,7 +6842,7 @@
         <v>41</v>
       </c>
       <c r="X32" s="63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y32" s="63" t="s">
         <v>41</v>
@@ -6837,10 +6857,10 @@
       <c r="AC32" s="63"/>
       <c r="AD32" s="63"/>
       <c r="AE32" s="63" t="s">
+        <v>378</v>
+      </c>
+      <c r="AF32" s="63" t="s">
         <v>379</v>
-      </c>
-      <c r="AF32" s="63" t="s">
-        <v>380</v>
       </c>
       <c r="AG32" s="63"/>
       <c r="AH32" s="63" t="s">
@@ -6849,33 +6869,33 @@
       <c r="AI32" s="63"/>
       <c r="AJ32" s="63"/>
     </row>
-    <row r="33" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="94">
         <v>2026</v>
       </c>
       <c r="D33" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="E33" s="37" t="s">
         <v>381</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="F33" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="F33" s="80" t="s">
+      <c r="G33" s="37" t="s">
         <v>383</v>
       </c>
-      <c r="G33" s="37" t="s">
-        <v>384</v>
-      </c>
       <c r="H33" s="37" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J33" s="37" t="s">
         <v>102</v>
       </c>
       <c r="K33" s="49" t="s">
-        <v>403</v>
+        <v>787</v>
       </c>
       <c r="L33" s="49" t="s">
         <v>240</v>
@@ -6887,7 +6907,7 @@
         <v>43</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P33" s="28">
         <v>5</v>
@@ -6905,57 +6925,57 @@
         <v>44</v>
       </c>
       <c r="W33" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="X33" s="37" t="s">
+        <v>783</v>
+      </c>
+      <c r="Y33" s="93" t="s">
+        <v>785</v>
+      </c>
+      <c r="Z33" s="37" t="s">
         <v>386</v>
       </c>
-      <c r="X33" s="37" t="s">
-        <v>794</v>
-      </c>
-      <c r="Y33" s="93" t="s">
-        <v>796</v>
-      </c>
-      <c r="Z33" s="37" t="s">
+      <c r="AA33" s="37" t="s">
+        <v>775</v>
+      </c>
+      <c r="AE33" s="37" t="s">
         <v>387</v>
       </c>
-      <c r="AA33" s="37" t="s">
-        <v>786</v>
-      </c>
-      <c r="AE33" s="37" t="s">
+      <c r="AF33" s="37" t="s">
         <v>388</v>
-      </c>
-      <c r="AF33" s="37" t="s">
-        <v>389</v>
       </c>
       <c r="AH33" s="37" t="s">
         <v>48</v>
       </c>
       <c r="AI33" s="37" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="79" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B34" s="28">
         <v>2024</v>
       </c>
       <c r="D34" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>391</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="F34" s="37" t="s">
         <v>392</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="G34" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="H34" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="O34" s="37" t="s">
         <v>394</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="O34" s="37" t="s">
-        <v>395</v>
       </c>
       <c r="P34" s="28">
         <v>5</v>
@@ -6973,22 +6993,22 @@
         <v>44</v>
       </c>
       <c r="W34" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="X34" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y34" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z34" s="37" t="s">
         <v>396</v>
       </c>
-      <c r="X34" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y34" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z34" s="37" t="s">
+      <c r="AE34" s="37" t="s">
         <v>397</v>
       </c>
-      <c r="AE34" s="37" t="s">
+      <c r="AF34" s="37" t="s">
         <v>398</v>
-      </c>
-      <c r="AF34" s="37" t="s">
-        <v>399</v>
       </c>
       <c r="AI34"/>
       <c r="AJ34"/>
@@ -7004,19 +7024,19 @@
         <v>10</v>
       </c>
       <c r="D35" s="49" t="s">
+        <v>399</v>
+      </c>
+      <c r="E35" s="49" t="s">
         <v>400</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="F35" s="56" t="s">
         <v>401</v>
       </c>
-      <c r="F35" s="56" t="s">
-        <v>402</v>
-      </c>
       <c r="G35" s="49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H35" s="49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I35" s="49" t="s">
         <v>41</v>
@@ -7025,7 +7045,7 @@
         <v>102</v>
       </c>
       <c r="K35" s="49" t="s">
-        <v>403</v>
+        <v>787</v>
       </c>
       <c r="L35" s="49" t="s">
         <v>240</v>
@@ -7037,7 +7057,7 @@
         <v>13</v>
       </c>
       <c r="O35" s="49" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P35" s="57">
         <v>5</v>
@@ -7059,28 +7079,28 @@
         <v>44</v>
       </c>
       <c r="W35" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="X35" s="56" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y35" s="49" t="s">
         <v>405</v>
-      </c>
-      <c r="X35" s="56" t="s">
-        <v>406</v>
-      </c>
-      <c r="Y35" s="49" t="s">
-        <v>407</v>
       </c>
       <c r="Z35" s="49" t="s">
         <v>216</v>
       </c>
       <c r="AA35" s="49" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AB35" s="63"/>
       <c r="AC35" s="63"/>
       <c r="AD35" s="63"/>
       <c r="AE35" s="63" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AF35" s="63" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG35" s="63"/>
       <c r="AH35" s="57" t="s">
@@ -7100,16 +7120,16 @@
         <v>9</v>
       </c>
       <c r="D36" s="49" t="s">
+        <v>409</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="F36" s="56" t="s">
         <v>411</v>
       </c>
-      <c r="E36" s="49" t="s">
+      <c r="G36" s="49" t="s">
         <v>412</v>
-      </c>
-      <c r="F36" s="56" t="s">
-        <v>413</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>414</v>
       </c>
       <c r="H36" s="49" t="s">
         <v>118</v>
@@ -7121,19 +7141,19 @@
         <v>61</v>
       </c>
       <c r="K36" s="49" t="s">
-        <v>415</v>
+        <v>788</v>
       </c>
       <c r="L36" s="49" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M36" s="49" t="s">
         <v>55</v>
       </c>
       <c r="N36" s="49" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O36" s="49" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P36" s="46">
         <v>6</v>
@@ -7157,30 +7177,30 @@
         <v>43</v>
       </c>
       <c r="W36" s="49" t="s">
+        <v>416</v>
+      </c>
+      <c r="X36" s="56" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y36" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="Z36" s="49" t="s">
         <v>419</v>
       </c>
-      <c r="X36" s="56" t="s">
+      <c r="AA36" s="49" t="s">
         <v>420</v>
-      </c>
-      <c r="Y36" s="49" t="s">
-        <v>421</v>
-      </c>
-      <c r="Z36" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA36" s="49" t="s">
-        <v>423</v>
       </c>
       <c r="AB36" s="63"/>
       <c r="AC36" s="63"/>
       <c r="AD36" s="49" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AE36" s="63" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AF36" s="63" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG36" s="63"/>
       <c r="AH36" s="57" t="s">
@@ -7200,13 +7220,13 @@
         <v>8.5</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G37" s="47" t="s">
         <v>117</v>
@@ -7218,13 +7238,13 @@
         <v>41</v>
       </c>
       <c r="J37" s="46" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="K37" s="46" t="s">
-        <v>430</v>
+        <v>789</v>
       </c>
       <c r="L37" s="46" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="M37" s="48" t="s">
         <v>121</v>
@@ -7233,7 +7253,7 @@
         <v>13</v>
       </c>
       <c r="O37" s="46" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="P37" s="49">
         <v>4</v>
@@ -7249,36 +7269,36 @@
       </c>
       <c r="T37" s="52"/>
       <c r="U37" s="70" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="V37" s="48" t="s">
         <v>44</v>
       </c>
       <c r="W37" s="48" t="s">
+        <v>430</v>
+      </c>
+      <c r="X37" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="Y37" s="48" t="s">
+        <v>432</v>
+      </c>
+      <c r="Z37" s="48" t="s">
+        <v>433</v>
+      </c>
+      <c r="AA37" s="48" t="s">
         <v>434</v>
-      </c>
-      <c r="X37" s="48" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y37" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="Z37" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="AA37" s="48" t="s">
-        <v>438</v>
       </c>
       <c r="AB37" s="48"/>
       <c r="AC37" s="48"/>
       <c r="AD37" s="48" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AE37" s="48" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AF37" s="48" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AG37" s="48"/>
       <c r="AH37" s="57" t="s">
@@ -7298,13 +7318,13 @@
         <v>8</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E38" s="55" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G38" s="49" t="s">
         <v>191</v>
@@ -7319,19 +7339,19 @@
         <v>102</v>
       </c>
       <c r="K38" s="49" t="s">
-        <v>192</v>
+        <v>790</v>
       </c>
       <c r="L38" s="49" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="M38" s="49" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="N38" s="49" t="s">
         <v>43</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="P38" s="49">
         <v>7</v>
@@ -7355,30 +7375,30 @@
         <v>43</v>
       </c>
       <c r="W38" s="49" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="X38" s="56" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Y38" s="49" t="s">
         <v>41</v>
       </c>
       <c r="Z38" s="49" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AA38" s="49" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AB38" s="63"/>
       <c r="AC38" s="63"/>
       <c r="AD38" s="49" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AE38" s="63" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="AF38" s="63" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG38" s="63"/>
       <c r="AH38" s="57" t="s">
@@ -7398,19 +7418,19 @@
         <v>7</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F39" s="56" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H39" s="49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I39" s="49" t="s">
         <v>41</v>
@@ -7419,10 +7439,10 @@
         <v>61</v>
       </c>
       <c r="K39" s="49" t="s">
-        <v>458</v>
+        <v>791</v>
       </c>
       <c r="L39" s="49" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="M39" s="49" t="s">
         <v>55</v>
@@ -7431,7 +7451,7 @@
         <v>43</v>
       </c>
       <c r="O39" s="49" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="P39" s="51">
         <v>6</v>
@@ -7453,30 +7473,30 @@
         <v>44</v>
       </c>
       <c r="W39" s="49" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="X39" s="56" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="Y39" s="49" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="Z39" s="49" t="s">
         <v>198</v>
       </c>
       <c r="AA39" s="49" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AB39" s="63"/>
       <c r="AC39" s="63"/>
       <c r="AD39" s="49" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AE39" s="63" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AF39" s="63" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AG39" s="63"/>
       <c r="AH39" s="57" t="s">
@@ -7496,13 +7516,13 @@
         <v>7</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G40" s="47" t="s">
         <v>117</v>
@@ -7513,14 +7533,14 @@
       <c r="I40" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="J40" s="49" t="s">
-        <v>102</v>
+      <c r="J40" s="46" t="s">
+        <v>61</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>430</v>
+        <v>789</v>
       </c>
       <c r="L40" s="46" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="M40" s="48" t="s">
         <v>121</v>
@@ -7529,7 +7549,7 @@
         <v>43</v>
       </c>
       <c r="O40" s="46" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="P40" s="51">
         <v>5</v>
@@ -7549,19 +7569,19 @@
         <v>44</v>
       </c>
       <c r="W40" s="48" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="X40" s="76" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="Y40" s="48" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="Z40" s="48" t="s">
         <v>41</v>
       </c>
       <c r="AA40" s="48" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AB40" s="48"/>
       <c r="AC40" s="48"/>
@@ -7569,10 +7589,10 @@
         <v>259</v>
       </c>
       <c r="AE40" s="48" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AF40" s="48" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AG40" s="48"/>
       <c r="AH40" s="57" t="s">
@@ -7592,13 +7612,13 @@
         <v>6</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F41" s="80" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G41" s="24" t="s">
         <v>145</v>
@@ -7610,13 +7630,13 @@
         <v>41</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="K41" s="22" t="s">
-        <v>253</v>
+        <v>797</v>
       </c>
       <c r="L41" s="22" t="s">
-        <v>254</v>
+        <v>792</v>
       </c>
       <c r="M41" s="23" t="s">
         <v>121</v>
@@ -7625,7 +7645,7 @@
         <v>43</v>
       </c>
       <c r="O41" s="22" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="P41" s="25">
         <v>6</v>
@@ -7645,26 +7665,26 @@
         <v>43</v>
       </c>
       <c r="W41" s="23" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="X41" s="80" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="Y41" s="23"/>
       <c r="Z41" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA41" s="23"/>
       <c r="AB41" s="23"/>
       <c r="AC41" s="23"/>
       <c r="AD41" s="23" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AE41" s="23" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AF41" s="23" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AG41" s="23"/>
       <c r="AH41" s="31" t="s">
@@ -7682,31 +7702,31 @@
         <v>0</v>
       </c>
       <c r="D42" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="F42" s="76" t="s">
+        <v>484</v>
+      </c>
+      <c r="G42" s="47" t="s">
+        <v>485</v>
+      </c>
+      <c r="H42" s="48" t="s">
+        <v>486</v>
+      </c>
+      <c r="I42" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" s="49" t="s">
         <v>487</v>
       </c>
-      <c r="E42" s="46" t="s">
+      <c r="K42" s="46" t="s">
+        <v>793</v>
+      </c>
+      <c r="L42" s="46" t="s">
         <v>488</v>
-      </c>
-      <c r="F42" s="76" t="s">
-        <v>489</v>
-      </c>
-      <c r="G42" s="47" t="s">
-        <v>490</v>
-      </c>
-      <c r="H42" s="48" t="s">
-        <v>491</v>
-      </c>
-      <c r="I42" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" s="49" t="s">
-        <v>492</v>
-      </c>
-      <c r="K42" s="46" t="s">
-        <v>493</v>
-      </c>
-      <c r="L42" s="46" t="s">
-        <v>494</v>
       </c>
       <c r="M42" s="48" t="s">
         <v>55</v>
@@ -7715,7 +7735,7 @@
         <v>43</v>
       </c>
       <c r="O42" s="46" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="P42" s="51">
         <v>7</v>
@@ -7738,27 +7758,27 @@
         <v>41</v>
       </c>
       <c r="X42" s="48" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="Y42" s="48" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="Z42" s="48" t="s">
         <v>198</v>
       </c>
       <c r="AA42" s="48" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AB42" s="48"/>
       <c r="AC42" s="48"/>
       <c r="AD42" s="48" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="AE42" s="48" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AF42" s="48" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AG42" s="48"/>
       <c r="AH42" s="57" t="s">
@@ -7778,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F43" s="80" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="H43" s="23" t="s">
         <v>118</v>
@@ -7799,7 +7819,7 @@
         <v>41</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="L43" s="24"/>
       <c r="M43" s="23" t="s">
@@ -7809,7 +7829,7 @@
         <v>43</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="P43" s="22">
         <v>6</v>
@@ -7830,7 +7850,7 @@
       </c>
       <c r="W43" s="23"/>
       <c r="X43" s="23" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="Y43" s="23" t="s">
         <v>41</v>
@@ -7843,10 +7863,10 @@
       <c r="AC43" s="23"/>
       <c r="AD43" s="23"/>
       <c r="AE43" s="23" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AF43" s="23" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="AG43" s="23"/>
       <c r="AH43" s="23" t="s">
@@ -7866,19 +7886,19 @@
         <v>0</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I44" s="23" t="s">
         <v>41</v>
@@ -7887,10 +7907,10 @@
         <v>102</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>515</v>
+        <v>794</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>55</v>
@@ -7899,7 +7919,7 @@
         <v>43</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P44" s="22">
         <v>4</v>
@@ -7919,13 +7939,13 @@
         <v>43</v>
       </c>
       <c r="W44" s="23" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="X44" s="80" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Y44" s="23" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="Z44" s="23" t="s">
         <v>216</v>
@@ -7934,13 +7954,13 @@
       <c r="AB44" s="23"/>
       <c r="AC44" s="23"/>
       <c r="AD44" s="23" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="AE44" s="23" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AF44" s="23" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AG44" s="23"/>
       <c r="AH44" s="23" t="s">
@@ -7958,16 +7978,16 @@
         <v>0</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F45" s="80" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H45" s="23" t="s">
         <v>101</v>
@@ -7976,13 +7996,13 @@
         <v>41</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>527</v>
+        <v>796</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>276</v>
+        <v>795</v>
       </c>
       <c r="M45" s="23" t="s">
         <v>55</v>
@@ -7991,7 +8011,7 @@
         <v>43</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="P45" s="22">
         <v>7</v>
@@ -8014,10 +8034,10 @@
         <v>41</v>
       </c>
       <c r="X45" s="23" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="Y45" s="23" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="Z45" s="23" t="s">
         <v>198</v>
@@ -8027,10 +8047,10 @@
       <c r="AC45" s="23"/>
       <c r="AD45" s="23"/>
       <c r="AE45" s="23" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AF45" s="23" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AG45" s="23"/>
       <c r="AH45" s="23" t="s">
@@ -8048,19 +8068,19 @@
         <v>0</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I46" s="23" t="s">
         <v>41</v>
@@ -8069,10 +8089,10 @@
         <v>102</v>
       </c>
       <c r="K46" s="22" t="s">
-        <v>515</v>
+        <v>794</v>
       </c>
       <c r="L46" s="22" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="M46" s="23" t="s">
         <v>55</v>
@@ -8081,7 +8101,7 @@
         <v>43</v>
       </c>
       <c r="O46" s="22" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="P46" s="35">
         <v>6</v>
@@ -8101,13 +8121,13 @@
         <v>43</v>
       </c>
       <c r="W46" s="23" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="X46" s="80" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="Y46" s="23" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="Z46" s="23" t="s">
         <v>216</v>
@@ -8117,10 +8137,10 @@
       <c r="AC46" s="23"/>
       <c r="AD46" s="23"/>
       <c r="AE46" s="23" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="AF46" s="23" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="AG46" s="23"/>
       <c r="AH46" s="23" t="s">
@@ -8137,22 +8157,22 @@
         <v>2025</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="G47" s="35" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="H47" s="37" t="s">
         <v>118</v>
       </c>
       <c r="I47" s="38" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="J47" s="37" t="s">
         <v>41</v>
@@ -8164,7 +8184,7 @@
         <v>41</v>
       </c>
       <c r="O47" s="35" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="P47" s="87">
         <v>5</v>
@@ -8182,22 +8202,22 @@
         <v>43</v>
       </c>
       <c r="W47" s="88" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="X47" s="80" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="Y47" s="37" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="Z47" s="37" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AE47" s="37" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AF47" s="37" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="AH47" s="37" t="s">
         <v>48</v>
@@ -8211,22 +8231,22 @@
         <v>2025</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="E48" s="35" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="G48" s="35" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="H48" s="37" t="s">
         <v>118</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="J48" s="37" t="s">
         <v>41</v>
@@ -8238,7 +8258,7 @@
         <v>41</v>
       </c>
       <c r="O48" s="35" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="P48" s="87">
         <v>5</v>
@@ -8256,7 +8276,7 @@
         <v>43</v>
       </c>
       <c r="W48" s="88" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="Y48" s="37" t="s">
         <v>41</v>
@@ -8265,10 +8285,10 @@
         <v>198</v>
       </c>
       <c r="AE48" s="37" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="AF48" s="37" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="AH48" s="37" t="s">
         <v>48</v>
@@ -8283,22 +8303,22 @@
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="61" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="E49" s="61" t="s">
         <v>41</v>
       </c>
       <c r="F49" s="62" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="G49" s="61" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="H49" s="63" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="I49" s="78" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="J49" s="63" t="s">
         <v>41</v>
@@ -8312,7 +8332,7 @@
         <v>41</v>
       </c>
       <c r="O49" s="61" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="P49" s="63">
         <v>4</v>
@@ -8348,10 +8368,10 @@
       <c r="AC49" s="63"/>
       <c r="AD49" s="63"/>
       <c r="AE49" s="63" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="AF49" s="63" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AG49" s="63"/>
       <c r="AH49" s="63" t="s">
@@ -8368,25 +8388,25 @@
         <v>2025</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="G50" s="35" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="M50" s="37" t="s">
         <v>41</v>
@@ -8395,7 +8415,7 @@
         <v>41</v>
       </c>
       <c r="O50" s="35" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="P50" s="37">
         <v>25</v>
@@ -8413,22 +8433,22 @@
         <v>44</v>
       </c>
       <c r="W50" s="37" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="X50" s="80" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="Y50" s="37" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="Z50" s="37" t="s">
         <v>41</v>
       </c>
       <c r="AE50" s="37" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="AF50" s="37" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="AH50" s="37" t="s">
         <v>48</v>
@@ -8443,22 +8463,22 @@
       </c>
       <c r="C51" s="28"/>
       <c r="D51" s="61" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="E51" s="61" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="F51" s="71" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="H51" s="63" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="I51" s="64" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="J51" s="63" t="s">
         <v>41</v>
@@ -8472,7 +8492,7 @@
         <v>41</v>
       </c>
       <c r="O51" s="61" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="P51" s="63">
         <v>6</v>
@@ -8492,10 +8512,10 @@
         <v>44</v>
       </c>
       <c r="W51" s="63" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="X51" s="76" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="Y51" s="63" t="s">
         <v>41</v>
@@ -8510,10 +8530,10 @@
       <c r="AC51" s="63"/>
       <c r="AD51" s="63"/>
       <c r="AE51" s="63" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="AF51" s="63" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="AG51" s="63"/>
       <c r="AH51" s="48" t="s">
@@ -8531,22 +8551,22 @@
       </c>
       <c r="C52" s="28"/>
       <c r="D52" s="61" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E52" s="61" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="F52" s="71" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="G52" s="61" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="H52" s="63" t="s">
         <v>118</v>
       </c>
       <c r="I52" s="64" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="J52" s="63" t="s">
         <v>41</v>
@@ -8560,7 +8580,7 @@
         <v>41</v>
       </c>
       <c r="O52" s="61" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="P52" s="63">
         <v>6</v>
@@ -8580,13 +8600,13 @@
         <v>43</v>
       </c>
       <c r="W52" s="63" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="X52" s="76" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="Y52" s="63" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="Z52" s="63" t="s">
         <v>41</v>
@@ -8598,10 +8618,10 @@
       <c r="AC52" s="63"/>
       <c r="AD52" s="63"/>
       <c r="AE52" s="63" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AF52" s="63" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AG52" s="63"/>
       <c r="AH52" s="63" t="s">
@@ -8618,25 +8638,25 @@
         <v>2025</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="F53" s="88" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="G53" s="35" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H53" s="37" t="s">
         <v>118</v>
       </c>
       <c r="I53" s="38" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="M53" s="37" t="s">
         <v>41</v>
@@ -8645,7 +8665,7 @@
         <v>41</v>
       </c>
       <c r="O53" s="35" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="P53" s="37">
         <v>6</v>
@@ -8675,10 +8695,10 @@
         <v>41</v>
       </c>
       <c r="AE53" s="37" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AF53" s="37" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="AH53" s="23" t="s">
         <v>48</v>
@@ -8693,22 +8713,22 @@
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="61" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E54" s="61" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="F54" s="62" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="G54" s="61" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="H54" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I54" s="64" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="J54" s="63" t="s">
         <v>41</v>
@@ -8722,7 +8742,7 @@
         <v>41</v>
       </c>
       <c r="O54" s="61" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="P54" s="63">
         <v>6</v>
@@ -8760,10 +8780,10 @@
       <c r="AC54" s="63"/>
       <c r="AD54" s="63"/>
       <c r="AE54" s="63" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="AF54" s="63" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="AG54" s="63"/>
       <c r="AH54" s="63" t="s">
@@ -8774,20 +8794,20 @@
     </row>
     <row r="55" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B55" s="82">
         <v>2025</v>
       </c>
       <c r="C55" s="28"/>
       <c r="D55" s="61" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="E55" s="61" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="F55" s="62" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="G55" s="64" t="s">
         <v>101</v>
@@ -8810,7 +8830,7 @@
         <v>41</v>
       </c>
       <c r="O55" s="63" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="P55" s="63">
         <v>4</v>
@@ -8848,10 +8868,10 @@
       <c r="AC55" s="63"/>
       <c r="AD55" s="63"/>
       <c r="AE55" s="63" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="AF55" s="63" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="AG55" s="63"/>
       <c r="AH55" s="63" t="s">
@@ -8869,16 +8889,16 @@
       </c>
       <c r="C56" s="28"/>
       <c r="D56" s="61" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="E56" s="61" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="F56" s="62" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="G56" s="61" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H56" s="63" t="s">
         <v>174</v>
@@ -8898,7 +8918,7 @@
         <v>41</v>
       </c>
       <c r="O56" s="61" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="P56" s="63">
         <v>6</v>
@@ -8921,7 +8941,7 @@
         <v>41</v>
       </c>
       <c r="X56" s="63" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="Y56" s="63" t="s">
         <v>41</v>
@@ -8936,10 +8956,10 @@
       <c r="AC56" s="63"/>
       <c r="AD56" s="63"/>
       <c r="AE56" s="63" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="AF56" s="63" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="AG56" s="63"/>
       <c r="AH56" s="63" t="s">
@@ -8957,16 +8977,16 @@
       </c>
       <c r="C57" s="28"/>
       <c r="D57" s="61" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E57" s="61" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="F57" s="62" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="G57" s="61" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H57" s="63" t="s">
         <v>174</v>
@@ -8986,7 +9006,7 @@
         <v>41</v>
       </c>
       <c r="O57" s="61" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="P57" s="63">
         <v>3</v>
@@ -9009,7 +9029,7 @@
         <v>41</v>
       </c>
       <c r="X57" s="63" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="Y57" s="63" t="s">
         <v>41</v>
@@ -9024,10 +9044,10 @@
       <c r="AC57" s="63"/>
       <c r="AD57" s="63"/>
       <c r="AE57" s="63" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="AF57" s="63" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="AG57" s="63"/>
       <c r="AH57" s="63" t="s">
@@ -9038,28 +9058,28 @@
     </row>
     <row r="58" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B58" s="28">
+        <v>389</v>
+      </c>
+      <c r="B58" s="94">
         <v>2025</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F58" s="80" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O58" s="37" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="P58" s="28">
         <v>4</v>
@@ -9077,48 +9097,48 @@
         <v>44</v>
       </c>
       <c r="W58" s="37" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="Y58" s="37" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="Z58" s="37" t="s">
         <v>41</v>
       </c>
       <c r="AE58" s="37" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="AF58" s="37" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="AH58" s="37" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
     <row r="59" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B59" s="28">
+        <v>389</v>
+      </c>
+      <c r="B59" s="94">
         <v>2025</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O59" s="37" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="P59" s="28">
         <v>6</v>
@@ -9136,48 +9156,48 @@
         <v>44</v>
       </c>
       <c r="W59" s="37" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="Y59" s="37" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="Z59" s="37" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AE59" s="37" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="AF59" s="37" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="AH59" s="37" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B60" s="28">
+        <v>389</v>
+      </c>
+      <c r="B60" s="94">
         <v>2025</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O60" s="37" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="P60" s="28">
         <v>10</v>
@@ -9195,22 +9215,22 @@
         <v>44</v>
       </c>
       <c r="W60" s="37" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="Y60" s="37" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="Z60" s="37" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="AE60" s="37" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="AF60" s="37" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="AH60" s="37" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="AI60"/>
       <c r="AJ60"/>
@@ -9224,13 +9244,13 @@
       </c>
       <c r="C61" s="89"/>
       <c r="D61" s="22" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="F61" s="80" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="G61" s="24" t="s">
         <v>145</v>
@@ -9241,14 +9261,14 @@
       <c r="I61" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="J61" s="31" t="s">
-        <v>61</v>
+      <c r="J61" s="25" t="s">
+        <v>73</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>253</v>
+        <v>797</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="M61" s="23" t="s">
         <v>121</v>
@@ -9257,7 +9277,7 @@
         <v>43</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="P61" s="22">
         <v>6</v>
@@ -9277,28 +9297,28 @@
         <v>43</v>
       </c>
       <c r="W61" s="23" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="X61" s="23"/>
       <c r="Y61" s="23" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="Z61" s="23" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="AA61" s="23" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="AB61" s="23"/>
       <c r="AC61" s="23"/>
       <c r="AD61" s="23" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="AE61" s="23" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="AF61" s="23" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="AG61" s="23"/>
       <c r="AH61" s="23" t="s">
@@ -9314,16 +9334,16 @@
       </c>
       <c r="C62" s="89"/>
       <c r="D62" s="46" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F62" s="48" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>118</v>
@@ -9332,13 +9352,13 @@
         <v>41</v>
       </c>
       <c r="J62" s="49" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>681</v>
+        <v>798</v>
       </c>
       <c r="L62" s="46" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="M62" s="48" t="s">
         <v>121</v>
@@ -9347,7 +9367,7 @@
         <v>44</v>
       </c>
       <c r="O62" s="46" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="P62" s="57">
         <v>5</v>
@@ -9367,28 +9387,28 @@
         <v>44</v>
       </c>
       <c r="W62" s="48" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="X62" s="90" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="Y62" s="48" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="Z62" s="48" t="s">
         <v>198</v>
       </c>
       <c r="AA62" s="48" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="AB62" s="48"/>
       <c r="AC62" s="48"/>
       <c r="AD62" s="48"/>
       <c r="AE62" s="48" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="AF62" s="48" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="AG62" s="48"/>
       <c r="AH62" s="48" t="s">
@@ -9408,31 +9428,31 @@
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="F63" s="80" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>41</v>
       </c>
       <c r="J63" s="25" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>695</v>
+        <v>799</v>
       </c>
       <c r="L63" s="22" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>55</v>
@@ -9441,7 +9461,7 @@
         <v>43</v>
       </c>
       <c r="O63" s="22" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="P63" s="87">
         <v>10</v>
@@ -9461,13 +9481,13 @@
         <v>44</v>
       </c>
       <c r="W63" s="91" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="X63" s="80" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="Y63" s="23" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="Z63" s="23" t="s">
         <v>198</v>
@@ -9477,10 +9497,10 @@
       <c r="AC63" s="23"/>
       <c r="AD63" s="23"/>
       <c r="AE63" s="23" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="AF63" s="23" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="AG63" s="23"/>
       <c r="AH63" s="23" t="s">
@@ -9491,26 +9511,26 @@
     </row>
     <row r="64" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B64" s="82">
         <v>2026</v>
       </c>
       <c r="C64" s="28"/>
       <c r="D64" s="61" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="E64" s="61" t="s">
         <v>41</v>
       </c>
       <c r="F64" s="63" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="G64" s="64" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="H64" s="63" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="I64" s="63" t="s">
         <v>41</v>
@@ -9527,7 +9547,7 @@
         <v>41</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="P64" s="63">
         <v>2</v>
@@ -9563,10 +9583,10 @@
       <c r="AC64" s="63"/>
       <c r="AD64" s="63"/>
       <c r="AE64" s="63" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="AF64" s="63" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="AG64" s="63"/>
       <c r="AH64" s="63" t="s">
@@ -9579,23 +9599,23 @@
       <c r="A65" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="94">
         <v>2026</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>41</v>
@@ -9604,10 +9624,10 @@
         <v>73</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>713</v>
+        <v>800</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="M65" s="37" t="s">
         <v>55</v>
@@ -9616,7 +9636,7 @@
         <v>43</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="P65" s="37">
         <v>6</v>
@@ -9634,22 +9654,22 @@
         <v>43</v>
       </c>
       <c r="W65" s="37" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="Y65" s="40" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="Z65" s="37" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AA65" s="37" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="AE65" s="37" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="AF65" s="37" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="AH65" s="23" t="s">
         <v>48</v>
@@ -9657,28 +9677,28 @@
     </row>
     <row r="66" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B66" s="28">
+        <v>389</v>
+      </c>
+      <c r="B66" s="94">
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O66" s="37" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="P66" s="37">
         <v>5</v>
@@ -9696,51 +9716,51 @@
         <v>44</v>
       </c>
       <c r="W66" s="37" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="X66" s="37" t="s">
         <v>41</v>
       </c>
       <c r="Y66" s="37" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="Z66" s="37" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="AE66" s="37" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="AF66" s="37" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="AH66" s="37" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
     </row>
     <row r="67" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B67" s="28">
+        <v>389</v>
+      </c>
+      <c r="B67" s="94">
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="O67" s="37" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="P67" s="28">
         <v>5</v>
@@ -9758,39 +9778,39 @@
         <v>44</v>
       </c>
       <c r="W67" s="37" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="AE67" s="37" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="AF67" s="37" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
     </row>
     <row r="68" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B68" s="28">
+        <v>389</v>
+      </c>
+      <c r="B68" s="94">
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O68" s="37" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="P68" s="28">
         <v>5</v>
@@ -9808,39 +9828,39 @@
         <v>44</v>
       </c>
       <c r="W68" s="37" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="AE68" s="37" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="AF68" s="37" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="69" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B69" s="28">
+        <v>389</v>
+      </c>
+      <c r="B69" s="94">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O69" s="37" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="P69" s="28">
         <v>5</v>
@@ -9858,39 +9878,39 @@
         <v>44</v>
       </c>
       <c r="W69" s="37" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="AE69" s="37" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="AF69" s="37" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="70" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B70" s="28">
+        <v>389</v>
+      </c>
+      <c r="B70" s="94">
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="F70" s="92" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O70" s="37" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="P70" s="28">
         <v>4</v>
@@ -9908,39 +9928,39 @@
         <v>44</v>
       </c>
       <c r="W70" s="37" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="AE70" s="37" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="AF70" s="37" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
     </row>
     <row r="71" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B71" s="28">
+        <v>389</v>
+      </c>
+      <c r="B71" s="94">
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O71" s="37" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="P71" s="28">
         <v>7</v>
@@ -9958,46 +9978,46 @@
         <v>44</v>
       </c>
       <c r="W71" s="37" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="Z71" s="37" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="AE71" s="37" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="AF71" s="37" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="AH71" s="37" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="AI71" s="37" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
     </row>
     <row r="72" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="78" t="s">
-        <v>373</v>
-      </c>
-      <c r="B72" s="65">
+        <v>372</v>
+      </c>
+      <c r="B72" s="95">
         <v>2026</v>
       </c>
       <c r="C72" s="28"/>
       <c r="D72" s="63" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="E72" s="63" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="G72" s="63" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="H72" s="63" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="I72" s="63" t="s">
         <v>41</v>
@@ -10014,7 +10034,7 @@
         <v>41</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="P72" s="65">
         <v>6</v>
@@ -10052,10 +10072,10 @@
       <c r="AC72" s="63"/>
       <c r="AD72" s="63"/>
       <c r="AE72" s="63" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="AF72" s="63" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="AG72" s="63"/>
       <c r="AH72" s="63" t="s">
@@ -10066,28 +10086,28 @@
     </row>
     <row r="73" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="B73" s="28">
+        <v>389</v>
+      </c>
+      <c r="B73" s="94">
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="F73" s="80" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="O73" s="37" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="P73" s="28">
         <v>6</v>
@@ -10105,35 +10125,35 @@
         <v>44</v>
       </c>
       <c r="W73" s="37" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="AE73" s="37" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="AF73" s="37" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
     </row>
     <row r="74" spans="1:36" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>390</v>
-      </c>
-      <c r="B74">
+        <v>389</v>
+      </c>
+      <c r="B74" s="96">
         <v>2026</v>
       </c>
       <c r="D74" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="E74" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="F74" s="92" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
       <c r="O74" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="P74">
         <v>6</v>
@@ -10148,28 +10168,2668 @@
         <v>44</v>
       </c>
       <c r="W74" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="Z74" s="37" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="AE74" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="AF74" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="AI74"/>
       <c r="AJ74"/>
     </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B75" s="94"/>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B76" s="94"/>
+    </row>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B77" s="94"/>
+    </row>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B78" s="94"/>
+    </row>
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B79" s="94"/>
+    </row>
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="B80" s="94"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81" s="94"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82" s="94"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83" s="94"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84" s="94"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85" s="94"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86" s="94"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87" s="94"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88" s="94"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89" s="94"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90" s="94"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91" s="94"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92" s="94"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93" s="94"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94" s="94"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95" s="94"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96" s="94"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97" s="94"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98" s="94"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99" s="94"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100" s="94"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101" s="94"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102" s="94"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103" s="94"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104" s="94"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105" s="94"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106" s="94"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107" s="94"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="94"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="94"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="94"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="94"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="94"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="94"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="94"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="94"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="94"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="94"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="94"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="94"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="94"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="94"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" s="94"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="94"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" s="94"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="94"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="94"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="94"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="94"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="94"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="94"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="94"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="94"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="94"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="94"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="94"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="94"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="94"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="94"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="94"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="94"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" s="94"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" s="94"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="94"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="94"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="94"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="94"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="94"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="94"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="94"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="94"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" s="94"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="94"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="94"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="94"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" s="94"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="94"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="94"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="94"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="94"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="94"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="94"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="94"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="94"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="94"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="94"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="94"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="94"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="94"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="94"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="94"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="94"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" s="94"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="94"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" s="94"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" s="94"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="94"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="94"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="94"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="94"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="94"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="94"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="94"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="94"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="94"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" s="94"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" s="94"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187" s="94"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188" s="94"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" s="94"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" s="94"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" s="94"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192" s="94"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B193" s="94"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B194" s="94"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B195" s="94"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B196" s="94"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B197" s="94"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B198" s="94"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199" s="94"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B200" s="94"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B201" s="94"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B202" s="94"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B203" s="94"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B204" s="94"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205" s="94"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B206" s="94"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B207" s="94"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208" s="94"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B209" s="94"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210" s="94"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B211" s="94"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B212" s="94"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B213" s="94"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B214" s="94"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B215" s="94"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216" s="94"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B217" s="94"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218" s="94"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B219" s="94"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220" s="94"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" s="94"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222" s="94"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" s="94"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" s="94"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B225" s="94"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226" s="94"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B227" s="94"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228" s="94"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229" s="94"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230" s="94"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231" s="94"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" s="94"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233" s="94"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" s="94"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235" s="94"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236" s="94"/>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B237" s="94"/>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B238" s="94"/>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B239" s="94"/>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B240" s="94"/>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241" s="94"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B242" s="94"/>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243" s="94"/>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B244" s="94"/>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B245" s="94"/>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B246" s="94"/>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B247" s="94"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248" s="94"/>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B249" s="94"/>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B250" s="94"/>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B251" s="94"/>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B252" s="94"/>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B253" s="94"/>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B254" s="94"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B255" s="94"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B256" s="94"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B257" s="94"/>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B258" s="94"/>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B259" s="94"/>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B260" s="94"/>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B261" s="94"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B262" s="94"/>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B263" s="94"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B264" s="94"/>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B265" s="94"/>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B266" s="94"/>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B267" s="94"/>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B268" s="94"/>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B269" s="94"/>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B270" s="94"/>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B271" s="94"/>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B272" s="94"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B273" s="94"/>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B274" s="94"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B275" s="94"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B276" s="94"/>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B277" s="94"/>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B278" s="94"/>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B279" s="94"/>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B280" s="94"/>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B281" s="94"/>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B282" s="94"/>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B283" s="94"/>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B284" s="94"/>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B285" s="94"/>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B286" s="94"/>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B287" s="94"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B288" s="94"/>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B289" s="94"/>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B290" s="94"/>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B291" s="94"/>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B292" s="94"/>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B293" s="94"/>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B294" s="94"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B295" s="94"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B296" s="94"/>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B297" s="94"/>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B298" s="94"/>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B299" s="94"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B300" s="94"/>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B301" s="94"/>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B302" s="94"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B303" s="94"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B304" s="94"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B305" s="94"/>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B306" s="94"/>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B307" s="94"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B308" s="94"/>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B309" s="94"/>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B310" s="94"/>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B311" s="94"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B312" s="94"/>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B313" s="94"/>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B314" s="94"/>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B315" s="94"/>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B316" s="94"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B317" s="94"/>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B318" s="94"/>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B319" s="94"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B320" s="94"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B321" s="94"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B322" s="94"/>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B323" s="94"/>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B324" s="94"/>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B325" s="94"/>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B326" s="94"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B327" s="94"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B328" s="94"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B329" s="94"/>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B330" s="94"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B331" s="94"/>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B332" s="94"/>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B333" s="94"/>
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B334" s="94"/>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B335" s="94"/>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B336" s="94"/>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B337" s="94"/>
+    </row>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B338" s="94"/>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B339" s="94"/>
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B340" s="94"/>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B341" s="94"/>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B342" s="94"/>
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B343" s="94"/>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B344" s="94"/>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B345" s="94"/>
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B346" s="94"/>
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B347" s="94"/>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B348" s="94"/>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B349" s="94"/>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B350" s="94"/>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B351" s="94"/>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B352" s="94"/>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B353" s="94"/>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B354" s="94"/>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B355" s="94"/>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B356" s="94"/>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B357" s="94"/>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B358" s="94"/>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B359" s="94"/>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B360" s="94"/>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B361" s="94"/>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B362" s="94"/>
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B363" s="94"/>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B364" s="94"/>
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B365" s="94"/>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B366" s="94"/>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B367" s="94"/>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B368" s="94"/>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B369" s="94"/>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B370" s="94"/>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B371" s="94"/>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B372" s="94"/>
+    </row>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B373" s="94"/>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B374" s="94"/>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B375" s="94"/>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B376" s="94"/>
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B377" s="94"/>
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B378" s="94"/>
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B379" s="94"/>
+    </row>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B380" s="94"/>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B381" s="94"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B382" s="94"/>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B383" s="94"/>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B384" s="94"/>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B385" s="94"/>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B386" s="94"/>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B387" s="94"/>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B388" s="94"/>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B389" s="94"/>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B390" s="94"/>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B391" s="94"/>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B392" s="94"/>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B393" s="94"/>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B394" s="94"/>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B395" s="94"/>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B396" s="94"/>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B397" s="94"/>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B398" s="94"/>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B399" s="94"/>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B400" s="94"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B401" s="94"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B402" s="94"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B403" s="94"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B404" s="94"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B405" s="94"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B406" s="94"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B407" s="94"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B408" s="94"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B409" s="94"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B410" s="94"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B411" s="94"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B412" s="94"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B413" s="94"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B414" s="94"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B415" s="94"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B416" s="94"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B417" s="94"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B418" s="94"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B419" s="94"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B420" s="94"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B421" s="94"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B422" s="94"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B423" s="94"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B424" s="94"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B425" s="94"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B426" s="94"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B427" s="94"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B428" s="94"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B429" s="94"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B430" s="94"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B431" s="94"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B432" s="94"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B433" s="94"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B434" s="94"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B435" s="94"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B436" s="94"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B437" s="94"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B438" s="94"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B439" s="94"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B440" s="94"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B441" s="94"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B442" s="94"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B443" s="94"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B444" s="94"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B445" s="94"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B446" s="94"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B447" s="94"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B448" s="94"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B449" s="94"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B450" s="94"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B451" s="94"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B452" s="94"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B453" s="94"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B454" s="94"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B455" s="94"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B456" s="94"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B457" s="94"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B458" s="94"/>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B459" s="94"/>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B460" s="94"/>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B461" s="94"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B462" s="94"/>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B463" s="94"/>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B464" s="94"/>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B465" s="94"/>
+    </row>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B466" s="94"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B467" s="94"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B468" s="94"/>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B469" s="94"/>
+    </row>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B470" s="94"/>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B471" s="94"/>
+    </row>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B472" s="94"/>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B473" s="94"/>
+    </row>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B474" s="94"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B475" s="94"/>
+    </row>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B476" s="94"/>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B477" s="94"/>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B478" s="94"/>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B479" s="94"/>
+    </row>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B480" s="94"/>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B481" s="94"/>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B482" s="94"/>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B483" s="94"/>
+    </row>
+    <row r="484" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B484" s="94"/>
+    </row>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B485" s="94"/>
+    </row>
+    <row r="486" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B486" s="94"/>
+    </row>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B487" s="94"/>
+    </row>
+    <row r="488" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B488" s="94"/>
+    </row>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B489" s="94"/>
+    </row>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B490" s="94"/>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B491" s="94"/>
+    </row>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B492" s="94"/>
+    </row>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B493" s="94"/>
+    </row>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B494" s="94"/>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B495" s="94"/>
+    </row>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B496" s="94"/>
+    </row>
+    <row r="497" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B497" s="94"/>
+    </row>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B498" s="94"/>
+    </row>
+    <row r="499" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B499" s="94"/>
+    </row>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B500" s="94"/>
+    </row>
+    <row r="501" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B501" s="94"/>
+    </row>
+    <row r="502" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B502" s="94"/>
+    </row>
+    <row r="503" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B503" s="94"/>
+    </row>
+    <row r="504" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B504" s="94"/>
+    </row>
+    <row r="505" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B505" s="94"/>
+    </row>
+    <row r="506" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B506" s="94"/>
+    </row>
+    <row r="507" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B507" s="94"/>
+    </row>
+    <row r="508" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B508" s="94"/>
+    </row>
+    <row r="509" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B509" s="94"/>
+    </row>
+    <row r="510" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B510" s="94"/>
+    </row>
+    <row r="511" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B511" s="94"/>
+    </row>
+    <row r="512" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B512" s="94"/>
+    </row>
+    <row r="513" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B513" s="94"/>
+    </row>
+    <row r="514" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B514" s="94"/>
+    </row>
+    <row r="515" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B515" s="94"/>
+    </row>
+    <row r="516" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B516" s="94"/>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B517" s="94"/>
+    </row>
+    <row r="518" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B518" s="94"/>
+    </row>
+    <row r="519" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B519" s="94"/>
+    </row>
+    <row r="520" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B520" s="94"/>
+    </row>
+    <row r="521" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B521" s="94"/>
+    </row>
+    <row r="522" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B522" s="94"/>
+    </row>
+    <row r="523" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B523" s="94"/>
+    </row>
+    <row r="524" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B524" s="94"/>
+    </row>
+    <row r="525" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B525" s="94"/>
+    </row>
+    <row r="526" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B526" s="94"/>
+    </row>
+    <row r="527" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B527" s="94"/>
+    </row>
+    <row r="528" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B528" s="94"/>
+    </row>
+    <row r="529" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B529" s="94"/>
+    </row>
+    <row r="530" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B530" s="94"/>
+    </row>
+    <row r="531" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B531" s="94"/>
+    </row>
+    <row r="532" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B532" s="94"/>
+    </row>
+    <row r="533" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B533" s="94"/>
+    </row>
+    <row r="534" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B534" s="94"/>
+    </row>
+    <row r="535" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B535" s="94"/>
+    </row>
+    <row r="536" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B536" s="94"/>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B537" s="94"/>
+    </row>
+    <row r="538" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B538" s="94"/>
+    </row>
+    <row r="539" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B539" s="94"/>
+    </row>
+    <row r="540" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B540" s="94"/>
+    </row>
+    <row r="541" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B541" s="94"/>
+    </row>
+    <row r="542" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B542" s="94"/>
+    </row>
+    <row r="543" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B543" s="94"/>
+    </row>
+    <row r="544" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B544" s="94"/>
+    </row>
+    <row r="545" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B545" s="94"/>
+    </row>
+    <row r="546" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B546" s="94"/>
+    </row>
+    <row r="547" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B547" s="94"/>
+    </row>
+    <row r="548" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B548" s="94"/>
+    </row>
+    <row r="549" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B549" s="94"/>
+    </row>
+    <row r="550" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B550" s="94"/>
+    </row>
+    <row r="551" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B551" s="94"/>
+    </row>
+    <row r="552" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B552" s="94"/>
+    </row>
+    <row r="553" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B553" s="94"/>
+    </row>
+    <row r="554" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B554" s="94"/>
+    </row>
+    <row r="555" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B555" s="94"/>
+    </row>
+    <row r="556" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B556" s="94"/>
+    </row>
+    <row r="557" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B557" s="94"/>
+    </row>
+    <row r="558" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B558" s="94"/>
+    </row>
+    <row r="559" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B559" s="94"/>
+    </row>
+    <row r="560" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B560" s="94"/>
+    </row>
+    <row r="561" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B561" s="94"/>
+    </row>
+    <row r="562" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B562" s="94"/>
+    </row>
+    <row r="563" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B563" s="94"/>
+    </row>
+    <row r="564" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B564" s="94"/>
+    </row>
+    <row r="565" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B565" s="94"/>
+    </row>
+    <row r="566" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B566" s="94"/>
+    </row>
+    <row r="567" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B567" s="94"/>
+    </row>
+    <row r="568" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B568" s="94"/>
+    </row>
+    <row r="569" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B569" s="94"/>
+    </row>
+    <row r="570" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B570" s="94"/>
+    </row>
+    <row r="571" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B571" s="94"/>
+    </row>
+    <row r="572" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B572" s="94"/>
+    </row>
+    <row r="573" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B573" s="94"/>
+    </row>
+    <row r="574" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B574" s="94"/>
+    </row>
+    <row r="575" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B575" s="94"/>
+    </row>
+    <row r="576" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B576" s="94"/>
+    </row>
+    <row r="577" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B577" s="94"/>
+    </row>
+    <row r="578" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B578" s="94"/>
+    </row>
+    <row r="579" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B579" s="94"/>
+    </row>
+    <row r="580" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B580" s="94"/>
+    </row>
+    <row r="581" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B581" s="94"/>
+    </row>
+    <row r="582" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B582" s="94"/>
+    </row>
+    <row r="583" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B583" s="94"/>
+    </row>
+    <row r="584" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B584" s="94"/>
+    </row>
+    <row r="585" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B585" s="94"/>
+    </row>
+    <row r="586" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B586" s="94"/>
+    </row>
+    <row r="587" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B587" s="94"/>
+    </row>
+    <row r="588" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B588" s="94"/>
+    </row>
+    <row r="589" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B589" s="94"/>
+    </row>
+    <row r="590" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B590" s="94"/>
+    </row>
+    <row r="591" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B591" s="94"/>
+    </row>
+    <row r="592" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B592" s="94"/>
+    </row>
+    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B593" s="94"/>
+    </row>
+    <row r="594" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B594" s="94"/>
+    </row>
+    <row r="595" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B595" s="94"/>
+    </row>
+    <row r="596" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B596" s="94"/>
+    </row>
+    <row r="597" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B597" s="94"/>
+    </row>
+    <row r="598" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B598" s="94"/>
+    </row>
+    <row r="599" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B599" s="94"/>
+    </row>
+    <row r="600" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B600" s="94"/>
+    </row>
+    <row r="601" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B601" s="94"/>
+    </row>
+    <row r="602" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B602" s="94"/>
+    </row>
+    <row r="603" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B603" s="94"/>
+    </row>
+    <row r="604" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B604" s="94"/>
+    </row>
+    <row r="605" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B605" s="94"/>
+    </row>
+    <row r="606" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B606" s="94"/>
+    </row>
+    <row r="607" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B607" s="94"/>
+    </row>
+    <row r="608" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B608" s="94"/>
+    </row>
+    <row r="609" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B609" s="94"/>
+    </row>
+    <row r="610" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B610" s="94"/>
+    </row>
+    <row r="611" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B611" s="94"/>
+    </row>
+    <row r="612" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B612" s="94"/>
+    </row>
+    <row r="613" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B613" s="94"/>
+    </row>
+    <row r="614" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B614" s="94"/>
+    </row>
+    <row r="615" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B615" s="94"/>
+    </row>
+    <row r="616" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B616" s="94"/>
+    </row>
+    <row r="617" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B617" s="94"/>
+    </row>
+    <row r="618" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B618" s="94"/>
+    </row>
+    <row r="619" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B619" s="94"/>
+    </row>
+    <row r="620" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B620" s="94"/>
+    </row>
+    <row r="621" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B621" s="94"/>
+    </row>
+    <row r="622" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B622" s="94"/>
+    </row>
+    <row r="623" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B623" s="94"/>
+    </row>
+    <row r="624" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B624" s="94"/>
+    </row>
+    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B625" s="94"/>
+    </row>
+    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B626" s="94"/>
+    </row>
+    <row r="627" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B627" s="94"/>
+    </row>
+    <row r="628" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B628" s="94"/>
+    </row>
+    <row r="629" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B629" s="94"/>
+    </row>
+    <row r="630" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B630" s="94"/>
+    </row>
+    <row r="631" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B631" s="94"/>
+    </row>
+    <row r="632" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B632" s="94"/>
+    </row>
+    <row r="633" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B633" s="94"/>
+    </row>
+    <row r="634" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B634" s="94"/>
+    </row>
+    <row r="635" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B635" s="94"/>
+    </row>
+    <row r="636" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B636" s="94"/>
+    </row>
+    <row r="637" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B637" s="94"/>
+    </row>
+    <row r="638" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B638" s="94"/>
+    </row>
+    <row r="639" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B639" s="94"/>
+    </row>
+    <row r="640" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B640" s="94"/>
+    </row>
+    <row r="641" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B641" s="94"/>
+    </row>
+    <row r="642" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B642" s="94"/>
+    </row>
+    <row r="643" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B643" s="94"/>
+    </row>
+    <row r="644" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B644" s="94"/>
+    </row>
+    <row r="645" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B645" s="94"/>
+    </row>
+    <row r="646" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B646" s="94"/>
+    </row>
+    <row r="647" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B647" s="94"/>
+    </row>
+    <row r="648" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B648" s="94"/>
+    </row>
+    <row r="649" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B649" s="94"/>
+    </row>
+    <row r="650" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B650" s="94"/>
+    </row>
+    <row r="651" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B651" s="94"/>
+    </row>
+    <row r="652" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B652" s="94"/>
+    </row>
+    <row r="653" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B653" s="94"/>
+    </row>
+    <row r="654" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B654" s="94"/>
+    </row>
+    <row r="655" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B655" s="94"/>
+    </row>
+    <row r="656" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B656" s="94"/>
+    </row>
+    <row r="657" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B657" s="94"/>
+    </row>
+    <row r="658" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B658" s="94"/>
+    </row>
+    <row r="659" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B659" s="94"/>
+    </row>
+    <row r="660" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B660" s="94"/>
+    </row>
+    <row r="661" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B661" s="94"/>
+    </row>
+    <row r="662" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B662" s="94"/>
+    </row>
+    <row r="663" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B663" s="94"/>
+    </row>
+    <row r="664" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B664" s="94"/>
+    </row>
+    <row r="665" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B665" s="94"/>
+    </row>
+    <row r="666" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B666" s="94"/>
+    </row>
+    <row r="667" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B667" s="94"/>
+    </row>
+    <row r="668" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B668" s="94"/>
+    </row>
+    <row r="669" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B669" s="94"/>
+    </row>
+    <row r="670" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B670" s="94"/>
+    </row>
+    <row r="671" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B671" s="94"/>
+    </row>
+    <row r="672" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B672" s="94"/>
+    </row>
+    <row r="673" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B673" s="94"/>
+    </row>
+    <row r="674" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B674" s="94"/>
+    </row>
+    <row r="675" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B675" s="94"/>
+    </row>
+    <row r="676" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B676" s="94"/>
+    </row>
+    <row r="677" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B677" s="94"/>
+    </row>
+    <row r="678" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B678" s="94"/>
+    </row>
+    <row r="679" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B679" s="94"/>
+    </row>
+    <row r="680" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B680" s="94"/>
+    </row>
+    <row r="681" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B681" s="94"/>
+    </row>
+    <row r="682" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B682" s="94"/>
+    </row>
+    <row r="683" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B683" s="94"/>
+    </row>
+    <row r="684" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B684" s="94"/>
+    </row>
+    <row r="685" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B685" s="94"/>
+    </row>
+    <row r="686" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B686" s="94"/>
+    </row>
+    <row r="687" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B687" s="94"/>
+    </row>
+    <row r="688" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B688" s="94"/>
+    </row>
+    <row r="689" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B689" s="94"/>
+    </row>
+    <row r="690" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B690" s="94"/>
+    </row>
+    <row r="691" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B691" s="94"/>
+    </row>
+    <row r="692" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B692" s="94"/>
+    </row>
+    <row r="693" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B693" s="94"/>
+    </row>
+    <row r="694" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B694" s="94"/>
+    </row>
+    <row r="695" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B695" s="94"/>
+    </row>
+    <row r="696" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B696" s="94"/>
+    </row>
+    <row r="697" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B697" s="94"/>
+    </row>
+    <row r="698" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B698" s="94"/>
+    </row>
+    <row r="699" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B699" s="94"/>
+    </row>
+    <row r="700" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B700" s="94"/>
+    </row>
+    <row r="701" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B701" s="94"/>
+    </row>
+    <row r="702" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B702" s="94"/>
+    </row>
+    <row r="703" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B703" s="94"/>
+    </row>
+    <row r="704" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B704" s="94"/>
+    </row>
+    <row r="705" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B705" s="94"/>
+    </row>
+    <row r="706" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B706" s="94"/>
+    </row>
+    <row r="707" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B707" s="94"/>
+    </row>
+    <row r="708" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B708" s="94"/>
+    </row>
+    <row r="709" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B709" s="94"/>
+    </row>
+    <row r="710" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B710" s="94"/>
+    </row>
+    <row r="711" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B711" s="94"/>
+    </row>
+    <row r="712" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B712" s="94"/>
+    </row>
+    <row r="713" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B713" s="94"/>
+    </row>
+    <row r="714" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B714" s="94"/>
+    </row>
+    <row r="715" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B715" s="94"/>
+    </row>
+    <row r="716" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B716" s="94"/>
+    </row>
+    <row r="717" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B717" s="94"/>
+    </row>
+    <row r="718" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B718" s="94"/>
+    </row>
+    <row r="719" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B719" s="94"/>
+    </row>
+    <row r="720" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B720" s="94"/>
+    </row>
+    <row r="721" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B721" s="94"/>
+    </row>
+    <row r="722" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B722" s="94"/>
+    </row>
+    <row r="723" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B723" s="94"/>
+    </row>
+    <row r="724" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B724" s="94"/>
+    </row>
+    <row r="725" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B725" s="94"/>
+    </row>
+    <row r="726" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B726" s="94"/>
+    </row>
+    <row r="727" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B727" s="94"/>
+    </row>
+    <row r="728" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B728" s="94"/>
+    </row>
+    <row r="729" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B729" s="94"/>
+    </row>
+    <row r="730" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B730" s="94"/>
+    </row>
+    <row r="731" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B731" s="94"/>
+    </row>
+    <row r="732" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B732" s="94"/>
+    </row>
+    <row r="733" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B733" s="94"/>
+    </row>
+    <row r="734" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B734" s="94"/>
+    </row>
+    <row r="735" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B735" s="94"/>
+    </row>
+    <row r="736" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B736" s="94"/>
+    </row>
+    <row r="737" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B737" s="94"/>
+    </row>
+    <row r="738" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B738" s="94"/>
+    </row>
+    <row r="739" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B739" s="94"/>
+    </row>
+    <row r="740" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B740" s="94"/>
+    </row>
+    <row r="741" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B741" s="94"/>
+    </row>
+    <row r="742" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B742" s="94"/>
+    </row>
+    <row r="743" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B743" s="94"/>
+    </row>
+    <row r="744" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B744" s="94"/>
+    </row>
+    <row r="745" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B745" s="94"/>
+    </row>
+    <row r="746" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B746" s="94"/>
+    </row>
+    <row r="747" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B747" s="94"/>
+    </row>
+    <row r="748" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B748" s="94"/>
+    </row>
+    <row r="749" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B749" s="94"/>
+    </row>
+    <row r="750" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B750" s="94"/>
+    </row>
+    <row r="751" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B751" s="94"/>
+    </row>
+    <row r="752" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B752" s="94"/>
+    </row>
+    <row r="753" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B753" s="94"/>
+    </row>
+    <row r="754" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B754" s="94"/>
+    </row>
+    <row r="755" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B755" s="94"/>
+    </row>
+    <row r="756" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B756" s="94"/>
+    </row>
+    <row r="757" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B757" s="94"/>
+    </row>
+    <row r="758" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B758" s="94"/>
+    </row>
+    <row r="759" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B759" s="94"/>
+    </row>
+    <row r="760" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B760" s="94"/>
+    </row>
+    <row r="761" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B761" s="94"/>
+    </row>
+    <row r="762" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B762" s="94"/>
+    </row>
+    <row r="763" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B763" s="94"/>
+    </row>
+    <row r="764" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B764" s="94"/>
+    </row>
+    <row r="765" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B765" s="94"/>
+    </row>
+    <row r="766" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B766" s="94"/>
+    </row>
+    <row r="767" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B767" s="94"/>
+    </row>
+    <row r="768" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B768" s="94"/>
+    </row>
+    <row r="769" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B769" s="94"/>
+    </row>
+    <row r="770" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B770" s="94"/>
+    </row>
+    <row r="771" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B771" s="94"/>
+    </row>
+    <row r="772" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B772" s="94"/>
+    </row>
+    <row r="773" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B773" s="94"/>
+    </row>
+    <row r="774" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B774" s="94"/>
+    </row>
+    <row r="775" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B775" s="94"/>
+    </row>
+    <row r="776" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B776" s="94"/>
+    </row>
+    <row r="777" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B777" s="94"/>
+    </row>
+    <row r="778" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B778" s="94"/>
+    </row>
+    <row r="779" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B779" s="94"/>
+    </row>
+    <row r="780" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B780" s="94"/>
+    </row>
+    <row r="781" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B781" s="94"/>
+    </row>
+    <row r="782" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B782" s="94"/>
+    </row>
+    <row r="783" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B783" s="94"/>
+    </row>
+    <row r="784" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B784" s="94"/>
+    </row>
+    <row r="785" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B785" s="94"/>
+    </row>
+    <row r="786" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B786" s="94"/>
+    </row>
+    <row r="787" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B787" s="94"/>
+    </row>
+    <row r="788" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B788" s="94"/>
+    </row>
+    <row r="789" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B789" s="94"/>
+    </row>
+    <row r="790" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B790" s="94"/>
+    </row>
+    <row r="791" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B791" s="94"/>
+    </row>
+    <row r="792" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B792" s="94"/>
+    </row>
+    <row r="793" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B793" s="94"/>
+    </row>
+    <row r="794" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B794" s="94"/>
+    </row>
+    <row r="795" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B795" s="94"/>
+    </row>
+    <row r="796" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B796" s="94"/>
+    </row>
+    <row r="797" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B797" s="94"/>
+    </row>
+    <row r="798" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B798" s="94"/>
+    </row>
+    <row r="799" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B799" s="94"/>
+    </row>
+    <row r="800" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B800" s="94"/>
+    </row>
+    <row r="801" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B801" s="94"/>
+    </row>
+    <row r="802" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B802" s="94"/>
+    </row>
+    <row r="803" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B803" s="94"/>
+    </row>
+    <row r="804" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B804" s="94"/>
+    </row>
+    <row r="805" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B805" s="94"/>
+    </row>
+    <row r="806" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B806" s="94"/>
+    </row>
+    <row r="807" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B807" s="94"/>
+    </row>
+    <row r="808" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B808" s="94"/>
+    </row>
+    <row r="809" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B809" s="94"/>
+    </row>
+    <row r="810" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B810" s="94"/>
+    </row>
+    <row r="811" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B811" s="94"/>
+    </row>
+    <row r="812" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B812" s="94"/>
+    </row>
+    <row r="813" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B813" s="94"/>
+    </row>
+    <row r="814" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B814" s="94"/>
+    </row>
+    <row r="815" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B815" s="94"/>
+    </row>
+    <row r="816" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B816" s="94"/>
+    </row>
+    <row r="817" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B817" s="94"/>
+    </row>
+    <row r="818" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B818" s="94"/>
+    </row>
+    <row r="819" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B819" s="94"/>
+    </row>
+    <row r="820" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B820" s="94"/>
+    </row>
+    <row r="821" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B821" s="94"/>
+    </row>
+    <row r="822" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B822" s="94"/>
+    </row>
+    <row r="823" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B823" s="94"/>
+    </row>
+    <row r="824" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B824" s="94"/>
+    </row>
+    <row r="825" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B825" s="94"/>
+    </row>
+    <row r="826" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B826" s="94"/>
+    </row>
+    <row r="827" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B827" s="94"/>
+    </row>
+    <row r="828" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B828" s="94"/>
+    </row>
+    <row r="829" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B829" s="94"/>
+    </row>
+    <row r="830" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B830" s="94"/>
+    </row>
+    <row r="831" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B831" s="94"/>
+    </row>
+    <row r="832" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B832" s="94"/>
+    </row>
+    <row r="833" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B833" s="94"/>
+    </row>
+    <row r="834" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B834" s="94"/>
+    </row>
+    <row r="835" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B835" s="94"/>
+    </row>
+    <row r="836" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B836" s="94"/>
+    </row>
+    <row r="837" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B837" s="94"/>
+    </row>
+    <row r="838" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B838" s="94"/>
+    </row>
+    <row r="839" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B839" s="94"/>
+    </row>
+    <row r="840" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B840" s="94"/>
+    </row>
+    <row r="841" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B841" s="94"/>
+    </row>
+    <row r="842" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B842" s="94"/>
+    </row>
+    <row r="843" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B843" s="94"/>
+    </row>
+    <row r="844" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B844" s="94"/>
+    </row>
+    <row r="845" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B845" s="94"/>
+    </row>
+    <row r="846" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B846" s="94"/>
+    </row>
+    <row r="847" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B847" s="94"/>
+    </row>
+    <row r="848" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B848" s="94"/>
+    </row>
+    <row r="849" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B849" s="94"/>
+    </row>
+    <row r="850" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B850" s="94"/>
+    </row>
+    <row r="851" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B851" s="94"/>
+    </row>
+    <row r="852" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B852" s="94"/>
+    </row>
+    <row r="853" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B853" s="94"/>
+    </row>
+    <row r="854" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B854" s="94"/>
+    </row>
+    <row r="855" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B855" s="94"/>
+    </row>
+    <row r="856" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B856" s="94"/>
+    </row>
+    <row r="857" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B857" s="94"/>
+    </row>
+    <row r="858" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B858" s="94"/>
+    </row>
+    <row r="859" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B859" s="94"/>
+    </row>
+    <row r="860" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B860" s="94"/>
+    </row>
+    <row r="861" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B861" s="94"/>
+    </row>
+    <row r="862" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B862" s="94"/>
+    </row>
+    <row r="863" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B863" s="94"/>
+    </row>
+    <row r="864" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B864" s="94"/>
+    </row>
+    <row r="865" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B865" s="94"/>
+    </row>
+    <row r="866" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B866" s="94"/>
+    </row>
+    <row r="867" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B867" s="94"/>
+    </row>
+    <row r="868" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B868" s="94"/>
+    </row>
+    <row r="869" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B869" s="94"/>
+    </row>
+    <row r="870" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B870" s="94"/>
+    </row>
+    <row r="871" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B871" s="94"/>
+    </row>
+    <row r="872" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B872" s="94"/>
+    </row>
+    <row r="873" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B873" s="94"/>
+    </row>
+    <row r="874" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B874" s="94"/>
+    </row>
+    <row r="875" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B875" s="94"/>
+    </row>
+    <row r="876" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B876" s="94"/>
+    </row>
+    <row r="877" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B877" s="94"/>
+    </row>
+    <row r="878" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B878" s="94"/>
+    </row>
+    <row r="879" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B879" s="94"/>
+    </row>
+    <row r="880" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B880" s="94"/>
+    </row>
+    <row r="881" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B881" s="94"/>
+    </row>
+    <row r="882" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B882" s="94"/>
+    </row>
+    <row r="883" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B883" s="94"/>
+    </row>
+    <row r="884" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B884" s="94"/>
+    </row>
+    <row r="885" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B885" s="94"/>
+    </row>
+    <row r="886" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B886" s="94"/>
+    </row>
+    <row r="887" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B887" s="94"/>
+    </row>
+    <row r="888" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B888" s="94"/>
+    </row>
+    <row r="889" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B889" s="94"/>
+    </row>
+    <row r="890" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B890" s="94"/>
+    </row>
+    <row r="891" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B891" s="94"/>
+    </row>
+    <row r="892" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B892" s="94"/>
+    </row>
+    <row r="893" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B893" s="94"/>
+    </row>
+    <row r="894" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B894" s="94"/>
+    </row>
+    <row r="895" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B895" s="94"/>
+    </row>
+    <row r="896" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B896" s="94"/>
+    </row>
+    <row r="897" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B897" s="94"/>
+    </row>
+    <row r="898" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B898" s="94"/>
+    </row>
+    <row r="899" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B899" s="94"/>
+    </row>
+    <row r="900" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B900" s="94"/>
+    </row>
+    <row r="901" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B901" s="94"/>
+    </row>
+    <row r="902" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B902" s="94"/>
+    </row>
+    <row r="903" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B903" s="94"/>
+    </row>
+    <row r="904" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B904" s="94"/>
+    </row>
+    <row r="905" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B905" s="94"/>
+    </row>
+    <row r="906" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B906" s="94"/>
+    </row>
+    <row r="907" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B907" s="94"/>
+    </row>
+    <row r="908" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B908" s="94"/>
+    </row>
+    <row r="909" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B909" s="94"/>
+    </row>
+    <row r="910" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B910" s="94"/>
+    </row>
+    <row r="911" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B911" s="94"/>
+    </row>
+    <row r="912" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B912" s="94"/>
+    </row>
+    <row r="913" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B913" s="94"/>
+    </row>
+    <row r="914" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B914" s="94"/>
+    </row>
+    <row r="915" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B915" s="94"/>
+    </row>
+    <row r="916" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B916" s="94"/>
+    </row>
+    <row r="917" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B917" s="94"/>
+    </row>
+    <row r="918" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B918" s="94"/>
+    </row>
+    <row r="919" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B919" s="94"/>
+    </row>
+    <row r="920" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B920" s="94"/>
+    </row>
+    <row r="921" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B921" s="94"/>
+    </row>
+    <row r="922" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B922" s="94"/>
+    </row>
+    <row r="923" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B923" s="94"/>
+    </row>
+    <row r="924" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B924" s="94"/>
+    </row>
+    <row r="925" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B925" s="94"/>
+    </row>
+    <row r="926" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B926" s="94"/>
+    </row>
+    <row r="927" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B927" s="94"/>
+    </row>
+    <row r="928" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B928" s="94"/>
+    </row>
+    <row r="929" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B929" s="94"/>
+    </row>
+    <row r="930" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B930" s="94"/>
+    </row>
+    <row r="931" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B931" s="94"/>
+    </row>
+    <row r="932" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B932" s="94"/>
+    </row>
+    <row r="933" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B933" s="94"/>
+    </row>
+    <row r="934" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B934" s="94"/>
+    </row>
+    <row r="935" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B935" s="94"/>
+    </row>
+    <row r="936" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B936" s="94"/>
+    </row>
+    <row r="937" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B937" s="94"/>
+    </row>
+    <row r="938" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B938" s="94"/>
+    </row>
+    <row r="939" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B939" s="94"/>
+    </row>
+    <row r="940" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B940" s="94"/>
+    </row>
+    <row r="941" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B941" s="94"/>
+    </row>
+    <row r="942" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B942" s="94"/>
+    </row>
+    <row r="943" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B943" s="94"/>
+    </row>
+    <row r="944" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B944" s="94"/>
+    </row>
+    <row r="945" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B945" s="94"/>
+    </row>
+    <row r="946" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B946" s="94"/>
+    </row>
+    <row r="947" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B947" s="94"/>
+    </row>
+    <row r="948" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B948" s="94"/>
+    </row>
+    <row r="949" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B949" s="94"/>
+    </row>
+    <row r="950" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B950" s="94"/>
+    </row>
+    <row r="951" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B951" s="94"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AJ74" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2.025"/>
+        <filter val="2.026"/>
+        <filter val="2025"/>
+        <filter val="2026"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:J1048576 M1:R1048576 V1:V1048576">
+  <conditionalFormatting sqref="M1:R1048576 V1:V1048576 E1:J1048576">
     <cfRule type="expression" dxfId="10" priority="8">
       <formula>LEN(TRIM(E1))=0</formula>
     </cfRule>
@@ -10179,14 +12839,14 @@
       <formula>LEN(TRIM(W1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X1:Y2 Z1:AA32 A1:B1048576 Y3 X4:Y32">
+  <conditionalFormatting sqref="X1:Y2 A1:B1048576 Y3 X4:Y32">
     <cfRule type="expression" dxfId="8" priority="13">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X34:AA1048576 X33 Z33:AA33">
+  <conditionalFormatting sqref="Z1:AA33 X33 X34:AA1048576">
     <cfRule type="expression" dxfId="7" priority="6">
-      <formula>LEN(TRIM(X33))=0</formula>
+      <formula>LEN(TRIM(X1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH1048576">

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1DA75DC-5395-8848-A590-278447BCE92E}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72BA24C-1FC2-6940-99FE-6E90FC8AB486}"/>
   <bookViews>
-    <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35860" yWindow="2620" windowWidth="35840" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -3005,13 +3005,13 @@
     <t>Índice de impacto JCR (2025): 2.2 (69/128 – Q3)</t>
   </si>
   <si>
-    <t>Índice de impacto JCR (2024): 4.5 (115/369 – Q2)</t>
-  </si>
-  <si>
     <t>Índice de impacto JCR (2025): 3.1 (26/104 – Q1)</t>
   </si>
   <si>
     <t>Índice de impacto JCR (2025): 3.1 (99/185, Q3)</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2025): 4.5 (115/369 – Q2)</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3238,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3507,13 +3507,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4579,7 +4572,7 @@
       <c r="AI7" s="9"/>
       <c r="AJ7" s="9"/>
     </row>
-    <row r="8" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
         <v>55</v>
       </c>
@@ -5311,7 +5304,7 @@
       <c r="AI15" s="63"/>
       <c r="AJ15" s="63"/>
     </row>
-    <row r="16" spans="1:36" s="53" customFormat="1" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="53" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="63" t="s">
         <v>55</v>
       </c>
@@ -5413,7 +5406,7 @@
       <c r="AI16" s="63"/>
       <c r="AJ16" s="63"/>
     </row>
-    <row r="17" spans="1:36" s="53" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="53" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="63" t="s">
         <v>55</v>
       </c>
@@ -5513,7 +5506,7 @@
       <c r="AI17" s="63"/>
       <c r="AJ17" s="63"/>
     </row>
-    <row r="18" spans="1:36" s="53" customFormat="1" ht="387.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" s="53" customFormat="1" ht="387.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="63" t="s">
         <v>55</v>
       </c>
@@ -5991,7 +5984,7 @@
       <c r="AI22" s="37"/>
       <c r="AJ22" s="37"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
         <v>55</v>
       </c>
@@ -6873,7 +6866,7 @@
       <c r="A33" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="94">
+      <c r="B33" s="37">
         <v>2026</v>
       </c>
       <c r="D33" s="37" t="s">
@@ -7109,7 +7102,7 @@
       <c r="AI35" s="63"/>
       <c r="AJ35" s="63"/>
     </row>
-    <row r="36" spans="1:36" s="54" customFormat="1" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" s="54" customFormat="1" ht="220.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="63" t="s">
         <v>55</v>
       </c>
@@ -7209,7 +7202,7 @@
       <c r="AI36" s="63"/>
       <c r="AJ36" s="63"/>
     </row>
-    <row r="37" spans="1:36" s="54" customFormat="1" ht="255" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" s="54" customFormat="1" ht="255" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="63" t="s">
         <v>55</v>
       </c>
@@ -7407,7 +7400,7 @@
       <c r="AI38" s="63"/>
       <c r="AJ38" s="63"/>
     </row>
-    <row r="39" spans="1:36" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" s="54" customFormat="1" ht="237.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="63" t="s">
         <v>55</v>
       </c>
@@ -7505,7 +7498,7 @@
       <c r="AI39" s="63"/>
       <c r="AJ39" s="63"/>
     </row>
-    <row r="40" spans="1:36" s="54" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" s="54" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="63" t="s">
         <v>55</v>
       </c>
@@ -7601,7 +7594,7 @@
       <c r="AI40" s="63"/>
       <c r="AJ40" s="63"/>
     </row>
-    <row r="41" spans="1:36" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="37" t="s">
         <v>55</v>
       </c>
@@ -7691,7 +7684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="63" t="s">
         <v>55</v>
       </c>
@@ -7787,7 +7780,7 @@
       <c r="AI42" s="63"/>
       <c r="AJ42" s="63"/>
     </row>
-    <row r="43" spans="1:36" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="37" t="s">
         <v>55</v>
       </c>
@@ -7967,7 +7960,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="37" t="s">
         <v>55</v>
       </c>
@@ -8149,7 +8142,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:36" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="79" t="s">
         <v>153</v>
       </c>
@@ -8223,7 +8216,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="79" t="s">
         <v>153</v>
       </c>
@@ -8294,7 +8287,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="78" t="s">
         <v>153</v>
       </c>
@@ -8380,7 +8373,7 @@
       <c r="AI49" s="63"/>
       <c r="AJ49" s="63"/>
     </row>
-    <row r="50" spans="1:36" ht="204" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" ht="204" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="79" t="s">
         <v>153</v>
       </c>
@@ -8454,7 +8447,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:36" s="54" customFormat="1" ht="153" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" s="54" customFormat="1" ht="153" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="78" t="s">
         <v>153</v>
       </c>
@@ -8542,7 +8535,7 @@
       <c r="AI51" s="63"/>
       <c r="AJ51" s="63"/>
     </row>
-    <row r="52" spans="1:36" s="54" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" s="54" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="78" t="s">
         <v>153</v>
       </c>
@@ -8630,7 +8623,7 @@
       <c r="AI52" s="63"/>
       <c r="AJ52" s="63"/>
     </row>
-    <row r="53" spans="1:36" ht="153" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" ht="153" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="79" t="s">
         <v>153</v>
       </c>
@@ -8704,7 +8697,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:36" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" s="54" customFormat="1" ht="237.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="78" t="s">
         <v>153</v>
       </c>
@@ -8792,7 +8785,7 @@
       <c r="AI54" s="63"/>
       <c r="AJ54" s="63"/>
     </row>
-    <row r="55" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="78" t="s">
         <v>350</v>
       </c>
@@ -8880,7 +8873,7 @@
       <c r="AI55" s="63"/>
       <c r="AJ55" s="63"/>
     </row>
-    <row r="56" spans="1:36" s="54" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" s="54" customFormat="1" ht="84.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="78" t="s">
         <v>35</v>
       </c>
@@ -8968,7 +8961,7 @@
       <c r="AI56" s="63"/>
       <c r="AJ56" s="63"/>
     </row>
-    <row r="57" spans="1:36" s="54" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" s="54" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="78" t="s">
         <v>35</v>
       </c>
@@ -9056,11 +9049,11 @@
       <c r="AI57" s="63"/>
       <c r="AJ57" s="63"/>
     </row>
-    <row r="58" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B58" s="94">
+      <c r="B58" s="37">
         <v>2025</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -9115,11 +9108,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B59" s="94">
+      <c r="B59" s="37">
         <v>2025</v>
       </c>
       <c r="D59" s="37" t="s">
@@ -9174,11 +9167,11 @@
         <v>646</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B60" s="94">
+      <c r="B60" s="37">
         <v>2025</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -9235,7 +9228,7 @@
       <c r="AI60"/>
       <c r="AJ60"/>
     </row>
-    <row r="61" spans="1:36" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="37" t="s">
         <v>55</v>
       </c>
@@ -9325,7 +9318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:36" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" s="54" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="63" t="s">
         <v>55</v>
       </c>
@@ -9355,7 +9348,7 @@
         <v>61</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="L62" s="46" t="s">
         <v>673</v>
@@ -9449,7 +9442,7 @@
         <v>102</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L63" s="22" t="s">
         <v>686</v>
@@ -9509,7 +9502,7 @@
       <c r="AI63"/>
       <c r="AJ63"/>
     </row>
-    <row r="64" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
         <v>350</v>
       </c>
@@ -9595,11 +9588,11 @@
       <c r="AI64" s="63"/>
       <c r="AJ64" s="63"/>
     </row>
-    <row r="65" spans="1:36" ht="288.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" ht="288.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="94">
+      <c r="B65" s="37">
         <v>2026</v>
       </c>
       <c r="D65" s="37" t="s">
@@ -9624,7 +9617,7 @@
         <v>73</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L65" s="37" t="s">
         <v>703</v>
@@ -9675,11 +9668,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B66" s="94">
+      <c r="B66" s="37">
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
@@ -9737,11 +9730,11 @@
         <v>779</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B67" s="94">
+      <c r="B67" s="37">
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
@@ -9787,11 +9780,11 @@
         <v>724</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B68" s="94">
+      <c r="B68" s="37">
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
@@ -9837,11 +9830,11 @@
         <v>731</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B69" s="94">
+      <c r="B69" s="37">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
@@ -9887,11 +9880,11 @@
         <v>738</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B70" s="94">
+      <c r="B70" s="37">
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
@@ -9937,11 +9930,11 @@
         <v>745</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B71" s="94">
+      <c r="B71" s="37">
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
@@ -9996,11 +9989,11 @@
         <v>781</v>
       </c>
     </row>
-    <row r="72" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="78" t="s">
         <v>372</v>
       </c>
-      <c r="B72" s="95">
+      <c r="B72" s="63">
         <v>2026</v>
       </c>
       <c r="C72" s="28"/>
@@ -10084,11 +10077,11 @@
       <c r="AI72" s="63"/>
       <c r="AJ72" s="63"/>
     </row>
-    <row r="73" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79" t="s">
         <v>389</v>
       </c>
-      <c r="B73" s="94">
+      <c r="B73" s="37">
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
@@ -10134,11 +10127,11 @@
         <v>767</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="34" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>389</v>
       </c>
-      <c r="B74" s="96">
+      <c r="B74">
         <v>2026</v>
       </c>
       <c r="D74" t="s">
@@ -10183,2644 +10176,2641 @@
       <c r="AJ74"/>
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B75" s="94"/>
+      <c r="B75" s="37"/>
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B76" s="94"/>
+      <c r="B76" s="37"/>
     </row>
     <row r="77" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B77" s="94"/>
+      <c r="B77" s="37"/>
     </row>
     <row r="78" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B78" s="94"/>
+      <c r="B78" s="37"/>
     </row>
     <row r="79" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B79" s="94"/>
+      <c r="B79" s="37"/>
     </row>
     <row r="80" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="B80" s="94"/>
+      <c r="B80" s="37"/>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="94"/>
+      <c r="B81" s="37"/>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="94"/>
+      <c r="B82" s="37"/>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="94"/>
+      <c r="B83" s="37"/>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="94"/>
+      <c r="B84" s="37"/>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="94"/>
+      <c r="B85" s="37"/>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="94"/>
+      <c r="B86" s="37"/>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="94"/>
+      <c r="B87" s="37"/>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="94"/>
+      <c r="B88" s="37"/>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="94"/>
+      <c r="B89" s="37"/>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="94"/>
+      <c r="B90" s="37"/>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="94"/>
+      <c r="B91" s="37"/>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="94"/>
+      <c r="B92" s="37"/>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="94"/>
+      <c r="B93" s="37"/>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="94"/>
+      <c r="B94" s="37"/>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="94"/>
+      <c r="B95" s="37"/>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="94"/>
+      <c r="B96" s="37"/>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97" s="94"/>
+      <c r="B97" s="37"/>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="94"/>
+      <c r="B98" s="37"/>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="94"/>
+      <c r="B99" s="37"/>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100" s="94"/>
+      <c r="B100" s="37"/>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="94"/>
+      <c r="B101" s="37"/>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="94"/>
+      <c r="B102" s="37"/>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103" s="94"/>
+      <c r="B103" s="37"/>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="94"/>
+      <c r="B104" s="37"/>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="94"/>
+      <c r="B105" s="37"/>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B106" s="94"/>
+      <c r="B106" s="37"/>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" s="94"/>
+      <c r="B107" s="37"/>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" s="94"/>
+      <c r="B108" s="37"/>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B109" s="94"/>
+      <c r="B109" s="37"/>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B110" s="94"/>
+      <c r="B110" s="37"/>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" s="94"/>
+      <c r="B111" s="37"/>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B112" s="94"/>
+      <c r="B112" s="37"/>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B113" s="94"/>
+      <c r="B113" s="37"/>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B114" s="94"/>
+      <c r="B114" s="37"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B115" s="94"/>
+      <c r="B115" s="37"/>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="94"/>
+      <c r="B116" s="37"/>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="94"/>
+      <c r="B117" s="37"/>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B118" s="94"/>
+      <c r="B118" s="37"/>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B119" s="94"/>
+      <c r="B119" s="37"/>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="94"/>
+      <c r="B120" s="37"/>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B121" s="94"/>
+      <c r="B121" s="37"/>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="94"/>
+      <c r="B122" s="37"/>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="94"/>
+      <c r="B123" s="37"/>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="94"/>
+      <c r="B124" s="37"/>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="94"/>
+      <c r="B125" s="37"/>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="94"/>
+      <c r="B126" s="37"/>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B127" s="94"/>
+      <c r="B127" s="37"/>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B128" s="94"/>
+      <c r="B128" s="37"/>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B129" s="94"/>
+      <c r="B129" s="37"/>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B130" s="94"/>
+      <c r="B130" s="37"/>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B131" s="94"/>
+      <c r="B131" s="37"/>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B132" s="94"/>
+      <c r="B132" s="37"/>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B133" s="94"/>
+      <c r="B133" s="37"/>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B134" s="94"/>
+      <c r="B134" s="37"/>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B135" s="94"/>
+      <c r="B135" s="37"/>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B136" s="94"/>
+      <c r="B136" s="37"/>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B137" s="94"/>
+      <c r="B137" s="37"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B138" s="94"/>
+      <c r="B138" s="37"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B139" s="94"/>
+      <c r="B139" s="37"/>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B140" s="94"/>
+      <c r="B140" s="37"/>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B141" s="94"/>
+      <c r="B141" s="37"/>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B142" s="94"/>
+      <c r="B142" s="37"/>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B143" s="94"/>
+      <c r="B143" s="37"/>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B144" s="94"/>
+      <c r="B144" s="37"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B145" s="94"/>
+      <c r="B145" s="37"/>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B146" s="94"/>
+      <c r="B146" s="37"/>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B147" s="94"/>
+      <c r="B147" s="37"/>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B148" s="94"/>
+      <c r="B148" s="37"/>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B149" s="94"/>
+      <c r="B149" s="37"/>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B150" s="94"/>
+      <c r="B150" s="37"/>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B151" s="94"/>
+      <c r="B151" s="37"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B152" s="94"/>
+      <c r="B152" s="37"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B153" s="94"/>
+      <c r="B153" s="37"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B154" s="94"/>
+      <c r="B154" s="37"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B155" s="94"/>
+      <c r="B155" s="37"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B156" s="94"/>
+      <c r="B156" s="37"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B157" s="94"/>
+      <c r="B157" s="37"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B158" s="94"/>
+      <c r="B158" s="37"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B159" s="94"/>
+      <c r="B159" s="37"/>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B160" s="94"/>
+      <c r="B160" s="37"/>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B161" s="94"/>
+      <c r="B161" s="37"/>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B162" s="94"/>
+      <c r="B162" s="37"/>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B163" s="94"/>
+      <c r="B163" s="37"/>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B164" s="94"/>
+      <c r="B164" s="37"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B165" s="94"/>
+      <c r="B165" s="37"/>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B166" s="94"/>
+      <c r="B166" s="37"/>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B167" s="94"/>
+      <c r="B167" s="37"/>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B168" s="94"/>
+      <c r="B168" s="37"/>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B169" s="94"/>
+      <c r="B169" s="37"/>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B170" s="94"/>
+      <c r="B170" s="37"/>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B171" s="94"/>
+      <c r="B171" s="37"/>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B172" s="94"/>
+      <c r="B172" s="37"/>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B173" s="94"/>
+      <c r="B173" s="37"/>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B174" s="94"/>
+      <c r="B174" s="37"/>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B175" s="94"/>
+      <c r="B175" s="37"/>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B176" s="94"/>
+      <c r="B176" s="37"/>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B177" s="94"/>
+      <c r="B177" s="37"/>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B178" s="94"/>
+      <c r="B178" s="37"/>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B179" s="94"/>
+      <c r="B179" s="37"/>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B180" s="94"/>
+      <c r="B180" s="37"/>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B181" s="94"/>
+      <c r="B181" s="37"/>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B182" s="94"/>
+      <c r="B182" s="37"/>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B183" s="94"/>
+      <c r="B183" s="37"/>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B184" s="94"/>
+      <c r="B184" s="37"/>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B185" s="94"/>
+      <c r="B185" s="37"/>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B186" s="94"/>
+      <c r="B186" s="37"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B187" s="94"/>
+      <c r="B187" s="37"/>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B188" s="94"/>
+      <c r="B188" s="37"/>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B189" s="94"/>
+      <c r="B189" s="37"/>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B190" s="94"/>
+      <c r="B190" s="37"/>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B191" s="94"/>
+      <c r="B191" s="37"/>
     </row>
     <row r="192" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B192" s="94"/>
+      <c r="B192" s="37"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B193" s="94"/>
+      <c r="B193" s="37"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B194" s="94"/>
+      <c r="B194" s="37"/>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B195" s="94"/>
+      <c r="B195" s="37"/>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B196" s="94"/>
+      <c r="B196" s="37"/>
     </row>
     <row r="197" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B197" s="94"/>
+      <c r="B197" s="37"/>
     </row>
     <row r="198" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B198" s="94"/>
+      <c r="B198" s="37"/>
     </row>
     <row r="199" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B199" s="94"/>
+      <c r="B199" s="37"/>
     </row>
     <row r="200" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B200" s="94"/>
+      <c r="B200" s="37"/>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B201" s="94"/>
+      <c r="B201" s="37"/>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B202" s="94"/>
+      <c r="B202" s="37"/>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B203" s="94"/>
+      <c r="B203" s="37"/>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B204" s="94"/>
+      <c r="B204" s="37"/>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B205" s="94"/>
+      <c r="B205" s="37"/>
     </row>
     <row r="206" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B206" s="94"/>
+      <c r="B206" s="37"/>
     </row>
     <row r="207" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B207" s="94"/>
+      <c r="B207" s="37"/>
     </row>
     <row r="208" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B208" s="94"/>
+      <c r="B208" s="37"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B209" s="94"/>
+      <c r="B209" s="37"/>
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B210" s="94"/>
+      <c r="B210" s="37"/>
     </row>
     <row r="211" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B211" s="94"/>
+      <c r="B211" s="37"/>
     </row>
     <row r="212" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B212" s="94"/>
+      <c r="B212" s="37"/>
     </row>
     <row r="213" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B213" s="94"/>
+      <c r="B213" s="37"/>
     </row>
     <row r="214" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B214" s="94"/>
+      <c r="B214" s="37"/>
     </row>
     <row r="215" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B215" s="94"/>
+      <c r="B215" s="37"/>
     </row>
     <row r="216" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B216" s="94"/>
+      <c r="B216" s="37"/>
     </row>
     <row r="217" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B217" s="94"/>
+      <c r="B217" s="37"/>
     </row>
     <row r="218" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B218" s="94"/>
+      <c r="B218" s="37"/>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B219" s="94"/>
+      <c r="B219" s="37"/>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B220" s="94"/>
+      <c r="B220" s="37"/>
     </row>
     <row r="221" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B221" s="94"/>
+      <c r="B221" s="37"/>
     </row>
     <row r="222" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B222" s="94"/>
+      <c r="B222" s="37"/>
     </row>
     <row r="223" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B223" s="94"/>
+      <c r="B223" s="37"/>
     </row>
     <row r="224" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B224" s="94"/>
+      <c r="B224" s="37"/>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B225" s="94"/>
+      <c r="B225" s="37"/>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B226" s="94"/>
+      <c r="B226" s="37"/>
     </row>
     <row r="227" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B227" s="94"/>
+      <c r="B227" s="37"/>
     </row>
     <row r="228" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B228" s="94"/>
+      <c r="B228" s="37"/>
     </row>
     <row r="229" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B229" s="94"/>
+      <c r="B229" s="37"/>
     </row>
     <row r="230" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B230" s="94"/>
+      <c r="B230" s="37"/>
     </row>
     <row r="231" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B231" s="94"/>
+      <c r="B231" s="37"/>
     </row>
     <row r="232" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B232" s="94"/>
+      <c r="B232" s="37"/>
     </row>
     <row r="233" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B233" s="94"/>
+      <c r="B233" s="37"/>
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B234" s="94"/>
+      <c r="B234" s="37"/>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B235" s="94"/>
+      <c r="B235" s="37"/>
     </row>
     <row r="236" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B236" s="94"/>
+      <c r="B236" s="37"/>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B237" s="94"/>
+      <c r="B237" s="37"/>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B238" s="94"/>
+      <c r="B238" s="37"/>
     </row>
     <row r="239" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B239" s="94"/>
+      <c r="B239" s="37"/>
     </row>
     <row r="240" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B240" s="94"/>
+      <c r="B240" s="37"/>
     </row>
     <row r="241" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B241" s="94"/>
+      <c r="B241" s="37"/>
     </row>
     <row r="242" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B242" s="94"/>
+      <c r="B242" s="37"/>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B243" s="94"/>
+      <c r="B243" s="37"/>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B244" s="94"/>
+      <c r="B244" s="37"/>
     </row>
     <row r="245" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B245" s="94"/>
+      <c r="B245" s="37"/>
     </row>
     <row r="246" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B246" s="94"/>
+      <c r="B246" s="37"/>
     </row>
     <row r="247" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B247" s="94"/>
+      <c r="B247" s="37"/>
     </row>
     <row r="248" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B248" s="94"/>
+      <c r="B248" s="37"/>
     </row>
     <row r="249" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B249" s="94"/>
+      <c r="B249" s="37"/>
     </row>
     <row r="250" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B250" s="94"/>
+      <c r="B250" s="37"/>
     </row>
     <row r="251" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B251" s="94"/>
+      <c r="B251" s="37"/>
     </row>
     <row r="252" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B252" s="94"/>
+      <c r="B252" s="37"/>
     </row>
     <row r="253" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B253" s="94"/>
+      <c r="B253" s="37"/>
     </row>
     <row r="254" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B254" s="94"/>
+      <c r="B254" s="37"/>
     </row>
     <row r="255" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B255" s="94"/>
+      <c r="B255" s="37"/>
     </row>
     <row r="256" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B256" s="94"/>
+      <c r="B256" s="37"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B257" s="94"/>
+      <c r="B257" s="37"/>
     </row>
     <row r="258" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B258" s="94"/>
+      <c r="B258" s="37"/>
     </row>
     <row r="259" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B259" s="94"/>
+      <c r="B259" s="37"/>
     </row>
     <row r="260" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B260" s="94"/>
+      <c r="B260" s="37"/>
     </row>
     <row r="261" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B261" s="94"/>
+      <c r="B261" s="37"/>
     </row>
     <row r="262" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B262" s="94"/>
+      <c r="B262" s="37"/>
     </row>
     <row r="263" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B263" s="94"/>
+      <c r="B263" s="37"/>
     </row>
     <row r="264" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B264" s="94"/>
+      <c r="B264" s="37"/>
     </row>
     <row r="265" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B265" s="94"/>
+      <c r="B265" s="37"/>
     </row>
     <row r="266" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B266" s="94"/>
+      <c r="B266" s="37"/>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B267" s="94"/>
+      <c r="B267" s="37"/>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B268" s="94"/>
+      <c r="B268" s="37"/>
     </row>
     <row r="269" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B269" s="94"/>
+      <c r="B269" s="37"/>
     </row>
     <row r="270" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B270" s="94"/>
+      <c r="B270" s="37"/>
     </row>
     <row r="271" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B271" s="94"/>
+      <c r="B271" s="37"/>
     </row>
     <row r="272" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B272" s="94"/>
+      <c r="B272" s="37"/>
     </row>
     <row r="273" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B273" s="94"/>
+      <c r="B273" s="37"/>
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B274" s="94"/>
+      <c r="B274" s="37"/>
     </row>
     <row r="275" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B275" s="94"/>
+      <c r="B275" s="37"/>
     </row>
     <row r="276" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B276" s="94"/>
+      <c r="B276" s="37"/>
     </row>
     <row r="277" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B277" s="94"/>
+      <c r="B277" s="37"/>
     </row>
     <row r="278" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B278" s="94"/>
+      <c r="B278" s="37"/>
     </row>
     <row r="279" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B279" s="94"/>
+      <c r="B279" s="37"/>
     </row>
     <row r="280" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B280" s="94"/>
+      <c r="B280" s="37"/>
     </row>
     <row r="281" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B281" s="94"/>
+      <c r="B281" s="37"/>
     </row>
     <row r="282" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B282" s="94"/>
+      <c r="B282" s="37"/>
     </row>
     <row r="283" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B283" s="94"/>
+      <c r="B283" s="37"/>
     </row>
     <row r="284" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B284" s="94"/>
+      <c r="B284" s="37"/>
     </row>
     <row r="285" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B285" s="94"/>
+      <c r="B285" s="37"/>
     </row>
     <row r="286" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B286" s="94"/>
+      <c r="B286" s="37"/>
     </row>
     <row r="287" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B287" s="94"/>
+      <c r="B287" s="37"/>
     </row>
     <row r="288" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B288" s="94"/>
+      <c r="B288" s="37"/>
     </row>
     <row r="289" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B289" s="94"/>
+      <c r="B289" s="37"/>
     </row>
     <row r="290" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B290" s="94"/>
+      <c r="B290" s="37"/>
     </row>
     <row r="291" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B291" s="94"/>
+      <c r="B291" s="37"/>
     </row>
     <row r="292" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B292" s="94"/>
+      <c r="B292" s="37"/>
     </row>
     <row r="293" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B293" s="94"/>
+      <c r="B293" s="37"/>
     </row>
     <row r="294" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B294" s="94"/>
+      <c r="B294" s="37"/>
     </row>
     <row r="295" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B295" s="94"/>
+      <c r="B295" s="37"/>
     </row>
     <row r="296" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B296" s="94"/>
+      <c r="B296" s="37"/>
     </row>
     <row r="297" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B297" s="94"/>
+      <c r="B297" s="37"/>
     </row>
     <row r="298" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B298" s="94"/>
+      <c r="B298" s="37"/>
     </row>
     <row r="299" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B299" s="94"/>
+      <c r="B299" s="37"/>
     </row>
     <row r="300" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B300" s="94"/>
+      <c r="B300" s="37"/>
     </row>
     <row r="301" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B301" s="94"/>
+      <c r="B301" s="37"/>
     </row>
     <row r="302" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B302" s="94"/>
+      <c r="B302" s="37"/>
     </row>
     <row r="303" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B303" s="94"/>
+      <c r="B303" s="37"/>
     </row>
     <row r="304" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B304" s="94"/>
+      <c r="B304" s="37"/>
     </row>
     <row r="305" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B305" s="94"/>
+      <c r="B305" s="37"/>
     </row>
     <row r="306" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B306" s="94"/>
+      <c r="B306" s="37"/>
     </row>
     <row r="307" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B307" s="94"/>
+      <c r="B307" s="37"/>
     </row>
     <row r="308" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B308" s="94"/>
+      <c r="B308" s="37"/>
     </row>
     <row r="309" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B309" s="94"/>
+      <c r="B309" s="37"/>
     </row>
     <row r="310" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B310" s="94"/>
+      <c r="B310" s="37"/>
     </row>
     <row r="311" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B311" s="94"/>
+      <c r="B311" s="37"/>
     </row>
     <row r="312" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B312" s="94"/>
+      <c r="B312" s="37"/>
     </row>
     <row r="313" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B313" s="94"/>
+      <c r="B313" s="37"/>
     </row>
     <row r="314" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B314" s="94"/>
+      <c r="B314" s="37"/>
     </row>
     <row r="315" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B315" s="94"/>
+      <c r="B315" s="37"/>
     </row>
     <row r="316" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B316" s="94"/>
+      <c r="B316" s="37"/>
     </row>
     <row r="317" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B317" s="94"/>
+      <c r="B317" s="37"/>
     </row>
     <row r="318" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B318" s="94"/>
+      <c r="B318" s="37"/>
     </row>
     <row r="319" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B319" s="94"/>
+      <c r="B319" s="37"/>
     </row>
     <row r="320" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B320" s="94"/>
+      <c r="B320" s="37"/>
     </row>
     <row r="321" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B321" s="94"/>
+      <c r="B321" s="37"/>
     </row>
     <row r="322" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B322" s="94"/>
+      <c r="B322" s="37"/>
     </row>
     <row r="323" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B323" s="94"/>
+      <c r="B323" s="37"/>
     </row>
     <row r="324" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B324" s="94"/>
+      <c r="B324" s="37"/>
     </row>
     <row r="325" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B325" s="94"/>
+      <c r="B325" s="37"/>
     </row>
     <row r="326" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B326" s="94"/>
+      <c r="B326" s="37"/>
     </row>
     <row r="327" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B327" s="94"/>
+      <c r="B327" s="37"/>
     </row>
     <row r="328" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B328" s="94"/>
+      <c r="B328" s="37"/>
     </row>
     <row r="329" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B329" s="94"/>
+      <c r="B329" s="37"/>
     </row>
     <row r="330" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B330" s="94"/>
+      <c r="B330" s="37"/>
     </row>
     <row r="331" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B331" s="94"/>
+      <c r="B331" s="37"/>
     </row>
     <row r="332" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B332" s="94"/>
+      <c r="B332" s="37"/>
     </row>
     <row r="333" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B333" s="94"/>
+      <c r="B333" s="37"/>
     </row>
     <row r="334" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B334" s="94"/>
+      <c r="B334" s="37"/>
     </row>
     <row r="335" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B335" s="94"/>
+      <c r="B335" s="37"/>
     </row>
     <row r="336" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B336" s="94"/>
+      <c r="B336" s="37"/>
     </row>
     <row r="337" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B337" s="94"/>
+      <c r="B337" s="37"/>
     </row>
     <row r="338" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B338" s="94"/>
+      <c r="B338" s="37"/>
     </row>
     <row r="339" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B339" s="94"/>
+      <c r="B339" s="37"/>
     </row>
     <row r="340" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B340" s="94"/>
+      <c r="B340" s="37"/>
     </row>
     <row r="341" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B341" s="94"/>
+      <c r="B341" s="37"/>
     </row>
     <row r="342" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B342" s="94"/>
+      <c r="B342" s="37"/>
     </row>
     <row r="343" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B343" s="94"/>
+      <c r="B343" s="37"/>
     </row>
     <row r="344" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B344" s="94"/>
+      <c r="B344" s="37"/>
     </row>
     <row r="345" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B345" s="94"/>
+      <c r="B345" s="37"/>
     </row>
     <row r="346" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B346" s="94"/>
+      <c r="B346" s="37"/>
     </row>
     <row r="347" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B347" s="94"/>
+      <c r="B347" s="37"/>
     </row>
     <row r="348" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B348" s="94"/>
+      <c r="B348" s="37"/>
     </row>
     <row r="349" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B349" s="94"/>
+      <c r="B349" s="37"/>
     </row>
     <row r="350" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B350" s="94"/>
+      <c r="B350" s="37"/>
     </row>
     <row r="351" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B351" s="94"/>
+      <c r="B351" s="37"/>
     </row>
     <row r="352" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B352" s="94"/>
+      <c r="B352" s="37"/>
     </row>
     <row r="353" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B353" s="94"/>
+      <c r="B353" s="37"/>
     </row>
     <row r="354" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B354" s="94"/>
+      <c r="B354" s="37"/>
     </row>
     <row r="355" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B355" s="94"/>
+      <c r="B355" s="37"/>
     </row>
     <row r="356" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B356" s="94"/>
+      <c r="B356" s="37"/>
     </row>
     <row r="357" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B357" s="94"/>
+      <c r="B357" s="37"/>
     </row>
     <row r="358" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B358" s="94"/>
+      <c r="B358" s="37"/>
     </row>
     <row r="359" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B359" s="94"/>
+      <c r="B359" s="37"/>
     </row>
     <row r="360" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B360" s="94"/>
+      <c r="B360" s="37"/>
     </row>
     <row r="361" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B361" s="94"/>
+      <c r="B361" s="37"/>
     </row>
     <row r="362" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B362" s="94"/>
+      <c r="B362" s="37"/>
     </row>
     <row r="363" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B363" s="94"/>
+      <c r="B363" s="37"/>
     </row>
     <row r="364" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B364" s="94"/>
+      <c r="B364" s="37"/>
     </row>
     <row r="365" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B365" s="94"/>
+      <c r="B365" s="37"/>
     </row>
     <row r="366" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B366" s="94"/>
+      <c r="B366" s="37"/>
     </row>
     <row r="367" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B367" s="94"/>
+      <c r="B367" s="37"/>
     </row>
     <row r="368" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B368" s="94"/>
+      <c r="B368" s="37"/>
     </row>
     <row r="369" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B369" s="94"/>
+      <c r="B369" s="37"/>
     </row>
     <row r="370" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B370" s="94"/>
+      <c r="B370" s="37"/>
     </row>
     <row r="371" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B371" s="94"/>
+      <c r="B371" s="37"/>
     </row>
     <row r="372" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B372" s="94"/>
+      <c r="B372" s="37"/>
     </row>
     <row r="373" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B373" s="94"/>
+      <c r="B373" s="37"/>
     </row>
     <row r="374" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B374" s="94"/>
+      <c r="B374" s="37"/>
     </row>
     <row r="375" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B375" s="94"/>
+      <c r="B375" s="37"/>
     </row>
     <row r="376" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B376" s="94"/>
+      <c r="B376" s="37"/>
     </row>
     <row r="377" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B377" s="94"/>
+      <c r="B377" s="37"/>
     </row>
     <row r="378" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B378" s="94"/>
+      <c r="B378" s="37"/>
     </row>
     <row r="379" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B379" s="94"/>
+      <c r="B379" s="37"/>
     </row>
     <row r="380" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B380" s="94"/>
+      <c r="B380" s="37"/>
     </row>
     <row r="381" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B381" s="94"/>
+      <c r="B381" s="37"/>
     </row>
     <row r="382" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B382" s="94"/>
+      <c r="B382" s="37"/>
     </row>
     <row r="383" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B383" s="94"/>
+      <c r="B383" s="37"/>
     </row>
     <row r="384" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B384" s="94"/>
+      <c r="B384" s="37"/>
     </row>
     <row r="385" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B385" s="94"/>
+      <c r="B385" s="37"/>
     </row>
     <row r="386" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B386" s="94"/>
+      <c r="B386" s="37"/>
     </row>
     <row r="387" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B387" s="94"/>
+      <c r="B387" s="37"/>
     </row>
     <row r="388" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B388" s="94"/>
+      <c r="B388" s="37"/>
     </row>
     <row r="389" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B389" s="94"/>
+      <c r="B389" s="37"/>
     </row>
     <row r="390" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B390" s="94"/>
+      <c r="B390" s="37"/>
     </row>
     <row r="391" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B391" s="94"/>
+      <c r="B391" s="37"/>
     </row>
     <row r="392" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B392" s="94"/>
+      <c r="B392" s="37"/>
     </row>
     <row r="393" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B393" s="94"/>
+      <c r="B393" s="37"/>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B394" s="94"/>
+      <c r="B394" s="37"/>
     </row>
     <row r="395" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B395" s="94"/>
+      <c r="B395" s="37"/>
     </row>
     <row r="396" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B396" s="94"/>
+      <c r="B396" s="37"/>
     </row>
     <row r="397" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B397" s="94"/>
+      <c r="B397" s="37"/>
     </row>
     <row r="398" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B398" s="94"/>
+      <c r="B398" s="37"/>
     </row>
     <row r="399" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B399" s="94"/>
+      <c r="B399" s="37"/>
     </row>
     <row r="400" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B400" s="94"/>
+      <c r="B400" s="37"/>
     </row>
     <row r="401" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B401" s="94"/>
+      <c r="B401" s="37"/>
     </row>
     <row r="402" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B402" s="94"/>
+      <c r="B402" s="37"/>
     </row>
     <row r="403" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B403" s="94"/>
+      <c r="B403" s="37"/>
     </row>
     <row r="404" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B404" s="94"/>
+      <c r="B404" s="37"/>
     </row>
     <row r="405" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B405" s="94"/>
+      <c r="B405" s="37"/>
     </row>
     <row r="406" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B406" s="94"/>
+      <c r="B406" s="37"/>
     </row>
     <row r="407" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B407" s="94"/>
+      <c r="B407" s="37"/>
     </row>
     <row r="408" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B408" s="94"/>
+      <c r="B408" s="37"/>
     </row>
     <row r="409" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B409" s="94"/>
+      <c r="B409" s="37"/>
     </row>
     <row r="410" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B410" s="94"/>
+      <c r="B410" s="37"/>
     </row>
     <row r="411" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B411" s="94"/>
+      <c r="B411" s="37"/>
     </row>
     <row r="412" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B412" s="94"/>
+      <c r="B412" s="37"/>
     </row>
     <row r="413" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B413" s="94"/>
+      <c r="B413" s="37"/>
     </row>
     <row r="414" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B414" s="94"/>
+      <c r="B414" s="37"/>
     </row>
     <row r="415" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B415" s="94"/>
+      <c r="B415" s="37"/>
     </row>
     <row r="416" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B416" s="94"/>
+      <c r="B416" s="37"/>
     </row>
     <row r="417" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B417" s="94"/>
+      <c r="B417" s="37"/>
     </row>
     <row r="418" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B418" s="94"/>
+      <c r="B418" s="37"/>
     </row>
     <row r="419" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B419" s="94"/>
+      <c r="B419" s="37"/>
     </row>
     <row r="420" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B420" s="94"/>
+      <c r="B420" s="37"/>
     </row>
     <row r="421" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B421" s="94"/>
+      <c r="B421" s="37"/>
     </row>
     <row r="422" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B422" s="94"/>
+      <c r="B422" s="37"/>
     </row>
     <row r="423" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B423" s="94"/>
+      <c r="B423" s="37"/>
     </row>
     <row r="424" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B424" s="94"/>
+      <c r="B424" s="37"/>
     </row>
     <row r="425" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B425" s="94"/>
+      <c r="B425" s="37"/>
     </row>
     <row r="426" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B426" s="94"/>
+      <c r="B426" s="37"/>
     </row>
     <row r="427" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B427" s="94"/>
+      <c r="B427" s="37"/>
     </row>
     <row r="428" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B428" s="94"/>
+      <c r="B428" s="37"/>
     </row>
     <row r="429" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B429" s="94"/>
+      <c r="B429" s="37"/>
     </row>
     <row r="430" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B430" s="94"/>
+      <c r="B430" s="37"/>
     </row>
     <row r="431" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B431" s="94"/>
+      <c r="B431" s="37"/>
     </row>
     <row r="432" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B432" s="94"/>
+      <c r="B432" s="37"/>
     </row>
     <row r="433" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B433" s="94"/>
+      <c r="B433" s="37"/>
     </row>
     <row r="434" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B434" s="94"/>
+      <c r="B434" s="37"/>
     </row>
     <row r="435" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B435" s="94"/>
+      <c r="B435" s="37"/>
     </row>
     <row r="436" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B436" s="94"/>
+      <c r="B436" s="37"/>
     </row>
     <row r="437" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B437" s="94"/>
+      <c r="B437" s="37"/>
     </row>
     <row r="438" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B438" s="94"/>
+      <c r="B438" s="37"/>
     </row>
     <row r="439" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B439" s="94"/>
+      <c r="B439" s="37"/>
     </row>
     <row r="440" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B440" s="94"/>
+      <c r="B440" s="37"/>
     </row>
     <row r="441" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B441" s="94"/>
+      <c r="B441" s="37"/>
     </row>
     <row r="442" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B442" s="94"/>
+      <c r="B442" s="37"/>
     </row>
     <row r="443" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B443" s="94"/>
+      <c r="B443" s="37"/>
     </row>
     <row r="444" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B444" s="94"/>
+      <c r="B444" s="37"/>
     </row>
     <row r="445" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B445" s="94"/>
+      <c r="B445" s="37"/>
     </row>
     <row r="446" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B446" s="94"/>
+      <c r="B446" s="37"/>
     </row>
     <row r="447" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B447" s="94"/>
+      <c r="B447" s="37"/>
     </row>
     <row r="448" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B448" s="94"/>
+      <c r="B448" s="37"/>
     </row>
     <row r="449" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B449" s="94"/>
+      <c r="B449" s="37"/>
     </row>
     <row r="450" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B450" s="94"/>
+      <c r="B450" s="37"/>
     </row>
     <row r="451" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B451" s="94"/>
+      <c r="B451" s="37"/>
     </row>
     <row r="452" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B452" s="94"/>
+      <c r="B452" s="37"/>
     </row>
     <row r="453" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B453" s="94"/>
+      <c r="B453" s="37"/>
     </row>
     <row r="454" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B454" s="94"/>
+      <c r="B454" s="37"/>
     </row>
     <row r="455" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B455" s="94"/>
+      <c r="B455" s="37"/>
     </row>
     <row r="456" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B456" s="94"/>
+      <c r="B456" s="37"/>
     </row>
     <row r="457" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B457" s="94"/>
+      <c r="B457" s="37"/>
     </row>
     <row r="458" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B458" s="94"/>
+      <c r="B458" s="37"/>
     </row>
     <row r="459" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B459" s="94"/>
+      <c r="B459" s="37"/>
     </row>
     <row r="460" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B460" s="94"/>
+      <c r="B460" s="37"/>
     </row>
     <row r="461" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B461" s="94"/>
+      <c r="B461" s="37"/>
     </row>
     <row r="462" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B462" s="94"/>
+      <c r="B462" s="37"/>
     </row>
     <row r="463" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B463" s="94"/>
+      <c r="B463" s="37"/>
     </row>
     <row r="464" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B464" s="94"/>
+      <c r="B464" s="37"/>
     </row>
     <row r="465" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B465" s="94"/>
+      <c r="B465" s="37"/>
     </row>
     <row r="466" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B466" s="94"/>
+      <c r="B466" s="37"/>
     </row>
     <row r="467" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B467" s="94"/>
+      <c r="B467" s="37"/>
     </row>
     <row r="468" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B468" s="94"/>
+      <c r="B468" s="37"/>
     </row>
     <row r="469" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B469" s="94"/>
+      <c r="B469" s="37"/>
     </row>
     <row r="470" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B470" s="94"/>
+      <c r="B470" s="37"/>
     </row>
     <row r="471" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B471" s="94"/>
+      <c r="B471" s="37"/>
     </row>
     <row r="472" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B472" s="94"/>
+      <c r="B472" s="37"/>
     </row>
     <row r="473" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B473" s="94"/>
+      <c r="B473" s="37"/>
     </row>
     <row r="474" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B474" s="94"/>
+      <c r="B474" s="37"/>
     </row>
     <row r="475" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B475" s="94"/>
+      <c r="B475" s="37"/>
     </row>
     <row r="476" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B476" s="94"/>
+      <c r="B476" s="37"/>
     </row>
     <row r="477" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B477" s="94"/>
+      <c r="B477" s="37"/>
     </row>
     <row r="478" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B478" s="94"/>
+      <c r="B478" s="37"/>
     </row>
     <row r="479" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B479" s="94"/>
+      <c r="B479" s="37"/>
     </row>
     <row r="480" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B480" s="94"/>
+      <c r="B480" s="37"/>
     </row>
     <row r="481" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B481" s="94"/>
+      <c r="B481" s="37"/>
     </row>
     <row r="482" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B482" s="94"/>
+      <c r="B482" s="37"/>
     </row>
     <row r="483" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B483" s="94"/>
+      <c r="B483" s="37"/>
     </row>
     <row r="484" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B484" s="94"/>
+      <c r="B484" s="37"/>
     </row>
     <row r="485" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B485" s="94"/>
+      <c r="B485" s="37"/>
     </row>
     <row r="486" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B486" s="94"/>
+      <c r="B486" s="37"/>
     </row>
     <row r="487" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B487" s="94"/>
+      <c r="B487" s="37"/>
     </row>
     <row r="488" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B488" s="94"/>
+      <c r="B488" s="37"/>
     </row>
     <row r="489" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B489" s="94"/>
+      <c r="B489" s="37"/>
     </row>
     <row r="490" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B490" s="94"/>
+      <c r="B490" s="37"/>
     </row>
     <row r="491" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B491" s="94"/>
+      <c r="B491" s="37"/>
     </row>
     <row r="492" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B492" s="94"/>
+      <c r="B492" s="37"/>
     </row>
     <row r="493" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B493" s="94"/>
+      <c r="B493" s="37"/>
     </row>
     <row r="494" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B494" s="94"/>
+      <c r="B494" s="37"/>
     </row>
     <row r="495" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B495" s="94"/>
+      <c r="B495" s="37"/>
     </row>
     <row r="496" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B496" s="94"/>
+      <c r="B496" s="37"/>
     </row>
     <row r="497" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B497" s="94"/>
+      <c r="B497" s="37"/>
     </row>
     <row r="498" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B498" s="94"/>
+      <c r="B498" s="37"/>
     </row>
     <row r="499" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B499" s="94"/>
+      <c r="B499" s="37"/>
     </row>
     <row r="500" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B500" s="94"/>
+      <c r="B500" s="37"/>
     </row>
     <row r="501" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B501" s="94"/>
+      <c r="B501" s="37"/>
     </row>
     <row r="502" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B502" s="94"/>
+      <c r="B502" s="37"/>
     </row>
     <row r="503" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B503" s="94"/>
+      <c r="B503" s="37"/>
     </row>
     <row r="504" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B504" s="94"/>
+      <c r="B504" s="37"/>
     </row>
     <row r="505" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B505" s="94"/>
+      <c r="B505" s="37"/>
     </row>
     <row r="506" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B506" s="94"/>
+      <c r="B506" s="37"/>
     </row>
     <row r="507" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B507" s="94"/>
+      <c r="B507" s="37"/>
     </row>
     <row r="508" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B508" s="94"/>
+      <c r="B508" s="37"/>
     </row>
     <row r="509" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B509" s="94"/>
+      <c r="B509" s="37"/>
     </row>
     <row r="510" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B510" s="94"/>
+      <c r="B510" s="37"/>
     </row>
     <row r="511" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B511" s="94"/>
+      <c r="B511" s="37"/>
     </row>
     <row r="512" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B512" s="94"/>
+      <c r="B512" s="37"/>
     </row>
     <row r="513" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B513" s="94"/>
+      <c r="B513" s="37"/>
     </row>
     <row r="514" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B514" s="94"/>
+      <c r="B514" s="37"/>
     </row>
     <row r="515" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B515" s="94"/>
+      <c r="B515" s="37"/>
     </row>
     <row r="516" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B516" s="94"/>
+      <c r="B516" s="37"/>
     </row>
     <row r="517" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B517" s="94"/>
+      <c r="B517" s="37"/>
     </row>
     <row r="518" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B518" s="94"/>
+      <c r="B518" s="37"/>
     </row>
     <row r="519" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B519" s="94"/>
+      <c r="B519" s="37"/>
     </row>
     <row r="520" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B520" s="94"/>
+      <c r="B520" s="37"/>
     </row>
     <row r="521" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B521" s="94"/>
+      <c r="B521" s="37"/>
     </row>
     <row r="522" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B522" s="94"/>
+      <c r="B522" s="37"/>
     </row>
     <row r="523" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B523" s="94"/>
+      <c r="B523" s="37"/>
     </row>
     <row r="524" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B524" s="94"/>
+      <c r="B524" s="37"/>
     </row>
     <row r="525" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B525" s="94"/>
+      <c r="B525" s="37"/>
     </row>
     <row r="526" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B526" s="94"/>
+      <c r="B526" s="37"/>
     </row>
     <row r="527" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B527" s="94"/>
+      <c r="B527" s="37"/>
     </row>
     <row r="528" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B528" s="94"/>
+      <c r="B528" s="37"/>
     </row>
     <row r="529" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B529" s="94"/>
+      <c r="B529" s="37"/>
     </row>
     <row r="530" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B530" s="94"/>
+      <c r="B530" s="37"/>
     </row>
     <row r="531" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B531" s="94"/>
+      <c r="B531" s="37"/>
     </row>
     <row r="532" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B532" s="94"/>
+      <c r="B532" s="37"/>
     </row>
     <row r="533" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B533" s="94"/>
+      <c r="B533" s="37"/>
     </row>
     <row r="534" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B534" s="94"/>
+      <c r="B534" s="37"/>
     </row>
     <row r="535" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B535" s="94"/>
+      <c r="B535" s="37"/>
     </row>
     <row r="536" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B536" s="94"/>
+      <c r="B536" s="37"/>
     </row>
     <row r="537" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B537" s="94"/>
+      <c r="B537" s="37"/>
     </row>
     <row r="538" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B538" s="94"/>
+      <c r="B538" s="37"/>
     </row>
     <row r="539" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B539" s="94"/>
+      <c r="B539" s="37"/>
     </row>
     <row r="540" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B540" s="94"/>
+      <c r="B540" s="37"/>
     </row>
     <row r="541" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B541" s="94"/>
+      <c r="B541" s="37"/>
     </row>
     <row r="542" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B542" s="94"/>
+      <c r="B542" s="37"/>
     </row>
     <row r="543" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B543" s="94"/>
+      <c r="B543" s="37"/>
     </row>
     <row r="544" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B544" s="94"/>
+      <c r="B544" s="37"/>
     </row>
     <row r="545" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B545" s="94"/>
+      <c r="B545" s="37"/>
     </row>
     <row r="546" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B546" s="94"/>
+      <c r="B546" s="37"/>
     </row>
     <row r="547" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B547" s="94"/>
+      <c r="B547" s="37"/>
     </row>
     <row r="548" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B548" s="94"/>
+      <c r="B548" s="37"/>
     </row>
     <row r="549" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B549" s="94"/>
+      <c r="B549" s="37"/>
     </row>
     <row r="550" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B550" s="94"/>
+      <c r="B550" s="37"/>
     </row>
     <row r="551" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B551" s="94"/>
+      <c r="B551" s="37"/>
     </row>
     <row r="552" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B552" s="94"/>
+      <c r="B552" s="37"/>
     </row>
     <row r="553" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B553" s="94"/>
+      <c r="B553" s="37"/>
     </row>
     <row r="554" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B554" s="94"/>
+      <c r="B554" s="37"/>
     </row>
     <row r="555" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B555" s="94"/>
+      <c r="B555" s="37"/>
     </row>
     <row r="556" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B556" s="94"/>
+      <c r="B556" s="37"/>
     </row>
     <row r="557" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B557" s="94"/>
+      <c r="B557" s="37"/>
     </row>
     <row r="558" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B558" s="94"/>
+      <c r="B558" s="37"/>
     </row>
     <row r="559" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B559" s="94"/>
+      <c r="B559" s="37"/>
     </row>
     <row r="560" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B560" s="94"/>
+      <c r="B560" s="37"/>
     </row>
     <row r="561" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B561" s="94"/>
+      <c r="B561" s="37"/>
     </row>
     <row r="562" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B562" s="94"/>
+      <c r="B562" s="37"/>
     </row>
     <row r="563" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B563" s="94"/>
+      <c r="B563" s="37"/>
     </row>
     <row r="564" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B564" s="94"/>
+      <c r="B564" s="37"/>
     </row>
     <row r="565" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B565" s="94"/>
+      <c r="B565" s="37"/>
     </row>
     <row r="566" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B566" s="94"/>
+      <c r="B566" s="37"/>
     </row>
     <row r="567" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B567" s="94"/>
+      <c r="B567" s="37"/>
     </row>
     <row r="568" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B568" s="94"/>
+      <c r="B568" s="37"/>
     </row>
     <row r="569" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B569" s="94"/>
+      <c r="B569" s="37"/>
     </row>
     <row r="570" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B570" s="94"/>
+      <c r="B570" s="37"/>
     </row>
     <row r="571" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B571" s="94"/>
+      <c r="B571" s="37"/>
     </row>
     <row r="572" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B572" s="94"/>
+      <c r="B572" s="37"/>
     </row>
     <row r="573" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B573" s="94"/>
+      <c r="B573" s="37"/>
     </row>
     <row r="574" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B574" s="94"/>
+      <c r="B574" s="37"/>
     </row>
     <row r="575" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B575" s="94"/>
+      <c r="B575" s="37"/>
     </row>
     <row r="576" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B576" s="94"/>
+      <c r="B576" s="37"/>
     </row>
     <row r="577" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B577" s="94"/>
+      <c r="B577" s="37"/>
     </row>
     <row r="578" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B578" s="94"/>
+      <c r="B578" s="37"/>
     </row>
     <row r="579" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B579" s="94"/>
+      <c r="B579" s="37"/>
     </row>
     <row r="580" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B580" s="94"/>
+      <c r="B580" s="37"/>
     </row>
     <row r="581" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B581" s="94"/>
+      <c r="B581" s="37"/>
     </row>
     <row r="582" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B582" s="94"/>
+      <c r="B582" s="37"/>
     </row>
     <row r="583" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B583" s="94"/>
+      <c r="B583" s="37"/>
     </row>
     <row r="584" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B584" s="94"/>
+      <c r="B584" s="37"/>
     </row>
     <row r="585" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B585" s="94"/>
+      <c r="B585" s="37"/>
     </row>
     <row r="586" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B586" s="94"/>
+      <c r="B586" s="37"/>
     </row>
     <row r="587" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B587" s="94"/>
+      <c r="B587" s="37"/>
     </row>
     <row r="588" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B588" s="94"/>
+      <c r="B588" s="37"/>
     </row>
     <row r="589" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B589" s="94"/>
+      <c r="B589" s="37"/>
     </row>
     <row r="590" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B590" s="94"/>
+      <c r="B590" s="37"/>
     </row>
     <row r="591" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B591" s="94"/>
+      <c r="B591" s="37"/>
     </row>
     <row r="592" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B592" s="94"/>
+      <c r="B592" s="37"/>
     </row>
     <row r="593" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B593" s="94"/>
+      <c r="B593" s="37"/>
     </row>
     <row r="594" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B594" s="94"/>
+      <c r="B594" s="37"/>
     </row>
     <row r="595" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B595" s="94"/>
+      <c r="B595" s="37"/>
     </row>
     <row r="596" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B596" s="94"/>
+      <c r="B596" s="37"/>
     </row>
     <row r="597" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B597" s="94"/>
+      <c r="B597" s="37"/>
     </row>
     <row r="598" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B598" s="94"/>
+      <c r="B598" s="37"/>
     </row>
     <row r="599" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B599" s="94"/>
+      <c r="B599" s="37"/>
     </row>
     <row r="600" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B600" s="94"/>
+      <c r="B600" s="37"/>
     </row>
     <row r="601" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B601" s="94"/>
+      <c r="B601" s="37"/>
     </row>
     <row r="602" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B602" s="94"/>
+      <c r="B602" s="37"/>
     </row>
     <row r="603" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B603" s="94"/>
+      <c r="B603" s="37"/>
     </row>
     <row r="604" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B604" s="94"/>
+      <c r="B604" s="37"/>
     </row>
     <row r="605" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B605" s="94"/>
+      <c r="B605" s="37"/>
     </row>
     <row r="606" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B606" s="94"/>
+      <c r="B606" s="37"/>
     </row>
     <row r="607" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B607" s="94"/>
+      <c r="B607" s="37"/>
     </row>
     <row r="608" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B608" s="94"/>
+      <c r="B608" s="37"/>
     </row>
     <row r="609" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B609" s="94"/>
+      <c r="B609" s="37"/>
     </row>
     <row r="610" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B610" s="94"/>
+      <c r="B610" s="37"/>
     </row>
     <row r="611" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B611" s="94"/>
+      <c r="B611" s="37"/>
     </row>
     <row r="612" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B612" s="94"/>
+      <c r="B612" s="37"/>
     </row>
     <row r="613" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B613" s="94"/>
+      <c r="B613" s="37"/>
     </row>
     <row r="614" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B614" s="94"/>
+      <c r="B614" s="37"/>
     </row>
     <row r="615" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B615" s="94"/>
+      <c r="B615" s="37"/>
     </row>
     <row r="616" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B616" s="94"/>
+      <c r="B616" s="37"/>
     </row>
     <row r="617" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B617" s="94"/>
+      <c r="B617" s="37"/>
     </row>
     <row r="618" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B618" s="94"/>
+      <c r="B618" s="37"/>
     </row>
     <row r="619" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B619" s="94"/>
+      <c r="B619" s="37"/>
     </row>
     <row r="620" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B620" s="94"/>
+      <c r="B620" s="37"/>
     </row>
     <row r="621" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B621" s="94"/>
+      <c r="B621" s="37"/>
     </row>
     <row r="622" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B622" s="94"/>
+      <c r="B622" s="37"/>
     </row>
     <row r="623" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B623" s="94"/>
+      <c r="B623" s="37"/>
     </row>
     <row r="624" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B624" s="94"/>
+      <c r="B624" s="37"/>
     </row>
     <row r="625" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B625" s="94"/>
+      <c r="B625" s="37"/>
     </row>
     <row r="626" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B626" s="94"/>
+      <c r="B626" s="37"/>
     </row>
     <row r="627" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B627" s="94"/>
+      <c r="B627" s="37"/>
     </row>
     <row r="628" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B628" s="94"/>
+      <c r="B628" s="37"/>
     </row>
     <row r="629" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B629" s="94"/>
+      <c r="B629" s="37"/>
     </row>
     <row r="630" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B630" s="94"/>
+      <c r="B630" s="37"/>
     </row>
     <row r="631" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B631" s="94"/>
+      <c r="B631" s="37"/>
     </row>
     <row r="632" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B632" s="94"/>
+      <c r="B632" s="37"/>
     </row>
     <row r="633" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B633" s="94"/>
+      <c r="B633" s="37"/>
     </row>
     <row r="634" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B634" s="94"/>
+      <c r="B634" s="37"/>
     </row>
     <row r="635" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B635" s="94"/>
+      <c r="B635" s="37"/>
     </row>
     <row r="636" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B636" s="94"/>
+      <c r="B636" s="37"/>
     </row>
     <row r="637" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B637" s="94"/>
+      <c r="B637" s="37"/>
     </row>
     <row r="638" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B638" s="94"/>
+      <c r="B638" s="37"/>
     </row>
     <row r="639" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B639" s="94"/>
+      <c r="B639" s="37"/>
     </row>
     <row r="640" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B640" s="94"/>
+      <c r="B640" s="37"/>
     </row>
     <row r="641" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B641" s="94"/>
+      <c r="B641" s="37"/>
     </row>
     <row r="642" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B642" s="94"/>
+      <c r="B642" s="37"/>
     </row>
     <row r="643" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B643" s="94"/>
+      <c r="B643" s="37"/>
     </row>
     <row r="644" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B644" s="94"/>
+      <c r="B644" s="37"/>
     </row>
     <row r="645" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B645" s="94"/>
+      <c r="B645" s="37"/>
     </row>
     <row r="646" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B646" s="94"/>
+      <c r="B646" s="37"/>
     </row>
     <row r="647" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B647" s="94"/>
+      <c r="B647" s="37"/>
     </row>
     <row r="648" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B648" s="94"/>
+      <c r="B648" s="37"/>
     </row>
     <row r="649" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B649" s="94"/>
+      <c r="B649" s="37"/>
     </row>
     <row r="650" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B650" s="94"/>
+      <c r="B650" s="37"/>
     </row>
     <row r="651" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B651" s="94"/>
+      <c r="B651" s="37"/>
     </row>
     <row r="652" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B652" s="94"/>
+      <c r="B652" s="37"/>
     </row>
     <row r="653" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B653" s="94"/>
+      <c r="B653" s="37"/>
     </row>
     <row r="654" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B654" s="94"/>
+      <c r="B654" s="37"/>
     </row>
     <row r="655" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B655" s="94"/>
+      <c r="B655" s="37"/>
     </row>
     <row r="656" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B656" s="94"/>
+      <c r="B656" s="37"/>
     </row>
     <row r="657" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B657" s="94"/>
+      <c r="B657" s="37"/>
     </row>
     <row r="658" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B658" s="94"/>
+      <c r="B658" s="37"/>
     </row>
     <row r="659" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B659" s="94"/>
+      <c r="B659" s="37"/>
     </row>
     <row r="660" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B660" s="94"/>
+      <c r="B660" s="37"/>
     </row>
     <row r="661" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B661" s="94"/>
+      <c r="B661" s="37"/>
     </row>
     <row r="662" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B662" s="94"/>
+      <c r="B662" s="37"/>
     </row>
     <row r="663" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B663" s="94"/>
+      <c r="B663" s="37"/>
     </row>
     <row r="664" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B664" s="94"/>
+      <c r="B664" s="37"/>
     </row>
     <row r="665" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B665" s="94"/>
+      <c r="B665" s="37"/>
     </row>
     <row r="666" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B666" s="94"/>
+      <c r="B666" s="37"/>
     </row>
     <row r="667" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B667" s="94"/>
+      <c r="B667" s="37"/>
     </row>
     <row r="668" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B668" s="94"/>
+      <c r="B668" s="37"/>
     </row>
     <row r="669" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B669" s="94"/>
+      <c r="B669" s="37"/>
     </row>
     <row r="670" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B670" s="94"/>
+      <c r="B670" s="37"/>
     </row>
     <row r="671" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B671" s="94"/>
+      <c r="B671" s="37"/>
     </row>
     <row r="672" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B672" s="94"/>
+      <c r="B672" s="37"/>
     </row>
     <row r="673" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B673" s="94"/>
+      <c r="B673" s="37"/>
     </row>
     <row r="674" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B674" s="94"/>
+      <c r="B674" s="37"/>
     </row>
     <row r="675" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B675" s="94"/>
+      <c r="B675" s="37"/>
     </row>
     <row r="676" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B676" s="94"/>
+      <c r="B676" s="37"/>
     </row>
     <row r="677" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B677" s="94"/>
+      <c r="B677" s="37"/>
     </row>
     <row r="678" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B678" s="94"/>
+      <c r="B678" s="37"/>
     </row>
     <row r="679" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B679" s="94"/>
+      <c r="B679" s="37"/>
     </row>
     <row r="680" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B680" s="94"/>
+      <c r="B680" s="37"/>
     </row>
     <row r="681" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B681" s="94"/>
+      <c r="B681" s="37"/>
     </row>
     <row r="682" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B682" s="94"/>
+      <c r="B682" s="37"/>
     </row>
     <row r="683" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B683" s="94"/>
+      <c r="B683" s="37"/>
     </row>
     <row r="684" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B684" s="94"/>
+      <c r="B684" s="37"/>
     </row>
     <row r="685" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B685" s="94"/>
+      <c r="B685" s="37"/>
     </row>
     <row r="686" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B686" s="94"/>
+      <c r="B686" s="37"/>
     </row>
     <row r="687" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B687" s="94"/>
+      <c r="B687" s="37"/>
     </row>
     <row r="688" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B688" s="94"/>
+      <c r="B688" s="37"/>
     </row>
     <row r="689" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B689" s="94"/>
+      <c r="B689" s="37"/>
     </row>
     <row r="690" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B690" s="94"/>
+      <c r="B690" s="37"/>
     </row>
     <row r="691" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B691" s="94"/>
+      <c r="B691" s="37"/>
     </row>
     <row r="692" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B692" s="94"/>
+      <c r="B692" s="37"/>
     </row>
     <row r="693" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B693" s="94"/>
+      <c r="B693" s="37"/>
     </row>
     <row r="694" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B694" s="94"/>
+      <c r="B694" s="37"/>
     </row>
     <row r="695" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B695" s="94"/>
+      <c r="B695" s="37"/>
     </row>
     <row r="696" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B696" s="94"/>
+      <c r="B696" s="37"/>
     </row>
     <row r="697" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B697" s="94"/>
+      <c r="B697" s="37"/>
     </row>
     <row r="698" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B698" s="94"/>
+      <c r="B698" s="37"/>
     </row>
     <row r="699" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B699" s="94"/>
+      <c r="B699" s="37"/>
     </row>
     <row r="700" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B700" s="94"/>
+      <c r="B700" s="37"/>
     </row>
     <row r="701" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B701" s="94"/>
+      <c r="B701" s="37"/>
     </row>
     <row r="702" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B702" s="94"/>
+      <c r="B702" s="37"/>
     </row>
     <row r="703" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B703" s="94"/>
+      <c r="B703" s="37"/>
     </row>
     <row r="704" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B704" s="94"/>
+      <c r="B704" s="37"/>
     </row>
     <row r="705" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B705" s="94"/>
+      <c r="B705" s="37"/>
     </row>
     <row r="706" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B706" s="94"/>
+      <c r="B706" s="37"/>
     </row>
     <row r="707" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B707" s="94"/>
+      <c r="B707" s="37"/>
     </row>
     <row r="708" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B708" s="94"/>
+      <c r="B708" s="37"/>
     </row>
     <row r="709" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B709" s="94"/>
+      <c r="B709" s="37"/>
     </row>
     <row r="710" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B710" s="94"/>
+      <c r="B710" s="37"/>
     </row>
     <row r="711" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B711" s="94"/>
+      <c r="B711" s="37"/>
     </row>
     <row r="712" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B712" s="94"/>
+      <c r="B712" s="37"/>
     </row>
     <row r="713" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B713" s="94"/>
+      <c r="B713" s="37"/>
     </row>
     <row r="714" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B714" s="94"/>
+      <c r="B714" s="37"/>
     </row>
     <row r="715" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B715" s="94"/>
+      <c r="B715" s="37"/>
     </row>
     <row r="716" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B716" s="94"/>
+      <c r="B716" s="37"/>
     </row>
     <row r="717" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B717" s="94"/>
+      <c r="B717" s="37"/>
     </row>
     <row r="718" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B718" s="94"/>
+      <c r="B718" s="37"/>
     </row>
     <row r="719" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B719" s="94"/>
+      <c r="B719" s="37"/>
     </row>
     <row r="720" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B720" s="94"/>
+      <c r="B720" s="37"/>
     </row>
     <row r="721" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B721" s="94"/>
+      <c r="B721" s="37"/>
     </row>
     <row r="722" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B722" s="94"/>
+      <c r="B722" s="37"/>
     </row>
     <row r="723" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B723" s="94"/>
+      <c r="B723" s="37"/>
     </row>
     <row r="724" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B724" s="94"/>
+      <c r="B724" s="37"/>
     </row>
     <row r="725" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B725" s="94"/>
+      <c r="B725" s="37"/>
     </row>
     <row r="726" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B726" s="94"/>
+      <c r="B726" s="37"/>
     </row>
     <row r="727" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B727" s="94"/>
+      <c r="B727" s="37"/>
     </row>
     <row r="728" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B728" s="94"/>
+      <c r="B728" s="37"/>
     </row>
     <row r="729" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B729" s="94"/>
+      <c r="B729" s="37"/>
     </row>
     <row r="730" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B730" s="94"/>
+      <c r="B730" s="37"/>
     </row>
     <row r="731" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B731" s="94"/>
+      <c r="B731" s="37"/>
     </row>
     <row r="732" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B732" s="94"/>
+      <c r="B732" s="37"/>
     </row>
     <row r="733" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B733" s="94"/>
+      <c r="B733" s="37"/>
     </row>
     <row r="734" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B734" s="94"/>
+      <c r="B734" s="37"/>
     </row>
     <row r="735" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B735" s="94"/>
+      <c r="B735" s="37"/>
     </row>
     <row r="736" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B736" s="94"/>
+      <c r="B736" s="37"/>
     </row>
     <row r="737" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B737" s="94"/>
+      <c r="B737" s="37"/>
     </row>
     <row r="738" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B738" s="94"/>
+      <c r="B738" s="37"/>
     </row>
     <row r="739" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B739" s="94"/>
+      <c r="B739" s="37"/>
     </row>
     <row r="740" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B740" s="94"/>
+      <c r="B740" s="37"/>
     </row>
     <row r="741" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B741" s="94"/>
+      <c r="B741" s="37"/>
     </row>
     <row r="742" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B742" s="94"/>
+      <c r="B742" s="37"/>
     </row>
     <row r="743" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B743" s="94"/>
+      <c r="B743" s="37"/>
     </row>
     <row r="744" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B744" s="94"/>
+      <c r="B744" s="37"/>
     </row>
     <row r="745" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B745" s="94"/>
+      <c r="B745" s="37"/>
     </row>
     <row r="746" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B746" s="94"/>
+      <c r="B746" s="37"/>
     </row>
     <row r="747" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B747" s="94"/>
+      <c r="B747" s="37"/>
     </row>
     <row r="748" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B748" s="94"/>
+      <c r="B748" s="37"/>
     </row>
     <row r="749" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B749" s="94"/>
+      <c r="B749" s="37"/>
     </row>
     <row r="750" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B750" s="94"/>
+      <c r="B750" s="37"/>
     </row>
     <row r="751" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B751" s="94"/>
+      <c r="B751" s="37"/>
     </row>
     <row r="752" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B752" s="94"/>
+      <c r="B752" s="37"/>
     </row>
     <row r="753" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B753" s="94"/>
+      <c r="B753" s="37"/>
     </row>
     <row r="754" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B754" s="94"/>
+      <c r="B754" s="37"/>
     </row>
     <row r="755" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B755" s="94"/>
+      <c r="B755" s="37"/>
     </row>
     <row r="756" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B756" s="94"/>
+      <c r="B756" s="37"/>
     </row>
     <row r="757" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B757" s="94"/>
+      <c r="B757" s="37"/>
     </row>
     <row r="758" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B758" s="94"/>
+      <c r="B758" s="37"/>
     </row>
     <row r="759" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B759" s="94"/>
+      <c r="B759" s="37"/>
     </row>
     <row r="760" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B760" s="94"/>
+      <c r="B760" s="37"/>
     </row>
     <row r="761" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B761" s="94"/>
+      <c r="B761" s="37"/>
     </row>
     <row r="762" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B762" s="94"/>
+      <c r="B762" s="37"/>
     </row>
     <row r="763" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B763" s="94"/>
+      <c r="B763" s="37"/>
     </row>
     <row r="764" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B764" s="94"/>
+      <c r="B764" s="37"/>
     </row>
     <row r="765" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B765" s="94"/>
+      <c r="B765" s="37"/>
     </row>
     <row r="766" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B766" s="94"/>
+      <c r="B766" s="37"/>
     </row>
     <row r="767" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B767" s="94"/>
+      <c r="B767" s="37"/>
     </row>
     <row r="768" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B768" s="94"/>
+      <c r="B768" s="37"/>
     </row>
     <row r="769" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B769" s="94"/>
+      <c r="B769" s="37"/>
     </row>
     <row r="770" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B770" s="94"/>
+      <c r="B770" s="37"/>
     </row>
     <row r="771" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B771" s="94"/>
+      <c r="B771" s="37"/>
     </row>
     <row r="772" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B772" s="94"/>
+      <c r="B772" s="37"/>
     </row>
     <row r="773" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B773" s="94"/>
+      <c r="B773" s="37"/>
     </row>
     <row r="774" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B774" s="94"/>
+      <c r="B774" s="37"/>
     </row>
     <row r="775" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B775" s="94"/>
+      <c r="B775" s="37"/>
     </row>
     <row r="776" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B776" s="94"/>
+      <c r="B776" s="37"/>
     </row>
     <row r="777" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B777" s="94"/>
+      <c r="B777" s="37"/>
     </row>
     <row r="778" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B778" s="94"/>
+      <c r="B778" s="37"/>
     </row>
     <row r="779" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B779" s="94"/>
+      <c r="B779" s="37"/>
     </row>
     <row r="780" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B780" s="94"/>
+      <c r="B780" s="37"/>
     </row>
     <row r="781" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B781" s="94"/>
+      <c r="B781" s="37"/>
     </row>
     <row r="782" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B782" s="94"/>
+      <c r="B782" s="37"/>
     </row>
     <row r="783" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B783" s="94"/>
+      <c r="B783" s="37"/>
     </row>
     <row r="784" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B784" s="94"/>
+      <c r="B784" s="37"/>
     </row>
     <row r="785" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B785" s="94"/>
+      <c r="B785" s="37"/>
     </row>
     <row r="786" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B786" s="94"/>
+      <c r="B786" s="37"/>
     </row>
     <row r="787" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B787" s="94"/>
+      <c r="B787" s="37"/>
     </row>
     <row r="788" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B788" s="94"/>
+      <c r="B788" s="37"/>
     </row>
     <row r="789" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B789" s="94"/>
+      <c r="B789" s="37"/>
     </row>
     <row r="790" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B790" s="94"/>
+      <c r="B790" s="37"/>
     </row>
     <row r="791" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B791" s="94"/>
+      <c r="B791" s="37"/>
     </row>
     <row r="792" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B792" s="94"/>
+      <c r="B792" s="37"/>
     </row>
     <row r="793" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B793" s="94"/>
+      <c r="B793" s="37"/>
     </row>
     <row r="794" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B794" s="94"/>
+      <c r="B794" s="37"/>
     </row>
     <row r="795" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B795" s="94"/>
+      <c r="B795" s="37"/>
     </row>
     <row r="796" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B796" s="94"/>
+      <c r="B796" s="37"/>
     </row>
     <row r="797" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B797" s="94"/>
+      <c r="B797" s="37"/>
     </row>
     <row r="798" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B798" s="94"/>
+      <c r="B798" s="37"/>
     </row>
     <row r="799" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B799" s="94"/>
+      <c r="B799" s="37"/>
     </row>
     <row r="800" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B800" s="94"/>
+      <c r="B800" s="37"/>
     </row>
     <row r="801" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B801" s="94"/>
+      <c r="B801" s="37"/>
     </row>
     <row r="802" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B802" s="94"/>
+      <c r="B802" s="37"/>
     </row>
     <row r="803" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B803" s="94"/>
+      <c r="B803" s="37"/>
     </row>
     <row r="804" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B804" s="94"/>
+      <c r="B804" s="37"/>
     </row>
     <row r="805" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B805" s="94"/>
+      <c r="B805" s="37"/>
     </row>
     <row r="806" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B806" s="94"/>
+      <c r="B806" s="37"/>
     </row>
     <row r="807" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B807" s="94"/>
+      <c r="B807" s="37"/>
     </row>
     <row r="808" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B808" s="94"/>
+      <c r="B808" s="37"/>
     </row>
     <row r="809" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B809" s="94"/>
+      <c r="B809" s="37"/>
     </row>
     <row r="810" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B810" s="94"/>
+      <c r="B810" s="37"/>
     </row>
     <row r="811" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B811" s="94"/>
+      <c r="B811" s="37"/>
     </row>
     <row r="812" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B812" s="94"/>
+      <c r="B812" s="37"/>
     </row>
     <row r="813" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B813" s="94"/>
+      <c r="B813" s="37"/>
     </row>
     <row r="814" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B814" s="94"/>
+      <c r="B814" s="37"/>
     </row>
     <row r="815" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B815" s="94"/>
+      <c r="B815" s="37"/>
     </row>
     <row r="816" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B816" s="94"/>
+      <c r="B816" s="37"/>
     </row>
     <row r="817" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B817" s="94"/>
+      <c r="B817" s="37"/>
     </row>
     <row r="818" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B818" s="94"/>
+      <c r="B818" s="37"/>
     </row>
     <row r="819" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B819" s="94"/>
+      <c r="B819" s="37"/>
     </row>
     <row r="820" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B820" s="94"/>
+      <c r="B820" s="37"/>
     </row>
     <row r="821" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B821" s="94"/>
+      <c r="B821" s="37"/>
     </row>
     <row r="822" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B822" s="94"/>
+      <c r="B822" s="37"/>
     </row>
     <row r="823" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B823" s="94"/>
+      <c r="B823" s="37"/>
     </row>
     <row r="824" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B824" s="94"/>
+      <c r="B824" s="37"/>
     </row>
     <row r="825" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B825" s="94"/>
+      <c r="B825" s="37"/>
     </row>
     <row r="826" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B826" s="94"/>
+      <c r="B826" s="37"/>
     </row>
     <row r="827" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B827" s="94"/>
+      <c r="B827" s="37"/>
     </row>
     <row r="828" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B828" s="94"/>
+      <c r="B828" s="37"/>
     </row>
     <row r="829" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B829" s="94"/>
+      <c r="B829" s="37"/>
     </row>
     <row r="830" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B830" s="94"/>
+      <c r="B830" s="37"/>
     </row>
     <row r="831" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B831" s="94"/>
+      <c r="B831" s="37"/>
     </row>
     <row r="832" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B832" s="94"/>
+      <c r="B832" s="37"/>
     </row>
     <row r="833" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B833" s="94"/>
+      <c r="B833" s="37"/>
     </row>
     <row r="834" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B834" s="94"/>
+      <c r="B834" s="37"/>
     </row>
     <row r="835" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B835" s="94"/>
+      <c r="B835" s="37"/>
     </row>
     <row r="836" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B836" s="94"/>
+      <c r="B836" s="37"/>
     </row>
     <row r="837" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B837" s="94"/>
+      <c r="B837" s="37"/>
     </row>
     <row r="838" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B838" s="94"/>
+      <c r="B838" s="37"/>
     </row>
     <row r="839" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B839" s="94"/>
+      <c r="B839" s="37"/>
     </row>
     <row r="840" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B840" s="94"/>
+      <c r="B840" s="37"/>
     </row>
     <row r="841" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B841" s="94"/>
+      <c r="B841" s="37"/>
     </row>
     <row r="842" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B842" s="94"/>
+      <c r="B842" s="37"/>
     </row>
     <row r="843" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B843" s="94"/>
+      <c r="B843" s="37"/>
     </row>
     <row r="844" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B844" s="94"/>
+      <c r="B844" s="37"/>
     </row>
     <row r="845" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B845" s="94"/>
+      <c r="B845" s="37"/>
     </row>
     <row r="846" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B846" s="94"/>
+      <c r="B846" s="37"/>
     </row>
     <row r="847" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B847" s="94"/>
+      <c r="B847" s="37"/>
     </row>
     <row r="848" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B848" s="94"/>
+      <c r="B848" s="37"/>
     </row>
     <row r="849" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B849" s="94"/>
+      <c r="B849" s="37"/>
     </row>
     <row r="850" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B850" s="94"/>
+      <c r="B850" s="37"/>
     </row>
     <row r="851" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B851" s="94"/>
+      <c r="B851" s="37"/>
     </row>
     <row r="852" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B852" s="94"/>
+      <c r="B852" s="37"/>
     </row>
     <row r="853" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B853" s="94"/>
+      <c r="B853" s="37"/>
     </row>
     <row r="854" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B854" s="94"/>
+      <c r="B854" s="37"/>
     </row>
     <row r="855" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B855" s="94"/>
+      <c r="B855" s="37"/>
     </row>
     <row r="856" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B856" s="94"/>
+      <c r="B856" s="37"/>
     </row>
     <row r="857" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B857" s="94"/>
+      <c r="B857" s="37"/>
     </row>
     <row r="858" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B858" s="94"/>
+      <c r="B858" s="37"/>
     </row>
     <row r="859" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B859" s="94"/>
+      <c r="B859" s="37"/>
     </row>
     <row r="860" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B860" s="94"/>
+      <c r="B860" s="37"/>
     </row>
     <row r="861" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B861" s="94"/>
+      <c r="B861" s="37"/>
     </row>
     <row r="862" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B862" s="94"/>
+      <c r="B862" s="37"/>
     </row>
     <row r="863" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B863" s="94"/>
+      <c r="B863" s="37"/>
     </row>
     <row r="864" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B864" s="94"/>
+      <c r="B864" s="37"/>
     </row>
     <row r="865" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B865" s="94"/>
+      <c r="B865" s="37"/>
     </row>
     <row r="866" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B866" s="94"/>
+      <c r="B866" s="37"/>
     </row>
     <row r="867" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B867" s="94"/>
+      <c r="B867" s="37"/>
     </row>
     <row r="868" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B868" s="94"/>
+      <c r="B868" s="37"/>
     </row>
     <row r="869" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B869" s="94"/>
+      <c r="B869" s="37"/>
     </row>
     <row r="870" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B870" s="94"/>
+      <c r="B870" s="37"/>
     </row>
     <row r="871" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B871" s="94"/>
+      <c r="B871" s="37"/>
     </row>
     <row r="872" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B872" s="94"/>
+      <c r="B872" s="37"/>
     </row>
     <row r="873" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B873" s="94"/>
+      <c r="B873" s="37"/>
     </row>
     <row r="874" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B874" s="94"/>
+      <c r="B874" s="37"/>
     </row>
     <row r="875" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B875" s="94"/>
+      <c r="B875" s="37"/>
     </row>
     <row r="876" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B876" s="94"/>
+      <c r="B876" s="37"/>
     </row>
     <row r="877" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B877" s="94"/>
+      <c r="B877" s="37"/>
     </row>
     <row r="878" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B878" s="94"/>
+      <c r="B878" s="37"/>
     </row>
     <row r="879" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B879" s="94"/>
+      <c r="B879" s="37"/>
     </row>
     <row r="880" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B880" s="94"/>
+      <c r="B880" s="37"/>
     </row>
     <row r="881" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B881" s="94"/>
+      <c r="B881" s="37"/>
     </row>
     <row r="882" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B882" s="94"/>
+      <c r="B882" s="37"/>
     </row>
     <row r="883" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B883" s="94"/>
+      <c r="B883" s="37"/>
     </row>
     <row r="884" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B884" s="94"/>
+      <c r="B884" s="37"/>
     </row>
     <row r="885" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B885" s="94"/>
+      <c r="B885" s="37"/>
     </row>
     <row r="886" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B886" s="94"/>
+      <c r="B886" s="37"/>
     </row>
     <row r="887" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B887" s="94"/>
+      <c r="B887" s="37"/>
     </row>
     <row r="888" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B888" s="94"/>
+      <c r="B888" s="37"/>
     </row>
     <row r="889" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B889" s="94"/>
+      <c r="B889" s="37"/>
     </row>
     <row r="890" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B890" s="94"/>
+      <c r="B890" s="37"/>
     </row>
     <row r="891" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B891" s="94"/>
+      <c r="B891" s="37"/>
     </row>
     <row r="892" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B892" s="94"/>
+      <c r="B892" s="37"/>
     </row>
     <row r="893" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B893" s="94"/>
+      <c r="B893" s="37"/>
     </row>
     <row r="894" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B894" s="94"/>
+      <c r="B894" s="37"/>
     </row>
     <row r="895" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B895" s="94"/>
+      <c r="B895" s="37"/>
     </row>
     <row r="896" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B896" s="94"/>
+      <c r="B896" s="37"/>
     </row>
     <row r="897" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B897" s="94"/>
+      <c r="B897" s="37"/>
     </row>
     <row r="898" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B898" s="94"/>
+      <c r="B898" s="37"/>
     </row>
     <row r="899" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B899" s="94"/>
+      <c r="B899" s="37"/>
     </row>
     <row r="900" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B900" s="94"/>
+      <c r="B900" s="37"/>
     </row>
     <row r="901" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B901" s="94"/>
+      <c r="B901" s="37"/>
     </row>
     <row r="902" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B902" s="94"/>
+      <c r="B902" s="37"/>
     </row>
     <row r="903" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B903" s="94"/>
+      <c r="B903" s="37"/>
     </row>
     <row r="904" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B904" s="94"/>
+      <c r="B904" s="37"/>
     </row>
     <row r="905" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B905" s="94"/>
+      <c r="B905" s="37"/>
     </row>
     <row r="906" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B906" s="94"/>
+      <c r="B906" s="37"/>
     </row>
     <row r="907" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B907" s="94"/>
+      <c r="B907" s="37"/>
     </row>
     <row r="908" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B908" s="94"/>
+      <c r="B908" s="37"/>
     </row>
     <row r="909" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B909" s="94"/>
+      <c r="B909" s="37"/>
     </row>
     <row r="910" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B910" s="94"/>
+      <c r="B910" s="37"/>
     </row>
     <row r="911" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B911" s="94"/>
+      <c r="B911" s="37"/>
     </row>
     <row r="912" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B912" s="94"/>
+      <c r="B912" s="37"/>
     </row>
     <row r="913" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B913" s="94"/>
+      <c r="B913" s="37"/>
     </row>
     <row r="914" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B914" s="94"/>
+      <c r="B914" s="37"/>
     </row>
     <row r="915" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B915" s="94"/>
+      <c r="B915" s="37"/>
     </row>
     <row r="916" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B916" s="94"/>
+      <c r="B916" s="37"/>
     </row>
     <row r="917" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B917" s="94"/>
+      <c r="B917" s="37"/>
     </row>
     <row r="918" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B918" s="94"/>
+      <c r="B918" s="37"/>
     </row>
     <row r="919" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B919" s="94"/>
+      <c r="B919" s="37"/>
     </row>
     <row r="920" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B920" s="94"/>
+      <c r="B920" s="37"/>
     </row>
     <row r="921" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B921" s="94"/>
+      <c r="B921" s="37"/>
     </row>
     <row r="922" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B922" s="94"/>
+      <c r="B922" s="37"/>
     </row>
     <row r="923" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B923" s="94"/>
+      <c r="B923" s="37"/>
     </row>
     <row r="924" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B924" s="94"/>
+      <c r="B924" s="37"/>
     </row>
     <row r="925" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B925" s="94"/>
+      <c r="B925" s="37"/>
     </row>
     <row r="926" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B926" s="94"/>
+      <c r="B926" s="37"/>
     </row>
     <row r="927" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B927" s="94"/>
+      <c r="B927" s="37"/>
     </row>
     <row r="928" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B928" s="94"/>
+      <c r="B928" s="37"/>
     </row>
     <row r="929" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B929" s="94"/>
+      <c r="B929" s="37"/>
     </row>
     <row r="930" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B930" s="94"/>
+      <c r="B930" s="37"/>
     </row>
     <row r="931" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B931" s="94"/>
+      <c r="B931" s="37"/>
     </row>
     <row r="932" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B932" s="94"/>
+      <c r="B932" s="37"/>
     </row>
     <row r="933" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B933" s="94"/>
+      <c r="B933" s="37"/>
     </row>
     <row r="934" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B934" s="94"/>
+      <c r="B934" s="37"/>
     </row>
     <row r="935" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B935" s="94"/>
+      <c r="B935" s="37"/>
     </row>
     <row r="936" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B936" s="94"/>
+      <c r="B936" s="37"/>
     </row>
     <row r="937" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B937" s="94"/>
+      <c r="B937" s="37"/>
     </row>
     <row r="938" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B938" s="94"/>
+      <c r="B938" s="37"/>
     </row>
     <row r="939" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B939" s="94"/>
+      <c r="B939" s="37"/>
     </row>
     <row r="940" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B940" s="94"/>
+      <c r="B940" s="37"/>
     </row>
     <row r="941" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B941" s="94"/>
+      <c r="B941" s="37"/>
     </row>
     <row r="942" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B942" s="94"/>
+      <c r="B942" s="37"/>
     </row>
     <row r="943" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B943" s="94"/>
+      <c r="B943" s="37"/>
     </row>
     <row r="944" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B944" s="94"/>
+      <c r="B944" s="37"/>
     </row>
     <row r="945" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B945" s="94"/>
+      <c r="B945" s="37"/>
     </row>
     <row r="946" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B946" s="94"/>
+      <c r="B946" s="37"/>
     </row>
     <row r="947" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B947" s="94"/>
+      <c r="B947" s="37"/>
     </row>
     <row r="948" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B948" s="94"/>
+      <c r="B948" s="37"/>
     </row>
     <row r="949" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B949" s="94"/>
+      <c r="B949" s="37"/>
     </row>
     <row r="950" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B950" s="94"/>
+      <c r="B950" s="37"/>
     </row>
     <row r="951" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B951" s="94"/>
+      <c r="B951" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AJ74" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="9">
       <filters>
-        <filter val="2.025"/>
-        <filter val="2.026"/>
-        <filter val="2025"/>
-        <filter val="2026"/>
+        <filter val="Q1"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -12829,7 +12819,7 @@
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:R1048576 V1:V1048576 E1:J1048576">
+  <conditionalFormatting sqref="E1:J1048576 M1:R1048576 V1:V1048576">
     <cfRule type="expression" dxfId="10" priority="8">
       <formula>LEN(TRIM(E1))=0</formula>
     </cfRule>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72BA24C-1FC2-6940-99FE-6E90FC8AB486}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="11_A01FD29891CAEC7929076C3559B1863E17DF08B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A082E9-4C2B-5842-BA7D-A2E24E9E2F23}"/>
   <bookViews>
-    <workbookView xWindow="-35860" yWindow="2620" windowWidth="35840" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AJ$74</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="803">
   <si>
     <t>Tipo</t>
   </si>
@@ -2425,9 +2438,6 @@
     <t>[https://arxiv.org/abs/2505.02271]</t>
   </si>
   <si>
-    <t>[https://github.com/dncampo/real-time-spatial-rag-for-smart-cities, https://github.com/javicond3/spatial_rag_vector_rag]</t>
-  </si>
-  <si>
     <t>The proliferation of Generative Artificial Ingelligence (AI), especially Large Language Models, presents transformative opportunities for urban applications through Urban Foundation Models. However, base models face limitations, as they only contain the knowledge available at the time of training, and updating them is both time-consuming and costly. Retrieval Augmented Generation (RAG) has emerged in the literature as the preferred approach for injecting contextual information into Foundation Models. It prevails over techniques such as fine-tuning, which are less effective in dynamic, real-time scenarios like those found in urban environments. However, traditional RAG architectures, based on semantic databases, knowledge graphs, structured data, or AI-powered web searches, do not fully meet the demands of urban contexts. Urban environments are complex systems characterized by large volumes of interconnected data, frequent updates, real-time processing requirements, security needs, and strong links to the physical world. This work proposes a real-time spatial RAG architecture that defines the necessary components for the effective integration of generative AI into cities, leveraging temporal and spatial filtering capabilities through linked data. The proposed architecture is implemented using FIWARE, an ecosystem of software components to develop smart city solutions and digital twins. The design and implementation are demonstrated through the use case of a tourism assistant in the city of Madrid. The use case serves to validate the correct integration of Foundation Models through the proposed RAG architecture.</t>
   </si>
   <si>
@@ -3013,12 +3023,21 @@
   <si>
     <t>Índice de impacto JCR (2025): 4.5 (115/369 – Q2)</t>
   </si>
+  <si>
+    <t>[https://www.linkedin.com/posts/tomorrow-our-colleague-javier-conde-share-7474393536004816896-bkeM]</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, BRIDGE-AI, TUCAN6-CM]</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.5281/zenodo.20889036, https://github.com/dncampo/real-time-spatial-rag-for-smart-cities, https://github.com/javicond3/spatial_rag_vector_rag]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3144,6 +3163,12 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -3238,7 +3263,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3506,6 +3531,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3893,7 +3921,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ951"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4026,13 +4053,13 @@
         <v>33</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AJ1" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="12" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="72" t="s">
         <v>35</v>
       </c>
@@ -4120,7 +4147,7 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" spans="1:36" s="12" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
@@ -4208,7 +4235,7 @@
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
     </row>
-    <row r="4" spans="1:36" s="12" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" s="12" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
@@ -4302,7 +4329,7 @@
       <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
     </row>
-    <row r="5" spans="1:36" s="53" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="63" t="s">
         <v>55</v>
       </c>
@@ -4396,7 +4423,7 @@
       <c r="AI5" s="63"/>
       <c r="AJ5" s="63"/>
     </row>
-    <row r="6" spans="1:36" s="12" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="12" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="72" t="s">
         <v>35</v>
       </c>
@@ -4484,7 +4511,7 @@
       <c r="AI6" s="9"/>
       <c r="AJ6" s="9"/>
     </row>
-    <row r="7" spans="1:36" s="12" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" s="12" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="72" t="s">
         <v>35</v>
       </c>
@@ -4672,7 +4699,7 @@
       <c r="AI8" s="63"/>
       <c r="AJ8" s="63"/>
     </row>
-    <row r="9" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="63" t="s">
         <v>55</v>
       </c>
@@ -4772,7 +4799,7 @@
       <c r="AI9" s="63"/>
       <c r="AJ9" s="63"/>
     </row>
-    <row r="10" spans="1:36" s="2" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
         <v>55</v>
       </c>
@@ -4864,7 +4891,7 @@
       <c r="AI10" s="37"/>
       <c r="AJ10" s="37"/>
     </row>
-    <row r="11" spans="1:36" s="2" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
         <v>55</v>
       </c>
@@ -4954,7 +4981,7 @@
       <c r="AI11" s="37"/>
       <c r="AJ11" s="37"/>
     </row>
-    <row r="12" spans="1:36" s="2" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="79" t="s">
         <v>153</v>
       </c>
@@ -5040,7 +5067,7 @@
       <c r="AI12" s="37"/>
       <c r="AJ12" s="37"/>
     </row>
-    <row r="13" spans="1:36" s="2" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="79" t="s">
         <v>35</v>
       </c>
@@ -5128,7 +5155,7 @@
       <c r="AI13" s="37"/>
       <c r="AJ13" s="37"/>
     </row>
-    <row r="14" spans="1:36" s="53" customFormat="1" ht="84.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="53" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="78" t="s">
         <v>35</v>
       </c>
@@ -5216,7 +5243,7 @@
       <c r="AI14" s="63"/>
       <c r="AJ14" s="63"/>
     </row>
-    <row r="15" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="78" t="s">
         <v>35</v>
       </c>
@@ -5608,7 +5635,7 @@
       <c r="AI18" s="63"/>
       <c r="AJ18" s="63"/>
     </row>
-    <row r="19" spans="1:36" s="53" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="63" t="s">
         <v>55</v>
       </c>
@@ -5708,7 +5735,7 @@
       <c r="AI19" s="63"/>
       <c r="AJ19" s="63"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" s="2" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
         <v>55</v>
       </c>
@@ -5802,7 +5829,7 @@
       <c r="AI20" s="37"/>
       <c r="AJ20" s="37"/>
     </row>
-    <row r="21" spans="1:36" s="2" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="2" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>55</v>
       </c>
@@ -5892,7 +5919,7 @@
       <c r="AI21" s="37"/>
       <c r="AJ21" s="37"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37" t="s">
         <v>55</v>
       </c>
@@ -5984,7 +6011,7 @@
       <c r="AI22" s="37"/>
       <c r="AJ22" s="37"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
         <v>55</v>
       </c>
@@ -6016,7 +6043,7 @@
         <v>73</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L23" s="22" t="s">
         <v>289</v>
@@ -6076,7 +6103,7 @@
       <c r="AI23" s="37"/>
       <c r="AJ23" s="37"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37" t="s">
         <v>55</v>
       </c>
@@ -6168,7 +6195,7 @@
       <c r="AI24" s="37"/>
       <c r="AJ24" s="37"/>
     </row>
-    <row r="25" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="78" t="s">
         <v>153</v>
       </c>
@@ -6256,7 +6283,7 @@
       <c r="AI25" s="63"/>
       <c r="AJ25" s="63"/>
     </row>
-    <row r="26" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="78" t="s">
         <v>153</v>
       </c>
@@ -6344,7 +6371,7 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="63"/>
     </row>
-    <row r="27" spans="1:36" s="53" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="78" t="s">
         <v>153</v>
       </c>
@@ -6432,7 +6459,7 @@
       <c r="AI27" s="63"/>
       <c r="AJ27" s="63"/>
     </row>
-    <row r="28" spans="1:36" s="53" customFormat="1" ht="322.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="78" t="s">
         <v>153</v>
       </c>
@@ -6520,7 +6547,7 @@
       <c r="AI28" s="63"/>
       <c r="AJ28" s="63"/>
     </row>
-    <row r="29" spans="1:36" s="53" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="78" t="s">
         <v>350</v>
       </c>
@@ -6608,7 +6635,7 @@
       <c r="AI29" s="63"/>
       <c r="AJ29" s="63"/>
     </row>
-    <row r="30" spans="1:36" s="53" customFormat="1" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="78" t="s">
         <v>350</v>
       </c>
@@ -6696,7 +6723,7 @@
       <c r="AI30" s="63"/>
       <c r="AJ30" s="63"/>
     </row>
-    <row r="31" spans="1:36" s="53" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" s="53" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="78" t="s">
         <v>35</v>
       </c>
@@ -6784,7 +6811,7 @@
       <c r="AI31" s="63"/>
       <c r="AJ31" s="63"/>
     </row>
-    <row r="32" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="78" t="s">
         <v>372</v>
       </c>
@@ -6888,7 +6915,7 @@
         <v>102</v>
       </c>
       <c r="K33" s="49" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L33" s="49" t="s">
         <v>240</v>
@@ -6921,16 +6948,16 @@
         <v>385</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="Y33" s="93" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="Z33" s="37" t="s">
         <v>386</v>
       </c>
       <c r="AA33" s="37" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AE33" s="37" t="s">
         <v>387</v>
@@ -6942,10 +6969,10 @@
         <v>48</v>
       </c>
       <c r="AI33" s="37" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="79" t="s">
         <v>389</v>
       </c>
@@ -7038,7 +7065,7 @@
         <v>102</v>
       </c>
       <c r="K35" s="49" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L35" s="49" t="s">
         <v>240</v>
@@ -7102,7 +7129,7 @@
       <c r="AI35" s="63"/>
       <c r="AJ35" s="63"/>
     </row>
-    <row r="36" spans="1:36" s="54" customFormat="1" ht="220.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" s="54" customFormat="1" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="63" t="s">
         <v>55</v>
       </c>
@@ -7134,7 +7161,7 @@
         <v>61</v>
       </c>
       <c r="K36" s="49" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L36" s="49" t="s">
         <v>413</v>
@@ -7202,7 +7229,7 @@
       <c r="AI36" s="63"/>
       <c r="AJ36" s="63"/>
     </row>
-    <row r="37" spans="1:36" s="54" customFormat="1" ht="255" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" s="54" customFormat="1" ht="255" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="63" t="s">
         <v>55</v>
       </c>
@@ -7234,7 +7261,7 @@
         <v>61</v>
       </c>
       <c r="K37" s="46" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L37" s="46" t="s">
         <v>427</v>
@@ -7332,7 +7359,7 @@
         <v>102</v>
       </c>
       <c r="K38" s="49" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L38" s="49" t="s">
         <v>441</v>
@@ -7400,7 +7427,7 @@
       <c r="AI38" s="63"/>
       <c r="AJ38" s="63"/>
     </row>
-    <row r="39" spans="1:36" s="54" customFormat="1" ht="237.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="63" t="s">
         <v>55</v>
       </c>
@@ -7432,7 +7459,7 @@
         <v>61</v>
       </c>
       <c r="K39" s="49" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L39" s="49" t="s">
         <v>454</v>
@@ -7498,7 +7525,7 @@
       <c r="AI39" s="63"/>
       <c r="AJ39" s="63"/>
     </row>
-    <row r="40" spans="1:36" s="54" customFormat="1" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" s="54" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="63" t="s">
         <v>55</v>
       </c>
@@ -7526,11 +7553,11 @@
       <c r="I40" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="J40" s="46" t="s">
+      <c r="J40" s="94" t="s">
         <v>61</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L40" s="46" t="s">
         <v>427</v>
@@ -7594,7 +7621,7 @@
       <c r="AI40" s="63"/>
       <c r="AJ40" s="63"/>
     </row>
-    <row r="41" spans="1:36" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="37" t="s">
         <v>55</v>
       </c>
@@ -7626,10 +7653,10 @@
         <v>73</v>
       </c>
       <c r="K41" s="22" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L41" s="22" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="M41" s="23" t="s">
         <v>121</v>
@@ -7684,7 +7711,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="63" t="s">
         <v>55</v>
       </c>
@@ -7716,7 +7743,7 @@
         <v>487</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L42" s="46" t="s">
         <v>488</v>
@@ -7780,7 +7807,7 @@
       <c r="AI42" s="63"/>
       <c r="AJ42" s="63"/>
     </row>
-    <row r="43" spans="1:36" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="37" t="s">
         <v>55</v>
       </c>
@@ -7900,7 +7927,7 @@
         <v>102</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L44" s="22" t="s">
         <v>509</v>
@@ -7960,7 +7987,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="37" t="s">
         <v>55</v>
       </c>
@@ -7992,10 +8019,10 @@
         <v>61</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M45" s="23" t="s">
         <v>55</v>
@@ -8082,7 +8109,7 @@
         <v>102</v>
       </c>
       <c r="K46" s="22" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L46" s="22" t="s">
         <v>509</v>
@@ -8142,7 +8169,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:36" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="79" t="s">
         <v>153</v>
       </c>
@@ -8216,7 +8243,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="79" t="s">
         <v>153</v>
       </c>
@@ -8287,7 +8314,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="78" t="s">
         <v>153</v>
       </c>
@@ -8373,7 +8400,7 @@
       <c r="AI49" s="63"/>
       <c r="AJ49" s="63"/>
     </row>
-    <row r="50" spans="1:36" ht="204" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="79" t="s">
         <v>153</v>
       </c>
@@ -8447,7 +8474,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:36" s="54" customFormat="1" ht="153" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" s="54" customFormat="1" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="78" t="s">
         <v>153</v>
       </c>
@@ -8535,7 +8562,7 @@
       <c r="AI51" s="63"/>
       <c r="AJ51" s="63"/>
     </row>
-    <row r="52" spans="1:36" s="54" customFormat="1" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" s="54" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="78" t="s">
         <v>153</v>
       </c>
@@ -8623,7 +8650,7 @@
       <c r="AI52" s="63"/>
       <c r="AJ52" s="63"/>
     </row>
-    <row r="53" spans="1:36" ht="153" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="79" t="s">
         <v>153</v>
       </c>
@@ -8697,7 +8724,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:36" s="54" customFormat="1" ht="237.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="78" t="s">
         <v>153</v>
       </c>
@@ -8785,7 +8812,7 @@
       <c r="AI54" s="63"/>
       <c r="AJ54" s="63"/>
     </row>
-    <row r="55" spans="1:36" s="54" customFormat="1" ht="118.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="78" t="s">
         <v>350</v>
       </c>
@@ -8873,7 +8900,7 @@
       <c r="AI55" s="63"/>
       <c r="AJ55" s="63"/>
     </row>
-    <row r="56" spans="1:36" s="54" customFormat="1" ht="84.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" s="54" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="78" t="s">
         <v>35</v>
       </c>
@@ -8961,7 +8988,7 @@
       <c r="AI56" s="63"/>
       <c r="AJ56" s="63"/>
     </row>
-    <row r="57" spans="1:36" s="54" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" s="54" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="78" t="s">
         <v>35</v>
       </c>
@@ -9049,7 +9076,7 @@
       <c r="AI57" s="63"/>
       <c r="AJ57" s="63"/>
     </row>
-    <row r="58" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="79" t="s">
         <v>389</v>
       </c>
@@ -9108,7 +9135,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="79" t="s">
         <v>389</v>
       </c>
@@ -9152,22 +9179,22 @@
         <v>642</v>
       </c>
       <c r="Y59" s="37" t="s">
+        <v>802</v>
+      </c>
+      <c r="Z59" s="37" t="s">
+        <v>801</v>
+      </c>
+      <c r="AE59" s="37" t="s">
         <v>643</v>
       </c>
-      <c r="Z59" s="37" t="s">
-        <v>445</v>
-      </c>
-      <c r="AE59" s="37" t="s">
+      <c r="AF59" s="37" t="s">
         <v>644</v>
       </c>
-      <c r="AF59" s="37" t="s">
+      <c r="AH59" s="37" t="s">
         <v>645</v>
       </c>
-      <c r="AH59" s="37" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="60" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="79" t="s">
         <v>389</v>
       </c>
@@ -9175,13 +9202,13 @@
         <v>2025</v>
       </c>
       <c r="D60" s="37" t="s">
+        <v>646</v>
+      </c>
+      <c r="E60" s="37" t="s">
         <v>647</v>
       </c>
-      <c r="E60" s="37" t="s">
+      <c r="F60" s="37" t="s">
         <v>648</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>649</v>
       </c>
       <c r="G60" s="37" t="s">
         <v>393</v>
@@ -9190,7 +9217,7 @@
         <v>393</v>
       </c>
       <c r="O60" s="37" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="P60" s="28">
         <v>10</v>
@@ -9208,27 +9235,30 @@
         <v>44</v>
       </c>
       <c r="W60" s="37" t="s">
+        <v>650</v>
+      </c>
+      <c r="Y60" s="37" t="s">
         <v>651</v>
       </c>
-      <c r="Y60" s="37" t="s">
+      <c r="Z60" s="37" t="s">
         <v>652</v>
       </c>
-      <c r="Z60" s="37" t="s">
+      <c r="AA60" s="37" t="s">
+        <v>800</v>
+      </c>
+      <c r="AE60" s="37" t="s">
         <v>653</v>
       </c>
-      <c r="AE60" s="37" t="s">
+      <c r="AF60" s="37" t="s">
         <v>654</v>
       </c>
-      <c r="AF60" s="37" t="s">
+      <c r="AH60" s="37" t="s">
         <v>655</v>
-      </c>
-      <c r="AH60" s="37" t="s">
-        <v>656</v>
       </c>
       <c r="AI60"/>
       <c r="AJ60"/>
     </row>
-    <row r="61" spans="1:36" ht="169.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="37" t="s">
         <v>55</v>
       </c>
@@ -9237,13 +9267,13 @@
       </c>
       <c r="C61" s="89"/>
       <c r="D61" s="22" t="s">
+        <v>656</v>
+      </c>
+      <c r="E61" s="22" t="s">
         <v>657</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="F61" s="80" t="s">
         <v>658</v>
-      </c>
-      <c r="F61" s="80" t="s">
-        <v>659</v>
       </c>
       <c r="G61" s="24" t="s">
         <v>145</v>
@@ -9258,10 +9288,10 @@
         <v>73</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="M61" s="23" t="s">
         <v>121</v>
@@ -9270,7 +9300,7 @@
         <v>43</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="P61" s="22">
         <v>6</v>
@@ -9290,35 +9320,35 @@
         <v>43</v>
       </c>
       <c r="W61" s="23" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="X61" s="23"/>
       <c r="Y61" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="Z61" s="23" t="s">
         <v>663</v>
       </c>
-      <c r="Z61" s="23" t="s">
+      <c r="AA61" s="23" t="s">
         <v>664</v>
-      </c>
-      <c r="AA61" s="23" t="s">
-        <v>665</v>
       </c>
       <c r="AB61" s="23"/>
       <c r="AC61" s="23"/>
       <c r="AD61" s="23" t="s">
+        <v>665</v>
+      </c>
+      <c r="AE61" s="23" t="s">
         <v>666</v>
       </c>
-      <c r="AE61" s="23" t="s">
+      <c r="AF61" s="23" t="s">
         <v>667</v>
-      </c>
-      <c r="AF61" s="23" t="s">
-        <v>668</v>
       </c>
       <c r="AG61" s="23"/>
       <c r="AH61" s="23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:36" s="54" customFormat="1" ht="186.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="63" t="s">
         <v>55</v>
       </c>
@@ -9327,16 +9357,16 @@
       </c>
       <c r="C62" s="89"/>
       <c r="D62" s="46" t="s">
+        <v>668</v>
+      </c>
+      <c r="E62" s="46" t="s">
         <v>669</v>
       </c>
-      <c r="E62" s="46" t="s">
+      <c r="F62" s="48" t="s">
         <v>670</v>
       </c>
-      <c r="F62" s="48" t="s">
+      <c r="G62" s="47" t="s">
         <v>671</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>672</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>118</v>
@@ -9348,10 +9378,10 @@
         <v>61</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L62" s="46" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M62" s="48" t="s">
         <v>121</v>
@@ -9360,7 +9390,7 @@
         <v>44</v>
       </c>
       <c r="O62" s="46" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P62" s="57">
         <v>5</v>
@@ -9380,28 +9410,28 @@
         <v>44</v>
       </c>
       <c r="W62" s="48" t="s">
+        <v>674</v>
+      </c>
+      <c r="X62" s="90" t="s">
         <v>675</v>
       </c>
-      <c r="X62" s="90" t="s">
+      <c r="Y62" s="48" t="s">
         <v>676</v>
-      </c>
-      <c r="Y62" s="48" t="s">
-        <v>677</v>
       </c>
       <c r="Z62" s="48" t="s">
         <v>198</v>
       </c>
       <c r="AA62" s="48" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AB62" s="48"/>
       <c r="AC62" s="48"/>
       <c r="AD62" s="48"/>
       <c r="AE62" s="48" t="s">
+        <v>678</v>
+      </c>
+      <c r="AF62" s="48" t="s">
         <v>679</v>
-      </c>
-      <c r="AF62" s="48" t="s">
-        <v>680</v>
       </c>
       <c r="AG62" s="48"/>
       <c r="AH62" s="48" t="s">
@@ -9421,19 +9451,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="E63" s="22" t="s">
         <v>681</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="F63" s="80" t="s">
         <v>682</v>
       </c>
-      <c r="F63" s="80" t="s">
+      <c r="G63" s="24" t="s">
         <v>683</v>
       </c>
-      <c r="G63" s="24" t="s">
+      <c r="H63" s="23" t="s">
         <v>684</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>685</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>41</v>
@@ -9442,10 +9472,10 @@
         <v>102</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L63" s="22" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>55</v>
@@ -9454,7 +9484,7 @@
         <v>43</v>
       </c>
       <c r="O63" s="22" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P63" s="87">
         <v>10</v>
@@ -9474,13 +9504,13 @@
         <v>44</v>
       </c>
       <c r="W63" s="91" t="s">
+        <v>687</v>
+      </c>
+      <c r="X63" s="80" t="s">
         <v>688</v>
       </c>
-      <c r="X63" s="80" t="s">
+      <c r="Y63" s="23" t="s">
         <v>689</v>
-      </c>
-      <c r="Y63" s="23" t="s">
-        <v>690</v>
       </c>
       <c r="Z63" s="23" t="s">
         <v>198</v>
@@ -9490,10 +9520,10 @@
       <c r="AC63" s="23"/>
       <c r="AD63" s="23"/>
       <c r="AE63" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="AF63" s="23" t="s">
         <v>691</v>
-      </c>
-      <c r="AF63" s="23" t="s">
-        <v>692</v>
       </c>
       <c r="AG63" s="23"/>
       <c r="AH63" s="23" t="s">
@@ -9502,7 +9532,7 @@
       <c r="AI63"/>
       <c r="AJ63"/>
     </row>
-    <row r="64" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
         <v>350</v>
       </c>
@@ -9511,19 +9541,19 @@
       </c>
       <c r="C64" s="28"/>
       <c r="D64" s="61" t="s">
+        <v>692</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="63" t="s">
         <v>693</v>
       </c>
-      <c r="E64" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="F64" s="63" t="s">
+      <c r="G64" s="64" t="s">
         <v>694</v>
       </c>
-      <c r="G64" s="64" t="s">
-        <v>695</v>
-      </c>
       <c r="H64" s="63" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I64" s="63" t="s">
         <v>41</v>
@@ -9540,7 +9570,7 @@
         <v>41</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P64" s="63">
         <v>2</v>
@@ -9576,10 +9606,10 @@
       <c r="AC64" s="63"/>
       <c r="AD64" s="63"/>
       <c r="AE64" s="63" t="s">
+        <v>696</v>
+      </c>
+      <c r="AF64" s="63" t="s">
         <v>697</v>
-      </c>
-      <c r="AF64" s="63" t="s">
-        <v>698</v>
       </c>
       <c r="AG64" s="63"/>
       <c r="AH64" s="63" t="s">
@@ -9588,7 +9618,7 @@
       <c r="AI64" s="63"/>
       <c r="AJ64" s="63"/>
     </row>
-    <row r="65" spans="1:36" ht="288.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" ht="288.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="79" t="s">
         <v>55</v>
       </c>
@@ -9596,16 +9626,16 @@
         <v>2026</v>
       </c>
       <c r="D65" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="E65" s="37" t="s">
         <v>699</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="F65" s="40" t="s">
         <v>700</v>
       </c>
-      <c r="F65" s="40" t="s">
+      <c r="G65" s="37" t="s">
         <v>701</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>702</v>
       </c>
       <c r="H65" s="37" t="s">
         <v>313</v>
@@ -9617,10 +9647,10 @@
         <v>73</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M65" s="37" t="s">
         <v>55</v>
@@ -9629,7 +9659,7 @@
         <v>43</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P65" s="37">
         <v>6</v>
@@ -9647,28 +9677,28 @@
         <v>43</v>
       </c>
       <c r="W65" s="37" t="s">
+        <v>704</v>
+      </c>
+      <c r="Y65" s="40" t="s">
         <v>705</v>
-      </c>
-      <c r="Y65" s="40" t="s">
-        <v>706</v>
       </c>
       <c r="Z65" s="37" t="s">
         <v>445</v>
       </c>
       <c r="AA65" s="37" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AE65" s="37" t="s">
+        <v>706</v>
+      </c>
+      <c r="AF65" s="37" t="s">
         <v>707</v>
-      </c>
-      <c r="AF65" s="37" t="s">
-        <v>708</v>
       </c>
       <c r="AH65" s="23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79" t="s">
         <v>389</v>
       </c>
@@ -9676,13 +9706,13 @@
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
+        <v>708</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="E66" s="37" t="s">
+      <c r="F66" s="37" t="s">
         <v>710</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>711</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>393</v>
@@ -9691,7 +9721,7 @@
         <v>393</v>
       </c>
       <c r="O66" s="37" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="P66" s="37">
         <v>5</v>
@@ -9709,28 +9739,28 @@
         <v>44</v>
       </c>
       <c r="W66" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="X66" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y66" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="X66" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y66" s="37" t="s">
+      <c r="Z66" s="37" t="s">
+        <v>781</v>
+      </c>
+      <c r="AE66" s="37" t="s">
         <v>714</v>
       </c>
-      <c r="Z66" s="37" t="s">
-        <v>782</v>
-      </c>
-      <c r="AE66" s="37" t="s">
+      <c r="AF66" s="37" t="s">
         <v>715</v>
       </c>
-      <c r="AF66" s="37" t="s">
-        <v>716</v>
-      </c>
       <c r="AH66" s="37" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="67" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79" t="s">
         <v>389</v>
       </c>
@@ -9738,22 +9768,22 @@
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
+        <v>716</v>
+      </c>
+      <c r="E67" s="37" t="s">
         <v>717</v>
       </c>
-      <c r="E67" s="37" t="s">
+      <c r="F67" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="G67" s="37" t="s">
         <v>719</v>
       </c>
-      <c r="G67" s="37" t="s">
+      <c r="H67" s="37" t="s">
+        <v>719</v>
+      </c>
+      <c r="O67" s="37" t="s">
         <v>720</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>720</v>
-      </c>
-      <c r="O67" s="37" t="s">
-        <v>721</v>
       </c>
       <c r="P67" s="28">
         <v>5</v>
@@ -9771,16 +9801,16 @@
         <v>44</v>
       </c>
       <c r="W67" s="37" t="s">
+        <v>721</v>
+      </c>
+      <c r="AE67" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="AE67" s="37" t="s">
+      <c r="AF67" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="AF67" s="37" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="68" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79" t="s">
         <v>389</v>
       </c>
@@ -9788,13 +9818,13 @@
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
+        <v>724</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>725</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="F68" s="37" t="s">
         <v>726</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>727</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>393</v>
@@ -9803,7 +9833,7 @@
         <v>393</v>
       </c>
       <c r="O68" s="37" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P68" s="28">
         <v>5</v>
@@ -9821,16 +9851,16 @@
         <v>44</v>
       </c>
       <c r="W68" s="37" t="s">
+        <v>728</v>
+      </c>
+      <c r="AE68" s="37" t="s">
         <v>729</v>
       </c>
-      <c r="AE68" s="37" t="s">
+      <c r="AF68" s="37" t="s">
         <v>730</v>
       </c>
-      <c r="AF68" s="37" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="69" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79" t="s">
         <v>389</v>
       </c>
@@ -9838,13 +9868,13 @@
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
+        <v>731</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="F69" s="37" t="s">
         <v>733</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>734</v>
       </c>
       <c r="G69" s="37" t="s">
         <v>393</v>
@@ -9853,7 +9883,7 @@
         <v>393</v>
       </c>
       <c r="O69" s="37" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P69" s="28">
         <v>5</v>
@@ -9871,16 +9901,16 @@
         <v>44</v>
       </c>
       <c r="W69" s="37" t="s">
+        <v>735</v>
+      </c>
+      <c r="AE69" s="37" t="s">
         <v>736</v>
       </c>
-      <c r="AE69" s="37" t="s">
+      <c r="AF69" s="37" t="s">
         <v>737</v>
       </c>
-      <c r="AF69" s="37" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="70" spans="1:36" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79" t="s">
         <v>389</v>
       </c>
@@ -9888,13 +9918,13 @@
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
+        <v>738</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>739</v>
       </c>
-      <c r="E70" s="37" t="s">
+      <c r="F70" s="92" t="s">
         <v>740</v>
-      </c>
-      <c r="F70" s="92" t="s">
-        <v>741</v>
       </c>
       <c r="G70" s="37" t="s">
         <v>393</v>
@@ -9903,7 +9933,7 @@
         <v>393</v>
       </c>
       <c r="O70" s="37" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P70" s="28">
         <v>4</v>
@@ -9921,16 +9951,16 @@
         <v>44</v>
       </c>
       <c r="W70" s="37" t="s">
+        <v>742</v>
+      </c>
+      <c r="AE70" s="37" t="s">
         <v>743</v>
       </c>
-      <c r="AE70" s="37" t="s">
+      <c r="AF70" s="37" t="s">
         <v>744</v>
       </c>
-      <c r="AF70" s="37" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="71" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79" t="s">
         <v>389</v>
       </c>
@@ -9938,13 +9968,13 @@
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
+        <v>745</v>
+      </c>
+      <c r="E71" s="37" t="s">
         <v>746</v>
       </c>
-      <c r="E71" s="37" t="s">
+      <c r="F71" s="37" t="s">
         <v>747</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>748</v>
       </c>
       <c r="G71" s="37" t="s">
         <v>393</v>
@@ -9953,7 +9983,7 @@
         <v>393</v>
       </c>
       <c r="O71" s="37" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P71" s="28">
         <v>7</v>
@@ -9971,25 +10001,25 @@
         <v>44</v>
       </c>
       <c r="W71" s="37" t="s">
+        <v>749</v>
+      </c>
+      <c r="Z71" s="37" t="s">
+        <v>777</v>
+      </c>
+      <c r="AE71" s="37" t="s">
         <v>750</v>
       </c>
-      <c r="Z71" s="37" t="s">
+      <c r="AF71" s="37" t="s">
+        <v>751</v>
+      </c>
+      <c r="AH71" s="37" t="s">
         <v>778</v>
       </c>
-      <c r="AE71" s="37" t="s">
-        <v>751</v>
-      </c>
-      <c r="AF71" s="37" t="s">
-        <v>752</v>
-      </c>
-      <c r="AH71" s="37" t="s">
-        <v>779</v>
-      </c>
       <c r="AI71" s="37" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="72" spans="1:36" s="54" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="78" t="s">
         <v>372</v>
       </c>
@@ -9998,19 +10028,19 @@
       </c>
       <c r="C72" s="28"/>
       <c r="D72" s="63" t="s">
+        <v>752</v>
+      </c>
+      <c r="E72" s="63" t="s">
         <v>753</v>
       </c>
-      <c r="E72" s="63" t="s">
+      <c r="F72" s="76" t="s">
         <v>754</v>
       </c>
-      <c r="F72" s="76" t="s">
+      <c r="G72" s="63" t="s">
         <v>755</v>
       </c>
-      <c r="G72" s="63" t="s">
-        <v>756</v>
-      </c>
       <c r="H72" s="63" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I72" s="63" t="s">
         <v>41</v>
@@ -10027,7 +10057,7 @@
         <v>41</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="P72" s="65">
         <v>6</v>
@@ -10065,10 +10095,10 @@
       <c r="AC72" s="63"/>
       <c r="AD72" s="63"/>
       <c r="AE72" s="63" t="s">
+        <v>757</v>
+      </c>
+      <c r="AF72" s="63" t="s">
         <v>758</v>
-      </c>
-      <c r="AF72" s="63" t="s">
-        <v>759</v>
       </c>
       <c r="AG72" s="63"/>
       <c r="AH72" s="63" t="s">
@@ -10077,7 +10107,7 @@
       <c r="AI72" s="63"/>
       <c r="AJ72" s="63"/>
     </row>
-    <row r="73" spans="1:36" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79" t="s">
         <v>389</v>
       </c>
@@ -10085,22 +10115,22 @@
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
+        <v>759</v>
+      </c>
+      <c r="E73" s="37" t="s">
         <v>760</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="F73" s="80" t="s">
         <v>761</v>
       </c>
-      <c r="F73" s="80" t="s">
+      <c r="G73" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="G73" s="37" t="s">
+      <c r="H73" s="37" t="s">
+        <v>762</v>
+      </c>
+      <c r="O73" s="37" t="s">
         <v>763</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>763</v>
-      </c>
-      <c r="O73" s="37" t="s">
-        <v>764</v>
       </c>
       <c r="P73" s="28">
         <v>6</v>
@@ -10118,16 +10148,16 @@
         <v>44</v>
       </c>
       <c r="W73" s="37" t="s">
+        <v>764</v>
+      </c>
+      <c r="AE73" s="37" t="s">
         <v>765</v>
       </c>
-      <c r="AE73" s="37" t="s">
+      <c r="AF73" s="37" t="s">
         <v>766</v>
       </c>
-      <c r="AF73" s="37" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="74" spans="1:36" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:36" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>389</v>
       </c>
@@ -10135,18 +10165,18 @@
         <v>2026</v>
       </c>
       <c r="D74" t="s">
+        <v>767</v>
+      </c>
+      <c r="E74" t="s">
         <v>768</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" s="92" t="s">
         <v>769</v>
-      </c>
-      <c r="F74" s="92" t="s">
-        <v>770</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
       <c r="O74" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P74">
         <v>6</v>
@@ -10161,16 +10191,16 @@
         <v>44</v>
       </c>
       <c r="W74" t="s">
+        <v>771</v>
+      </c>
+      <c r="Z74" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="AE74" t="s">
         <v>772</v>
       </c>
-      <c r="Z74" s="37" t="s">
-        <v>777</v>
-      </c>
-      <c r="AE74" t="s">
+      <c r="AF74" t="s">
         <v>773</v>
-      </c>
-      <c r="AF74" t="s">
-        <v>774</v>
       </c>
       <c r="AI74"/>
       <c r="AJ74"/>
@@ -12807,13 +12837,7 @@
       <c r="B951" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ74" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="Q1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AJ74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Preprint">
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="11_386E33471CAE4E6257066C3559E546796DFEEC98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31909DD6-97EB-C049-82C1-FF0EA6A9143C}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="11_386E33471CAE4E6257066C3559E546796DFEEC98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB071CB1-37F8-2548-83D8-E90BD646F1F0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="839">
   <si>
     <t>Tipo</t>
   </si>
@@ -3137,6 +3137,29 @@
   </si>
   <si>
     <t>E. Barra, S. López-Pernas, J. Conde, A. Gordillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2608.02618</t>
+  </si>
+  <si>
+    <t>T. Fu, J. Conde, C. Arriaga, G. Martínez, P. Reviriego, J. Coronado-Blázquez</t>
+  </si>
+  <si>
+    <t>no enviado a ningún sitio</t>
+  </si>
+  <si>
+    <t>@misc{fu2026hivemindescapingllmhomogeneity,
+      title={Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling}, 
+      author={Tairan Fu and Javier Conde and Carlos Arriaga and Gonzalo Martínez and Pedro Reviriego and Javier Coronado-Blázquez},
+      year={2026},
+      eprint={2608.02618},
+      archivePrefix={arXiv},
+      primaryClass={cs.AI},
+      url={https://arxiv.org/abs/2608.02618}, 
+}</t>
   </si>
 </sst>
 </file>
@@ -3688,16 +3711,6 @@
   <dxfs count="10">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3743,6 +3756,16 @@
       <fill>
         <patternFill>
           <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11004,8 +11027,49 @@
         <v>670</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="B77" s="37"/>
+    <row r="77" spans="1:42" ht="221" x14ac:dyDescent="0.2">
+      <c r="A77" s="79" t="s">
+        <v>402</v>
+      </c>
+      <c r="B77" s="37">
+        <v>2026</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>834</v>
+      </c>
+      <c r="F77" s="92" t="s">
+        <v>835</v>
+      </c>
+      <c r="G77" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="H77" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="O77" s="37" t="s">
+        <v>836</v>
+      </c>
+      <c r="P77" s="28">
+        <v>6</v>
+      </c>
+      <c r="Q77" s="28">
+        <v>2</v>
+      </c>
+      <c r="R77" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE77" s="37" t="s">
+        <v>814</v>
+      </c>
+      <c r="AK77" s="95" t="s">
+        <v>838</v>
+      </c>
+      <c r="AM77" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="AN77" s="37" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="78" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B78" s="37"/>
@@ -13634,44 +13698,44 @@
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC34:AF59 AD60:AF60 A1:B1048576 AA1:AA1048576 AC61:AF1048576 E1:J1048576 M1:R1048576">
-    <cfRule type="expression" dxfId="0" priority="8">
+  <conditionalFormatting sqref="A1:B1048576 M1:R1048576 AA1:AA1048576 AC34:AF59 AD60:AF60 E1:J1048576 AC61:AF1048576">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AB1048576">
-    <cfRule type="containsBlanks" dxfId="8" priority="7">
+    <cfRule type="containsBlanks" dxfId="7" priority="7">
       <formula>LEN(TRIM(AB1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD2 AD3 AC4:AD32">
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>LEN(TRIM(AC1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE1:AF33 AC33">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>LEN(TRIM(AC1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM1048576">
-    <cfRule type="containsText" dxfId="5" priority="16" operator="containsText" text="Status_internal">
+    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Status_internal">
       <formula>NOT(ISERROR(SEARCH("Status_internal",AM2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="17" operator="notEqual">
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="notEqual">
       <formula>"published"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM1:AO1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>LEN(TRIM(AM1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP1:AP1048576 AN2:AO1048576">
-    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
       <formula>LEN(TRIM(AN1))=0</formula>
     </cfRule>
-    <cfRule type="notContainsText" dxfId="1" priority="5" operator="notContains" text="TODO">
+    <cfRule type="notContainsText" dxfId="0" priority="5" operator="notContains" text="TODO">
       <formula>ISERROR(SEARCH("TODO",AN1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13770,6 +13834,7 @@
     <hyperlink ref="F60" r:id="rId92" xr:uid="{122B9BB9-F65A-1B41-A77D-2195CBA21762}"/>
     <hyperlink ref="AC60" r:id="rId93" xr:uid="{D7EB4DC4-3B2A-6946-8EA0-4F4BF86F1DB6}"/>
     <hyperlink ref="AC59" r:id="rId94" xr:uid="{83AAFCC6-FDB5-2C4D-A65C-242E4200B9CE}"/>
+    <hyperlink ref="F77" r:id="rId95" xr:uid="{57B1C321-5715-A842-87D3-B601835EE54B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="11_386E33471CAE4E6257066C3559E546796DFEEC98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB071CB1-37F8-2548-83D8-E90BD646F1F0}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CCB788-4113-FF4B-8FFD-9CF263FD6A76}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="38400" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AP$76</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="846">
   <si>
     <t>Tipo</t>
   </si>
@@ -156,6 +143,9 @@
   </si>
   <si>
     <t>Comment</t>
+  </si>
+  <si>
+    <t>TODO MIO</t>
   </si>
   <si>
     <t>TODO</t>
@@ -1099,6 +1089,356 @@
 }</t>
   </si>
   <si>
+    <t>Open Conversational LLMs do not know most Spanish words</t>
+  </si>
+  <si>
+    <t>hFOr9nPyWt4C</t>
+  </si>
+  <si>
+    <t>http://journal.sepln.org/sepln/ojs/ojs/index.php/pln/article/view/6603</t>
+  </si>
+  <si>
+    <t>Procesamiento del Lenguaje Natural</t>
+  </si>
+  <si>
+    <t>SEPLN</t>
+  </si>
+  <si>
+    <t>Índice de impacto JCR (2024): 1.3 (102/306 – Q2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> “Linguistics” - ESCI</t>
+  </si>
+  <si>
+    <t>J. Conde, M. González, N. Melero, R. Ferrando, G. Martínez, E. Merino-Gómez, J. Hernández, P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2403.15491]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/93786/</t>
+  </si>
+  <si>
+    <t>[https://zenodo.org/doi/10.5281/zenodo.
+10797991          ]</t>
+  </si>
+  <si>
+    <t>The growing interest in Large Language Models (LLMs) and in particular in conversational models with which users can interact has led to the development of a large number of open-source chat LLMs. These models are evaluated on a wide range of benchmarks to assess their capabilities in answering questions or solving problems on almost any possible topic or to test their ability to reason or interpret texts. Instead, the evaluation of the knowledge that these models have of the languages has received much less attention. For example, the words that they can recognize and use in different languages. In this paper, we evaluate the knowledge that open-source chat LLMs have of Spanish words by testing a sample of words in a reference dictionary. The results show that open-source chat LLMs produce incorrect meanings for an important fraction of the words and are not able to use most of the words correctly to write sentences with context. These results show how Spanish is left behind in the open-source LLM race and highlight the need to push for linguistic fairness in conversational LLMs ensuring that they provide similar performance across languages.</t>
+  </si>
+  <si>
+    <t>@misc{Conde2024Open,
+  title = {Open Conversational LLMs do not know most Spanish words},
+  author = {Conde, Javier and González, Miguel and Melero, Nina and Ferrando, Raquel and Martínez, Gonzalo and Merino-Gómez, Elena and Hernández, José Alberto and Reviriego, Pedro},
+  year = {2024},
+  eprint = {2403.15491},
+  archivePrefix = {arXiv},
+  note = {arXiv:2403.15491},
+}</t>
+  </si>
+  <si>
+    <t>Designing Metadata for the Use of Artificial Intelligence in Academia</t>
+  </si>
+  <si>
+    <t>7PzlFSSx8tAC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3605098.3636201</t>
+  </si>
+  <si>
+    <t>The 39th ACM/SIGAPP Symposium On Applied Computing</t>
+  </si>
+  <si>
+    <t>ACM</t>
+  </si>
+  <si>
+    <t>Ávila, Spain</t>
+  </si>
+  <si>
+    <t>J. Conde, G. Martínez, P. Reviriego, J. Salvachúa, J. Hernández</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.1145/3605098.3636201]</t>
+  </si>
+  <si>
+    <t>[https://oa.upm.es/83196]</t>
+  </si>
+  <si>
+    <t>Academic writing is one of the most important tasks in Academia. The pressure to "publish or perish" drives researchers to use all the tools available to try to improve their papers and their impact. Generative artificial intelligence (AI) that can create content such as text, tables, and images can be used for many tasks in academic writing such as summarizing, translating, paraphrasing, data analysis, and presentation. Therefore, AI is expected to be widely used in academic writing in the near future and have a significant impact. Understanding this impact is far from trivial and needs to be carefully studied. The first step in doing so is to be able to identify papers written with the help of AI tools. This can be done by adding metadata on the use of AI in academic results. In this paper, we embark on an initial endeavor to devise such metadata and delineate the potential advantages that the inclusion of AI-related metadata in academic publications may bring forth.</t>
+  </si>
+  <si>
+    <t>@inproceedings{Conde2024Designing,
+  title = {Designing Metadata for the Use of Artificial Intelligence in Academia},
+  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro and Salvachúa, Joaquín and Hernández, José Alberto},
+  booktitle = {Proceedings of the 39th ACM/SIGAPP Symposium on Applied Computing},
+  year = {2024},
+  publisher = {ACM},
+  doi = {10.1145/3605098.3636201},
+}</t>
+  </si>
+  <si>
+    <t>The Temporal Dynamics of Procrastination and Its Impact on Academic Performance: The Case of a Task-Oriented Programming Course</t>
+  </si>
+  <si>
+    <t>QIV2ME_5wuYC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3605098.3636072</t>
+  </si>
+  <si>
+    <t>CORE Multiconference</t>
+  </si>
+  <si>
+    <t>J. Conde, S. López-Pernas, E. Barra, M. Saqr</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.1145/3605098.3636072]</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/83197/</t>
+  </si>
+  <si>
+    <t>[FUN4DATE, Programa Propio UPM]</t>
+  </si>
+  <si>
+    <t>Procrastination is one of the most common problems among students causing mental health issues, low motivation, and poor academic performance. The emergence of Learning Management Systems has made it possible to accurately pinpoint when procrastination takes place due to the unobtrusive collection of fine-grained data from students. However, most studies that analyze procrastination regard it as an intrinsic characteristic of students. In this work, we study procrastination as a process that unfolds with time. We use sequence analysis to map the evolution of students' procrastination behavior over a task-oriented programming course. Our findings evince that students' procrastination is not constant throughout a course and that students who tend to procrastinate are those who achieve worse academic performance.</t>
+  </si>
+  <si>
+    <t>@inproceedings{Conde2024The,
+  title = {The Temporal Dynamics of Procrastination and its Impact on Academic Performance: The Case of a Task-oriented Programming Course},
+  author = {Conde, Javier and López-Pernas, Sonsoles and Barra, Enrique and Saqr, Mohammed},
+  booktitle = {Proceedings of the 39th ACM/SIGAPP Symposium on Applied Computing},
+  year = {2024},
+  publisher = {ACM},
+  doi = {10.1145/3605098.3636072},
+}</t>
+  </si>
+  <si>
+    <t>Round Trip Times (RTTs): Comparing Terrestrial and LEO Satellite Networks</t>
+  </si>
+  <si>
+    <t>9ZlFYXVOiuMC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICIN60470.2024.10494421</t>
+  </si>
+  <si>
+    <t>27th Conference on Innovation in Clouds, Internet and Networks (ICIN)</t>
+  </si>
+  <si>
+    <t>Paris, France</t>
+  </si>
+  <si>
+    <t>J. Conde, G. Martínez, P. Reviriego, J. Hernández</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/83194</t>
+  </si>
+  <si>
+    <t>One of the potential advantages of Low Earth Orbiting (LEO) satellite constellation networks is the reduction in delay, which is critical for some services and applications. Theoretically, LEO satellite networks have a lower propagation delay when the endpoints are at distances longer than a few thousand km due to the higher propagation speed of radio transmission compared to fiber. However, the theoretical analysis makes assumptions about transmission paths that are not valid in all cases and does not account for other factors that influence delay, such as processing or queuing delays. Therefore, experimental studies are needed based on measurements and simulations. This paper presents the first comparison between real Round Trip Time (RTT) measurements on terrestrial networks and simulated RTTs on different LEO constellations. The results confirm the potential benefits of LEO constellations not only in reducing RTT values, but also in reducing their dispersion versus distance.</t>
+  </si>
+  <si>
+    <t>@inproceedings{Conde2024Round,
+  title = {Round Trip Times (RTTs): Comparing Terrestrial and LEO Satellite Networks},
+  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro and Hernández, José Alberto},
+  booktitle = {2024 27th Conference on Innovation in Clouds, Internet and Networks (ICIN)},
+  year = {2024},
+  publisher = {IEEE},
+  doi = {10.1109/icin60470.2024.10494421},
+}</t>
+  </si>
+  <si>
+    <t>Evaluación del conocimiento léxico de ChatGPT con ChatWords</t>
+  </si>
+  <si>
+    <t>LkGwnXOMwfcC</t>
+  </si>
+  <si>
+    <t>https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf</t>
+  </si>
+  <si>
+    <t>SEL 2024</t>
+  </si>
+  <si>
+    <t>SEL (Sociedad Española de Lingüística)</t>
+  </si>
+  <si>
+    <t>Madrid, Spain</t>
+  </si>
+  <si>
+    <t>G. Martínez, J. Conde, P. Reviriego, E. Merino, J. Hernández</t>
+  </si>
+  <si>
+    <t>[https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf]</t>
+  </si>
+  <si>
+    <t>[https://www.upm.es/?id=CON03210&amp;prefmt=articulo&amp;fmt=detail]</t>
+  </si>
+  <si>
+    <t>Comunicación en SEL 2024 sobre la evaluación del conocimiento léxico de ChatGPT con ChatWords, herramienta para valorar la competencia léxica de LLMs en español.</t>
+  </si>
+  <si>
+    <t>@misc{Conde2024ChatWords,
+  title = {Evaluación del conocimiento léxico de ChatGPT con ChatWords},
+  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro},
+  year = {2024},
+  publisher = {SEL 2024},
+  url = {https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf},
+}</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Data Fusion and Homogenization: Two key aspects for building Digital Twins of Smart Spaces. In: Smart Spaces</t>
+  </si>
+  <si>
+    <t>mVmsd5A6BfQC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/B978-0-443-13462-3.00002-9</t>
+  </si>
+  <si>
+    <t>A. Muñoz-Arcentales, J. Conde, Á. Alonso, J. Salvachúa, W. Velasquez, S. López-Pernas</t>
+  </si>
+  <si>
+    <t>Book chapter examining data fusion and homogenization as key aspects for building digital twins of smart spaces using FIWARE as enabling technology for integrating heterogeneous data sources.</t>
+  </si>
+  <si>
+    <t>@incollection{MunozArcentales2024Data,
+  title = {Data fusion and homogenization},
+  author = {Munoz-Arcentales, Andres and Conde, Javier and Alonso, Álvaro and Salvachúa, Joaquín and Velasquez, Washington and López-Pernas, Sonsoles},
+  booktitle = {Smart Spaces},
+  year = {2024},
+  publisher = {Elsevier},
+  doi = {10.1016/b978-0-443-13462-3.00002-9},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Broad Collection of Datasets for Educational Research Training and Application. In: Learning analytics methods and tutorial: A practical guide using R </t>
+  </si>
+  <si>
+    <t>L8Ckcad2t8MC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/978-3-031-54464-4_2</t>
+  </si>
+  <si>
+    <t>Springer</t>
+  </si>
+  <si>
+    <t>S. López-Pernas, M. Saqr, J. Conde, L. Del-Río-Carazo</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.1007/978-3-031-54464-4_2]</t>
+  </si>
+  <si>
+    <t>AbstractIn this chapter, we present the main types of data that are used in learning analytics research. Learning analytics has grown to encompass the digital trails left by online learning technologies—clicks, events, and interactions—, sensor data and self-reports among others. We present a collection of curated real-life open datasets that represent the most common types of educational data. The datasets have been collected from diverse sources such as learning management systems, online forums, and surveys. These datasets are used throughout the book to illustrate methods of analysis such as sequence analysis, social network analysis, Markov models, predictive analytics and structure equation modeling, to mention a few. Each data set in the chapter is presented with its context, main properties, links to the original source, as well as a brief exploratory data analysis.</t>
+  </si>
+  <si>
+    <t>@incollection{LpezPernas2024A,
+  title = {A Broad Collection of Datasets for Educational Research Training and Application},
+  author = {López-Pernas, Sonsoles and Saqr, Mohammed and Conde, Javier and Del-Río-Carazo, Laura},
+  booktitle = {Learning Analytics Methods and Tutorials},
+  year = {2024},
+  publisher = {Springer Nature Switzerland},
+  doi = {10.1007/978-3-031-54464-4_2},
+}</t>
+  </si>
+  <si>
+    <t>Integración de la Inteligencia Artificial en la Educación Superior: Potencial, Desafíos y Oportunidades</t>
+  </si>
+  <si>
+    <t>JV2RwH3_ST0C</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/83317/</t>
+  </si>
+  <si>
+    <t>Monografía Innovación Educativa UPM</t>
+  </si>
+  <si>
+    <t>E. Barra, J. Quemada, D. López, J. Conde, C. Badenes, A. Gordillo</t>
+  </si>
+  <si>
+    <t>Informe sobre el potencial e impacto de la IA en la educación superior, ofreciendo visión integral sobre cómo la IA está transformando la docencia universitaria, con análisis de oportunidades, desafíos y recomendaciones.</t>
+  </si>
+  <si>
+    <t>@misc{Barra2024IntegracionIA,
+  title = {Integración de la Inteligencia Artificial en la Educación Superior: Potencial, Desafíos y Oportunidades},
+  author = {Barra, Enrique and Conde, Javier and others},
+  year = {2024},
+  publisher = {Universidad Politécnica de Madrid},
+  url = {https://oa.upm.es/83317/},
+}</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Integrating Artificial Intelligence in Higher Education: Potential, Challenges and Opportunities</t>
+  </si>
+  <si>
+    <t>blknAaTinKkC</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/85213/</t>
+  </si>
+  <si>
+    <t>UPM Innovación Educativa</t>
+  </si>
+  <si>
+    <t>E. Barra Arias, J. Quemada Vives, D. López Fernández, J. Conde Díaz</t>
+  </si>
+  <si>
+    <t>Report on the impact and potential of Artificial Intelligence in Higher Education (English version). Provides a comprehensive overview of how AI is impacting higher education, with opportunities, challenges, and recommendations.</t>
+  </si>
+  <si>
+    <t>@misc{Barra2024IntegratingAI,
+  title = {Integrating Artificial Intelligence in Higher Education: Potential, Challenges and Opportunities},
+  author = {Barra, Enrique and Conde, Javier and others},
+  year = {2024},
+  publisher = {Universidad Politécnica de Madrid},
+  url = {https://oa.upm.es/85213/},
+}</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
+  </si>
+  <si>
+    <t>qxL8FJ1GzNcC</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2402.06693</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>J. Conde, A. Pozo, A. Munoz-Arcentales, J. Choque, Á. Alonso</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2402.06693]</t>
+  </si>
+  <si>
+    <t>[Eunomia, YODA]</t>
+  </si>
+  <si>
+    <t>The term Data Space, understood as the secure exchange of data in distributed systems, ensuring openness, transparency, decentralization, sovereignty, and interoperability of information, has gained importance during the last years. However, Data Spaces are in an initial phase of definition, and new research is necessary to address their requirements. The Open Data ecosystem can be understood as one of the precursors of Data Spaces as it provides mechanisms to ensure the interoperability of information through resource discovery, information exchange, and aggregation via metadata. However, Data Spaces require more advanced capabilities including the automatic and scalable generation and publication of high-quality metadata. In this work, we present a set of software tools that facilitate the automatic generation and publication of metadata, the modeling of datasets through standards, and the assessment of the quality of the generated metadata. We validate all these tools through the YODA Open Data Portal showing how they can be connected to integrate Open Data into Data Spaces.</t>
+  </si>
+  <si>
+    <t>@misc{Conde2024Fostering,
+  title = {Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata},
+  author = {Conde, Javier and Munoz-Arcentales, Andres and others},
+  year = {2024},
+  eprint = {2402.06693},
+  archivePrefix = {arXiv},
+  note = {arXiv:2402.06693},
+}</t>
+  </si>
+  <si>
     <t>AI-generated estimates of familiarity, concreteness, valence, and arousal for over 100,000 Spanish words</t>
   </si>
   <si>
@@ -1149,409 +1489,19 @@
 }</t>
   </si>
   <si>
-    <t>Open Conversational LLMs do not know most Spanish words</t>
-  </si>
-  <si>
-    <t>hFOr9nPyWt4C</t>
-  </si>
-  <si>
-    <t>http://journal.sepln.org/sepln/ojs/ojs/index.php/pln/article/view/6603</t>
-  </si>
-  <si>
-    <t>Procesamiento del Lenguaje Natural</t>
-  </si>
-  <si>
-    <t>SEPLN</t>
-  </si>
-  <si>
-    <t>Índice de impacto JCR (2024): 1.3 (102/306 – Q2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> “Linguistics” - ESCI</t>
-  </si>
-  <si>
-    <t>J. Conde, M. González, N. Melero, R. Ferrando, G. Martínez, E. Merino-Gómez, J. Hernández, P. Reviriego</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2403.15491]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/93786/</t>
-  </si>
-  <si>
-    <t>[https://zenodo.org/doi/10.5281/zenodo.
-10797991          ]</t>
-  </si>
-  <si>
-    <t>The growing interest in Large Language Models (LLMs) and in particular in conversational models with which users can interact has led to the development of a large number of open-source chat LLMs. These models are evaluated on a wide range of benchmarks to assess their capabilities in answering questions or solving problems on almost any possible topic or to test their ability to reason or interpret texts. Instead, the evaluation of the knowledge that these models have of the languages has received much less attention. For example, the words that they can recognize and use in different languages. In this paper, we evaluate the knowledge that open-source chat LLMs have of Spanish words by testing a sample of words in a reference dictionary. The results show that open-source chat LLMs produce incorrect meanings for an important fraction of the words and are not able to use most of the words correctly to write sentences with context. These results show how Spanish is left behind in the open-source LLM race and highlight the need to push for linguistic fairness in conversational LLMs ensuring that they provide similar performance across languages.</t>
-  </si>
-  <si>
-    <t>@misc{Conde2024Open,
-  title = {Open Conversational LLMs do not know most Spanish words},
-  author = {Conde, Javier and González, Miguel and Melero, Nina and Ferrando, Raquel and Martínez, Gonzalo and Merino-Gómez, Elena and Hernández, José Alberto and Reviriego, Pedro},
-  year = {2024},
-  eprint = {2403.15491},
-  archivePrefix = {arXiv},
-  note = {arXiv:2403.15491},
-}</t>
-  </si>
-  <si>
-    <t>Designing Metadata for the Use of Artificial Intelligence in Academia</t>
-  </si>
-  <si>
-    <t>7PzlFSSx8tAC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3605098.3636201</t>
-  </si>
-  <si>
-    <t>The 39th ACM/SIGAPP Symposium On Applied Computing</t>
-  </si>
-  <si>
-    <t>ACM</t>
-  </si>
-  <si>
-    <t>Ávila, Spain</t>
-  </si>
-  <si>
-    <t>J. Conde, G. Martínez, P. Reviriego, J. Salvachúa, J. Hernández</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.1145/3605098.3636201]</t>
-  </si>
-  <si>
-    <t>[https://oa.upm.es/83196]</t>
-  </si>
-  <si>
-    <t>Academic writing is one of the most important tasks in Academia. The pressure to "publish or perish" drives researchers to use all the tools available to try to improve their papers and their impact. Generative artificial intelligence (AI) that can create content such as text, tables, and images can be used for many tasks in academic writing such as summarizing, translating, paraphrasing, data analysis, and presentation. Therefore, AI is expected to be widely used in academic writing in the near future and have a significant impact. Understanding this impact is far from trivial and needs to be carefully studied. The first step in doing so is to be able to identify papers written with the help of AI tools. This can be done by adding metadata on the use of AI in academic results. In this paper, we embark on an initial endeavor to devise such metadata and delineate the potential advantages that the inclusion of AI-related metadata in academic publications may bring forth.</t>
-  </si>
-  <si>
-    <t>@inproceedings{Conde2024Designing,
-  title = {Designing Metadata for the Use of Artificial Intelligence in Academia},
-  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro and Salvachúa, Joaquín and Hernández, José Alberto},
-  booktitle = {Proceedings of the 39th ACM/SIGAPP Symposium on Applied Computing},
-  year = {2024},
-  publisher = {ACM},
-  doi = {10.1145/3605098.3636201},
-}</t>
-  </si>
-  <si>
-    <t>The Temporal Dynamics of Procrastination and Its Impact on Academic Performance: The Case of a Task-Oriented Programming Course</t>
-  </si>
-  <si>
-    <t>QIV2ME_5wuYC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3605098.3636072</t>
-  </si>
-  <si>
-    <t>CORE Multiconference</t>
-  </si>
-  <si>
-    <t>J. Conde, S. López-Pernas, E. Barra, M. Saqr</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.1145/3605098.3636072]</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83197/</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, Programa Propio UPM]</t>
-  </si>
-  <si>
-    <t>Procrastination is one of the most common problems among students causing mental health issues, low motivation, and poor academic performance. The emergence of Learning Management Systems has made it possible to accurately pinpoint when procrastination takes place due to the unobtrusive collection of fine-grained data from students. However, most studies that analyze procrastination regard it as an intrinsic characteristic of students. In this work, we study procrastination as a process that unfolds with time. We use sequence analysis to map the evolution of students' procrastination behavior over a task-oriented programming course. Our findings evince that students' procrastination is not constant throughout a course and that students who tend to procrastinate are those who achieve worse academic performance.</t>
-  </si>
-  <si>
-    <t>@inproceedings{Conde2024The,
-  title = {The Temporal Dynamics of Procrastination and its Impact on Academic Performance: The Case of a Task-oriented Programming Course},
-  author = {Conde, Javier and López-Pernas, Sonsoles and Barra, Enrique and Saqr, Mohammed},
-  booktitle = {Proceedings of the 39th ACM/SIGAPP Symposium on Applied Computing},
-  year = {2024},
-  publisher = {ACM},
-  doi = {10.1145/3605098.3636072},
-}</t>
-  </si>
-  <si>
-    <t>Round Trip Times (RTTs): Comparing Terrestrial and LEO Satellite Networks</t>
-  </si>
-  <si>
-    <t>9ZlFYXVOiuMC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1109/ICIN60470.2024.10494421</t>
-  </si>
-  <si>
-    <t>27th Conference on Innovation in Clouds, Internet and Networks (ICIN)</t>
-  </si>
-  <si>
-    <t>Paris, France</t>
-  </si>
-  <si>
-    <t>J. Conde, G. Martínez, P. Reviriego, J. Hernández</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83194</t>
-  </si>
-  <si>
-    <t>One of the potential advantages of Low Earth Orbiting (LEO) satellite constellation networks is the reduction in delay, which is critical for some services and applications. Theoretically, LEO satellite networks have a lower propagation delay when the endpoints are at distances longer than a few thousand km due to the higher propagation speed of radio transmission compared to fiber. However, the theoretical analysis makes assumptions about transmission paths that are not valid in all cases and does not account for other factors that influence delay, such as processing or queuing delays. Therefore, experimental studies are needed based on measurements and simulations. This paper presents the first comparison between real Round Trip Time (RTT) measurements on terrestrial networks and simulated RTTs on different LEO constellations. The results confirm the potential benefits of LEO constellations not only in reducing RTT values, but also in reducing their dispersion versus distance.</t>
-  </si>
-  <si>
-    <t>@inproceedings{Conde2024Round,
-  title = {Round Trip Times (RTTs): Comparing Terrestrial and LEO Satellite Networks},
-  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro and Hernández, José Alberto},
-  booktitle = {2024 27th Conference on Innovation in Clouds, Internet and Networks (ICIN)},
-  year = {2024},
-  publisher = {IEEE},
-  doi = {10.1109/icin60470.2024.10494421},
-}</t>
-  </si>
-  <si>
-    <t>Evaluación del conocimiento léxico de ChatGPT con ChatWords</t>
-  </si>
-  <si>
-    <t>LkGwnXOMwfcC</t>
-  </si>
-  <si>
-    <t>https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf</t>
-  </si>
-  <si>
-    <t>SEL 2024</t>
-  </si>
-  <si>
-    <t>SEL (Sociedad Española de Lingüística)</t>
-  </si>
-  <si>
-    <t>Madrid, Spain</t>
-  </si>
-  <si>
-    <t>G. Martínez, J. Conde, P. Reviriego, E. Merino, J. Hernández</t>
-  </si>
-  <si>
-    <t>[https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf]</t>
-  </si>
-  <si>
-    <t>[https://www.upm.es/?id=CON03210&amp;prefmt=articulo&amp;fmt=detail]</t>
-  </si>
-  <si>
-    <t>Comunicación en SEL 2024 sobre la evaluación del conocimiento léxico de ChatGPT con ChatWords, herramienta para valorar la competencia léxica de LLMs en español.</t>
-  </si>
-  <si>
-    <t>@misc{Conde2024ChatWords,
-  title = {Evaluación del conocimiento léxico de ChatGPT con ChatWords},
-  author = {Conde, Javier and Martínez, Gonzalo and Reviriego, Pedro},
-  year = {2024},
-  publisher = {SEL 2024},
-  url = {https://www.sel.edu.es/wp-content/uploads/go-x/u/a08bbe82-2b51-4e97-ad0c-8ac7f0addc4a/Book-de-resumenes-2024-FINAL.pdf},
-}</t>
-  </si>
-  <si>
-    <t>Book</t>
-  </si>
-  <si>
-    <t>Data Fusion and Homogenization: Two key aspects for building Digital Twins of Smart Spaces. In: Smart Spaces</t>
-  </si>
-  <si>
-    <t>mVmsd5A6BfQC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/B978-0-443-13462-3.00002-9</t>
-  </si>
-  <si>
-    <t>A. Muñoz-Arcentales, J. Conde, Á. Alonso, J. Salvachúa, W. Velasquez, S. López-Pernas</t>
-  </si>
-  <si>
-    <t>Book chapter examining data fusion and homogenization as key aspects for building digital twins of smart spaces using FIWARE as enabling technology for integrating heterogeneous data sources.</t>
-  </si>
-  <si>
-    <t>@incollection{MunozArcentales2024Data,
-  title = {Data fusion and homogenization},
-  author = {Munoz-Arcentales, Andres and Conde, Javier and Alonso, Álvaro and Salvachúa, Joaquín and Velasquez, Washington and López-Pernas, Sonsoles},
-  booktitle = {Smart Spaces},
-  year = {2024},
-  publisher = {Elsevier},
-  doi = {10.1016/b978-0-443-13462-3.00002-9},
-}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Broad Collection of Datasets for Educational Research Training and Application. In: Learning analytics methods and tutorial: A practical guide using R </t>
-  </si>
-  <si>
-    <t>L8Ckcad2t8MC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/978-3-031-54464-4_2</t>
-  </si>
-  <si>
-    <t>Springer</t>
-  </si>
-  <si>
-    <t>S. López-Pernas, M. Saqr, J. Conde, L. Del-Río-Carazo</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.1007/978-3-031-54464-4_2]</t>
-  </si>
-  <si>
-    <t>AbstractIn this chapter, we present the main types of data that are used in learning analytics research. Learning analytics has grown to encompass the digital trails left by online learning technologies—clicks, events, and interactions—, sensor data and self-reports among others. We present a collection of curated real-life open datasets that represent the most common types of educational data. The datasets have been collected from diverse sources such as learning management systems, online forums, and surveys. These datasets are used throughout the book to illustrate methods of analysis such as sequence analysis, social network analysis, Markov models, predictive analytics and structure equation modeling, to mention a few. Each data set in the chapter is presented with its context, main properties, links to the original source, as well as a brief exploratory data analysis.</t>
-  </si>
-  <si>
-    <t>@incollection{LpezPernas2024A,
-  title = {A Broad Collection of Datasets for Educational Research Training and Application},
-  author = {López-Pernas, Sonsoles and Saqr, Mohammed and Conde, Javier and Del-Río-Carazo, Laura},
-  booktitle = {Learning Analytics Methods and Tutorials},
-  year = {2024},
-  publisher = {Springer Nature Switzerland},
-  doi = {10.1007/978-3-031-54464-4_2},
-}</t>
-  </si>
-  <si>
-    <t>Integración de la Inteligencia Artificial en la Educación Superior: Potencial, Desafíos y Oportunidades</t>
-  </si>
-  <si>
-    <t>JV2RwH3_ST0C</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/83317/</t>
-  </si>
-  <si>
-    <t>Monografía Innovación Educativa UPM</t>
-  </si>
-  <si>
-    <t>E. Barra, J. Quemada, D. López, J. Conde, C. Badenes, A. Gordillo</t>
-  </si>
-  <si>
-    <t>Informe sobre el potencial e impacto de la IA en la educación superior, ofreciendo visión integral sobre cómo la IA está transformando la docencia universitaria, con análisis de oportunidades, desafíos y recomendaciones.</t>
-  </si>
-  <si>
-    <t>@misc{Barra2024IntegracionIA,
-  title = {Integración de la Inteligencia Artificial en la Educación Superior: Potencial, Desafíos y Oportunidades},
-  author = {Barra, Enrique and Conde, Javier and others},
-  year = {2024},
-  publisher = {Universidad Politécnica de Madrid},
-  url = {https://oa.upm.es/83317/},
-}</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Integrating Artificial Intelligence in Higher Education: Potential, Challenges and Opportunities</t>
-  </si>
-  <si>
-    <t>blknAaTinKkC</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/85213/</t>
-  </si>
-  <si>
-    <t>UPM Innovación Educativa</t>
-  </si>
-  <si>
-    <t>E. Barra Arias, J. Quemada Vives, D. López Fernández, J. Conde Díaz</t>
-  </si>
-  <si>
-    <t>Report on the impact and potential of Artificial Intelligence in Higher Education (English version). Provides a comprehensive overview of how AI is impacting higher education, with opportunities, challenges, and recommendations.</t>
-  </si>
-  <si>
-    <t>@misc{Barra2024IntegratingAI,
-  title = {Integrating Artificial Intelligence in Higher Education: Potential, Challenges and Opportunities},
-  author = {Barra, Enrique and Conde, Javier and others},
-  year = {2024},
-  publisher = {Universidad Politécnica de Madrid},
-  url = {https://oa.upm.es/85213/},
-}</t>
-  </si>
-  <si>
-    <t>When Do Large Language Models (LLMs) Struggle to Count Letters?</t>
-  </si>
-  <si>
-    <t>j3f4tGmQtD8C</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3818606</t>
+    <t>Beware of Words: Evaluating the Lexical Diversity of Conversational LLMs using ChatGPT as Case Study</t>
+  </si>
+  <si>
+    <t>HDshCWvjkbEC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3696459</t>
   </si>
   <si>
     <t>ACM Transactions on Intelligent Systems and Technology</t>
   </si>
   <si>
     <t>Índice de impacto JCR (2025): 10.7 (9/266 – Q1 [D1])</t>
-  </si>
-  <si>
-    <t>T. Fu, R. Ferrando, J. Conde, C. Arriaga, P. Reviriego</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2412.18626]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	https://oa.upm.es/96506/</t>
-  </si>
-  <si>
-    <t>[https://doi.org/10.5281/zenodo.20112756]</t>
-  </si>
-  <si>
-    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
-  </si>
-  <si>
-    <t>[https://www.linkedin.com/posts/javier-conde-diaz_upm-polimi-airesearch-share-7464786001824120832-5kPN/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
-  </si>
-  <si>
-    <t>Large Language Models (LLMs) have achieved unprecedented performance on many complex tasks, being able, for example, to answer questions on almost any topic. However, they struggle with other simple tasks, such as counting the occurrences of letters in a word, as illustrated by the inability of many LLMs to count the number of &amp;#34;r&amp;#34; letters in &amp;#34;strawberry&amp;#34;. Several works have studied this problem and linked it to the tokenization used by LLMs, to the intrinsic limitations of the attention mechanism, or to the lack of character-level training data. In this paper, we conduct an experimental study to evaluate the relations between the LLM errors when counting letters with 1) the frequency of the word and its components in the training dataset and 2) the complexity of the counting operation. We present a comprehensive analysis of the errors of LLMs when counting letter occurrences by evaluating a representative group of models over a large number of words. The results show a number of consistent trends in the models evaluated: 1) models are capable of recognizing the letters but not counting them; 2) the frequency of the word and tokens in the word does not have a significant impact on the LLM errors; 3) there is a positive correlation of letter frequency with errors, more frequent letters tend to have more counting errors, 4) the errors show a strong correlation with the number of letters or tokens in a word and 5) the strongest correlation occurs with the number of letters with counts larger than one, with most models being unable to correctly count words in which letters appear more than twice.</t>
-  </si>
-  <si>
-    <t>@article{fu2024when,
-  title={When Do Large Language Models (LLMs) Struggle to Count Letters?},
-  author={Fu, Tairan and Ferrando, Raquel and Conde, Javier and Arriaga, Carlos and Reviriego, Pedro},
-  journal={ACM Transactions on Intelligent Systems and Technology},
-  year={2024},
-  publisher={ACM},
-  doi={10.1145/3818606}
-}</t>
-  </si>
-  <si>
-    <t>Preprint</t>
-  </si>
-  <si>
-    <t>Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata</t>
-  </si>
-  <si>
-    <t>qxL8FJ1GzNcC</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2402.06693</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>J. Conde, A. Pozo, A. Munoz-Arcentales, J. Choque, Á. Alonso</t>
-  </si>
-  <si>
-    <t>[https://arxiv.org/abs/2402.06693]</t>
-  </si>
-  <si>
-    <t>[Eunomia, YODA]</t>
-  </si>
-  <si>
-    <t>The term Data Space, understood as the secure exchange of data in distributed systems, ensuring openness, transparency, decentralization, sovereignty, and interoperability of information, has gained importance during the last years. However, Data Spaces are in an initial phase of definition, and new research is necessary to address their requirements. The Open Data ecosystem can be understood as one of the precursors of Data Spaces as it provides mechanisms to ensure the interoperability of information through resource discovery, information exchange, and aggregation via metadata. However, Data Spaces require more advanced capabilities including the automatic and scalable generation and publication of high-quality metadata. In this work, we present a set of software tools that facilitate the automatic generation and publication of metadata, the modeling of datasets through standards, and the assessment of the quality of the generated metadata. We validate all these tools through the YODA Open Data Portal showing how they can be connected to integrate Open Data into Data Spaces.</t>
-  </si>
-  <si>
-    <t>@misc{Conde2024Fostering,
-  title = {Fostering the integration of European Open Data into Data Spaces through High-Quality Metadata},
-  author = {Conde, Javier and Munoz-Arcentales, Andres and others},
-  year = {2024},
-  eprint = {2402.06693},
-  archivePrefix = {arXiv},
-  note = {arXiv:2402.06693},
-}</t>
-  </si>
-  <si>
-    <t>Beware of Words: Evaluating the Lexical Diversity of Conversational LLMs using ChatGPT as Case Study</t>
-  </si>
-  <si>
-    <t>HDshCWvjkbEC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3696459</t>
   </si>
   <si>
     <t>G. Martínez, J. Hernández, J. Conde, P. Reviriego, E. Merino-Gomez</t>
@@ -1865,6 +1815,9 @@
     <t>https://oa.upm.es/87994</t>
   </si>
   <si>
+    <t>[FUN4DATE, SMARTY, OpenAI Research Access Program]</t>
+  </si>
+  <si>
     <t>Lo malo que es un paper de columna</t>
   </si>
   <si>
@@ -2141,7 +2094,7 @@
     <t>The Generative Energy Arena (GEA): Incorporating Energy Awareness in Large Language Model Human Evaluations</t>
   </si>
   <si>
-    <t>35N4QoGY0k4C</t>
+    <t>1sJd4Hv_s6UC</t>
   </si>
   <si>
     <t>https://doi.org/10.1109/fllm67465.2025.11391090</t>
@@ -2492,6 +2445,46 @@
     <t xml:space="preserve">sent </t>
   </si>
   <si>
+    <t>When Do Large Language Models (LLMs) Struggle to Count Letters?</t>
+  </si>
+  <si>
+    <t>j3f4tGmQtD8C</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3818606</t>
+  </si>
+  <si>
+    <t>T. Fu, R. Ferrando, J. Conde, C. Arriaga, P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2412.18626]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	https://oa.upm.es/96506/</t>
+  </si>
+  <si>
+    <t>[https://doi.org/10.5281/zenodo.20112756]</t>
+  </si>
+  <si>
+    <t>[https://www.linkedin.com/posts/javier-conde-diaz_upm-polimi-airesearch-share-7464786001824120832-5kPN/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+  </si>
+  <si>
+    <t>Large Language Models (LLMs) have achieved unprecedented performance on many complex tasks, being able, for example, to answer questions on almost any topic. However, they struggle with other simple tasks, such as counting the occurrences of letters in a word, as illustrated by the inability of many LLMs to count the number of &amp;#34;r&amp;#34; letters in &amp;#34;strawberry&amp;#34;. Several works have studied this problem and linked it to the tokenization used by LLMs, to the intrinsic limitations of the attention mechanism, or to the lack of character-level training data. In this paper, we conduct an experimental study to evaluate the relations between the LLM errors when counting letters with 1) the frequency of the word and its components in the training dataset and 2) the complexity of the counting operation. We present a comprehensive analysis of the errors of LLMs when counting letter occurrences by evaluating a representative group of models over a large number of words. The results show a number of consistent trends in the models evaluated: 1) models are capable of recognizing the letters but not counting them; 2) the frequency of the word and tokens in the word does not have a significant impact on the LLM errors; 3) there is a positive correlation of letter frequency with errors, more frequent letters tend to have more counting errors, 4) the errors show a strong correlation with the number of letters or tokens in a word and 5) the strongest correlation occurs with the number of letters with counts larger than one, with most models being unable to correctly count words in which letters appear more than twice.</t>
+  </si>
+  <si>
+    <t>@article{fu2024when,
+  title={When Do Large Language Models (LLMs) Struggle to Count Letters?},
+  author={Fu, Tairan and Ferrando, Raquel and Conde, Javier and Arriaga, Carlos and Reviriego, Pedro},
+  journal={ACM Transactions on Intelligent Systems and Technology},
+  year={2024},
+  publisher={ACM},
+  doi={10.1145/3818606}
+}</t>
+  </si>
+  <si>
+    <t>Enviar noticia cuando esté publicado en upm</t>
+  </si>
+  <si>
     <t>Real-time spatial retrieval augmented generation for urban environments</t>
   </si>
   <si>
@@ -2507,10 +2500,16 @@
     <t>[https://arxiv.org/abs/2505.02271]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/97418/</t>
+  </si>
+  <si>
     <t>[https://doi.org/10.5281/zenodo.20889036, https://github.com/dncampo/real-time-spatial-rag-for-smart-cities, https://github.com/javicond3/spatial_rag_vector_rag]</t>
   </si>
   <si>
     <t>[FUN4DATE, BRIDGE-AI, TUCAN6-CM]</t>
+  </si>
+  <si>
+    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/]</t>
   </si>
   <si>
     <t>The proliferation of Generative Artificial Ingelligence (AI), especially Large Language Models, presents transformative opportunities for urban applications through Urban Foundation Models. However, base models face limitations, as they only contain the knowledge available at the time of training, and updating them is both time-consuming and costly. Retrieval Augmented Generation (RAG) has emerged in the literature as the preferred approach for injecting contextual information into Foundation Models. It prevails over techniques such as fine-tuning, which are less effective in dynamic, real-time scenarios like those found in urban environments. However, traditional RAG architectures, based on semantic databases, knowledge graphs, structured data, or AI-powered web searches, do not fully meet the demands of urban contexts. Urban environments are complex systems characterized by large volumes of interconnected data, frequent updates, real-time processing requirements, security needs, and strong links to the physical world. This work proposes a real-time spatial RAG architecture that defines the necessary components for the effective integration of generative AI into cities, leveraging temporal and spatial filtering capabilities through linked data. The proposed architecture is implemented using FIWARE, an ecosystem of software components to develop smart city solutions and digital twins. The design and implementation are demonstrated through the use case of a tourism assistant in the city of Madrid. The use case serves to validate the correct integration of Foundation Models through the proposed RAG architecture.</t>
@@ -2526,7 +2525,10 @@
 }</t>
   </si>
   <si>
-    <t>accepted</t>
+    <t>published-early</t>
+  </si>
+  <si>
+    <t>Hacer noticia, actualizar versión arxiv a versión de revista (en teoría ya está)</t>
   </si>
   <si>
     <t>Adding LLMs to the psycholinguistic norming toolbox: A practical guide to getting the most out of human ratings</t>
@@ -2535,22 +2537,50 @@
     <t>g5m5HwL7SMYC</t>
   </si>
   <si>
+    <t>https://doi.org/10.3758/s13428-026-03129-3</t>
+  </si>
+  <si>
     <t>J. Conde, M. Grandury, T. Fu, C. Arriaga, G. Martínez, T. Clark, S. Trott, C. G. Green, P. Reviriego, M. Brysbaert</t>
   </si>
   <si>
     <t>[https://arxiv.org/abs/2509.14405]</t>
   </si>
   <si>
+    <t>https://oa.upm.es/97414/</t>
+  </si>
+  <si>
+    <t>[https://github.com/WordsGPT/psycholinguistics_framework, https://doi.org/10.5281/zenodo.17141353]</t>
+  </si>
+  <si>
     <t>[SMARTY, Programa Propio UPM]</t>
   </si>
   <si>
+    <t>[https://www.linkedin.com/posts/tomorrow-our-colleague-javier-conde-share-7474393536004816896-bkeM, https://www.upm.es/?id=CON23321&amp;prefmt=articulo&amp;fmt=detail, https://efs.efeservicios.com/texto/capaz-descifrar-caracteristicas-lenguaje-parecian-exclusivas-humanos/55018439374, https://www.abc.com.py/ciencia/2025/11/03/la-ia-capaz-de-descifrar-caracteristicas-del-lenguaje-que-parecian-exclusivas-de-humanos/, https://www.lavanguardia.com/tecnologia/20251103/11223637/ia-capaz-descifrar-caracteristicas-lenguaje-parecian-exclusivas-humanos-agenciaslv20251103.html, https://www.linkedin.com/posts/javier-conde-diaz_psicolingaesaedstica-ia-llm-share-7487825960554397697-Er63/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
     <t>Word-level psycholinguistic norms lend empirical support to theories of language processing. However, obtaining such human-based measures is not always feasible or straightforward. One promising approach is to augment human norming datasets by using Large Language Models (LLMs) to predict these characteristics directly, a practice that is rapidly gaining popularity in psycholinguistics and cognitive science. However, the novelty of this approach (and the relative inscrutability of LLMs) necessitates the adoption of rigorous methodologies that guide researchers through this process, present the range of possible approaches, and clarify limitations that are not immediately apparent, but may, in some cases, render the use of LLMs impractical. In this work, we present a comprehensive methodology for estimating word characteristics with LLMs, enriched with practical advice and lessons learned from our own experience. Our approach covers both the direct use of base LLMs and the fine-tuning of models, an alternative that can yield substantial performance gains in certain scenarios. A major emphasis in the guide is the validation of LLM-generated data with human &amp;#34;gold standard&amp;#34; norms. We also present a software framework that implements our methodology and supports both commercial and open-weight models. We illustrate the proposed approach with a case study on estimating word familiarity in English. Using base models, we achieved a Spearman correlation of 0.8 with human ratings, which increased to 0.9 when employing fine-tuned models. This methodology, framework, and set of best practices aim to serve as a reference for future research on leveraging LLMs for psycholinguistic and lexical studies.</t>
   </si>
   <si>
+    <t>@article{conde2026adding,
+  author  = {Conde, J. and Grandury, M. and Fu, T. and others},
+  title   = {Adding {LLMs} to the psycholinguistic norming toolbox: {A} practical guide to getting the most out of human ratings},
+  journal = {Behavior Research Methods},
+  volume  = {58},
+  number  = {253},
+  pages   = {253},
+  year    = {2026},
+  doi     = {10.3758/s13428-026-03129-3},
+  url     = {https://doi.org/10.3758/s13428-026-03129-3}
+}</t>
+  </si>
+  <si>
     <t>Stochastic Streets: A Walk Through Random LLM Address Generation in four European Cities</t>
   </si>
   <si>
-    <t>M05iB0D1s5AC</t>
+    <t>P5F9QuxV20EC</t>
   </si>
   <si>
     <t>https://doi.org/10.1109/mc.2025.3611067</t>
@@ -2869,6 +2899,9 @@
     <t>https://arxiv.org/abs/2603.09981</t>
   </si>
   <si>
+    <t>Leon, Spain</t>
+  </si>
+  <si>
     <t>T. Fu, J. Conde, P. Reviriego, J. Coronado-Blázquez, N. Melero</t>
   </si>
   <si>
@@ -2888,6 +2921,12 @@
 }</t>
   </si>
   <si>
+    <t>accepted</t>
+  </si>
+  <si>
+    <t>Aceptado como póster</t>
+  </si>
+  <si>
     <t>How does fine-tuning improve sensorimotor representations in large language models?</t>
   </si>
   <si>
@@ -3021,6 +3060,11 @@
   </si>
   <si>
     <t>FUN4DATE, TUCAN6-CM, BRIDGE-AI</t>
+  </si>
+  <si>
+    <t>[https://short.upm.es/aewi0,
+https://short.upm.es/hk60w,
+https://short.upm.es/i48zs, https://samermakes.com/blog/WCS/]</t>
   </si>
   <si>
     <t>Modern Large Language Models (LLMs) are often criticized for producing repetitive and homogeneous text, despite possessing vast latent vocabularies. While previous research has focused on model knowledge and training data, we investigate the role of decoding mechanics in suppressing linguistic diversity. We introduce the Word Coverage Score (WCS), a metric that quantifies the extent to which contextually appropriate human vocabulary is mathematically pruned by standard sampling filters (e.g., Top-k, Top-p, and Min-p). Rather than assessing static knowledge, the WCS measures the lexical survival rate of low-frequency, high-information human words as a function of sampling parameters. By auditing open-weight models on human-authored corpus fragments, we identify which logical lexical choices are rendered unreachable by the decoder, even when they reside within the probability space. Our results provide quantitative evidence that industry-standard sampling defaults act as unintended censorship mechanisms, smoothing the unique textures of human expression into a homogenized discourse. The WCS offers a rigorous framework for optimizing the trade-off between text coherence and lexical richness, providing a diagnostic tool for preserving the diversity of human language in generative models.</t>
@@ -3040,6 +3084,9 @@
     <t>Using AI-powered multiple-choice question generation for self-regulated learning</t>
   </si>
   <si>
+    <t>dshw04ExmUIC</t>
+  </si>
+  <si>
     <t>https://doi.org/10.6018/red.711091</t>
   </si>
   <si>
@@ -3058,9 +3105,6 @@
     <t>E. Barra, A. Pilicita, J. Conde, A. Pozo, S. López-Pernas, P. Reviriego</t>
   </si>
   <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>https://oa.upm.es/97165/</t>
   </si>
   <si>
@@ -3082,73 +3126,25 @@
     <t>10.1109/MITP.2026.3712183</t>
   </si>
   <si>
-    <t>TODO MIO</t>
-  </si>
-  <si>
-    <t>Enviar noticia cuando esté publicado en upm</t>
-  </si>
-  <si>
-    <t>[https://short.upm.es/aewi0,
-https://short.upm.es/hk60w,
-https://short.upm.es/i48zs, https://samermakes.com/blog/WCS/]</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3758/s13428-026-03129-3</t>
-  </si>
-  <si>
-    <t>@article{conde2026adding,
-  author  = {Conde, J. and Grandury, M. and Fu, T. and others},
-  title   = {Adding {LLMs} to the psycholinguistic norming toolbox: {A} practical guide to getting the most out of human ratings},
-  journal = {Behavior Research Methods},
-  volume  = {58},
-  number  = {253},
-  pages   = {253},
-  year    = {2026},
-  doi     = {10.3758/s13428-026-03129-3},
-  url     = {https://doi.org/10.3758/s13428-026-03129-3}
-}</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/97414/</t>
-  </si>
-  <si>
-    <t>[https://github.com/WordsGPT/psycholinguistics_framework, https://doi.org/10.5281/zenodo.17141353]</t>
-  </si>
-  <si>
-    <t>[https://www.linkedin.com/posts/tomorrow-our-colleague-javier-conde-share-7474393536004816896-bkeM, https://www.upm.es/?id=CON23321&amp;prefmt=articulo&amp;fmt=detail, https://efs.efeservicios.com/texto/capaz-descifrar-caracteristicas-lenguaje-parecian-exclusivas-humanos/55018439374, https://www.abc.com.py/ciencia/2025/11/03/la-ia-capaz-de-descifrar-caracteristicas-del-lenguaje-que-parecian-exclusivas-de-humanos/, https://www.lavanguardia.com/tecnologia/20251103/11223637/ia-capaz-descifrar-caracteristicas-lenguaje-parecian-exclusivas-humanos-agenciaslv20251103.html, https://www.linkedin.com/posts/javier-conde-diaz_psicolingaesaedstica-ia-llm-share-7487825960554397697-Er63/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAC4AtuYBgD6ic-rMJXU60tP7ZnYJXrU5Cn0]</t>
-  </si>
-  <si>
-    <t>published-early</t>
-  </si>
-  <si>
-    <t>https://oa.upm.es/97418/</t>
-  </si>
-  <si>
-    <t>Hacer noticia, actualizar versión arxiv a versión de revista (en teoría ya está)</t>
-  </si>
-  <si>
-    <t>[https://www.growkudos.com/publications/10.1145%25252F3831675/reader, https://scipapermill.com/2026/08/01/foundation-models-from-urban-ai-to-genomic-insights-and-the-unseen-challenges/]</t>
-  </si>
-  <si>
-    <t>Leon, Spain</t>
-  </si>
-  <si>
-    <t>Aceptado como póster</t>
-  </si>
-  <si>
     <t>E. Barra, S. López-Pernas, J. Conde, A. Gordillo</t>
   </si>
   <si>
     <t xml:space="preserve">	Beyond the Hivemind: Escaping LLM Homogeneity via Meta-Persona Anchoring and Sequential Temperature Scaling </t>
   </si>
   <si>
+    <t>KxtntwgDAa4C</t>
+  </si>
+  <si>
     <t>https://arxiv.org/abs/2608.02618</t>
   </si>
   <si>
     <t>T. Fu, J. Conde, C. Arriaga, G. Martínez, P. Reviriego, J. Coronado-Blázquez</t>
   </si>
   <si>
-    <t>no enviado a ningún sitio</t>
+    <t>[https://arxiv.org/abs/2608.02618]</t>
+  </si>
+  <si>
+    <t>Recent studies have identified an "Artificial Hivemind" effect in Large Language Models (LLMs) causing models to converge on a narrow, homogenized consensus even for open questions. This semantic collapse limits the diversity of AI, resulting in high inter-response similarity even under high-temperature sampling. In this paper, we propose a novel mitigation framework to increase diversity: Meta-Persona Anchoring combined with Filtered Temperature Scaling (FTS). Our approach utilizes a two-stage generation process: first, the model is prompted to self-select a unique, idiosyncratic persona to anchor its starting point; second, we apply a dual-stage sampling sieve, utilizing Top-k filtering to preserve grammatical validity followed by extreme temperature scaling on the surviving candidates to explore the broadened probability distribution. We evaluate our method using the INFINITY-CHAT dataset on state-of-the-art open weight models under 20B parameters. Our results demonstrate a significant reduction in semantic convergence, with average pairwise cosine similarity dropping. Our scheme achieves a majority of questions below the 0.7 threshold, effectively reducing the gap between artificial mode collapse and human-level typological diversity. We provide our implementation as an open-source framework to enable more diverse and creative AI deployments.</t>
   </si>
   <si>
     <t>@misc{fu2026hivemindescapingllmhomogeneity,
@@ -3160,6 +3156,18 @@
       primaryClass={cs.AI},
       url={https://arxiv.org/abs/2608.02618}, 
 }</t>
+  </si>
+  <si>
+    <t>cowork_2026-08-10: Id_google_scholar añadido -&gt; KxtntwgDAa4C; Citas GS vacio -&gt; 0; Open Access anadido (arXiv); Sumary (abstract) anadido desde Google Scholar</t>
+  </si>
+  <si>
+    <t>Decoding-Level Taboo: A Diagnostic Stress Test for LLM Robustness</t>
+  </si>
+  <si>
+    <t>T. Chuyo Kamijo, O. Rottenstreich, J. Conde, G. Martínez, P. Reviriego</t>
+  </si>
+  <si>
+    <t>[https://arxiv.org/abs/2608.09900, https://huggingface.co/papers/2608.09900]</t>
   </si>
 </sst>
 </file>
@@ -4097,8 +4105,8 @@
     <col min="40" max="40" width="48.5" style="37" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="48.5" style="37" customWidth="1"/>
     <col min="42" max="42" width="99.1640625" style="37" bestFit="1" customWidth="1"/>
-    <col min="43" max="45" width="8.83203125" style="1" customWidth="1"/>
-    <col min="46" max="16384" width="8.83203125" style="1"/>
+    <col min="43" max="46" width="8.83203125" style="1" customWidth="1"/>
+    <col min="47" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4223,51 +4231,51 @@
         <v>39</v>
       </c>
       <c r="AO1" s="4" t="s">
-        <v>819</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="73">
         <v>2018</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" s="9">
         <v>1</v>
@@ -4276,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S2" s="6">
         <v>0</v>
@@ -4289,35 +4297,35 @@
       <c r="Y2" s="11"/>
       <c r="Z2" s="11"/>
       <c r="AA2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB2" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AK2" s="97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN2" s="9"/>
       <c r="AO2" s="9"/>
@@ -4325,43 +4333,43 @@
     </row>
     <row r="3" spans="1:42" s="12" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="73">
         <v>2020</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P3" s="9">
         <v>1</v>
@@ -4370,10 +4378,10 @@
         <v>1</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S3" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="11"/>
@@ -4383,35 +4391,35 @@
       <c r="Y3" s="11"/>
       <c r="Z3" s="11"/>
       <c r="AA3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB3" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" s="74" t="s">
-        <v>57</v>
-      </c>
       <c r="AD3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG3" s="9"/>
       <c r="AH3" s="9"/>
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" s="97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AL3" s="9"/>
       <c r="AM3" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN3" s="9"/>
       <c r="AO3" s="9"/>
@@ -4419,7 +4427,7 @@
     </row>
     <row r="4" spans="1:42" s="12" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="72">
         <v>2021</v>
@@ -4428,40 +4436,40 @@
         <v>5</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="75" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N4" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4" s="18">
         <v>6</v>
@@ -4470,10 +4478,10 @@
         <v>3</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S4" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T4" s="19"/>
       <c r="U4" s="20"/>
@@ -4483,35 +4491,35 @@
       <c r="Y4" s="20"/>
       <c r="Z4" s="20"/>
       <c r="AA4" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB4" s="75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" s="76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD4" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE4" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF4" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16"/>
       <c r="AI4" s="16"/>
       <c r="AJ4" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK4" s="98" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL4" s="16"/>
       <c r="AM4" s="77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN4" s="9"/>
       <c r="AO4" s="9"/>
@@ -4519,7 +4527,7 @@
     </row>
     <row r="5" spans="1:42" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="78">
         <v>2021</v>
@@ -4528,40 +4536,40 @@
         <v>4</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M5" s="48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O5" s="50" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P5" s="51">
         <v>6</v>
@@ -4570,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S5" s="52">
         <v>18</v>
@@ -4583,35 +4591,35 @@
       <c r="Y5" s="70"/>
       <c r="Z5" s="70"/>
       <c r="AA5" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB5" s="48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC5" s="48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE5" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF5" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG5" s="48"/>
       <c r="AH5" s="48"/>
       <c r="AI5" s="48"/>
       <c r="AJ5" s="48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AK5" s="99" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL5" s="48"/>
       <c r="AM5" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN5" s="63"/>
       <c r="AO5" s="63"/>
@@ -4619,43 +4627,43 @@
     </row>
     <row r="6" spans="1:42" s="12" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="73">
         <v>2021</v>
       </c>
       <c r="C6" s="28"/>
       <c r="D6" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P6" s="9">
         <v>11</v>
@@ -4664,7 +4672,7 @@
         <v>4</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S6" s="6">
         <v>9</v>
@@ -4677,35 +4685,35 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB6" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG6" s="9"/>
       <c r="AH6" s="9"/>
       <c r="AI6" s="9"/>
       <c r="AJ6" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AK6" s="97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AL6" s="9"/>
       <c r="AM6" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN6" s="9"/>
       <c r="AO6" s="9"/>
@@ -4713,43 +4721,43 @@
     </row>
     <row r="7" spans="1:42" s="12" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="73">
         <v>2021</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P7" s="9">
         <v>4</v>
@@ -4758,7 +4766,7 @@
         <v>2</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S7" s="6">
         <v>0</v>
@@ -4771,35 +4779,35 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB7" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AC7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF7" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG7" s="9"/>
       <c r="AH7" s="9"/>
       <c r="AI7" s="9"/>
       <c r="AJ7" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" s="97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AL7" s="9"/>
       <c r="AM7" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN7" s="9"/>
       <c r="AO7" s="9"/>
@@ -4807,7 +4815,7 @@
     </row>
     <row r="8" spans="1:42" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="78">
         <v>2022</v>
@@ -4816,40 +4824,40 @@
         <v>10</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H8" s="57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I8" s="57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" s="57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8" s="57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O8" s="57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P8" s="49">
         <v>7</v>
@@ -4858,10 +4866,10 @@
         <v>1</v>
       </c>
       <c r="R8" s="57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S8" s="58">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T8" s="58">
         <v>63</v>
@@ -4882,42 +4890,42 @@
         <v>43</v>
       </c>
       <c r="Z8" s="59" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA8" s="57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB8" s="57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC8" s="56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD8" s="57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AE8" s="57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF8" s="57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG8" s="57"/>
       <c r="AH8" s="57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AI8" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AJ8" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK8" s="100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AL8" s="57"/>
       <c r="AM8" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN8" s="63"/>
       <c r="AO8" s="63"/>
@@ -4925,7 +4933,7 @@
     </row>
     <row r="9" spans="1:42" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="78">
         <v>2022</v>
@@ -4934,40 +4942,40 @@
         <v>10</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H9" s="57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J9" s="57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L9" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M9" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N9" s="57" t="s">
         <v>13</v>
       </c>
       <c r="O9" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P9" s="49">
         <v>5</v>
@@ -4976,10 +4984,10 @@
         <v>1</v>
       </c>
       <c r="R9" s="57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S9" s="58">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T9" s="58">
         <v>107</v>
@@ -4998,42 +5006,42 @@
       </c>
       <c r="Y9" s="60"/>
       <c r="Z9" s="60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA9" s="57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB9" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AC9" s="92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AD9" s="57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AE9" s="57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF9" s="57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG9" s="57"/>
       <c r="AH9" s="57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AI9" s="57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AJ9" s="57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" s="100" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AL9" s="57"/>
       <c r="AM9" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN9" s="63"/>
       <c r="AO9" s="63"/>
@@ -5041,7 +5049,7 @@
     </row>
     <row r="10" spans="1:42" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="79">
         <v>2022</v>
@@ -5050,40 +5058,40 @@
         <v>7</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O10" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P10" s="22">
         <v>5</v>
@@ -5092,7 +5100,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S10" s="27">
         <v>28</v>
@@ -5105,33 +5113,33 @@
       <c r="Y10" s="33"/>
       <c r="Z10" s="33"/>
       <c r="AA10" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB10" s="23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AD10" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE10" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF10" s="23"/>
       <c r="AG10" s="23"/>
       <c r="AH10" s="23"/>
       <c r="AI10" s="23"/>
       <c r="AJ10" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AK10" s="101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL10" s="23"/>
       <c r="AM10" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN10" s="37"/>
       <c r="AO10" s="37"/>
@@ -5139,7 +5147,7 @@
     </row>
     <row r="11" spans="1:42" s="2" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="79">
         <v>2022</v>
@@ -5148,38 +5156,38 @@
         <v>4</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F11" s="80" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N11" s="23"/>
       <c r="O11" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" s="22">
         <v>5</v>
@@ -5188,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S11" s="27">
         <v>11</v>
@@ -5201,33 +5209,33 @@
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
       <c r="AA11" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB11" s="23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AC11" s="80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AF11" s="23"/>
       <c r="AG11" s="23"/>
       <c r="AH11" s="23"/>
       <c r="AI11" s="23"/>
       <c r="AJ11" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AK11" s="101" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AL11" s="23"/>
       <c r="AM11" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN11" s="37"/>
       <c r="AO11" s="37"/>
@@ -5235,43 +5243,43 @@
     </row>
     <row r="12" spans="1:42" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="79">
         <v>2023</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" s="37"/>
       <c r="L12" s="37"/>
       <c r="M12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P12" s="37">
         <v>5</v>
@@ -5280,7 +5288,7 @@
         <v>2</v>
       </c>
       <c r="R12" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S12" s="28">
         <v>3</v>
@@ -5293,33 +5301,33 @@
       <c r="Y12" s="39"/>
       <c r="Z12" s="39"/>
       <c r="AA12" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE12" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF12" s="37"/>
       <c r="AG12" s="37"/>
       <c r="AH12" s="37"/>
       <c r="AI12" s="37"/>
       <c r="AJ12" s="37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AK12" s="95" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL12" s="37"/>
       <c r="AM12" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN12" s="37"/>
       <c r="AO12" s="37"/>
@@ -5327,43 +5335,43 @@
     </row>
     <row r="13" spans="1:42" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="81">
         <v>2023</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K13" s="37"/>
       <c r="L13" s="37"/>
       <c r="M13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O13" s="35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P13" s="37">
         <v>5</v>
@@ -5372,10 +5380,10 @@
         <v>2</v>
       </c>
       <c r="R13" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S13" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" s="28"/>
       <c r="U13" s="39"/>
@@ -5385,35 +5393,35 @@
       <c r="Y13" s="39"/>
       <c r="Z13" s="39"/>
       <c r="AA13" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC13" s="80" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF13" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG13" s="37"/>
       <c r="AH13" s="37"/>
       <c r="AI13" s="37"/>
       <c r="AJ13" s="37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AK13" s="95" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL13" s="37"/>
       <c r="AM13" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN13" s="37"/>
       <c r="AO13" s="37"/>
@@ -5421,43 +5429,43 @@
     </row>
     <row r="14" spans="1:42" s="53" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="82">
         <v>2023</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" s="61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G14" s="61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I14" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" s="63"/>
       <c r="L14" s="63"/>
       <c r="M14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P14" s="63">
         <v>1</v>
@@ -5466,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="R14" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S14" s="65">
         <v>0</v>
@@ -5479,35 +5487,35 @@
       <c r="Y14" s="66"/>
       <c r="Z14" s="66"/>
       <c r="AA14" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC14" s="63" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AD14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF14" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG14" s="63"/>
       <c r="AH14" s="63"/>
       <c r="AI14" s="63"/>
       <c r="AJ14" s="63" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AK14" s="102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL14" s="63"/>
       <c r="AM14" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN14" s="63"/>
       <c r="AO14" s="63"/>
@@ -5515,43 +5523,43 @@
     </row>
     <row r="15" spans="1:42" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="82">
         <v>2023</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E15" s="61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G15" s="61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I15" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K15" s="63"/>
       <c r="L15" s="63"/>
       <c r="M15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P15" s="63">
         <v>4</v>
@@ -5560,7 +5568,7 @@
         <v>2</v>
       </c>
       <c r="R15" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S15" s="65">
         <v>4</v>
@@ -5573,35 +5581,35 @@
       <c r="Y15" s="66"/>
       <c r="Z15" s="66"/>
       <c r="AA15" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB15" s="63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AC15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF15" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG15" s="63"/>
       <c r="AH15" s="63"/>
       <c r="AI15" s="63"/>
       <c r="AJ15" s="63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AK15" s="102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL15" s="63"/>
       <c r="AM15" s="63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN15" s="63"/>
       <c r="AO15" s="63"/>
@@ -5609,7 +5617,7 @@
     </row>
     <row r="16" spans="1:42" s="53" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="78">
         <v>2024</v>
@@ -5618,40 +5626,40 @@
         <v>9</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I16" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" s="49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M16" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N16" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O16" s="49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P16" s="49">
         <v>6</v>
@@ -5660,7 +5668,7 @@
         <v>4</v>
       </c>
       <c r="R16" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S16" s="67">
         <v>8</v>
@@ -5677,39 +5685,39 @@
       <c r="Y16" s="68"/>
       <c r="Z16" s="68"/>
       <c r="AA16" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB16" s="49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AC16" s="56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AD16" s="49" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AE16" s="49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF16" s="49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG16" s="63"/>
       <c r="AH16" s="49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI16" s="49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AJ16" s="63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AK16" s="102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL16" s="63"/>
       <c r="AM16" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN16" s="63"/>
       <c r="AO16" s="63"/>
@@ -5717,7 +5725,7 @@
     </row>
     <row r="17" spans="1:42" s="53" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="78">
         <v>2024</v>
@@ -5726,40 +5734,40 @@
         <v>8.5</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K17" s="49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M17" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N17" s="49" t="s">
         <v>13</v>
       </c>
       <c r="O17" s="49" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P17" s="49">
         <v>4</v>
@@ -5768,13 +5776,13 @@
         <v>2</v>
       </c>
       <c r="R17" s="49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S17" s="67">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T17" s="69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U17" s="67">
         <v>15</v>
@@ -5785,37 +5793,37 @@
       <c r="Y17" s="67"/>
       <c r="Z17" s="67"/>
       <c r="AA17" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB17" s="49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AC17" s="56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AD17" s="49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AE17" s="49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AF17" s="49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG17" s="63"/>
       <c r="AH17" s="63"/>
       <c r="AI17" s="49" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AJ17" s="63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK17" s="102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL17" s="63"/>
       <c r="AM17" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN17" s="63"/>
       <c r="AO17" s="63"/>
@@ -5823,7 +5831,7 @@
     </row>
     <row r="18" spans="1:42" s="53" customFormat="1" ht="387.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="78">
         <v>2024</v>
@@ -5832,40 +5840,40 @@
         <v>8</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I18" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L18" s="49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M18" s="49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N18" s="49" t="s">
         <v>13</v>
       </c>
       <c r="O18" s="49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P18" s="49">
         <v>6</v>
@@ -5874,10 +5882,10 @@
         <v>6</v>
       </c>
       <c r="R18" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S18" s="67">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" s="67">
         <v>3</v>
@@ -5891,39 +5899,39 @@
       <c r="Y18" s="68"/>
       <c r="Z18" s="68"/>
       <c r="AA18" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB18" s="49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC18" s="56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AD18" s="49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AE18" s="49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF18" s="49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG18" s="63"/>
       <c r="AH18" s="49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AI18" s="49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AJ18" s="63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AK18" s="102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL18" s="63"/>
       <c r="AM18" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN18" s="63"/>
       <c r="AO18" s="63"/>
@@ -5931,7 +5939,7 @@
     </row>
     <row r="19" spans="1:42" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="78">
         <v>2024</v>
@@ -5940,40 +5948,40 @@
         <v>8</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F19" s="56" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H19" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K19" s="49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L19" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M19" s="49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N19" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O19" s="49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P19" s="49">
         <v>5</v>
@@ -5982,10 +5990,10 @@
         <v>1</v>
       </c>
       <c r="R19" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S19" s="67">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" s="67">
         <v>3</v>
@@ -5999,37 +6007,37 @@
       <c r="Y19" s="68"/>
       <c r="Z19" s="68"/>
       <c r="AA19" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB19" s="49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AC19" s="56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AD19" s="49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AE19" s="49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF19" s="49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG19" s="63"/>
       <c r="AH19" s="63"/>
       <c r="AI19" s="49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ19" s="63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK19" s="102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL19" s="63"/>
       <c r="AM19" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN19" s="63"/>
       <c r="AO19" s="63"/>
@@ -6037,7 +6045,7 @@
     </row>
     <row r="20" spans="1:42" s="2" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="79">
         <v>2024</v>
@@ -6046,40 +6054,40 @@
         <v>6</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P20" s="22">
         <v>6</v>
@@ -6088,13 +6096,13 @@
         <v>1</v>
       </c>
       <c r="R20" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S20" s="44">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T20" s="44" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="U20" s="39"/>
       <c r="V20" s="39"/>
@@ -6103,33 +6111,33 @@
       <c r="Y20" s="39"/>
       <c r="Z20" s="39"/>
       <c r="AA20" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB20" s="37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC20" s="80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AD20" s="37"/>
       <c r="AE20" s="37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF20" s="37"/>
       <c r="AG20" s="37"/>
       <c r="AH20" s="37"/>
       <c r="AI20" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AJ20" s="37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AK20" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL20" s="37"/>
       <c r="AM20" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN20" s="37"/>
       <c r="AO20" s="37"/>
@@ -6137,7 +6145,7 @@
     </row>
     <row r="21" spans="1:42" s="2" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="79">
         <v>2024</v>
@@ -6146,40 +6154,40 @@
         <v>4</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J21" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O21" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P21" s="26">
         <v>6</v>
@@ -6188,10 +6196,10 @@
         <v>1</v>
       </c>
       <c r="R21" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S21" s="27">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T21" s="27"/>
       <c r="U21" s="33"/>
@@ -6201,31 +6209,31 @@
       <c r="Y21" s="33"/>
       <c r="Z21" s="33"/>
       <c r="AA21" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB21" s="23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AC21" s="80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AD21" s="23"/>
       <c r="AE21" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF21" s="23"/>
       <c r="AG21" s="23"/>
       <c r="AH21" s="23"/>
       <c r="AI21" s="23"/>
       <c r="AJ21" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AK21" s="101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL21" s="23"/>
       <c r="AM21" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN21" s="37"/>
       <c r="AO21" s="37"/>
@@ -6233,7 +6241,7 @@
     </row>
     <row r="22" spans="1:42" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="79">
         <v>2024</v>
@@ -6242,40 +6250,40 @@
         <v>3</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O22" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P22" s="22">
         <v>7</v>
@@ -6284,7 +6292,7 @@
         <v>2</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S22" s="27">
         <v>9</v>
@@ -6297,33 +6305,33 @@
       <c r="Y22" s="33"/>
       <c r="Z22" s="33"/>
       <c r="AA22" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB22" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC22" s="23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AD22" s="23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AE22" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AF22" s="23"/>
       <c r="AG22" s="23"/>
       <c r="AH22" s="23"/>
       <c r="AI22" s="23"/>
       <c r="AJ22" s="23" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AK22" s="101" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL22" s="23"/>
       <c r="AM22" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN22" s="37"/>
       <c r="AO22" s="37"/>
@@ -6331,7 +6339,7 @@
     </row>
     <row r="23" spans="1:42" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="79">
         <v>2024</v>
@@ -6340,40 +6348,40 @@
         <v>0</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F23" s="80" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O23" s="22" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="P23" s="22">
         <v>8</v>
@@ -6382,10 +6390,10 @@
         <v>1</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S23" s="27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" s="27"/>
       <c r="U23" s="33"/>
@@ -6395,33 +6403,33 @@
       <c r="Y23" s="33"/>
       <c r="Z23" s="33"/>
       <c r="AA23" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB23" s="23" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="AC23" s="23" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="AD23" s="23" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="AE23" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
       <c r="AI23" s="23"/>
       <c r="AJ23" s="23" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="AK23" s="101" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="AL23" s="23"/>
       <c r="AM23" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN23" s="37"/>
       <c r="AO23" s="37"/>
@@ -6429,43 +6437,43 @@
     </row>
     <row r="24" spans="1:42" s="2" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B24" s="78">
         <v>2024</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="61" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="J24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K24" s="63"/>
       <c r="L24" s="63"/>
       <c r="M24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="P24" s="63">
         <v>5</v>
@@ -6474,10 +6482,10 @@
         <v>1</v>
       </c>
       <c r="R24" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S24" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" s="65"/>
       <c r="U24" s="66"/>
@@ -6487,35 +6495,35 @@
       <c r="Y24" s="66"/>
       <c r="Z24" s="66"/>
       <c r="AA24" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB24" s="63" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="AC24" s="63" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="AD24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF24" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG24" s="63"/>
       <c r="AH24" s="63"/>
       <c r="AI24" s="63"/>
       <c r="AJ24" s="63" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="AK24" s="102" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="AL24" s="63"/>
       <c r="AM24" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN24" s="63"/>
       <c r="AO24" s="63"/>
@@ -6523,43 +6531,43 @@
     </row>
     <row r="25" spans="1:42" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="78">
         <v>2024</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="61" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="F25" s="71" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="G25" s="61" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I25" s="64" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="J25" s="63" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="K25" s="63"/>
       <c r="L25" s="63"/>
       <c r="M25" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N25" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O25" s="61" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="P25" s="63">
         <v>4</v>
@@ -6568,10 +6576,10 @@
         <v>1</v>
       </c>
       <c r="R25" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S25" s="65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T25" s="65"/>
       <c r="U25" s="66"/>
@@ -6581,35 +6589,35 @@
       <c r="Y25" s="66"/>
       <c r="Z25" s="66"/>
       <c r="AA25" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB25" s="63" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="AC25" s="76" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="AD25" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE25" s="63" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="AF25" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG25" s="63"/>
       <c r="AH25" s="63"/>
       <c r="AI25" s="63"/>
       <c r="AJ25" s="63" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="AK25" s="102" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AL25" s="63"/>
       <c r="AM25" s="48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN25" s="63"/>
       <c r="AO25" s="63"/>
@@ -6617,43 +6625,43 @@
     </row>
     <row r="26" spans="1:42" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" s="78">
         <v>2024</v>
       </c>
       <c r="C26" s="28"/>
       <c r="D26" s="61" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="E26" s="61" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="G26" s="61" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I26" s="64" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="J26" s="63" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="K26" s="63"/>
       <c r="L26" s="63"/>
       <c r="M26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="P26" s="63">
         <v>4</v>
@@ -6662,10 +6670,10 @@
         <v>1</v>
       </c>
       <c r="R26" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S26" s="65">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T26" s="65"/>
       <c r="U26" s="66"/>
@@ -6675,35 +6683,35 @@
       <c r="Y26" s="66"/>
       <c r="Z26" s="66"/>
       <c r="AA26" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC26" s="76" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="AD26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF26" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG26" s="63"/>
       <c r="AH26" s="63"/>
       <c r="AI26" s="63"/>
       <c r="AJ26" s="63" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="AK26" s="102" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="AL26" s="63"/>
       <c r="AM26" s="48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN26" s="63"/>
       <c r="AO26" s="63"/>
@@ -6711,43 +6719,43 @@
     </row>
     <row r="27" spans="1:42" s="53" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" s="78">
         <v>2024</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="61" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="I27" s="64" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="J27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K27" s="63"/>
       <c r="L27" s="63"/>
       <c r="M27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="P27" s="63">
         <v>5</v>
@@ -6756,10 +6764,10 @@
         <v>2</v>
       </c>
       <c r="R27" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S27" s="65">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T27" s="65"/>
       <c r="U27" s="66"/>
@@ -6769,35 +6777,35 @@
       <c r="Y27" s="66"/>
       <c r="Z27" s="66"/>
       <c r="AA27" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB27" s="63" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="AC27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE27" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF27" s="63" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="AG27" s="63"/>
       <c r="AH27" s="63"/>
       <c r="AI27" s="63"/>
       <c r="AJ27" s="63" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="AK27" s="102" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="AL27" s="63"/>
       <c r="AM27" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN27" s="63"/>
       <c r="AO27" s="63"/>
@@ -6805,43 +6813,43 @@
     </row>
     <row r="28" spans="1:42" s="53" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="78" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B28" s="82">
         <v>2024</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="61" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E28" s="61" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="F28" s="62" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="G28" s="64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H28" s="63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" s="63"/>
       <c r="L28" s="63"/>
       <c r="M28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="P28" s="63">
         <v>6</v>
@@ -6850,7 +6858,7 @@
         <v>2</v>
       </c>
       <c r="R28" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S28" s="65">
         <v>2</v>
@@ -6863,35 +6871,35 @@
       <c r="Y28" s="66"/>
       <c r="Z28" s="66"/>
       <c r="AA28" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF28" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG28" s="63"/>
       <c r="AH28" s="63"/>
       <c r="AI28" s="63"/>
       <c r="AJ28" s="63" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AK28" s="102" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AL28" s="63"/>
       <c r="AM28" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN28" s="63"/>
       <c r="AO28" s="63"/>
@@ -6899,43 +6907,43 @@
     </row>
     <row r="29" spans="1:42" s="53" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="78" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B29" s="82">
         <v>2024</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="61" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E29" s="61" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="G29" s="64" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="H29" s="63" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K29" s="63"/>
       <c r="L29" s="63"/>
       <c r="M29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O29" s="63" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="P29" s="63">
         <v>4</v>
@@ -6944,7 +6952,7 @@
         <v>3</v>
       </c>
       <c r="R29" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S29" s="65">
         <v>23</v>
@@ -6957,35 +6965,35 @@
       <c r="Y29" s="66"/>
       <c r="Z29" s="66"/>
       <c r="AA29" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB29" s="63" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="AC29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF29" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG29" s="63"/>
       <c r="AH29" s="63"/>
       <c r="AI29" s="63"/>
       <c r="AJ29" s="63" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AK29" s="102" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AL29" s="63"/>
       <c r="AM29" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN29" s="63"/>
       <c r="AO29" s="63"/>
@@ -6993,43 +7001,43 @@
     </row>
     <row r="30" spans="1:42" s="53" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="82">
         <v>2024</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="61" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="E30" s="61" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="F30" s="62" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="G30" s="61" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="H30" s="63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I30" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" s="63"/>
       <c r="L30" s="63"/>
       <c r="M30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="P30" s="63">
         <v>6</v>
@@ -7038,10 +7046,10 @@
         <v>4</v>
       </c>
       <c r="R30" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S30" s="65">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T30" s="65"/>
       <c r="U30" s="66"/>
@@ -7051,35 +7059,35 @@
       <c r="Y30" s="66"/>
       <c r="Z30" s="66"/>
       <c r="AA30" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC30" s="63" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AD30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF30" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG30" s="63"/>
       <c r="AH30" s="63"/>
       <c r="AI30" s="63"/>
       <c r="AJ30" s="63" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="AK30" s="102" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="AL30" s="63"/>
       <c r="AM30" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN30" s="63"/>
       <c r="AO30" s="63"/>
@@ -7087,26 +7095,26 @@
     </row>
     <row r="31" spans="1:42" s="53" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="78" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B31" s="102">
         <v>2024</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="63" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="E31" s="63" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="F31" s="63" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="G31" s="63" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="H31" s="63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I31" s="63"/>
       <c r="J31" s="63"/>
@@ -7115,7 +7123,7 @@
       <c r="M31" s="63"/>
       <c r="N31" s="63"/>
       <c r="O31" s="63" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="P31" s="65">
         <v>4</v>
@@ -7124,7 +7132,7 @@
         <v>4</v>
       </c>
       <c r="R31" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S31" s="65">
         <v>0</v>
@@ -7137,35 +7145,35 @@
       <c r="Y31" s="66"/>
       <c r="Z31" s="66"/>
       <c r="AA31" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB31" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC31" s="63" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AD31" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE31" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF31" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG31" s="63"/>
       <c r="AH31" s="63"/>
       <c r="AI31" s="63"/>
       <c r="AJ31" s="63" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="AK31" s="102" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="AL31" s="63"/>
       <c r="AM31" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN31" s="63"/>
       <c r="AO31" s="63"/>
@@ -7173,26 +7181,26 @@
     </row>
     <row r="32" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B32" s="95">
         <v>2024</v>
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="37" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="I32" s="37"/>
       <c r="J32" s="37"/>
@@ -7201,7 +7209,7 @@
       <c r="M32" s="37"/>
       <c r="N32" s="37"/>
       <c r="O32" s="37" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="P32" s="28">
         <v>5</v>
@@ -7210,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="R32" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S32" s="28">
         <v>7</v>
@@ -7223,29 +7231,29 @@
       <c r="Y32" s="39"/>
       <c r="Z32" s="39"/>
       <c r="AA32" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB32" s="37" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="AC32" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD32" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE32" s="37" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="AF32" s="37"/>
       <c r="AG32" s="37"/>
       <c r="AH32" s="37"/>
       <c r="AI32" s="37"/>
       <c r="AJ32" s="37" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="AK32" s="95" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="AL32" s="37"/>
       <c r="AM32" s="37"/>
@@ -7255,7 +7263,7 @@
     </row>
     <row r="33" spans="1:42" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B33" s="79">
         <v>2025</v>
@@ -7264,40 +7272,40 @@
         <v>0</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>292</v>
+        <v>387</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="F33" s="80" t="s">
-        <v>294</v>
+        <v>389</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>295</v>
+        <v>390</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>296</v>
+        <v>391</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J33" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>297</v>
+        <v>392</v>
       </c>
       <c r="L33" s="22" t="s">
-        <v>298</v>
+        <v>393</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N33" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O33" s="22" t="s">
-        <v>299</v>
+        <v>394</v>
       </c>
       <c r="P33" s="22">
         <v>4</v>
@@ -7306,10 +7314,10 @@
         <v>2</v>
       </c>
       <c r="R33" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S33" s="27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T33" s="27"/>
       <c r="U33" s="33"/>
@@ -7319,38 +7327,39 @@
       <c r="Y33" s="33"/>
       <c r="Z33" s="33"/>
       <c r="AA33" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB33" s="23" t="s">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="AC33" s="80" t="s">
-        <v>301</v>
+        <v>396</v>
       </c>
       <c r="AD33" s="105" t="s">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="AE33" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF33" s="23"/>
       <c r="AG33" s="23"/>
       <c r="AH33" s="23"/>
       <c r="AI33" s="23"/>
       <c r="AJ33" s="23" t="s">
-        <v>303</v>
+        <v>398</v>
       </c>
       <c r="AK33" s="101" t="s">
-        <v>304</v>
+        <v>399</v>
       </c>
       <c r="AL33" s="23"/>
       <c r="AM33" s="31" t="s">
-        <v>54</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AP33"/>
     </row>
     <row r="34" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" s="78">
         <v>2025</v>
@@ -7359,40 +7368,40 @@
         <v>10</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="E34" s="49" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="F34" s="56" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="G34" s="49" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H34" s="49" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I34" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J34" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K34" s="49" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="L34" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M34" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N34" s="49" t="s">
         <v>13</v>
       </c>
       <c r="O34" s="49" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="P34" s="57">
         <v>5</v>
@@ -7401,13 +7410,13 @@
         <v>3</v>
       </c>
       <c r="R34" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S34" s="69">
         <v>46</v>
       </c>
       <c r="T34" s="69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U34" s="66"/>
       <c r="V34" s="66"/>
@@ -7416,35 +7425,35 @@
       <c r="Y34" s="66"/>
       <c r="Z34" s="66"/>
       <c r="AA34" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB34" s="49" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="AC34" s="56" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AD34" s="49" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="AE34" s="49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AF34" s="49" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="AG34" s="63"/>
       <c r="AH34" s="63"/>
       <c r="AI34" s="63"/>
       <c r="AJ34" s="63" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AK34" s="102" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="AL34" s="63"/>
       <c r="AM34" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN34" s="63"/>
       <c r="AO34" s="63"/>
@@ -7452,7 +7461,7 @@
     </row>
     <row r="35" spans="1:42" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35" s="78">
         <v>2025</v>
@@ -7461,40 +7470,40 @@
         <v>9</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E35" s="49" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="F35" s="56" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="G35" s="49" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="H35" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J35" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K35" s="49" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="L35" s="49" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="M35" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N35" s="49" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="O35" s="49" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="P35" s="46">
         <v>6</v>
@@ -7503,7 +7512,7 @@
         <v>2</v>
       </c>
       <c r="R35" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S35" s="67">
         <v>3</v>
@@ -7520,37 +7529,37 @@
       <c r="Y35" s="67"/>
       <c r="Z35" s="67"/>
       <c r="AA35" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB35" s="49" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AC35" s="56" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="AD35" s="49" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="AE35" s="49" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="AF35" s="49" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="AG35" s="63"/>
       <c r="AH35" s="63"/>
       <c r="AI35" s="49" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="AJ35" s="63" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AK35" s="102" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="AL35" s="63"/>
       <c r="AM35" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN35" s="63"/>
       <c r="AO35" s="63"/>
@@ -7558,7 +7567,7 @@
     </row>
     <row r="36" spans="1:42" s="54" customFormat="1" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" s="78">
         <v>2025</v>
@@ -7567,40 +7576,40 @@
         <v>8.5</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="F36" s="56" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H36" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I36" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="L36" s="46" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="M36" s="48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N36" s="48" t="s">
         <v>13</v>
       </c>
       <c r="O36" s="46" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="P36" s="49">
         <v>4</v>
@@ -7609,14 +7618,14 @@
         <v>3</v>
       </c>
       <c r="R36" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S36" s="85">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T36" s="52"/>
       <c r="U36" s="70" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="V36" s="70"/>
       <c r="W36" s="70"/>
@@ -7624,37 +7633,37 @@
       <c r="Y36" s="70"/>
       <c r="Z36" s="70"/>
       <c r="AA36" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB36" s="48" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="AC36" s="48" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="AD36" s="48" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="AE36" s="48" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="AF36" s="48" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AG36" s="48"/>
       <c r="AH36" s="48"/>
       <c r="AI36" s="48" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AJ36" s="48" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="AK36" s="99" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="AL36" s="48"/>
       <c r="AM36" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN36" s="63"/>
       <c r="AO36" s="63"/>
@@ -7662,7 +7671,7 @@
     </row>
     <row r="37" spans="1:42" s="54" customFormat="1" ht="255" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="78">
         <v>2025</v>
@@ -7671,40 +7680,40 @@
         <v>8</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="E37" s="55" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J37" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K37" s="49" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="L37" s="49" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="M37" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N37" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O37" s="49" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="P37" s="49">
         <v>7</v>
@@ -7713,7 +7722,7 @@
         <v>5</v>
       </c>
       <c r="R37" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S37" s="67">
         <v>3</v>
@@ -7730,37 +7739,37 @@
       <c r="Y37" s="67"/>
       <c r="Z37" s="67"/>
       <c r="AA37" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB37" s="49" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="AC37" s="56" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AD37" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE37" s="49" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="AF37" s="49" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="AG37" s="63"/>
       <c r="AH37" s="63"/>
       <c r="AI37" s="49" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="AJ37" s="63" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="AK37" s="102" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="AL37" s="63"/>
       <c r="AM37" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN37" s="63"/>
       <c r="AO37" s="63"/>
@@ -7768,7 +7777,7 @@
     </row>
     <row r="38" spans="1:42" s="54" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B38" s="78">
         <v>2025</v>
@@ -7777,40 +7786,40 @@
         <v>7</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="G38" s="49" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="H38" s="49" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J38" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K38" s="49" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="L38" s="49" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="M38" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N38" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="P38" s="51">
         <v>6</v>
@@ -7819,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="R38" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S38" s="67">
         <v>11</v>
@@ -7834,37 +7843,37 @@
       <c r="Y38" s="66"/>
       <c r="Z38" s="66"/>
       <c r="AA38" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB38" s="49" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="AC38" s="56" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AD38" s="49" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AE38" s="49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF38" s="49" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="AG38" s="63"/>
       <c r="AH38" s="63"/>
       <c r="AI38" s="49" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AJ38" s="63" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="AK38" s="102" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="AL38" s="63"/>
       <c r="AM38" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN38" s="63"/>
       <c r="AO38" s="63"/>
@@ -7872,7 +7881,7 @@
     </row>
     <row r="39" spans="1:42" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B39" s="78">
         <v>2025</v>
@@ -7881,40 +7890,40 @@
         <v>7</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="G39" s="47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H39" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I39" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J39" s="93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" s="46" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="L39" s="46" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="M39" s="48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N39" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O39" s="46" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="P39" s="51">
         <v>5</v>
@@ -7923,7 +7932,7 @@
         <v>3</v>
       </c>
       <c r="R39" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S39" s="52">
         <v>2</v>
@@ -7936,37 +7945,37 @@
       <c r="Y39" s="70"/>
       <c r="Z39" s="70"/>
       <c r="AA39" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB39" s="48" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="AC39" s="76" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="AD39" s="48" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AE39" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF39" s="48" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="AG39" s="48"/>
       <c r="AH39" s="48"/>
       <c r="AI39" s="48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AJ39" s="48" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="AK39" s="99" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="AL39" s="48"/>
       <c r="AM39" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN39" s="63"/>
       <c r="AO39" s="63"/>
@@ -7974,7 +7983,7 @@
     </row>
     <row r="40" spans="1:42" s="54" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="79">
         <v>2025</v>
@@ -7983,40 +7992,40 @@
         <v>6</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F40" s="80" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K40" s="22" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="L40" s="22" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="M40" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N40" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O40" s="22" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="P40" s="25">
         <v>6</v>
@@ -8025,7 +8034,7 @@
         <v>1</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S40" s="27">
         <v>6</v>
@@ -8038,33 +8047,33 @@
       <c r="Y40" s="33"/>
       <c r="Z40" s="33"/>
       <c r="AA40" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB40" s="23" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="AC40" s="80" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="AD40" s="23"/>
       <c r="AE40" s="23" t="s">
-        <v>398</v>
+        <v>488</v>
       </c>
       <c r="AF40" s="23"/>
       <c r="AG40" s="23"/>
       <c r="AH40" s="23"/>
       <c r="AI40" s="23" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="AJ40" s="23" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="AK40" s="101" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="AL40" s="23"/>
       <c r="AM40" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN40" s="37"/>
       <c r="AO40" s="37"/>
@@ -8072,7 +8081,7 @@
     </row>
     <row r="41" spans="1:42" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B41" s="78">
         <v>2025</v>
@@ -8081,40 +8090,40 @@
         <v>0</v>
       </c>
       <c r="D41" s="46" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="G41" s="47" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="H41" s="48" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="I41" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J41" s="49" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="L41" s="46" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="M41" s="48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N41" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O41" s="46" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="P41" s="51">
         <v>7</v>
@@ -8123,10 +8132,10 @@
         <v>2</v>
       </c>
       <c r="R41" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S41" s="52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" s="52"/>
       <c r="U41" s="70"/>
@@ -8136,37 +8145,37 @@
       <c r="Y41" s="70"/>
       <c r="Z41" s="70"/>
       <c r="AA41" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB41" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC41" s="48" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="AD41" s="48" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="AE41" s="48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF41" s="48" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AG41" s="48"/>
       <c r="AH41" s="48"/>
       <c r="AI41" s="48" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AJ41" s="48" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="AK41" s="99" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="AL41" s="48"/>
       <c r="AM41" s="57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN41" s="63"/>
       <c r="AO41" s="53"/>
@@ -8174,7 +8183,7 @@
     </row>
     <row r="42" spans="1:42" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" s="79">
         <v>2025</v>
@@ -8183,38 +8192,38 @@
         <v>0</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="F42" s="80" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I42" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" s="22" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="L42" s="24"/>
       <c r="M42" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N42" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O42" s="22" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="P42" s="22">
         <v>6</v>
@@ -8223,7 +8232,7 @@
         <v>5</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S42" s="27">
         <v>2</v>
@@ -8236,31 +8245,31 @@
       <c r="Y42" s="33"/>
       <c r="Z42" s="33"/>
       <c r="AA42" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB42" s="23"/>
       <c r="AC42" s="23" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="AD42" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE42" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF42" s="23"/>
       <c r="AG42" s="23"/>
       <c r="AH42" s="23"/>
       <c r="AI42" s="23"/>
       <c r="AJ42" s="23" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="AK42" s="101" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="AL42" s="23"/>
       <c r="AM42" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN42" s="37"/>
       <c r="AO42" s="37"/>
@@ -8268,7 +8277,7 @@
     </row>
     <row r="43" spans="1:42" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43" s="79">
         <v>2025</v>
@@ -8277,40 +8286,40 @@
         <v>0</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J43" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N43" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>299</v>
+        <v>394</v>
       </c>
       <c r="P43" s="22">
         <v>4</v>
@@ -8319,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S43" s="27">
         <v>3</v>
@@ -8332,40 +8341,40 @@
       <c r="Y43" s="33"/>
       <c r="Z43" s="33"/>
       <c r="AA43" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB43" s="23" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="AC43" s="80" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="AD43" s="23" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="AE43" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AF43" s="23"/>
       <c r="AG43" s="23"/>
       <c r="AH43" s="23"/>
       <c r="AI43" s="23" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="AJ43" s="23" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="AK43" s="101" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="AL43" s="23"/>
       <c r="AM43" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:42" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" s="79">
         <v>2025</v>
@@ -8374,40 +8383,40 @@
         <v>0</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="F44" s="80" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J44" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="L44" s="22" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N44" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O44" s="22" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="P44" s="22">
         <v>7</v>
@@ -8416,7 +8425,7 @@
         <v>6</v>
       </c>
       <c r="R44" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S44" s="27">
         <v>2</v>
@@ -8429,38 +8438,38 @@
       <c r="Y44" s="33"/>
       <c r="Z44" s="33"/>
       <c r="AA44" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB44" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC44" s="23" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="AD44" s="23" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="AE44" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF44" s="23"/>
       <c r="AG44" s="23"/>
       <c r="AH44" s="23"/>
       <c r="AI44" s="23"/>
       <c r="AJ44" s="23" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="AK44" s="101" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="AL44" s="23"/>
       <c r="AM44" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:42" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B45" s="79">
         <v>2025</v>
@@ -8469,40 +8478,40 @@
         <v>0</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="M45" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N45" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="P45" s="35">
         <v>6</v>
@@ -8511,10 +8520,10 @@
         <v>4</v>
       </c>
       <c r="R45" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S45" s="27">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T45" s="27"/>
       <c r="U45" s="33"/>
@@ -8524,72 +8533,72 @@
       <c r="Y45" s="33"/>
       <c r="Z45" s="33"/>
       <c r="AA45" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB45" s="23" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="AC45" s="80" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="AD45" s="23" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="AE45" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AF45" s="23"/>
       <c r="AG45" s="23"/>
       <c r="AH45" s="23"/>
       <c r="AI45" s="23"/>
       <c r="AJ45" s="23" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="AK45" s="101" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="AL45" s="23"/>
       <c r="AM45" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AP45" s="106"/>
     </row>
     <row r="46" spans="1:42" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="79">
         <v>2025</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="G46" s="35" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O46" s="35" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="P46" s="87">
         <v>5</v>
@@ -8598,74 +8607,74 @@
         <v>1</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S46" s="28">
         <v>2</v>
       </c>
       <c r="AA46" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB46" s="88" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="AC46" s="80" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="AD46" s="37" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AE46" s="37" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="AJ46" s="37" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AK46" s="95" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="AM46" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AO46" s="2"/>
       <c r="AP46" s="2"/>
     </row>
     <row r="47" spans="1:42" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" s="79">
         <v>2025</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="G47" s="35" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I47" s="38" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="J47" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M47" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N47" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O47" s="35" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="P47" s="87">
         <v>5</v>
@@ -8674,72 +8683,72 @@
         <v>4</v>
       </c>
       <c r="R47" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S47" s="28">
         <v>0</v>
       </c>
       <c r="AA47" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB47" s="88" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="AD47" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE47" s="37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AJ47" s="37" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="AK47" s="95" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AM47" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AP47" s="106"/>
     </row>
     <row r="48" spans="1:42" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B48" s="78">
         <v>2025</v>
       </c>
       <c r="D48" s="61" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E48" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="G48" s="61" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="H48" s="63" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="I48" s="78" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="J48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" s="63"/>
       <c r="L48" s="63"/>
       <c r="M48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O48" s="61" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="P48" s="63">
         <v>4</v>
@@ -8748,7 +8757,7 @@
         <v>2</v>
       </c>
       <c r="R48" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S48" s="65">
         <v>0</v>
@@ -8761,33 +8770,33 @@
       <c r="Y48" s="66"/>
       <c r="Z48" s="66"/>
       <c r="AA48" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE48" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF48" s="63"/>
       <c r="AG48" s="63"/>
       <c r="AH48" s="63"/>
       <c r="AI48" s="63"/>
       <c r="AJ48" s="63" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AK48" s="102" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="AL48" s="63"/>
       <c r="AM48" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN48" s="63"/>
       <c r="AO48" s="53"/>
@@ -8795,43 +8804,43 @@
     </row>
     <row r="49" spans="1:42" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B49" s="79">
         <v>2025</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="35" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="G49" s="35" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="I49" s="38" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="K49" s="37"/>
       <c r="L49" s="37"/>
       <c r="M49" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N49" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O49" s="35" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="P49" s="37">
         <v>25</v>
@@ -8840,7 +8849,7 @@
         <v>11</v>
       </c>
       <c r="R49" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S49" s="28">
         <v>6</v>
@@ -8853,33 +8862,33 @@
       <c r="Y49" s="39"/>
       <c r="Z49" s="39"/>
       <c r="AA49" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB49" s="37" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="AC49" s="80" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="AD49" s="37" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="AE49" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF49" s="37"/>
       <c r="AG49" s="37"/>
       <c r="AH49" s="37"/>
       <c r="AI49" s="37"/>
       <c r="AJ49" s="37" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="AK49" s="95" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="AL49" s="37"/>
       <c r="AM49" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN49" s="37"/>
       <c r="AO49" s="37"/>
@@ -8887,42 +8896,42 @@
     </row>
     <row r="50" spans="1:42" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B50" s="78">
         <v>2025</v>
       </c>
       <c r="D50" s="61" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E50" s="61" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="F50" s="71" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="G50" s="61" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="H50" s="63" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="I50" s="64" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="J50" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" s="63"/>
       <c r="L50" s="63"/>
       <c r="M50" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N50" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O50" s="61" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="P50" s="63">
         <v>6</v>
@@ -8931,10 +8940,10 @@
         <v>1</v>
       </c>
       <c r="R50" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S50" s="65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T50" s="65"/>
       <c r="U50" s="66"/>
@@ -8944,35 +8953,35 @@
       <c r="Y50" s="66"/>
       <c r="Z50" s="66"/>
       <c r="AA50" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB50" s="63" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="AC50" s="76" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="AD50" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE50" s="63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF50" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG50" s="63"/>
       <c r="AH50" s="63"/>
       <c r="AI50" s="63"/>
       <c r="AJ50" s="63" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="AK50" s="102" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="AL50" s="63"/>
       <c r="AM50" s="48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN50" s="63"/>
       <c r="AO50" s="53"/>
@@ -8980,43 +8989,43 @@
     </row>
     <row r="51" spans="1:42" s="54" customFormat="1" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B51" s="78">
         <v>2025</v>
       </c>
       <c r="C51" s="28"/>
       <c r="D51" s="61" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E51" s="61" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="F51" s="71" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="H51" s="63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I51" s="64" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="J51" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" s="63"/>
       <c r="L51" s="63"/>
       <c r="M51" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N51" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O51" s="61" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="P51" s="63">
         <v>6</v>
@@ -9025,10 +9034,10 @@
         <v>4</v>
       </c>
       <c r="R51" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S51" s="65">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T51" s="65"/>
       <c r="U51" s="66"/>
@@ -9038,35 +9047,35 @@
       <c r="Y51" s="66"/>
       <c r="Z51" s="66"/>
       <c r="AA51" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB51" s="63" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="AC51" s="76" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="AD51" s="63" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="AE51" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF51" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG51" s="63"/>
       <c r="AH51" s="63"/>
       <c r="AI51" s="63"/>
       <c r="AJ51" s="63" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="AK51" s="102" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="AL51" s="63"/>
       <c r="AM51" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN51" s="63"/>
       <c r="AO51" s="63"/>
@@ -9074,43 +9083,43 @@
     </row>
     <row r="52" spans="1:42" s="54" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B52" s="79">
         <v>2025</v>
       </c>
       <c r="C52" s="28"/>
       <c r="D52" s="35" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="F52" s="88" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="G52" s="35" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="J52" s="37" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="K52" s="37"/>
       <c r="L52" s="37"/>
       <c r="M52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O52" s="35" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="P52" s="37">
         <v>6</v>
@@ -9119,7 +9128,7 @@
         <v>2</v>
       </c>
       <c r="R52" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S52" s="28">
         <v>0</v>
@@ -9132,33 +9141,33 @@
       <c r="Y52" s="39"/>
       <c r="Z52" s="39"/>
       <c r="AA52" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC52" s="37"/>
       <c r="AD52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF52" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG52" s="37"/>
       <c r="AH52" s="37"/>
       <c r="AI52" s="37"/>
       <c r="AJ52" s="37" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="AK52" s="95" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="AL52" s="37"/>
       <c r="AM52" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN52" s="37"/>
       <c r="AO52" s="37"/>
@@ -9166,42 +9175,42 @@
     </row>
     <row r="53" spans="1:42" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B53" s="78">
         <v>2025</v>
       </c>
       <c r="D53" s="61" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="E53" s="61" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="F53" s="62" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="G53" s="61" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="H53" s="63" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="I53" s="64" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="J53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" s="63"/>
       <c r="L53" s="63"/>
       <c r="M53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O53" s="61" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="P53" s="63">
         <v>6</v>
@@ -9210,7 +9219,7 @@
         <v>5</v>
       </c>
       <c r="R53" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S53" s="65">
         <v>2</v>
@@ -9223,35 +9232,35 @@
       <c r="Y53" s="66"/>
       <c r="Z53" s="66"/>
       <c r="AA53" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF53" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG53" s="63"/>
       <c r="AH53" s="63"/>
       <c r="AI53" s="63"/>
       <c r="AJ53" s="63" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="AK53" s="102" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="AL53" s="63"/>
       <c r="AM53" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN53" s="63"/>
       <c r="AO53" s="63"/>
@@ -9259,43 +9268,43 @@
     </row>
     <row r="54" spans="1:42" s="54" customFormat="1" ht="237.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="78" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B54" s="82">
         <v>2025</v>
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="61" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E54" s="61" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F54" s="62" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="G54" s="64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H54" s="63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" s="63"/>
       <c r="L54" s="63"/>
       <c r="M54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O54" s="63" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="P54" s="63">
         <v>4</v>
@@ -9304,7 +9313,7 @@
         <v>1</v>
       </c>
       <c r="R54" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S54" s="65">
         <v>0</v>
@@ -9317,35 +9326,35 @@
       <c r="Y54" s="66"/>
       <c r="Z54" s="66"/>
       <c r="AA54" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF54" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG54" s="63"/>
       <c r="AH54" s="63"/>
       <c r="AI54" s="63"/>
       <c r="AJ54" s="63" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="AK54" s="102" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="AL54" s="63"/>
       <c r="AM54" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN54" s="63"/>
       <c r="AO54" s="63"/>
@@ -9353,43 +9362,43 @@
     </row>
     <row r="55" spans="1:42" s="54" customFormat="1" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" s="82">
         <v>2025</v>
       </c>
       <c r="C55" s="28"/>
       <c r="D55" s="61" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="E55" s="61" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="F55" s="62" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="G55" s="61" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="H55" s="63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I55" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" s="63"/>
       <c r="L55" s="63"/>
       <c r="M55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O55" s="61" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="P55" s="63">
         <v>6</v>
@@ -9398,7 +9407,7 @@
         <v>3</v>
       </c>
       <c r="R55" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S55" s="65">
         <v>0</v>
@@ -9411,35 +9420,35 @@
       <c r="Y55" s="66"/>
       <c r="Z55" s="66"/>
       <c r="AA55" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC55" s="63" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="AD55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF55" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG55" s="63"/>
       <c r="AH55" s="63"/>
       <c r="AI55" s="63"/>
       <c r="AJ55" s="63" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="AK55" s="102" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="AL55" s="63"/>
       <c r="AM55" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN55" s="63"/>
       <c r="AO55" s="63"/>
@@ -9447,43 +9456,43 @@
     </row>
     <row r="56" spans="1:42" s="54" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B56" s="82">
         <v>2025</v>
       </c>
       <c r="C56" s="28"/>
       <c r="D56" s="61" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="E56" s="61" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="F56" s="62" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="G56" s="61" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="H56" s="63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I56" s="64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" s="63"/>
       <c r="L56" s="63"/>
       <c r="M56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O56" s="61" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="P56" s="63">
         <v>3</v>
@@ -9492,7 +9501,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S56" s="65">
         <v>0</v>
@@ -9505,35 +9514,35 @@
       <c r="Y56" s="66"/>
       <c r="Z56" s="66"/>
       <c r="AA56" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC56" s="63" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="AD56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF56" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG56" s="63"/>
       <c r="AH56" s="63"/>
       <c r="AI56" s="63"/>
       <c r="AJ56" s="63" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="AK56" s="102" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="AL56" s="63"/>
       <c r="AM56" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN56" s="63"/>
       <c r="AO56" s="63"/>
@@ -9541,26 +9550,26 @@
     </row>
     <row r="57" spans="1:42" s="54" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B57" s="37">
         <v>2025</v>
       </c>
       <c r="C57" s="28"/>
       <c r="D57" s="37" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="I57" s="37"/>
       <c r="J57" s="37"/>
@@ -9569,7 +9578,7 @@
       <c r="M57" s="37"/>
       <c r="N57" s="37"/>
       <c r="O57" s="37" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="P57" s="28">
         <v>4</v>
@@ -9578,7 +9587,7 @@
         <v>2</v>
       </c>
       <c r="R57" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S57" s="28">
         <v>0</v>
@@ -9591,31 +9600,31 @@
       <c r="Y57" s="39"/>
       <c r="Z57" s="39"/>
       <c r="AA57" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB57" s="37" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="AC57" s="37"/>
       <c r="AD57" s="37" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="AE57" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF57" s="37"/>
       <c r="AG57" s="37"/>
       <c r="AH57" s="37"/>
       <c r="AI57" s="37"/>
       <c r="AJ57" s="37" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="AK57" s="95" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="AL57" s="37"/>
       <c r="AM57" s="37" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="AN57" s="37"/>
       <c r="AO57" s="37"/>
@@ -9623,7 +9632,7 @@
     </row>
     <row r="58" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B58" s="37">
         <v>2026</v>
@@ -9632,40 +9641,40 @@
         <v>10</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>389</v>
+        <v>652</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>390</v>
+        <v>653</v>
       </c>
       <c r="F58" s="80" t="s">
-        <v>391</v>
+        <v>654</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K58" s="49" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="L58" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M58" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N58" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O58" s="37" t="s">
-        <v>394</v>
+        <v>655</v>
       </c>
       <c r="P58" s="28">
         <v>5</v>
@@ -9674,45 +9683,46 @@
         <v>3</v>
       </c>
       <c r="R58" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S58" s="28">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA58" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB58" s="37" t="s">
-        <v>395</v>
+        <v>656</v>
       </c>
       <c r="AC58" s="37" t="s">
-        <v>396</v>
+        <v>657</v>
       </c>
       <c r="AD58" s="104" t="s">
-        <v>397</v>
+        <v>658</v>
       </c>
       <c r="AE58" s="37" t="s">
-        <v>398</v>
+        <v>488</v>
       </c>
       <c r="AF58" s="37" t="s">
-        <v>399</v>
+        <v>659</v>
       </c>
       <c r="AJ58" s="37" t="s">
-        <v>400</v>
+        <v>660</v>
       </c>
       <c r="AK58" s="95" t="s">
-        <v>401</v>
+        <v>661</v>
       </c>
       <c r="AM58" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AO58" s="37" t="s">
-        <v>820</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="AP58"/>
     </row>
     <row r="59" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" s="37">
         <v>2026</v>
@@ -9721,40 +9731,40 @@
         <v>10</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F59" s="92" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K59" s="49" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="L59" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M59" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N59" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O59" s="37" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P59" s="28">
         <v>6</v>
@@ -9763,45 +9773,46 @@
         <v>2</v>
       </c>
       <c r="R59" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S59" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA59" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB59" s="37" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AC59" s="92" t="s">
-        <v>828</v>
+        <v>668</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AE59" s="37" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AF59" s="37" t="s">
-        <v>830</v>
+        <v>671</v>
       </c>
       <c r="AJ59" s="37" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AK59" s="95" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AM59" s="37" t="s">
-        <v>827</v>
+        <v>674</v>
       </c>
       <c r="AO59" s="37" t="s">
-        <v>829</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="AP59"/>
     </row>
     <row r="60" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60" s="63">
         <v>2026</v>
@@ -9810,40 +9821,40 @@
         <v>0</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E60" s="63" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="F60" s="108" t="s">
-        <v>822</v>
+        <v>678</v>
       </c>
       <c r="G60" s="47" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="H60" s="48" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I60" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J60" s="49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K60" s="46" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="L60" s="46" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="M60" s="48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N60" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="P60" s="65">
         <v>10</v>
@@ -9852,10 +9863,10 @@
         <v>1</v>
       </c>
       <c r="R60" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S60" s="65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T60" s="65"/>
       <c r="U60" s="66"/>
@@ -9865,37 +9876,37 @@
       <c r="Y60" s="66"/>
       <c r="Z60" s="66"/>
       <c r="AA60" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB60" s="63" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="AC60" s="108" t="s">
-        <v>824</v>
+        <v>681</v>
       </c>
       <c r="AD60" s="63" t="s">
-        <v>825</v>
+        <v>682</v>
       </c>
       <c r="AE60" s="63" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="AF60" s="63" t="s">
-        <v>826</v>
+        <v>684</v>
       </c>
       <c r="AG60" s="63" t="s">
-        <v>811</v>
+        <v>685</v>
       </c>
       <c r="AH60" s="63"/>
       <c r="AI60" s="63"/>
       <c r="AJ60" s="63" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="AK60" s="102" t="s">
-        <v>823</v>
+        <v>687</v>
       </c>
       <c r="AL60" s="63"/>
       <c r="AM60" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN60" s="63"/>
       <c r="AO60" s="63"/>
@@ -9903,7 +9914,7 @@
     </row>
     <row r="61" spans="1:42" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="79">
         <v>2026</v>
@@ -9912,40 +9923,40 @@
         <v>5</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="F61" s="80" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="M61" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N61" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="P61" s="22">
         <v>6</v>
@@ -9954,7 +9965,7 @@
         <v>4</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S61" s="27">
         <v>0</v>
@@ -9967,42 +9978,42 @@
       <c r="Y61" s="33"/>
       <c r="Z61" s="33"/>
       <c r="AA61" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB61" s="23" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="AC61" s="23"/>
       <c r="AD61" s="23" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="AE61" s="23" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="AF61" s="23" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="AG61" s="23"/>
       <c r="AH61" s="23"/>
       <c r="AI61" s="23" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="AJ61" s="23" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="AK61" s="101" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="AL61" s="23"/>
       <c r="AM61" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AO61" s="2"/>
       <c r="AP61"/>
     </row>
     <row r="62" spans="1:42" s="54" customFormat="1" ht="186.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="78">
         <v>2026</v>
@@ -10011,40 +10022,40 @@
         <v>7</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="F62" s="108" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="H62" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I62" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J62" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="L62" s="46" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="M62" s="48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N62" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O62" s="46" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="P62" s="57">
         <v>5</v>
@@ -10053,10 +10064,10 @@
         <v>2</v>
       </c>
       <c r="R62" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S62" s="52">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T62" s="52"/>
       <c r="U62" s="70"/>
@@ -10066,35 +10077,35 @@
       <c r="Y62" s="70"/>
       <c r="Z62" s="70"/>
       <c r="AA62" s="48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB62" s="48" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="AC62" s="90" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="AD62" s="48" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="AE62" s="48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF62" s="48" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="AG62" s="48"/>
       <c r="AH62" s="48"/>
       <c r="AI62" s="48"/>
       <c r="AJ62" s="48" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="AK62" s="99" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="AL62" s="48"/>
       <c r="AM62" s="48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN62" s="63"/>
       <c r="AO62" s="63"/>
@@ -10102,7 +10113,7 @@
     </row>
     <row r="63" spans="1:42" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" s="79">
         <v>2026</v>
@@ -10111,40 +10122,40 @@
         <v>0</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="F63" s="80" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J63" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="L63" s="22" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N63" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O63" s="22" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="P63" s="87">
         <v>10</v>
@@ -10153,10 +10164,10 @@
         <v>2</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S63" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T63" s="27"/>
       <c r="U63" s="33"/>
@@ -10166,40 +10177,40 @@
       <c r="Y63" s="33"/>
       <c r="Z63" s="33"/>
       <c r="AA63" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB63" s="91" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="AC63" s="80" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="AD63" s="23" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="AE63" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF63" s="23"/>
       <c r="AG63" s="23"/>
       <c r="AH63" s="23"/>
       <c r="AI63" s="23"/>
       <c r="AJ63" s="23" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="AK63" s="101" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="AL63" s="23"/>
       <c r="AM63" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AO63" s="2"/>
       <c r="AP63"/>
     </row>
     <row r="64" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="78" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B64" s="82">
         <v>2026</v>
@@ -10208,36 +10219,36 @@
         <v>0</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="E64" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F64" s="63" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="G64" s="64" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="H64" s="63" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="I64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K64" s="63"/>
       <c r="L64" s="63"/>
       <c r="M64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="P64" s="63">
         <v>2</v>
@@ -10246,7 +10257,7 @@
         <v>1</v>
       </c>
       <c r="R64" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S64" s="65"/>
       <c r="T64" s="65"/>
@@ -10257,35 +10268,35 @@
       <c r="Y64" s="66"/>
       <c r="Z64" s="66"/>
       <c r="AA64" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF64" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG64" s="63"/>
       <c r="AH64" s="63"/>
       <c r="AI64" s="63"/>
       <c r="AJ64" s="63" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="AK64" s="102" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="AL64" s="63"/>
       <c r="AM64" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN64" s="63"/>
       <c r="AO64" s="63"/>
@@ -10293,7 +10304,7 @@
     </row>
     <row r="65" spans="1:42" ht="288.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B65" s="37">
         <v>2026</v>
@@ -10302,40 +10313,40 @@
         <v>5</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="M65" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N65" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="P65" s="37">
         <v>6</v>
@@ -10344,62 +10355,61 @@
         <v>2</v>
       </c>
       <c r="R65" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S65" s="28">
         <v>3</v>
       </c>
       <c r="AA65" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB65" s="37" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="AD65" s="40" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="AE65" s="37" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="AF65" s="37" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="AJ65" s="37" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="AK65" s="95" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="AM65" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AO65" s="2"/>
-      <c r="AP65"/>
     </row>
     <row r="66" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B66" s="37">
         <v>2026</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O66" s="37" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="P66" s="37">
         <v>5</v>
@@ -10408,60 +10418,60 @@
         <v>3</v>
       </c>
       <c r="R66" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S66" s="28">
         <v>0</v>
       </c>
       <c r="AA66" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB66" s="37" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="AC66" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD66" s="37" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="AE66" s="37" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="AJ66" s="37" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="AK66" s="95" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="AM66" s="37" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
     </row>
     <row r="67" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B67" s="37">
         <v>2026</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="O67" s="37" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="P67" s="28">
         <v>5</v>
@@ -10470,48 +10480,48 @@
         <v>2</v>
       </c>
       <c r="R67" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S67" s="28">
         <v>0</v>
       </c>
       <c r="AA67" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB67" s="37" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="AJ67" s="37" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="AK67" s="95" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
     </row>
     <row r="68" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B68" s="37">
         <v>2026</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O68" s="37" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="P68" s="28">
         <v>5</v>
@@ -10520,50 +10530,49 @@
         <v>3</v>
       </c>
       <c r="R68" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S68" s="28">
         <v>1</v>
       </c>
       <c r="AA68" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB68" s="37" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="AJ68" s="37" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="AK68" s="95" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="AO68" s="2"/>
-      <c r="AP68"/>
     </row>
     <row r="69" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B69" s="37">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>831</v>
+        <v>772</v>
       </c>
       <c r="O69" s="37" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="P69" s="28">
         <v>5</v>
@@ -10572,54 +10581,54 @@
         <v>2</v>
       </c>
       <c r="R69" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S69" s="28">
         <v>0</v>
       </c>
       <c r="AA69" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB69" s="37" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="AJ69" s="37" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="AK69" s="95" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="AM69" s="37" t="s">
-        <v>670</v>
+        <v>777</v>
       </c>
       <c r="AN69" s="37" t="s">
-        <v>832</v>
+        <v>778</v>
       </c>
     </row>
     <row r="70" spans="1:42" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B70" s="37">
         <v>2026</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="F70" s="92" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O70" s="37" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="P70" s="28">
         <v>4</v>
@@ -10628,48 +10637,49 @@
         <v>2</v>
       </c>
       <c r="R70" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S70" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA70" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB70" s="37" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="AJ70" s="37" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="AK70" s="95" t="s">
-        <v>771</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="AP70"/>
     </row>
     <row r="71" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B71" s="37">
         <v>2026</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O71" s="37" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="P71" s="28">
         <v>7</v>
@@ -10678,36 +10688,37 @@
         <v>3</v>
       </c>
       <c r="R71" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S71" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA71" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB71" s="37" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="AE71" s="37" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="AJ71" s="37" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="AK71" s="95" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="AM71" s="37" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="AN71" s="37" t="s">
-        <v>780</v>
-      </c>
+        <v>794</v>
+      </c>
+      <c r="AP71"/>
     </row>
     <row r="72" spans="1:42" s="54" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="78" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B72" s="63">
         <v>2026</v>
@@ -10716,36 +10727,36 @@
         <v>0</v>
       </c>
       <c r="D72" s="63" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="E72" s="63" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="G72" s="63" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="H72" s="63" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="I72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K72" s="63"/>
       <c r="L72" s="63"/>
       <c r="M72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O72" s="63" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="P72" s="65">
         <v>6</v>
@@ -10754,7 +10765,7 @@
         <v>2</v>
       </c>
       <c r="R72" s="63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S72" s="65">
         <v>0</v>
@@ -10767,35 +10778,35 @@
       <c r="Y72" s="66"/>
       <c r="Z72" s="66"/>
       <c r="AA72" s="63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AD72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF72" s="63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG72" s="63"/>
       <c r="AH72" s="63"/>
       <c r="AI72" s="63"/>
       <c r="AJ72" s="63" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="AK72" s="102" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="AL72" s="63"/>
       <c r="AM72" s="63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN72" s="63"/>
       <c r="AO72" s="63"/>
@@ -10803,28 +10814,28 @@
     </row>
     <row r="73" spans="1:42" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B73" s="37">
         <v>2026</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="F73" s="80" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="O73" s="37" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="P73" s="28">
         <v>6</v>
@@ -10833,42 +10844,42 @@
         <v>4</v>
       </c>
       <c r="R73" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S73" s="28">
         <v>0</v>
       </c>
       <c r="AA73" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB73" s="37" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="AJ73" s="37" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="AK73" s="95" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="74" spans="1:42" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B74">
         <v>2026</v>
       </c>
       <c r="D74" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="E74" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="F74" s="92" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="O74" t="s">
-        <v>799</v>
+        <v>813</v>
       </c>
       <c r="P74">
         <v>6</v>
@@ -10877,7 +10888,7 @@
         <v>2</v>
       </c>
       <c r="R74" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -10888,57 +10899,60 @@
       <c r="Y74" s="94"/>
       <c r="Z74" s="94"/>
       <c r="AA74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB74" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="AE74" s="37" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="AF74" s="37" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="AJ74" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="AK74" s="103" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
     </row>
     <row r="75" spans="1:42" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B75" s="37">
         <v>2026</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>804</v>
+        <v>819</v>
+      </c>
+      <c r="E75" t="s">
+        <v>820</v>
       </c>
       <c r="F75" s="92" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>807</v>
+        <v>823</v>
       </c>
       <c r="J75" s="37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="L75" s="37" t="s">
-        <v>809</v>
+        <v>825</v>
       </c>
       <c r="M75" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O75" s="37" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="P75" s="28">
         <v>6</v>
@@ -10947,72 +10961,73 @@
         <v>3</v>
       </c>
       <c r="R75" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S75" s="28">
         <v>0</v>
       </c>
       <c r="AA75" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC75" s="92" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="AD75" s="92" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="AE75" s="37" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="AK75" s="95" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="AM75" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN75" s="37" t="s">
-        <v>816</v>
-      </c>
+        <v>831</v>
+      </c>
+      <c r="AP75"/>
     </row>
     <row r="76" spans="1:42" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B76" s="37">
         <v>2026</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J76" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K76" s="49" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="L76" s="49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M76" s="37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N76" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O76" s="37" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="P76" s="28">
         <v>4</v>
@@ -11021,33 +11036,36 @@
         <v>3</v>
       </c>
       <c r="R76" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM76" s="37" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="77" spans="1:42" ht="221" x14ac:dyDescent="0.2">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="77" spans="1:42" ht="221" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="79" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B77" s="37">
         <v>2026</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>834</v>
+        <v>835</v>
+      </c>
+      <c r="E77" t="s">
+        <v>836</v>
       </c>
       <c r="F77" s="92" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O77" s="37" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="P77" s="28">
         <v>6</v>
@@ -11056,23 +11074,64 @@
         <v>2</v>
       </c>
       <c r="R77" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>839</v>
       </c>
       <c r="AE77" s="37" t="s">
-        <v>814</v>
+        <v>829</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>840</v>
       </c>
       <c r="AK77" s="95" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="AM77" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="AN77" s="37" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="B78" s="37"/>
+        <v>196</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="78" spans="1:42" ht="102" x14ac:dyDescent="0.2">
+      <c r="A78" s="79" t="s">
+        <v>377</v>
+      </c>
+      <c r="B78" s="37">
+        <v>2026</v>
+      </c>
+      <c r="D78" s="37" t="s">
+        <v>843</v>
+      </c>
+      <c r="G78" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="O78" s="37" t="s">
+        <v>844</v>
+      </c>
+      <c r="P78" s="28">
+        <v>5</v>
+      </c>
+      <c r="Q78" s="28">
+        <v>3</v>
+      </c>
+      <c r="R78" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB78" s="37" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE78" s="37" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B79" s="37"/>
@@ -13688,7 +13747,7 @@
       <c r="B949" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP76" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:AP76" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AP76">
       <sortCondition ref="B1:B76"/>
     </sortState>
@@ -13698,7 +13757,7 @@
       <formula>NOT(ISERROR(SEARCH("Preprint",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1048576 M1:R1048576 AA1:AA1048576 AC34:AF59 AD60:AF60 E1:J1048576 AC61:AF1048576">
+  <conditionalFormatting sqref="A1:B1048576 E1:J1048576 M1:R1048576 AA1:AA1048576 AC34:AF59 AD60:AF60 AC61:AF1048576">
     <cfRule type="expression" dxfId="8" priority="8">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
@@ -13771,70 +13830,70 @@
     <hyperlink ref="AC19" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
     <hyperlink ref="AC20" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="AC21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="AC33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F23" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F24" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="AC25" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F26" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="AC26" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F27" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F28" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F29" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F30" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F58" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F34" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="AC34" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F35" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="AC35" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F36" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="AC36" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F37" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="AC37" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F38" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="AC38" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F39" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="AC39" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F40" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="AC40" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F41" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F42" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="AC43" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F44" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="AC45" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F46" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="AC46" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F47" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F49" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="AC49" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F50" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="AC50" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F51" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="AC51" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F53" r:id="rId73" location="page=487" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F54" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F55" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F56" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F57" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F23" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F24" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F25" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="AC25" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F26" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="AC26" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F27" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F28" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F29" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F30" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F33" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="AC33" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F34" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="AC34" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F35" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="AC35" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F36" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="AC36" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F37" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="AC37" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F38" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="AC38" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F39" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="AC39" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F40" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="AC40" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F41" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F42" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="AC43" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F44" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="AC45" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F46" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="AC46" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F47" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F49" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="AC49" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F50" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="AC50" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F51" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="AC51" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F53" r:id="rId72" location="page=487" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F54" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F55" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F56" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F57" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F58" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
     <hyperlink ref="F59" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F61" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F62" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="AC62" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F63" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="AC63" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F65" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F70" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F72" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F73" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F74" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F75" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="AC75" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="AD75" r:id="rId91" display="https://doi.org/10.5281/zenodo.21380299" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F60" r:id="rId92" xr:uid="{122B9BB9-F65A-1B41-A77D-2195CBA21762}"/>
-    <hyperlink ref="AC60" r:id="rId93" xr:uid="{D7EB4DC4-3B2A-6946-8EA0-4F4BF86F1DB6}"/>
-    <hyperlink ref="AC59" r:id="rId94" xr:uid="{83AAFCC6-FDB5-2C4D-A65C-242E4200B9CE}"/>
-    <hyperlink ref="F77" r:id="rId95" xr:uid="{57B1C321-5715-A842-87D3-B601835EE54B}"/>
+    <hyperlink ref="AC59" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F60" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="AC60" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F61" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F62" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="AC62" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F63" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="AC63" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F65" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F70" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F72" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F73" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F74" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F75" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="AC75" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="AD75" r:id="rId94" display="https://doi.org/10.5281/zenodo.21380299" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F77" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Publications.xlsx
+++ b/data/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Publicaciones/00_publications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CCB788-4113-FF4B-8FFD-9CF263FD6A76}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{8DE93FE9-F55A-A042-929D-0733C8507109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A652C4E-49F7-0D4D-89B0-88360FD4E66E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="38400" windowHeight="17240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="2240" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="849">
   <si>
     <t>Tipo</t>
   </si>
@@ -3168,6 +3168,15 @@
   </si>
   <si>
     <t>[https://arxiv.org/abs/2608.09900, https://huggingface.co/papers/2608.09900]</t>
+  </si>
+  <si>
+    <t>[https://lnkd.in/p/eS8dQ3fZ,]</t>
+  </si>
+  <si>
+    <t>FUN4DATE, ENDGAME, IGLUE</t>
+  </si>
+  <si>
+    <t>https://oa.upm.es/97555/</t>
   </si>
 </sst>
 </file>
@@ -5697,7 +5706,7 @@
         <v>206</v>
       </c>
       <c r="AE16" s="49" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="AF16" s="49" t="s">
         <v>208</v>
@@ -11038,8 +11047,17 @@
       <c r="R76" s="37" t="s">
         <v>51</v>
       </c>
+      <c r="AC76" s="92" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE76" s="37" t="s">
+        <v>847</v>
+      </c>
+      <c r="AF76" s="92" t="s">
+        <v>846</v>
+      </c>
       <c r="AM76" s="37" t="s">
-        <v>777</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:42" ht="221" customHeight="1" x14ac:dyDescent="0.2">
@@ -13894,6 +13912,8 @@
     <hyperlink ref="AC75" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="AD75" r:id="rId94" display="https://doi.org/10.5281/zenodo.21380299" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
     <hyperlink ref="F77" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="AF76" r:id="rId96" display="https://lnkd.in/p/eS8dQ3fZ" xr:uid="{0B677043-826E-834D-868D-4B423761D01A}"/>
+    <hyperlink ref="AC76" r:id="rId97" xr:uid="{3EDB0987-2302-D449-AB7F-B05F134CEDA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
